--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A70796A-13AC-4AA9-8444-C47D5142C655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48DBEF2-0D35-4B24-9620-94DA138EFE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="154">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -531,6 +531,9 @@
   </si>
   <si>
     <t>* USD 2024/t</t>
+  </si>
+  <si>
+    <t>TFM_INS-TS</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1279,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48DBEF2-0D35-4B24-9620-94DA138EFE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A86615-FB74-4034-8568-A4A96F1C4CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -128,9 +128,6 @@
     <t>Trd_electricity export</t>
   </si>
   <si>
-    <t>~TFM_INS-TS: attribute=flo_cost</t>
-  </si>
-  <si>
     <t>pset_co</t>
   </si>
   <si>
@@ -534,6 +531,9 @@
   </si>
   <si>
     <t>TFM_INS-TS</t>
+  </si>
+  <si>
+    <t>TFM_INS-TS: attribute=flo_cost</t>
   </si>
 </sst>
 </file>
@@ -938,7 +938,7 @@
   <sheetData>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
       <c r="N3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.35">
@@ -1019,7 +1019,7 @@
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>2.9033099999999998</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
@@ -1206,16 +1206,16 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
         <v>75</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>76</v>
       </c>
-      <c r="E18" t="s">
-        <v>77</v>
-      </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -1223,13 +1223,13 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
         <v>78</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
       </c>
       <c r="E19">
         <v>338.40000000000003</v>
@@ -1237,13 +1237,13 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20">
         <v>198</v>
@@ -1251,13 +1251,13 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21">
         <v>252</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
         <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
@@ -1368,12 +1368,12 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F34">
         <v>180</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F35">
         <v>87</v>
@@ -1427,60 +1427,60 @@
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" t="s">
         <v>106</v>
       </c>
-      <c r="I1" t="s">
-        <v>107</v>
-      </c>
       <c r="N1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="S1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AE1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AJ1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AN1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AR1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
       </c>
       <c r="I2" t="s">
         <v>1</v>
       </c>
       <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
         <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
       </c>
       <c r="L2" t="s">
         <v>12</v>
@@ -1489,10 +1489,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
         <v>32</v>
-      </c>
-      <c r="P2" t="s">
-        <v>33</v>
       </c>
       <c r="Q2" t="s">
         <v>12</v>
@@ -1501,34 +1501,34 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" t="s">
         <v>32</v>
-      </c>
-      <c r="U2" t="s">
-        <v>33</v>
       </c>
       <c r="V2" t="s">
         <v>12</v>
       </c>
       <c r="X2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD2" t="s">
         <v>32</v>
       </c>
-      <c r="Y2" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>33</v>
-      </c>
       <c r="AE2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AF2" t="s">
         <v>1</v>
@@ -1537,31 +1537,31 @@
         <v>1</v>
       </c>
       <c r="AI2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>32</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>33</v>
       </c>
       <c r="AL2" t="s">
         <v>1</v>
       </c>
       <c r="AM2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AN2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR2" t="s">
         <v>35</v>
       </c>
-      <c r="AP2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>36</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.35">
@@ -1570,64 +1570,64 @@
         <v/>
       </c>
       <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
         <v>86</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" t="s">
         <v>38</v>
       </c>
-      <c r="E3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>88</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>89</v>
       </c>
       <c r="K3">
         <v>0.13112133015375788</v>
       </c>
       <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" t="s">
         <v>40</v>
       </c>
-      <c r="N3" t="s">
-        <v>41</v>
-      </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P3">
         <v>0.12504651804277112</v>
       </c>
       <c r="Q3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U3">
         <v>0.12825501911757625</v>
       </c>
       <c r="V3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA3">
         <v>1E-3</v>
@@ -1639,7 +1639,7 @@
         <v>0.16087081189037786</v>
       </c>
       <c r="AE3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF3" t="s">
         <v>8</v>
@@ -1648,16 +1648,16 @@
         <v>6</v>
       </c>
       <c r="AI3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AJ3">
         <v>0.11820818077291764</v>
       </c>
       <c r="AL3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AN3">
         <v>6.7453183173023845E-2</v>
@@ -1666,69 +1666,69 @@
         <v>2020</v>
       </c>
       <c r="AQ3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AR3">
         <v>0</v>
       </c>
       <c r="AS3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
         <v>90</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
         <v>91</v>
-      </c>
-      <c r="G4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s">
-        <v>92</v>
       </c>
       <c r="K4">
         <v>1.1273184373715762E-3</v>
       </c>
       <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
         <v>40</v>
       </c>
-      <c r="N4" t="s">
-        <v>41</v>
-      </c>
       <c r="O4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P4">
         <v>0.12923909287156352</v>
       </c>
       <c r="Q4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U4">
         <v>0.1460828987272339</v>
       </c>
       <c r="V4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA4">
         <v>1E-3</v>
@@ -1740,7 +1740,7 @@
         <v>5.2547713165767528E-2</v>
       </c>
       <c r="AE4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AF4" t="s">
         <v>8</v>
@@ -1749,16 +1749,16 @@
         <v>6</v>
       </c>
       <c r="AI4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AJ4">
         <v>9.765399900437545E-2</v>
       </c>
       <c r="AL4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AN4">
         <v>0.21742041059208561</v>
@@ -1767,69 +1767,69 @@
         <v>2020</v>
       </c>
       <c r="AQ4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AR4">
         <v>0</v>
       </c>
       <c r="AS4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
         <v>93</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
         <v>94</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s">
-        <v>95</v>
       </c>
       <c r="K5">
         <v>1.1826578944686741E-2</v>
       </c>
       <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
         <v>40</v>
       </c>
-      <c r="N5" t="s">
-        <v>41</v>
-      </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P5">
         <v>2.3904696128463698E-2</v>
       </c>
       <c r="Q5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U5">
         <v>2.5606675575038346E-2</v>
       </c>
       <c r="V5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA5">
         <v>1E-3</v>
@@ -1841,7 +1841,7 @@
         <v>3.5896543437005365E-2</v>
       </c>
       <c r="AE5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AF5" t="s">
         <v>8</v>
@@ -1850,16 +1850,16 @@
         <v>6</v>
       </c>
       <c r="AI5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AJ5">
         <v>2.1376827284429509E-2</v>
       </c>
       <c r="AL5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AN5">
         <v>6.4867911695789315E-2</v>
@@ -1868,63 +1868,63 @@
         <v>2020</v>
       </c>
       <c r="AQ5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AR5">
         <v>0</v>
       </c>
       <c r="AS5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s">
         <v>96</v>
-      </c>
-      <c r="I6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" t="s">
-        <v>97</v>
       </c>
       <c r="K6">
         <v>0.32597484269725724</v>
       </c>
       <c r="L6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s">
         <v>40</v>
       </c>
-      <c r="N6" t="s">
-        <v>41</v>
-      </c>
       <c r="O6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P6">
         <v>0.11223960491803744</v>
       </c>
       <c r="Q6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U6">
         <v>0.10502838298522549</v>
       </c>
       <c r="V6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA6">
         <v>1E-3</v>
@@ -1936,7 +1936,7 @@
         <v>0.16263862301005233</v>
       </c>
       <c r="AE6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF6" t="s">
         <v>8</v>
@@ -1945,16 +1945,16 @@
         <v>6</v>
       </c>
       <c r="AI6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ6">
         <v>0.13104968035048054</v>
       </c>
       <c r="AL6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AN6">
         <v>0.181059958051627</v>
@@ -1963,60 +1963,60 @@
         <v>2020</v>
       </c>
       <c r="AQ6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AR6">
         <v>0</v>
       </c>
       <c r="AS6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K7">
         <v>1.6040529306304684E-2</v>
       </c>
       <c r="L7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" t="s">
         <v>40</v>
       </c>
-      <c r="N7" t="s">
-        <v>41</v>
-      </c>
       <c r="O7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P7">
         <v>0.11331093849743473</v>
       </c>
       <c r="Q7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U7">
         <v>0.11482957147402537</v>
       </c>
       <c r="V7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA7">
         <v>1E-3</v>
@@ -2028,7 +2028,7 @@
         <v>5.3125160563193538E-2</v>
       </c>
       <c r="AE7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AF7" t="s">
         <v>8</v>
@@ -2037,16 +2037,16 @@
         <v>6</v>
       </c>
       <c r="AI7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ7">
         <v>0.11255019110607196</v>
       </c>
       <c r="AL7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AN7">
         <v>0.29479690034051531</v>
@@ -2055,60 +2055,60 @@
         <v>2021</v>
       </c>
       <c r="AQ7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AR7">
         <v>0</v>
       </c>
       <c r="AS7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K8">
         <v>4.5036365618117004E-2</v>
       </c>
       <c r="L8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" t="s">
         <v>40</v>
       </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
       <c r="O8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P8">
         <v>2.178054005059079E-2</v>
       </c>
       <c r="Q8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U8">
         <v>2.2211636421743067E-2</v>
       </c>
       <c r="V8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA8">
         <v>1E-3</v>
@@ -2120,7 +2120,7 @@
         <v>3.6291010947302131E-2</v>
       </c>
       <c r="AE8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF8" t="s">
         <v>8</v>
@@ -2129,16 +2129,16 @@
         <v>6</v>
       </c>
       <c r="AI8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ8">
         <v>2.3834110177054908E-2</v>
       </c>
       <c r="AL8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AN8">
         <v>0.18791773337227902</v>
@@ -2147,60 +2147,60 @@
         <v>2021</v>
       </c>
       <c r="AQ8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AR8">
         <v>0</v>
       </c>
       <c r="AS8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K9">
         <v>0.33590262553839051</v>
       </c>
       <c r="L9" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" t="s">
         <v>40</v>
       </c>
-      <c r="N9" t="s">
-        <v>41</v>
-      </c>
       <c r="O9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P9">
         <v>7.9597285699010006E-2</v>
       </c>
       <c r="Q9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U9">
         <v>5.8632453318071452E-2</v>
       </c>
       <c r="V9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA9">
         <v>1E-3</v>
@@ -2212,7 +2212,7 @@
         <v>0.16263862301005233</v>
       </c>
       <c r="AE9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AF9" t="s">
         <v>8</v>
@@ -2221,16 +2221,16 @@
         <v>6</v>
       </c>
       <c r="AI9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ9">
         <v>0.11748145961359424</v>
       </c>
       <c r="AL9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AN9">
         <v>0.13319460828738694</v>
@@ -2239,60 +2239,60 @@
         <v>2021</v>
       </c>
       <c r="AQ9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AR9">
         <v>0</v>
       </c>
       <c r="AS9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>3.8494528096615951E-2</v>
       </c>
       <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" t="s">
         <v>40</v>
       </c>
-      <c r="N10" t="s">
-        <v>41</v>
-      </c>
       <c r="O10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P10">
         <v>8.1809459054675793E-2</v>
       </c>
       <c r="Q10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U10">
         <v>7.4076611827312455E-2</v>
       </c>
       <c r="V10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA10">
         <v>1E-3</v>
@@ -2304,7 +2304,7 @@
         <v>5.3125160563193538E-2</v>
       </c>
       <c r="AE10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="s">
         <v>8</v>
@@ -2313,16 +2313,16 @@
         <v>6</v>
       </c>
       <c r="AI10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ10">
         <v>8.4800799390331486E-2</v>
       </c>
       <c r="AL10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AN10">
         <v>0.27571202448049736</v>
@@ -2331,60 +2331,60 @@
         <v>2021</v>
       </c>
       <c r="AQ10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AR10">
         <v>0</v>
       </c>
       <c r="AS10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K11">
         <v>5.1451874561372068E-2</v>
       </c>
       <c r="L11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" t="s">
         <v>40</v>
       </c>
-      <c r="N11" t="s">
-        <v>41</v>
-      </c>
       <c r="O11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P11">
         <v>1.5762397414136396E-2</v>
       </c>
       <c r="Q11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U11">
         <v>1.2054658101026138E-2</v>
       </c>
       <c r="V11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA11">
         <v>1E-3</v>
@@ -2396,7 +2396,7 @@
         <v>3.6291010947302131E-2</v>
       </c>
       <c r="AE11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF11" t="s">
         <v>8</v>
@@ -2405,16 +2405,16 @@
         <v>6</v>
       </c>
       <c r="AI11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AJ11">
         <v>2.0570847331150249E-2</v>
       </c>
       <c r="AL11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AN11">
         <v>9.8544131462115603E-2</v>
@@ -2423,60 +2423,60 @@
         <v>2022</v>
       </c>
       <c r="AQ11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AR11">
         <v>0</v>
       </c>
       <c r="AS11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K12">
         <v>4.1769964791773688E-2</v>
       </c>
       <c r="L12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" t="s">
         <v>40</v>
       </c>
-      <c r="N12" t="s">
-        <v>41</v>
-      </c>
       <c r="O12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P12">
         <v>0.13910975598870917</v>
       </c>
       <c r="Q12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U12">
         <v>0.14285175524219881</v>
       </c>
       <c r="V12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA12">
         <v>1E-3</v>
@@ -2488,7 +2488,7 @@
         <v>0.15910300077070333</v>
       </c>
       <c r="AE12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF12" t="s">
         <v>8</v>
@@ -2497,16 +2497,16 @@
         <v>6</v>
       </c>
       <c r="AI12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AJ12">
         <v>0.13067071966028027</v>
       </c>
       <c r="AL12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AN12">
         <v>9.4996431311812124E-2</v>
@@ -2515,60 +2515,60 @@
         <v>2022</v>
       </c>
       <c r="AQ12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AR12">
         <v>0</v>
       </c>
       <c r="AS12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" t="s">
         <v>40</v>
       </c>
-      <c r="N13" t="s">
-        <v>41</v>
-      </c>
       <c r="O13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P13">
         <v>0.1328412824161386</v>
       </c>
       <c r="Q13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U13">
         <v>0.14314271457517094</v>
       </c>
       <c r="V13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA13">
         <v>1E-3</v>
@@ -2580,7 +2580,7 @@
         <v>5.197026576834151E-2</v>
       </c>
       <c r="AE13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AF13" t="s">
         <v>8</v>
@@ -2589,16 +2589,16 @@
         <v>6</v>
       </c>
       <c r="AI13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AJ13">
         <v>0.11789293365992742</v>
       </c>
       <c r="AL13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AN13">
         <v>0.17683972082772126</v>
@@ -2607,60 +2607,60 @@
         <v>2022</v>
       </c>
       <c r="AQ13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AR13">
         <v>0</v>
       </c>
       <c r="AS13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K14">
         <v>1.2540418543543095E-3</v>
       </c>
       <c r="L14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" t="s">
         <v>40</v>
       </c>
-      <c r="N14" t="s">
-        <v>41</v>
-      </c>
       <c r="O14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P14">
         <v>2.5358428918473137E-2</v>
       </c>
       <c r="Q14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U14">
         <v>2.7227622635379315E-2</v>
       </c>
       <c r="V14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA14">
         <v>1E-3</v>
@@ -2672,7 +2672,7 @@
         <v>3.5502075926708607E-2</v>
       </c>
       <c r="AE14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AF14" t="s">
         <v>8</v>
@@ -2681,16 +2681,16 @@
         <v>6</v>
       </c>
       <c r="AI14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AJ14">
         <v>2.3910251649386354E-2</v>
       </c>
       <c r="AL14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AN14">
         <v>7.423298333369277E-2</v>
@@ -2699,60 +2699,60 @@
         <v>2022</v>
       </c>
       <c r="AQ14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AR14">
         <v>0</v>
       </c>
       <c r="AS14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K15">
         <v>0.13043755141224658</v>
       </c>
       <c r="L15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P15">
         <v>0.12553296894209429</v>
       </c>
       <c r="Q15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U15">
         <v>0.12767434976558359</v>
       </c>
       <c r="V15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA15">
         <v>1E-3</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="AI15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AJ15">
         <v>0.11491480071761173</v>
@@ -2769,49 +2769,49 @@
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.35">
       <c r="I16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K16">
         <v>1.1907924780644593E-3</v>
       </c>
       <c r="L16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P16">
         <v>0.1325213456520582</v>
       </c>
       <c r="Q16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U16">
         <v>0.14061823930498868</v>
       </c>
       <c r="V16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA16">
         <v>1E-3</v>
@@ -2820,7 +2820,7 @@
         <v>5</v>
       </c>
       <c r="AI16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AJ16">
         <v>0.11343014511581903</v>
@@ -2828,49 +2828,49 @@
     </row>
     <row r="17" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K17">
         <v>1.1533083888786525E-2</v>
       </c>
       <c r="L17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P17">
         <v>2.4645667696570315E-2</v>
       </c>
       <c r="Q17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U17">
         <v>2.5388069366133078E-2</v>
       </c>
       <c r="V17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA17">
         <v>1E-3</v>
@@ -2879,7 +2879,7 @@
         <v>5</v>
       </c>
       <c r="AI17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AJ17">
         <v>2.0885252413625318E-2</v>
@@ -2887,49 +2887,49 @@
     </row>
     <row r="18" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K18">
         <v>0.32835803432705835</v>
       </c>
       <c r="L18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P18">
         <v>0.10072660432774716</v>
       </c>
       <c r="Q18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U18">
         <v>0.11049044788132463</v>
       </c>
       <c r="V18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA18">
         <v>1E-3</v>
@@ -2938,7 +2938,7 @@
         <v>5</v>
       </c>
       <c r="AI18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ18">
         <v>0.11618686907147086</v>
@@ -2946,49 +2946,49 @@
     </row>
     <row r="19" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K19">
         <v>1.4650438890933879E-2</v>
       </c>
       <c r="L19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P19">
         <v>0.11313834221180283</v>
       </c>
       <c r="Q19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U19">
         <v>0.11510387450460316</v>
       </c>
       <c r="V19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA19">
         <v>1E-3</v>
@@ -2997,7 +2997,7 @@
         <v>5</v>
       </c>
       <c r="AI19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ19">
         <v>0.11485062661500635</v>
@@ -3005,49 +3005,49 @@
     </row>
     <row r="20" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K20">
         <v>4.5164390949668322E-2</v>
       </c>
       <c r="L20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P20">
         <v>2.0367354299406455E-2</v>
       </c>
       <c r="Q20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U20">
         <v>2.2717226593956107E-2</v>
       </c>
       <c r="V20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA20">
         <v>1E-3</v>
@@ -3056,7 +3056,7 @@
         <v>5</v>
       </c>
       <c r="AI20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ20">
         <v>2.1125383361665393E-2</v>
@@ -3064,49 +3064,49 @@
     </row>
     <row r="21" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K21">
         <v>0.33561434870423984</v>
       </c>
       <c r="L21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P21">
         <v>7.4851005301479756E-2</v>
       </c>
       <c r="Q21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U21">
         <v>6.4770986622185736E-2</v>
       </c>
       <c r="V21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA21">
         <v>1E-3</v>
@@ -3115,7 +3115,7 @@
         <v>5</v>
       </c>
       <c r="AI21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ21">
         <v>0.11653911207601672</v>
@@ -3123,49 +3123,49 @@
     </row>
     <row r="22" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>3.524310839296195E-2</v>
       </c>
       <c r="L22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P22">
         <v>8.2921888656091305E-2</v>
       </c>
       <c r="Q22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U22">
         <v>7.116516022436771E-2</v>
       </c>
       <c r="V22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA22">
         <v>1E-3</v>
@@ -3174,7 +3174,7 @@
         <v>5</v>
       </c>
       <c r="AI22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ22">
         <v>0.11417854497501884</v>
@@ -3182,49 +3182,49 @@
     </row>
     <row r="23" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K23">
         <v>4.934939454917707E-2</v>
       </c>
       <c r="L23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P23">
         <v>1.4816908194568044E-2</v>
       </c>
       <c r="Q23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U23">
         <v>1.3654935997665195E-2</v>
       </c>
       <c r="V23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA23">
         <v>1E-3</v>
@@ -3233,7 +3233,7 @@
         <v>5</v>
       </c>
       <c r="AI23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AJ23">
         <v>2.1131908763385672E-2</v>
@@ -3241,49 +3241,49 @@
     </row>
     <row r="24" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K24">
         <v>4.6931710747620793E-2</v>
       </c>
       <c r="L24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P24">
         <v>0.14476340865714046</v>
       </c>
       <c r="Q24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U24">
         <v>0.14242997731860263</v>
       </c>
       <c r="V24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA24">
         <v>1E-3</v>
@@ -3292,7 +3292,7 @@
         <v>5</v>
       </c>
       <c r="AI24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AJ24">
         <v>0.11351511345077332</v>
@@ -3300,49 +3300,49 @@
     </row>
     <row r="25" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P25">
         <v>0.13980790689267938</v>
       </c>
       <c r="Q25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U25">
         <v>0.13952110054866063</v>
       </c>
       <c r="V25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA25">
         <v>1E-3</v>
@@ -3351,7 +3351,7 @@
         <v>5</v>
       </c>
       <c r="AI25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AJ25">
         <v>0.11259215715032031</v>
@@ -3359,49 +3359,49 @@
     </row>
     <row r="26" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K26">
         <v>1.5271456592435997E-3</v>
       </c>
       <c r="L26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P26">
         <v>2.5906599168361417E-2</v>
       </c>
       <c r="Q26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U26">
         <v>2.6465631871926132E-2</v>
       </c>
       <c r="V26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA26">
         <v>1E-3</v>
@@ -3410,7 +3410,7 @@
         <v>5</v>
       </c>
       <c r="AI26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AJ26">
         <v>2.0650086289286402E-2</v>
@@ -3418,49 +3418,49 @@
     </row>
     <row r="27" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K27">
         <v>0.12946371659654152</v>
       </c>
       <c r="L27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P27">
         <v>0.12351433556883835</v>
       </c>
       <c r="Q27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U27">
         <v>0.13000667834123067</v>
       </c>
       <c r="V27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA27">
         <v>1E-3</v>
@@ -3468,49 +3468,49 @@
     </row>
     <row r="28" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K28">
         <v>1.1890659952457959E-3</v>
       </c>
       <c r="L28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P28">
         <v>0.1276064124261225</v>
       </c>
       <c r="Q28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U28">
         <v>0.1493447595855007</v>
       </c>
       <c r="V28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA28">
         <v>1E-3</v>
@@ -3518,49 +3518,49 @@
     </row>
     <row r="29" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K29">
         <v>1.1641178367336654E-2</v>
       </c>
       <c r="L29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P29">
         <v>2.4071670414895937E-2</v>
       </c>
       <c r="Q29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U29">
         <v>2.4557391106324163E-2</v>
       </c>
       <c r="V29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA29">
         <v>1E-3</v>
@@ -3568,49 +3568,49 @@
     </row>
     <row r="30" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K30">
         <v>0.3282040069905483</v>
       </c>
       <c r="L30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P30">
         <v>0.10743651573839856</v>
       </c>
       <c r="Q30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U30">
         <v>9.9733771623240097E-2</v>
       </c>
       <c r="V30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA30">
         <v>1E-3</v>
@@ -3618,49 +3618,49 @@
     </row>
     <row r="31" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K31">
         <v>1.405724243635203E-2</v>
       </c>
       <c r="L31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P31">
         <v>0.11261469323631694</v>
       </c>
       <c r="Q31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U31">
         <v>0.11794909889203112</v>
       </c>
       <c r="V31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA31">
         <v>1E-3</v>
@@ -3668,49 +3668,49 @@
     </row>
     <row r="32" spans="9:36" x14ac:dyDescent="0.35">
       <c r="I32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K32">
         <v>4.3907688164808209E-2</v>
       </c>
       <c r="L32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P32">
         <v>2.0812569196136516E-2</v>
       </c>
       <c r="Q32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U32">
         <v>2.1149634260240101E-2</v>
       </c>
       <c r="V32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA32">
         <v>1E-3</v>
@@ -3718,49 +3718,49 @@
     </row>
     <row r="33" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K33">
         <v>0.33403597655725259</v>
       </c>
       <c r="L33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P33">
         <v>8.1661604151791981E-2</v>
       </c>
       <c r="Q33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U33">
         <v>6.0610473518661813E-2</v>
       </c>
       <c r="V33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA33">
         <v>1E-3</v>
@@ -3768,49 +3768,49 @@
     </row>
     <row r="34" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>3.4785762810850281E-2</v>
       </c>
       <c r="L34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P34">
         <v>8.4711064271707354E-2</v>
       </c>
       <c r="Q34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U34">
         <v>7.46624292608115E-2</v>
       </c>
       <c r="V34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA34">
         <v>1E-3</v>
@@ -3818,49 +3818,49 @@
     </row>
     <row r="35" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K35">
         <v>4.9542588554788984E-2</v>
       </c>
       <c r="L35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P35">
         <v>1.6467166750910506E-2</v>
       </c>
       <c r="Q35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U35">
         <v>1.0355765141517342E-2</v>
       </c>
       <c r="V35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA35">
         <v>1E-3</v>
@@ -3868,49 +3868,49 @@
     </row>
     <row r="36" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K36">
         <v>5.1502029941549995E-2</v>
       </c>
       <c r="L36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P36">
         <v>0.13903683459611321</v>
       </c>
       <c r="Q36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U36">
         <v>0.14073200965808416</v>
       </c>
       <c r="V36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA36">
         <v>1E-3</v>
@@ -3918,49 +3918,49 @@
     </row>
     <row r="37" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P37">
         <v>0.1366006422733719</v>
       </c>
       <c r="Q37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U37">
         <v>0.1440053677999748</v>
       </c>
       <c r="V37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA37">
         <v>1E-3</v>
@@ -3968,49 +3968,49 @@
     </row>
     <row r="38" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K38">
         <v>1.6707435847249606E-3</v>
       </c>
       <c r="L38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P38">
         <v>2.5466491375397582E-2</v>
       </c>
       <c r="Q38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U38">
         <v>2.6892620812382216E-2</v>
       </c>
       <c r="V38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA38">
         <v>1E-3</v>
@@ -4018,3698 +4018,3698 @@
     </row>
     <row r="39" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K39">
         <v>0.13788965436774442</v>
       </c>
       <c r="L39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P39">
         <v>0.13047343663957478</v>
       </c>
       <c r="Q39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U39">
         <v>0.12531261547904199</v>
       </c>
       <c r="V39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P40">
         <v>0.1431973274361146</v>
       </c>
       <c r="Q40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U40">
         <v>0.13083677858151507</v>
       </c>
       <c r="V40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K41">
         <v>6.665227354950779E-3</v>
       </c>
       <c r="L41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P41">
         <v>2.4574192809648652E-2</v>
       </c>
       <c r="Q41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U41">
         <v>2.4337979615677702E-2</v>
       </c>
       <c r="V41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K42">
         <v>0.33262402906176292</v>
       </c>
       <c r="L42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P42">
         <v>0.10204606651976254</v>
       </c>
       <c r="Q42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U42">
         <v>0.11870502168186438</v>
       </c>
       <c r="V42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K43">
         <v>1.2215618714814573E-2</v>
       </c>
       <c r="L43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P43">
         <v>0.12042192738740498</v>
       </c>
       <c r="Q43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U43">
         <v>0.11390109476905269</v>
       </c>
       <c r="V43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K44">
         <v>3.3338127056515725E-2</v>
       </c>
       <c r="L44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P44">
         <v>2.1339892428197442E-2</v>
       </c>
       <c r="Q44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U44">
         <v>2.2997350797858758E-2</v>
       </c>
       <c r="V44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K45">
         <v>0.34863486920426295</v>
       </c>
       <c r="L45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P45">
         <v>6.2841226611418957E-2</v>
       </c>
       <c r="Q45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U45">
         <v>7.56193724210978E-2</v>
       </c>
       <c r="V45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K46">
         <v>3.237111227528975E-2</v>
       </c>
       <c r="L46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P46">
         <v>7.5773194606755301E-2</v>
       </c>
       <c r="Q46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U46">
         <v>7.8710494349623947E-2</v>
       </c>
       <c r="V46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K47">
         <v>4.6006957860412742E-2</v>
       </c>
       <c r="L47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P47">
         <v>1.1933080578166047E-2</v>
       </c>
       <c r="Q47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U47">
         <v>1.5791474080911815E-2</v>
       </c>
       <c r="V47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="9:27" x14ac:dyDescent="0.35">
       <c r="I48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K48">
         <v>4.9775657695302372E-2</v>
       </c>
       <c r="L48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P48">
         <v>0.14210599138999719</v>
       </c>
       <c r="Q48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U48">
         <v>0.13827583527529683</v>
       </c>
       <c r="V48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P49">
         <v>0.1390792088165978</v>
       </c>
       <c r="Q49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U49">
         <v>0.13027355061043067</v>
       </c>
       <c r="V49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K50">
         <v>4.7874640894123255E-4</v>
       </c>
       <c r="L50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P50">
         <v>2.6214454776361244E-2</v>
       </c>
       <c r="Q50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U50">
         <v>2.5238432337622796E-2</v>
       </c>
       <c r="V50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K51">
         <v>0.13518500255937776</v>
       </c>
       <c r="L51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P51">
         <v>0.12809669945662192</v>
       </c>
       <c r="Q51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U51">
         <v>0.12467109914282766</v>
       </c>
       <c r="V51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K52">
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P52">
         <v>0.14294726666526825</v>
       </c>
       <c r="Q52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U52">
         <v>0.13382803187589917</v>
       </c>
       <c r="V52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K53">
         <v>6.5204805630098154E-3</v>
       </c>
       <c r="L53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P53">
         <v>2.4189539484698222E-2</v>
       </c>
       <c r="Q53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U53">
         <v>2.4967780745612622E-2</v>
       </c>
       <c r="V53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K54">
         <v>0.33039684491230631</v>
       </c>
       <c r="L54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P54">
         <v>0.10285460315212781</v>
       </c>
       <c r="Q54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U54">
         <v>0.11664154412601307</v>
       </c>
       <c r="V54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K55">
         <v>1.2482741430276839E-2</v>
       </c>
       <c r="L55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P55">
         <v>0.12296274182225456</v>
       </c>
       <c r="Q55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U55">
         <v>0.11335612280245598</v>
       </c>
       <c r="V55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K56">
         <v>3.5984208919912102E-2</v>
       </c>
       <c r="L56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P56">
         <v>2.0846528140558419E-2</v>
       </c>
       <c r="Q56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U56">
         <v>2.3005859457604739E-2</v>
       </c>
       <c r="V56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K57">
         <v>0.35073305870189714</v>
       </c>
       <c r="L57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P57">
         <v>6.4472987117987726E-2</v>
       </c>
       <c r="Q57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U57">
         <v>7.3140825094525477E-2</v>
       </c>
       <c r="V57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K58">
         <v>3.0681573777721495E-2</v>
       </c>
       <c r="L58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P58">
         <v>7.9953031459588916E-2</v>
       </c>
       <c r="Q58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S58" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T58" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U58">
         <v>7.6077494228898229E-2</v>
       </c>
       <c r="V58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z58" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K59">
         <v>4.7990186592358958E-2</v>
       </c>
       <c r="L59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P59">
         <v>1.0831192914898173E-2</v>
       </c>
       <c r="Q59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S59" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U59">
         <v>1.5532888872722767E-2</v>
       </c>
       <c r="V59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z59" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K60">
         <v>4.9167361721862965E-2</v>
       </c>
       <c r="L60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P60">
         <v>0.13902163776782839</v>
       </c>
       <c r="Q60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U60">
         <v>0.13962403881435137</v>
       </c>
       <c r="V60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K61">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P61">
         <v>0.13757753926262756</v>
       </c>
       <c r="Q61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S61" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U61">
         <v>0.13350837678361063</v>
       </c>
       <c r="V61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z61" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K62">
         <v>8.5854082127588885E-4</v>
       </c>
       <c r="L62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P62">
         <v>2.6246232755542848E-2</v>
       </c>
       <c r="Q62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U62">
         <v>2.5645938055476915E-2</v>
       </c>
       <c r="V62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K63">
         <v>0.13704076089809919</v>
       </c>
       <c r="L63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N63" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P63">
         <v>0.129199134059795</v>
       </c>
       <c r="Q63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U63">
         <v>0.12368926256070416</v>
       </c>
       <c r="V63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P64">
         <v>0.14280869488679127</v>
       </c>
       <c r="Q64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U64">
         <v>0.12747679200925857</v>
       </c>
       <c r="V64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K65">
         <v>7.0322590090935045E-3</v>
       </c>
       <c r="L65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N65" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P65">
         <v>2.4746674590950292E-2</v>
       </c>
       <c r="Q65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U65">
         <v>2.3067692074372089E-2</v>
       </c>
       <c r="V65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K66">
         <v>0.32259962229292977</v>
       </c>
       <c r="L66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P66">
         <v>0.10145405837111347</v>
       </c>
       <c r="Q66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U66">
         <v>0.11862035712137464</v>
       </c>
       <c r="V66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K67">
         <v>1.3251866353888513E-2</v>
       </c>
       <c r="L67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N67" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P67">
         <v>0.1224410278960416</v>
       </c>
       <c r="Q67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U67">
         <v>0.1148814989821436</v>
       </c>
       <c r="V67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K68">
         <v>3.6136904502904348E-2</v>
       </c>
       <c r="L68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P68">
         <v>2.1439916031275898E-2</v>
       </c>
       <c r="Q68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U68">
         <v>2.2505030581402973E-2</v>
       </c>
       <c r="V68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K69">
         <v>0.35515918624160248</v>
       </c>
       <c r="L69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P69">
         <v>6.4543167279016975E-2</v>
       </c>
       <c r="Q69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U69">
         <v>7.9650483940907499E-2</v>
       </c>
       <c r="V69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K70">
         <v>3.4514306565389688E-2</v>
       </c>
       <c r="L70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N70" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P70">
         <v>7.6872225586629289E-2</v>
       </c>
       <c r="Q70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U70">
         <v>8.2244647409811092E-2</v>
       </c>
       <c r="V70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y70" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K71">
         <v>4.9394952078643153E-2</v>
       </c>
       <c r="L71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N71" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P71">
         <v>1.1833148583530682E-2</v>
       </c>
       <c r="Q71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S71" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U71">
         <v>1.5986762686449111E-2</v>
       </c>
       <c r="V71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z71" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K72">
         <v>4.4204161507446889E-2</v>
       </c>
       <c r="L72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P72">
         <v>0.14072958796265375</v>
       </c>
       <c r="Q72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U72">
         <v>0.13808023417662429</v>
       </c>
       <c r="V72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N73" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P73">
         <v>0.13765800710196696</v>
       </c>
       <c r="Q73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U73">
         <v>0.12909541092671956</v>
       </c>
       <c r="V73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K74">
         <v>6.659805500025261E-4</v>
       </c>
       <c r="L74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N74" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P74">
         <v>2.6274357650236987E-2</v>
       </c>
       <c r="Q74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U74">
         <v>2.4701827530234009E-2</v>
       </c>
       <c r="V74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I75" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K75">
         <v>0.13513344077982872</v>
       </c>
       <c r="L75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P75">
         <v>0.12638981598557553</v>
       </c>
       <c r="Q75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U75">
         <v>0.12537255776816833</v>
       </c>
       <c r="V75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I76" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K76">
         <v>9.1977132144519005E-6</v>
       </c>
       <c r="L76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N76" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P76">
         <v>0.13795376593518585</v>
       </c>
       <c r="Q76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S76" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U76">
         <v>0.12835957880225679</v>
       </c>
       <c r="V76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z76" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I77" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K77">
         <v>6.2570617343817641E-3</v>
       </c>
       <c r="L77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N77" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P77">
         <v>2.4843309428039376E-2</v>
       </c>
       <c r="Q77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U77">
         <v>2.3320356706553878E-2</v>
       </c>
       <c r="V77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K78">
         <v>0.3480669294670633</v>
       </c>
       <c r="L78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N78" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P78">
         <v>0.1016527773886627</v>
       </c>
       <c r="Q78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S78" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U78">
         <v>0.11469765734497872</v>
       </c>
       <c r="V78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z78" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K79">
         <v>1.2737580689977754E-2</v>
       </c>
       <c r="L79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P79">
         <v>0.12060953065136704</v>
       </c>
       <c r="Q79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U79">
         <v>0.11162259586870374</v>
       </c>
       <c r="V79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K80">
         <v>3.1219377433426988E-2</v>
       </c>
       <c r="L80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P80">
         <v>2.1498054495739747E-2</v>
       </c>
       <c r="Q80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U80">
         <v>2.1517963250247976E-2</v>
       </c>
       <c r="V80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K81">
         <v>0.33990377348327583</v>
       </c>
       <c r="L81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P81">
         <v>6.554953323933016E-2</v>
       </c>
       <c r="Q81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U81">
         <v>7.8999880889482274E-2</v>
       </c>
       <c r="V81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I82" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K82">
         <v>3.5489840043300767E-2</v>
       </c>
       <c r="L82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N82" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P82">
         <v>7.5936162267840598E-2</v>
       </c>
       <c r="Q82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U82">
         <v>8.1505940440433272E-2</v>
       </c>
       <c r="V82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="83" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K83">
         <v>4.0860842555058716E-2</v>
       </c>
       <c r="L83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N83" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P83">
         <v>1.2418773706407926E-2</v>
       </c>
       <c r="Q83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U83">
         <v>1.5592576483644194E-2</v>
       </c>
       <c r="V83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I84" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K84">
         <v>5.0252056606882284E-2</v>
       </c>
       <c r="L84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P84">
         <v>0.14750541621321081</v>
       </c>
       <c r="Q84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U84">
         <v>0.1402166445993536</v>
       </c>
       <c r="V84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I85" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K85">
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N85" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P85">
         <v>0.13936386512639157</v>
       </c>
       <c r="Q85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U85">
         <v>0.1335633330395827</v>
       </c>
       <c r="V85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I86" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K86">
         <v>6.9899493587908369E-5</v>
       </c>
       <c r="L86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N86" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P86">
         <v>2.6278995562247855E-2</v>
       </c>
       <c r="Q86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S86" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U86">
         <v>2.5230914806595842E-2</v>
       </c>
       <c r="V86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z86" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I87" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K87">
         <v>0.13416989637934093</v>
       </c>
       <c r="L87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N87" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P87">
         <v>0.12580073214139489</v>
       </c>
       <c r="Q87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U87">
         <v>0.12631543640639967</v>
       </c>
       <c r="V87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K88">
         <v>2.291419966374588E-6</v>
       </c>
       <c r="L88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N88" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P88">
         <v>0.13943599824207575</v>
       </c>
       <c r="Q88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U88">
         <v>0.12569744558972437</v>
       </c>
       <c r="V88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K89">
         <v>6.4756062968297336E-3</v>
       </c>
       <c r="L89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N89" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P89">
         <v>2.5136160161585271E-2</v>
       </c>
       <c r="Q89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S89" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U89">
         <v>2.3629214050528882E-2</v>
       </c>
       <c r="V89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z89" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I90" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K90">
         <v>0.34616332644244802</v>
       </c>
       <c r="L90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N90" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P90">
         <v>0.10991843774896405</v>
       </c>
       <c r="Q90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S90" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U90">
         <v>0.11434150037628311</v>
       </c>
       <c r="V90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z90" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="91" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I91" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K91">
         <v>1.2930636028432523E-2</v>
       </c>
       <c r="L91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N91" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P91">
         <v>0.11945616844315941</v>
       </c>
       <c r="Q91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S91" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U91">
         <v>0.11413102808994473</v>
       </c>
       <c r="V91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z91" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I92" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K92">
         <v>3.0055862146451947E-2</v>
       </c>
       <c r="L92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N92" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P92">
         <v>2.2436381028912631E-2</v>
       </c>
       <c r="Q92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U92">
         <v>2.097136390331587E-2</v>
       </c>
       <c r="V92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K93">
         <v>0.34000998277130884</v>
       </c>
       <c r="L93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N93" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P93">
         <v>6.593608910998304E-2</v>
       </c>
       <c r="Q93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S93" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U93">
         <v>7.684101920754563E-2</v>
       </c>
       <c r="V93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z93" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I94" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K94">
         <v>3.3067352280655542E-2</v>
       </c>
       <c r="L94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N94" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P94">
         <v>7.8642770753477795E-2</v>
       </c>
       <c r="Q94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S94" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U94">
         <v>8.3343886016292584E-2</v>
       </c>
       <c r="V94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z94" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I95" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K95">
         <v>4.2309536326529722E-2</v>
       </c>
       <c r="L95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N95" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P95">
         <v>1.3836938284508195E-2</v>
       </c>
       <c r="Q95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U95">
         <v>1.4928584313169086E-2</v>
       </c>
       <c r="V95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="96" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I96" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K96">
         <v>5.4698413363997639E-2</v>
       </c>
       <c r="L96" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N96" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P96">
         <v>0.1386152975371186</v>
       </c>
       <c r="Q96" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S96" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U96">
         <v>0.138578783548439</v>
       </c>
       <c r="V96" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z96" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="97" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K97">
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N97" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P97">
         <v>0.13512354523104875</v>
       </c>
       <c r="Q97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S97" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U97">
         <v>0.13621329250753636</v>
       </c>
       <c r="V97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z97" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="98" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J98" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K98">
         <v>1.1709654404024687E-4</v>
       </c>
       <c r="L98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O98" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P98">
         <v>2.5661481317773408E-2</v>
       </c>
       <c r="Q98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S98" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T98" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U98">
         <v>2.500844599081932E-2</v>
       </c>
       <c r="V98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z98" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I99" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K99">
         <v>0.14050968220146234</v>
       </c>
       <c r="L99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N99" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P99">
         <v>0.1267671949798799</v>
       </c>
       <c r="Q99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S99" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U99">
         <v>0.12571372506412062</v>
       </c>
       <c r="V99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z99" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I100" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J100" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K100">
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O100" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P100">
         <v>0.13876772986981015</v>
       </c>
       <c r="Q100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S100" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T100" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U100">
         <v>0.12657401175035871</v>
       </c>
       <c r="V100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z100" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="101" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I101" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K101">
         <v>6.331618867427489E-3</v>
       </c>
       <c r="L101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N101" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P101">
         <v>2.506295410048941E-2</v>
       </c>
       <c r="Q101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S101" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U101">
         <v>2.3927906584502445E-2</v>
       </c>
       <c r="V101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z101" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I102" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J102" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K102">
         <v>0.33121410256383899</v>
       </c>
       <c r="L102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N102" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O102" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P102">
         <v>0.10332983278032665</v>
       </c>
       <c r="Q102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S102" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T102" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U102">
         <v>0.11151391291783615</v>
       </c>
       <c r="V102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z102" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="103" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I103" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J103" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K103">
         <v>1.2958816654800859E-2</v>
       </c>
       <c r="L103" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N103" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O103" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P103">
         <v>0.11777530862955292</v>
       </c>
       <c r="Q103" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S103" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T103" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U103">
         <v>0.11062553350565904</v>
       </c>
       <c r="V103" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z103" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="104" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I104" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K104">
         <v>3.3746773172483729E-2</v>
       </c>
       <c r="L104" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N104" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P104">
         <v>2.1128161076743861E-2</v>
       </c>
       <c r="Q104" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S104" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U104">
         <v>2.0357355210697727E-2</v>
       </c>
       <c r="V104" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z104" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I105" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J105" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K105">
         <v>0.34938181661706941</v>
       </c>
       <c r="L105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N105" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O105" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P105">
         <v>6.9630153205998191E-2</v>
       </c>
       <c r="Q105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S105" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T105" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U105">
         <v>7.9319803306361777E-2</v>
       </c>
       <c r="V105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y105" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z105" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="106" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I106" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J106" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K106">
         <v>3.5005730754924899E-2</v>
       </c>
       <c r="L106" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N106" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O106" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P106">
         <v>7.567705618236456E-2</v>
       </c>
       <c r="Q106" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S106" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T106" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U106">
         <v>8.104053391824248E-2</v>
       </c>
       <c r="V106" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y106" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z106" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="107" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I107" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J107" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K107">
         <v>4.5873641820294388E-2</v>
       </c>
       <c r="L107" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N107" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O107" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P107">
         <v>1.405419420329863E-2</v>
       </c>
       <c r="Q107" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S107" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T107" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U107">
         <v>1.5152995180316965E-2</v>
       </c>
       <c r="V107" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z107" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="108" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I108" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J108" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K108">
         <v>4.4759317459311727E-2</v>
       </c>
       <c r="L108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N108" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O108" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P108">
         <v>0.14235751042892741</v>
       </c>
       <c r="Q108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S108" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T108" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U108">
         <v>0.14104084598799538</v>
       </c>
       <c r="V108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z108" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I109" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J109" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K109">
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N109" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O109" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P109">
         <v>0.13917553905188212</v>
       </c>
       <c r="Q109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S109" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T109" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U109">
         <v>0.13898725953801011</v>
       </c>
       <c r="V109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y109" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z109" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I110" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K110">
         <v>2.184998883840245E-4</v>
       </c>
       <c r="L110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N110" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P110">
         <v>2.6274365490724042E-2</v>
       </c>
       <c r="Q110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S110" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T110" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U110">
         <v>2.5746117035898256E-2</v>
       </c>
       <c r="V110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z110" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I111" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J111" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K111">
         <v>0.13922781277973365</v>
       </c>
       <c r="L111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N111" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O111" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P111">
         <v>0.12733260672506325</v>
       </c>
       <c r="Q111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S111" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T111" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U111">
         <v>0.12594751915143254</v>
       </c>
       <c r="V111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y111" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z111" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="112" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I112" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J112" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K112">
         <v>3.2459343820410072E-5</v>
       </c>
       <c r="L112" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N112" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O112" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P112">
         <v>0.14173308433155787</v>
       </c>
       <c r="Q112" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T112" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U112">
         <v>0.13067799487984125</v>
       </c>
       <c r="V112" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y112" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="113" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I113" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K113">
         <v>5.9820562363117596E-3</v>
       </c>
       <c r="L113" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N113" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P113">
         <v>2.5244253728599505E-2</v>
       </c>
       <c r="Q113" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T113" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U113">
         <v>2.4901503527877254E-2</v>
       </c>
       <c r="V113" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I114" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J114" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K114">
         <v>0.34434183574985155</v>
       </c>
       <c r="L114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N114" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O114" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P114">
         <v>0.10375622367614544</v>
       </c>
       <c r="Q114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S114" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T114" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U114">
         <v>0.10284574176169634</v>
       </c>
       <c r="V114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y114" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z114" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I115" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J115" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K115">
         <v>1.2758174343801717E-2</v>
       </c>
       <c r="L115" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N115" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O115" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P115">
         <v>0.12028123022816023</v>
       </c>
       <c r="Q115" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S115" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T115" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U115">
         <v>0.10828860141798145</v>
       </c>
       <c r="V115" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y115" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z115" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="116" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I116" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K116">
         <v>3.189142205120217E-2</v>
       </c>
       <c r="L116" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N116" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P116">
         <v>2.1737932659842332E-2</v>
       </c>
       <c r="Q116" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S116" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U116">
         <v>2.0556576325748206E-2</v>
       </c>
       <c r="V116" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y116" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z116" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="117" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I117" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J117" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K117">
         <v>0.34274457192434349</v>
       </c>
       <c r="L117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N117" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O117" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P117">
         <v>6.3532964121559052E-2</v>
       </c>
       <c r="Q117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S117" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T117" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U117">
         <v>7.7883070934806939E-2</v>
       </c>
       <c r="V117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y117" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z117" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I118" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J118" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K118">
         <v>3.6784391902611284E-2</v>
       </c>
       <c r="L118" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N118" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O118" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P118">
         <v>7.6382750604245514E-2</v>
       </c>
       <c r="Q118" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S118" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T118" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U118">
         <v>8.5439837550152109E-2</v>
       </c>
       <c r="V118" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y118" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z118" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I119" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J119" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K119">
         <v>4.1302924302350365E-2</v>
       </c>
       <c r="L119" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N119" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O119" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P119">
         <v>1.2385615422098289E-2</v>
       </c>
       <c r="Q119" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T119" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U119">
         <v>1.6291379670146322E-2</v>
       </c>
       <c r="V119" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="120" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I120" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J120" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K120">
         <v>4.4911935384215486E-2</v>
       </c>
       <c r="L120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N120" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O120" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P120">
         <v>0.14263676093132049</v>
       </c>
       <c r="Q120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S120" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T120" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U120">
         <v>0.14212507009010286</v>
       </c>
       <c r="V120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y120" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z120" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I121" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J121" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K121">
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N121" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O121" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P121">
         <v>0.1385722979114157</v>
       </c>
       <c r="Q121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T121" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U121">
         <v>0.13947244725593388</v>
       </c>
       <c r="V121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y121" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I122" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J122" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K122">
         <v>2.2415981755578517E-5</v>
       </c>
       <c r="L122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N122" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O122" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P122">
         <v>2.6404279659992709E-2</v>
       </c>
       <c r="Q122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T122" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U122">
         <v>2.5570257434281173E-2</v>
       </c>
       <c r="V122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y122" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Z122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -7730,12 +7730,12 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -7743,16 +7743,16 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
         <v>115</v>
       </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>116</v>
-      </c>
-      <c r="E4" t="s">
-        <v>117</v>
       </c>
       <c r="F4">
         <v>2025</v>
@@ -7766,16 +7766,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
         <v>118</v>
-      </c>
-      <c r="B5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" t="s">
-        <v>119</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -7792,16 +7792,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E6">
         <v>0.1</v>
@@ -7818,16 +7818,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -7841,16 +7841,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -7867,16 +7867,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -7903,7 +7903,7 @@
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -7911,7 +7911,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -7919,13 +7919,13 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5">
         <v>2100</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -8008,7 +8008,7 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.35">
@@ -8036,7 +8036,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>2.5760000000000001</v>
@@ -8048,7 +8048,7 @@
         <v>2.6659999999999999</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.35">
@@ -8056,7 +8056,7 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -8068,7 +8068,7 @@
         <v>3.5</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -8095,12 +8095,12 @@
   <sheetData>
     <row r="5" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.35">
@@ -8108,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>2022</v>
@@ -8134,10 +8134,10 @@
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3">
         <v>35.145058821884028</v>
@@ -8168,10 +8168,10 @@
     </row>
     <row r="9" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="3">
         <v>96.367112810707454</v>
@@ -8202,10 +8202,10 @@
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3">
         <v>46.470588235294123</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3">
         <v>45.792000000000002</v>
@@ -8265,37 +8265,37 @@
     </row>
     <row r="16" spans="2:24" x14ac:dyDescent="0.35">
       <c r="L16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N16" t="s">
+        <v>140</v>
+      </c>
+      <c r="O16" t="s">
         <v>141</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
+        <v>143</v>
+      </c>
+      <c r="R16" t="s">
+        <v>136</v>
+      </c>
+      <c r="T16" t="s">
+        <v>133</v>
+      </c>
+      <c r="U16" t="s">
+        <v>134</v>
+      </c>
+      <c r="V16" t="s">
+        <v>139</v>
+      </c>
+      <c r="W16" t="s">
         <v>142</v>
       </c>
-      <c r="P16" t="s">
-        <v>144</v>
-      </c>
-      <c r="R16" t="s">
-        <v>137</v>
-      </c>
-      <c r="T16" t="s">
-        <v>134</v>
-      </c>
-      <c r="U16" t="s">
+      <c r="X16" t="s">
         <v>135</v>
-      </c>
-      <c r="V16" t="s">
-        <v>140</v>
-      </c>
-      <c r="W16" t="s">
-        <v>143</v>
-      </c>
-      <c r="X16" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="17" spans="12:24" x14ac:dyDescent="0.35">
@@ -8315,13 +8315,13 @@
         <v>3600000</v>
       </c>
       <c r="Q17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R17">
         <v>3412142</v>
       </c>
       <c r="T17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U17">
         <v>79</v>
@@ -8341,13 +8341,13 @@
     </row>
     <row r="18" spans="12:24" x14ac:dyDescent="0.35">
       <c r="Q18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R18" s="1">
         <v>588235</v>
       </c>
       <c r="T18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="U18">
         <v>10.3</v>
@@ -8367,13 +8367,13 @@
     </row>
     <row r="19" spans="12:24" x14ac:dyDescent="0.35">
       <c r="Q19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R19">
         <v>150000</v>
       </c>
       <c r="T19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U19">
         <v>112</v>
@@ -8393,7 +8393,7 @@
     </row>
     <row r="20" spans="12:24" x14ac:dyDescent="0.35">
       <c r="T20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="V20">
         <v>12.72</v>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A86615-FB74-4034-8568-A4A96F1C4CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B190DA16-CCF2-463F-A397-1A3480A38BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="necessary_for_some_reason" sheetId="6" r:id="rId4"/>
     <sheet name="trade" sheetId="2" r:id="rId5"/>
     <sheet name="fuel_costs" sheetId="3" r:id="rId6"/>
+    <sheet name="constraints" sheetId="7" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="160">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -534,6 +535,24 @@
   </si>
   <si>
     <t>TFM_INS-TS: attribute=flo_cost</t>
+  </si>
+  <si>
+    <t>~UC_T:UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>Pset_Set</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UC_max_oil_shale_capacity</t>
+  </si>
+  <si>
+    <t>C02Captured</t>
   </si>
 </sst>
 </file>
@@ -578,11 +597,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8406,4 +8426,79 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1758F-E590-4DA8-B461-246947AA96DE}">
+  <dimension ref="A2:G8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>2030</v>
+      </c>
+      <c r="F5">
+        <v>2050</v>
+      </c>
+      <c r="G5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B190DA16-CCF2-463F-A397-1A3480A38BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372837BB-EF09-4E22-BBEB-B0127633219C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -552,7 +552,7 @@
     <t>UC_max_oil_shale_capacity</t>
   </si>
   <si>
-    <t>C02Captured</t>
+    <t>-C02Captured</t>
   </si>
 </sst>
 </file>
@@ -8430,7 +8430,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1758F-E590-4DA8-B461-246947AA96DE}">
-  <dimension ref="A2:G8"/>
+  <dimension ref="A2:G6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
@@ -8493,11 +8493,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372837BB-EF09-4E22-BBEB-B0127633219C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F07D28-5C8A-47F2-A566-18C3515F9719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="169">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -546,13 +546,40 @@
     <t>Pset_Set</t>
   </si>
   <si>
+    <t>LimType</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>EST</t>
+  </si>
+  <si>
     <t>UC_RHSRT~0</t>
   </si>
   <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UC_min_solid_2035</t>
+  </si>
+  <si>
+    <t>pp_controllable</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>Minimum solid fuel power plants penetration</t>
+  </si>
+  <si>
     <t>UC_max_oil_shale_capacity</t>
   </si>
   <si>
-    <t>-C02Captured</t>
+    <t>Subcritical Coal,Supercritical Coal</t>
+  </si>
+  <si>
+    <t>UP</t>
   </si>
 </sst>
 </file>
@@ -8430,66 +8457,157 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1758F-E590-4DA8-B461-246947AA96DE}">
-  <dimension ref="A2:G6"/>
+  <dimension ref="A2:I17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="E4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>155</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>156</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5">
+      <c r="D6" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7">
         <v>2030</v>
       </c>
-      <c r="F5">
+      <c r="E7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0.28299999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8">
         <v>2050</v>
       </c>
-      <c r="G5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6">
-        <v>0.28299999999999997</v>
-      </c>
-      <c r="F6">
+      <c r="E8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
-      <c r="G6">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15">
+        <v>2030</v>
+      </c>
+      <c r="E15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16">
+        <v>2035</v>
+      </c>
+      <c r="E16" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>164</v>
+      </c>
+      <c r="G17">
         <v>3</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997D792C-4708-4C33-9AE4-47CD786B5559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7011B4-4A88-4B75-AB59-833CFBD88B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="262">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -857,6 +857,9 @@
   <si>
     <t>~TFM_INS-AT</t>
   </si>
+  <si>
+    <t>TFM_DINS-AT</t>
+  </si>
 </sst>
 </file>
 
@@ -1771,7 +1774,7 @@
         <v>260</v>
       </c>
       <c r="AK1" t="s">
-        <v>86</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.35">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7011B4-4A88-4B75-AB59-833CFBD88B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FB4B6C-4045-42D9-819C-DCD2385DA842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="261">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -857,9 +857,6 @@
   <si>
     <t>~TFM_INS-AT</t>
   </si>
-  <si>
-    <t>TFM_DINS-AT</t>
-  </si>
 </sst>
 </file>
 
@@ -1774,7 +1771,7 @@
         <v>260</v>
       </c>
       <c r="AK1" t="s">
-        <v>261</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.35">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE61DDE6-B724-4142-9FC7-6D4D5F5486CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED0D6FC-F920-4D0F-BCD3-38BA545B9410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -44281,7 +44281,7 @@
         <v>143</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6BDF41-F5A4-4225-8EA4-DD8B69C32F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18A5C0F-0444-4041-BB80-75C47FABB0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -1594,6 +1594,9 @@
         <v>79</v>
       </c>
       <c r="E19">
+        <v>100</v>
+      </c>
+      <c r="H19">
         <v>338.40000000000003</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D29BD5E-0674-449B-B982-6A41D7FF4CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBEB4F8-FA58-4224-BA9B-AFCBDE6573F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -1310,48 +1310,45 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D5">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="E5">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="F5">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="G5">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H5">
-        <v>2045</v>
-      </c>
-      <c r="I5">
         <v>2050</v>
       </c>
-      <c r="J5" t="s">
+      <c r="I5" t="s">
         <v>2</v>
       </c>
+      <c r="M5">
+        <v>8.5</v>
+      </c>
       <c r="N5">
-        <v>8.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="O5">
-        <v>8.6999999999999993</v>
+        <v>10.4</v>
       </c>
       <c r="P5">
-        <v>10.4</v>
+        <v>12.2</v>
       </c>
       <c r="Q5">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="R5">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="S5">
-        <v>15</v>
-      </c>
-      <c r="T5">
         <v>16</v>
       </c>
     </row>
@@ -1360,27 +1357,24 @@
         <v>71</v>
       </c>
       <c r="C6">
-        <v>2.9033099999999998</v>
+        <v>3.3980000000000001</v>
       </c>
       <c r="D6">
-        <v>3.3980000000000001</v>
+        <v>3.57</v>
       </c>
       <c r="E6">
-        <v>3.57</v>
+        <v>3.9750000000000001</v>
       </c>
       <c r="F6">
-        <v>3.9750000000000001</v>
+        <v>4.3120000000000003</v>
       </c>
       <c r="G6">
-        <v>4.3120000000000003</v>
+        <v>4.5830000000000002</v>
       </c>
       <c r="H6">
-        <v>4.5830000000000002</v>
-      </c>
-      <c r="I6">
         <v>4.798</v>
       </c>
-      <c r="J6" t="s">
+      <c r="I6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1389,27 +1383,24 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>2.0885600000000002</v>
+        <v>2.6019999999999999</v>
       </c>
       <c r="D7">
-        <v>2.6019999999999999</v>
+        <v>2.6349999999999998</v>
       </c>
       <c r="E7">
-        <v>2.6349999999999998</v>
+        <v>2.657</v>
       </c>
       <c r="F7">
-        <v>2.657</v>
+        <v>2.806</v>
       </c>
       <c r="G7">
-        <v>2.806</v>
+        <v>3.008</v>
       </c>
       <c r="H7">
-        <v>3.008</v>
-      </c>
-      <c r="I7">
         <v>3.306</v>
       </c>
-      <c r="J7" t="s">
+      <c r="I7" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1418,27 +1409,24 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>1.96688</v>
+        <v>2.1909999999999998</v>
       </c>
       <c r="D8">
-        <v>2.1909999999999998</v>
+        <v>2.3180000000000001</v>
       </c>
       <c r="E8">
-        <v>2.3180000000000001</v>
+        <v>2.5470000000000002</v>
       </c>
       <c r="F8">
-        <v>2.5470000000000002</v>
+        <v>2.7719999999999998</v>
       </c>
       <c r="G8">
-        <v>2.7719999999999998</v>
+        <v>2.9969999999999999</v>
       </c>
       <c r="H8">
-        <v>2.9969999999999999</v>
-      </c>
-      <c r="I8">
         <v>3.206</v>
       </c>
-      <c r="J8" t="s">
+      <c r="I8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1447,62 +1435,75 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>3.5150000000000001E-2</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="D9">
-        <v>0.28100000000000003</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="E9">
-        <v>0.58599999999999997</v>
+        <v>1.095</v>
       </c>
       <c r="F9">
-        <v>1.095</v>
+        <v>1.4690000000000001</v>
       </c>
       <c r="G9">
-        <v>1.4690000000000001</v>
+        <v>2.3660000000000001</v>
       </c>
       <c r="H9">
-        <v>2.3660000000000001</v>
-      </c>
-      <c r="I9">
         <v>3.2690000000000001</v>
       </c>
-      <c r="J9" t="s">
+      <c r="I9" t="s">
         <v>4</v>
+      </c>
+      <c r="N9">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>2.9033099999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <v>2.0885600000000002</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
+      <c r="N12">
+        <v>1.96688</v>
+      </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13">
-        <v>9.950000000000081E-2</v>
+        <v>0.43282499999999935</v>
       </c>
       <c r="D13">
-        <v>0.43282499999999935</v>
+        <v>0.8755999999999986</v>
       </c>
       <c r="E13">
-        <v>0.8755999999999986</v>
+        <v>1.5402599999999982</v>
       </c>
       <c r="F13">
-        <v>1.5402599999999982</v>
+        <v>2.3064099999999979</v>
       </c>
       <c r="G13">
-        <v>2.3064099999999979</v>
+        <v>2.3123799999999974</v>
       </c>
       <c r="H13">
-        <v>2.3123799999999974</v>
-      </c>
-      <c r="I13">
         <v>2.5670999999999964</v>
       </c>
-      <c r="J13" t="s">
+      <c r="I13" t="s">
         <v>4</v>
+      </c>
+      <c r="N13">
+        <v>3.5150000000000001E-2</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
@@ -1516,30 +1517,30 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>0.13133999999999996</v>
       </c>
       <c r="F14">
-        <v>0.13133999999999996</v>
+        <v>0.30645999999999995</v>
       </c>
       <c r="G14">
-        <v>0.30645999999999995</v>
+        <v>0.32635999999999987</v>
       </c>
       <c r="H14">
-        <v>0.32635999999999987</v>
-      </c>
-      <c r="I14">
         <v>0.76415999999999984</v>
       </c>
-      <c r="J14" t="s">
+      <c r="I14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="O17">
+        <v>9.950000000000081E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>2</v>
       </c>
@@ -1558,8 +1559,11 @@
       <c r="G18" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>76</v>
       </c>
@@ -1573,7 +1577,7 @@
         <v>338.40000000000003</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>76</v>
       </c>
@@ -1587,7 +1591,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>76</v>
       </c>
@@ -1601,7 +1605,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>81</v>
       </c>
@@ -43423,7 +43427,7 @@
         <v>90</v>
       </c>
       <c r="F4">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="G4">
         <v>2040</v>
@@ -43603,142 +43607,139 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0573AE-84FA-4F18-8D18-B7F3EC5B3273}">
-  <dimension ref="B4:V14"/>
+  <dimension ref="B4:U14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D5">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="E5">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="F5">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="G5">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="H5">
-        <v>2045</v>
-      </c>
-      <c r="I5">
         <v>2050</v>
       </c>
+      <c r="I5" t="s">
+        <v>2</v>
+      </c>
       <c r="J5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
         <v>12</v>
       </c>
+      <c r="P5" t="s">
+        <v>255</v>
+      </c>
       <c r="Q5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="S5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="T5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="U5" t="s">
-        <v>259</v>
-      </c>
-      <c r="V5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
         <v>7.18</v>
       </c>
+      <c r="I6" t="s">
+        <v>14</v>
+      </c>
       <c r="J6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="P6" t="s">
         <v>261</v>
       </c>
+      <c r="Q6">
+        <v>1147</v>
+      </c>
       <c r="R6">
-        <v>1147</v>
+        <v>1259</v>
       </c>
       <c r="S6">
-        <v>1259</v>
+        <v>1016</v>
       </c>
       <c r="T6">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7">
         <v>6.17</v>
       </c>
+      <c r="I7" t="s">
+        <v>14</v>
+      </c>
       <c r="J7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" t="s">
         <v>15</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="P7" t="s">
         <v>262</v>
       </c>
+      <c r="Q7">
+        <v>850</v>
+      </c>
       <c r="R7">
-        <v>850</v>
+        <v>1149</v>
       </c>
       <c r="S7">
-        <v>1149</v>
+        <v>1016</v>
       </c>
       <c r="T7">
-        <v>1016</v>
+        <v>0</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="Q8" t="s">
         <v>263</v>
       </c>
       <c r="R8">
-        <f>SUM(R6:R7)/COUNT(R6:R7)</f>
+        <f>SUM(Q6:Q7)/COUNT(Q6:Q7)</f>
         <v>998.5</v>
       </c>
       <c r="S8">
-        <f t="shared" ref="S8:T8" si="0">SUM(S6:S7)/COUNT(S6:S7)</f>
+        <f t="shared" ref="S8:T8" si="0">SUM(R6:R7)/COUNT(R6:R7)</f>
         <v>1204</v>
       </c>
       <c r="T8">
@@ -43746,7 +43747,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="Q9" t="s">
         <v>265</v>
       </c>
@@ -43755,12 +43756,12 @@
         <v>3218.5</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
       </c>
@@ -43780,7 +43781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -43803,7 +43804,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>13</v>
       </c>
@@ -43830,32 +43831,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BDE16D-C995-4313-9FD3-ABCD01C0EB3D}">
-  <dimension ref="B5:X20"/>
+  <dimension ref="B5:W20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>1</v>
       </c>
@@ -43863,28 +43864,25 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E7">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="F7">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="G7">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="H7">
-        <v>2040</v>
+        <v>2045</v>
       </c>
       <c r="I7">
-        <v>2045</v>
-      </c>
-      <c r="J7">
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>18</v>
       </c>
@@ -43895,30 +43893,27 @@
         <v>35.145058821884028</v>
       </c>
       <c r="E8" s="3">
-        <v>35.145058821884028</v>
+        <f>D8-(D8*0.02)</f>
+        <v>34.442157645446351</v>
       </c>
       <c r="F8" s="3">
         <f>E8-(E8*0.02)</f>
-        <v>34.442157645446351</v>
+        <v>33.75331449253742</v>
       </c>
       <c r="G8" s="3">
-        <f>F8-(F8*0.02)</f>
-        <v>33.75331449253742</v>
+        <f>F8+(F8*0.02)</f>
+        <v>34.428380782388167</v>
       </c>
       <c r="H8" s="3">
-        <f>G8+(G8*0.02)</f>
-        <v>34.428380782388167</v>
+        <f t="shared" ref="H8:I8" si="0">G8+(G8*0.02)</f>
+        <v>35.11694839803593</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" ref="I8:J8" si="0">H8+(H8*0.02)</f>
-        <v>35.11694839803593</v>
-      </c>
-      <c r="J8" s="3">
         <f t="shared" si="0"/>
         <v>35.819287365996651</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>19</v>
       </c>
@@ -43929,30 +43924,27 @@
         <v>96.367112810707454</v>
       </c>
       <c r="E9" s="3">
-        <v>96.367112810707454</v>
+        <f>D9-(D9*$E$13)</f>
+        <v>94.439770554493307</v>
       </c>
       <c r="F9" s="3">
-        <f>E9-(E9*$F$13)</f>
-        <v>94.439770554493307</v>
+        <f t="shared" ref="F9:I9" si="1">E9-(E9*$E$13)</f>
+        <v>92.550975143403434</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" ref="G9:J9" si="1">F9-(F9*$F$13)</f>
-        <v>92.550975143403434</v>
+        <f t="shared" si="1"/>
+        <v>90.699955640535364</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="1"/>
-        <v>90.699955640535364</v>
+        <v>88.885956527724659</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="1"/>
-        <v>88.885956527724659</v>
-      </c>
-      <c r="J9" s="3">
-        <f t="shared" si="1"/>
         <v>87.108237397170171</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>20</v>
       </c>
@@ -43963,25 +43955,22 @@
         <v>46.470588235294123</v>
       </c>
       <c r="E10" s="3">
-        <v>46.470588235294123</v>
+        <v>58.830000000000005</v>
       </c>
       <c r="F10" s="3">
-        <v>58.830000000000005</v>
+        <v>53.53</v>
       </c>
       <c r="G10" s="3">
         <v>53.53</v>
       </c>
       <c r="H10" s="3">
-        <v>53.53</v>
+        <v>55.120000000000005</v>
       </c>
       <c r="I10" s="3">
-        <v>55.120000000000005</v>
-      </c>
-      <c r="J10" s="3">
         <v>60.419999999999995</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>21</v>
       </c>
@@ -43992,166 +43981,163 @@
         <v>45.792000000000002</v>
       </c>
       <c r="E11" s="3">
-        <v>45.792000000000002</v>
+        <v>24.96</v>
       </c>
       <c r="F11" s="3">
         <v>24.96</v>
       </c>
       <c r="G11" s="3">
-        <v>24.96</v>
+        <v>23.52</v>
       </c>
       <c r="H11" s="3">
-        <v>23.52</v>
+        <v>23.759999999999998</v>
       </c>
       <c r="I11" s="3">
-        <v>23.759999999999998</v>
-      </c>
-      <c r="J11" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="F13">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="E13">
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="K16" t="s">
+        <v>120</v>
+      </c>
       <c r="L16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M16" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="N16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
-      </c>
-      <c r="P16" t="s">
         <v>117</v>
       </c>
-      <c r="R16" t="s">
+      <c r="Q16" t="s">
         <v>110</v>
       </c>
+      <c r="S16" t="s">
+        <v>107</v>
+      </c>
       <c r="T16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U16" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="V16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="W16" t="s">
-        <v>116</v>
-      </c>
-      <c r="X16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="12:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <v>4.1840000000000002</v>
+      </c>
       <c r="L17">
-        <v>4.1840000000000002</v>
+        <v>1.0550558526</v>
       </c>
       <c r="M17">
-        <v>1.0550558526</v>
+        <v>6.12</v>
       </c>
       <c r="N17">
-        <v>6.12</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
-      </c>
-      <c r="P17">
         <v>3600000</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="P17" t="s">
         <v>106</v>
       </c>
-      <c r="R17">
+      <c r="Q17">
         <v>3412142</v>
       </c>
-      <c r="T17" t="s">
+      <c r="S17" t="s">
         <v>20</v>
       </c>
-      <c r="U17">
+      <c r="T17">
         <v>79</v>
       </c>
+      <c r="U17" s="2">
+        <f>T17/M17</f>
+        <v>12.908496732026144</v>
+      </c>
       <c r="V17" s="2">
-        <f>U17/N17</f>
-        <v>12.908496732026144</v>
+        <f>U17*N17</f>
+        <v>46.470588235294123</v>
       </c>
       <c r="W17" s="2">
-        <f>V17*O17</f>
-        <v>46.470588235294123</v>
-      </c>
-      <c r="X17" s="2">
-        <f>V17*P17</f>
+        <f>U17*O17</f>
         <v>46470588.235294119</v>
       </c>
     </row>
-    <row r="18" spans="12:24" x14ac:dyDescent="0.25">
-      <c r="Q18" t="s">
+    <row r="18" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
         <v>111</v>
       </c>
-      <c r="R18" s="1">
+      <c r="Q18" s="1">
         <v>588235</v>
       </c>
-      <c r="T18" t="s">
+      <c r="S18" t="s">
         <v>118</v>
       </c>
-      <c r="U18">
+      <c r="T18">
         <v>10.3</v>
       </c>
+      <c r="U18" s="2">
+        <f>T18/L17</f>
+        <v>9.7625163394122296</v>
+      </c>
       <c r="V18" s="2">
-        <f>U18/M17</f>
-        <v>9.7625163394122296</v>
+        <f>U18*N17</f>
+        <v>35.145058821884028</v>
       </c>
       <c r="W18" s="2">
-        <f>V18*O17</f>
-        <v>35.145058821884028</v>
-      </c>
-      <c r="X18" s="2">
-        <f>V18*P17</f>
+        <f>U18*O17</f>
         <v>35145058.821884029</v>
       </c>
     </row>
-    <row r="19" spans="12:24" x14ac:dyDescent="0.25">
-      <c r="Q19" t="s">
+    <row r="19" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="P19" t="s">
         <v>112</v>
       </c>
-      <c r="R19">
+      <c r="Q19">
         <v>150000</v>
       </c>
-      <c r="T19" t="s">
+      <c r="S19" t="s">
         <v>19</v>
       </c>
-      <c r="U19">
+      <c r="T19">
         <v>112</v>
       </c>
+      <c r="U19" s="2">
+        <f>T19/K17</f>
+        <v>26.768642447418738</v>
+      </c>
       <c r="V19" s="2">
-        <f>U19/L17</f>
-        <v>26.768642447418738</v>
+        <f>U19*N17</f>
+        <v>96.367112810707454</v>
       </c>
       <c r="W19" s="2">
-        <f>V19*O17</f>
-        <v>96.367112810707454</v>
-      </c>
-      <c r="X19" s="2">
-        <f>V19*P17</f>
+        <f>U19*O17</f>
         <v>96367112.810707465</v>
       </c>
     </row>
-    <row r="20" spans="12:24" x14ac:dyDescent="0.25">
-      <c r="T20" t="s">
+    <row r="20" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="S20" t="s">
         <v>121</v>
       </c>
+      <c r="U20">
+        <v>12.72</v>
+      </c>
       <c r="V20">
-        <v>12.72</v>
-      </c>
-      <c r="W20">
-        <f>V20*O17</f>
+        <f>U20*N17</f>
         <v>45.792000000000002</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBEB4F8-FA58-4224-BA9B-AFCBDE6573F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDA0746-5C4E-4503-8F1B-4407E8791950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9896" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9909" uniqueCount="274">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -872,6 +872,30 @@
   <si>
     <t>Keskmine kokku</t>
   </si>
+  <si>
+    <t>~UC_T: FX</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>UCE_Solar capacity aggregation for peak</t>
+  </si>
+  <si>
+    <t>ElcAgg_Solar</t>
+  </si>
+  <si>
+    <t>UCE_Wind capacity aggregation for peak</t>
+  </si>
+  <si>
+    <t>ElcAgg_Wind</t>
+  </si>
+  <si>
+    <t>wind*</t>
+  </si>
+  <si>
+    <t>*aggregate solar and wind</t>
+  </si>
 </sst>
 </file>
 
@@ -43570,15 +43594,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A318F2-D986-4B43-9E10-D5047049B529}">
-  <dimension ref="A3:C5"/>
+  <dimension ref="A3:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -43589,7 +43618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -43598,6 +43627,75 @@
       </c>
       <c r="C5" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDA0746-5C4E-4503-8F1B-4407E8791950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF62037-09DC-4FE2-82F0-29229D191997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43594,7 +43594,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A318F2-D986-4B43-9E10-D5047049B529}">
-  <dimension ref="A3:F13"/>
+  <dimension ref="A3:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -43602,12 +43602,12 @@
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -43618,7 +43618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -43629,12 +43629,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -43650,11 +43650,11 @@
       <c r="E9" t="s">
         <v>129</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>268</v>
       </c>
@@ -43668,7 +43668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>91</v>
       </c>
@@ -43676,7 +43676,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>270</v>
       </c>
@@ -43690,7 +43690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>272</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF62037-09DC-4FE2-82F0-29229D191997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58F1D85-0D32-497E-9FAB-7CCD07BED44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9909" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9908" uniqueCount="273">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -893,9 +893,6 @@
   <si>
     <t>wind*</t>
   </si>
-  <si>
-    <t>*aggregate solar and wind</t>
-  </si>
 </sst>
 </file>
 
@@ -43594,7 +43591,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A318F2-D986-4B43-9E10-D5047049B529}">
-  <dimension ref="A3:G13"/>
+  <dimension ref="A3:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -43602,12 +43599,12 @@
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -43618,7 +43615,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -43629,12 +43626,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -43650,11 +43647,8 @@
       <c r="E9" t="s">
         <v>129</v>
       </c>
-      <c r="G9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>268</v>
       </c>
@@ -43668,7 +43662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>91</v>
       </c>
@@ -43676,7 +43670,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>270</v>
       </c>
@@ -43690,7 +43684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>272</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58F1D85-0D32-497E-9FAB-7CCD07BED44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0D263A-2AA6-432B-91DD-1F9531A171E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43591,7 +43591,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A318F2-D986-4B43-9E10-D5047049B529}">
-  <dimension ref="A3:E13"/>
+  <dimension ref="A3:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -43599,12 +43599,12 @@
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -43615,7 +43615,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -43626,69 +43626,69 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
         <v>124</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D11" t="s">
         <v>267</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E11" t="s">
         <v>35</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F11" t="s">
         <v>127</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
         <v>268</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D12" t="s">
         <v>269</v>
       </c>
-      <c r="D10">
+      <c r="F12">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="G12">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
         <v>91</v>
       </c>
-      <c r="D11">
+      <c r="F13">
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
         <v>270</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D14" t="s">
         <v>271</v>
       </c>
-      <c r="D12">
+      <c r="F14">
         <v>1</v>
       </c>
-      <c r="E12">
+      <c r="G14">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
         <v>272</v>
       </c>
-      <c r="D13">
+      <c r="F15">
         <v>-1</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0D263A-2AA6-432B-91DD-1F9531A171E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B19A1B-38D2-4818-A3A1-6EBC4EB639F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9908" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9909" uniqueCount="273">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -43591,7 +43591,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A318F2-D986-4B43-9E10-D5047049B529}">
-  <dimension ref="A3:G15"/>
+  <dimension ref="A3:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -43599,12 +43599,12 @@
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -43615,7 +43615,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -43626,69 +43626,74 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F10" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" t="s">
+        <v>267</v>
+      </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>267</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>268</v>
       </c>
-      <c r="D12" t="s">
+      <c r="B12" t="s">
         <v>269</v>
       </c>
-      <c r="F12">
+      <c r="D12">
         <v>1</v>
       </c>
-      <c r="G12">
+      <c r="E12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E13" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
         <v>91</v>
       </c>
-      <c r="F13">
+      <c r="D13">
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>270</v>
       </c>
-      <c r="D14" t="s">
+      <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="F14">
+      <c r="D14">
         <v>1</v>
       </c>
-      <c r="G14">
+      <c r="E14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E15" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
-      <c r="F15">
+      <c r="D15">
         <v>-1</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B19A1B-38D2-4818-A3A1-6EBC4EB639F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C94E523-7404-41AE-ADE8-B7E64ED56F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9909" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9914" uniqueCount="275">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -893,6 +893,12 @@
   <si>
     <t>wind*</t>
   </si>
+  <si>
+    <t>ncap_bnd</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
 </sst>
 </file>
 
@@ -44245,7 +44251,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1758F-E590-4DA8-B461-246947AA96DE}">
-  <dimension ref="A2:I16"/>
+  <dimension ref="A2:I21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
@@ -44382,6 +44388,33 @@
         <v>3</v>
       </c>
     </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>274</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B21">
+        <v>2025</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C94E523-7404-41AE-ADE8-B7E64ED56F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C8FD6D-A271-43E4-8222-E40F913C06E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9914" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9909" uniqueCount="273">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -893,12 +893,6 @@
   <si>
     <t>wind*</t>
   </si>
-  <si>
-    <t>ncap_bnd</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
 </sst>
 </file>
 
@@ -44251,7 +44245,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1758F-E590-4DA8-B461-246947AA96DE}">
-  <dimension ref="A2:I21"/>
+  <dimension ref="A2:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
@@ -44388,33 +44382,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" t="s">
-        <v>274</v>
-      </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>273</v>
-      </c>
-      <c r="B21">
-        <v>2025</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB9FD71-554C-49C2-A9E2-56AE8D61EA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5A8D6A-91DC-41B5-AF3D-BFDCEAD96E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9909" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9909" uniqueCount="274">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -893,6 +893,9 @@
   <si>
     <t>UC_T:UC_RHSRT</t>
   </si>
+  <si>
+    <t>UC_Sets: R_E: AllRegions</t>
+  </si>
 </sst>
 </file>
 
@@ -44257,7 +44260,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5A8D6A-91DC-41B5-AF3D-BFDCEAD96E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFB340A-985A-4613-B240-E711949E6C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43707,139 +43707,142 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0573AE-84FA-4F18-8D18-B7F3EC5B3273}">
-  <dimension ref="B4:U14"/>
+  <dimension ref="B4:V14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5">
+        <v>2022</v>
+      </c>
+      <c r="D5">
         <v>2025</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>2030</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>2035</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>2040</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2045</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>2050</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>2</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>12</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>254</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>255</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>256</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>257</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>258</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
         <v>7.18</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>14</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>15</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>260</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>1147</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>1259</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>1016</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7">
         <v>6.17</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>14</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>15</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>261</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>850</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>1149</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>1016</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="Q8" t="s">
         <v>262</v>
       </c>
       <c r="R8">
-        <f>SUM(Q6:Q7)/COUNT(Q6:Q7)</f>
+        <f>SUM(R6:R7)/COUNT(R6:R7)</f>
         <v>998.5</v>
       </c>
       <c r="S8">
-        <f t="shared" ref="S8:T8" si="0">SUM(R6:R7)/COUNT(R6:R7)</f>
+        <f t="shared" ref="S8:T8" si="0">SUM(S6:S7)/COUNT(S6:S7)</f>
         <v>1204</v>
       </c>
       <c r="T8">
@@ -43847,7 +43850,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="Q9" t="s">
         <v>264</v>
       </c>
@@ -43856,12 +43859,12 @@
         <v>3218.5</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
       </c>
@@ -43869,19 +43872,22 @@
         <v>12</v>
       </c>
       <c r="D12">
+        <v>2022</v>
+      </c>
+      <c r="E12">
         <v>2025</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>2030</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>2040</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -43897,14 +43903,17 @@
       <c r="F13">
         <v>0.32185000000000002</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13">
+        <v>0.32185000000000002</v>
+      </c>
+      <c r="H13" t="s">
         <v>24</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>13</v>
       </c>
@@ -43920,7 +43929,10 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
         <v>24</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFB340A-985A-4613-B240-E711949E6C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DC9B89-D6C5-4D51-B630-2F6CF85F9FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9909" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9915" uniqueCount="276">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -896,15 +896,22 @@
   <si>
     <t>UC_Sets: R_E: AllRegions</t>
   </si>
+  <si>
+    <t>2022 (aastane tarbimine)</t>
+  </si>
+  <si>
+    <t>2022 (%)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,6 +921,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -936,18 +950,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -988,21 +1005,21 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1289,21 +1306,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:T22"/>
+  <dimension ref="B3:W22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
       <c r="N3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -1328,180 +1347,223 @@
       <c r="T4">
         <v>2050</v>
       </c>
-    </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="W4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5">
+        <v>2022</v>
+      </c>
+      <c r="D5">
         <v>2025</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>2030</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>2035</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>2040</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2045</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>2050</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>2</v>
       </c>
-      <c r="M5">
+      <c r="N5">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="O5">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="P5">
+        <v>10.4</v>
+      </c>
+      <c r="Q5">
+        <v>12.2</v>
+      </c>
+      <c r="R5">
+        <v>14.2</v>
+      </c>
+      <c r="S5">
+        <v>15</v>
+      </c>
+      <c r="T5">
+        <v>16</v>
+      </c>
+      <c r="W5">
         <v>8.5</v>
       </c>
-      <c r="N5">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="O5">
-        <v>10.4</v>
-      </c>
-      <c r="P5">
-        <v>12.2</v>
-      </c>
-      <c r="Q5">
-        <v>14.2</v>
-      </c>
-      <c r="R5">
-        <v>15</v>
-      </c>
-      <c r="S5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6">
+        <f>$N$5*O10</f>
+        <v>3.2471999999999999</v>
+      </c>
+      <c r="D6">
         <v>3.3980000000000001</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>3.57</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>3.9750000000000001</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>4.3120000000000003</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>4.5830000000000002</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>4.798</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7">
+        <f t="shared" ref="C7:C9" si="0">$N$5*O11</f>
+        <v>2.5911999999999997</v>
+      </c>
+      <c r="D7">
         <v>2.6019999999999999</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>2.6349999999999998</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>2.657</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>2.806</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>3.008</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>3.306</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8">
+        <f t="shared" si="0"/>
+        <v>2.2795999999999998</v>
+      </c>
+      <c r="D8">
         <v>2.1909999999999998</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>2.3180000000000001</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>2.5470000000000002</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>2.7719999999999998</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>2.9969999999999999</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>3.206</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9">
+        <f t="shared" si="0"/>
+        <v>7.3799999999999991E-2</v>
+      </c>
+      <c r="D9">
         <v>0.28100000000000003</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.58599999999999997</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>1.095</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>1.4690000000000001</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>2.3660000000000001</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>3.2690000000000001</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>4</v>
       </c>
-      <c r="N9">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="O9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M10" t="s">
+        <v>71</v>
+      </c>
       <c r="N10">
         <v>2.9033099999999998</v>
       </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="O10" s="5">
+        <v>0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M11" t="s">
+        <v>5</v>
+      </c>
       <c r="N11">
         <v>2.0885600000000002</v>
       </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="O11" s="5">
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
+      <c r="M12" t="s">
+        <v>6</v>
+      </c>
       <c r="N12">
         <v>1.96688</v>
       </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="O12" s="5">
+        <v>0.27800000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -1526,11 +1588,17 @@
       <c r="I13" t="s">
         <v>4</v>
       </c>
+      <c r="M13" t="s">
+        <v>7</v>
+      </c>
       <c r="N13">
         <v>3.5150000000000001E-2</v>
       </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="O13" s="5">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>3</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DC9B89-D6C5-4D51-B630-2F6CF85F9FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D98E6C5-1826-4423-9109-30582E2DBC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -1380,7 +1380,7 @@
         <v>2</v>
       </c>
       <c r="N5">
-        <v>8.1999999999999993</v>
+        <v>8.5</v>
       </c>
       <c r="O5">
         <v>8.6999999999999993</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C6">
         <f>$N$5*O10</f>
-        <v>3.2471999999999999</v>
+        <v>3.3660000000000001</v>
       </c>
       <c r="D6">
         <v>3.3980000000000001</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C9" si="0">$N$5*O11</f>
-        <v>2.5911999999999997</v>
+        <v>2.6859999999999999</v>
       </c>
       <c r="D7">
         <v>2.6019999999999999</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>2.2795999999999998</v>
+        <v>2.3630000000000004</v>
       </c>
       <c r="D8">
         <v>2.1909999999999998</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>7.3799999999999991E-2</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="D9">
         <v>0.28100000000000003</v>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEED74BA-FC04-4985-8D47-B0AFE8FFA25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1F87DB-9AFF-4FE8-BCD7-C941AFC48C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9927" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9935" uniqueCount="280">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -908,6 +908,12 @@
   <si>
     <t>TFM_INS-TS</t>
   </si>
+  <si>
+    <t>Trd_electricity import_ru</t>
+  </si>
+  <si>
+    <t>Trd_electricity export_ru</t>
+  </si>
 </sst>
 </file>
 
@@ -43781,19 +43787,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0573AE-84FA-4F18-8D18-B7F3EC5B3273}">
-  <dimension ref="B4:V16"/>
+  <dimension ref="B4:Y18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -43842,8 +43851,14 @@
       <c r="V5" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X5" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>272</v>
       </c>
@@ -43877,8 +43892,14 @@
       <c r="V6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X6">
+        <v>910</v>
+      </c>
+      <c r="Y6">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>273</v>
       </c>
@@ -43912,8 +43933,14 @@
       <c r="V7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="X7">
+        <v>350</v>
+      </c>
+      <c r="Y7">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>274</v>
       </c>
@@ -43937,15 +43964,31 @@
         <v>998.5</v>
       </c>
       <c r="S8">
-        <f t="shared" ref="S8:T8" si="0">SUM(S6:S7)/COUNT(S6:S7)</f>
+        <f t="shared" ref="S8:Y8" si="0">SUM(S6:S7)/COUNT(S6:S7)</f>
         <v>1204</v>
       </c>
       <c r="T8">
         <f t="shared" si="0"/>
         <v>1016</v>
       </c>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>635</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>275</v>
       </c>
@@ -43969,12 +44012,12 @@
         <v>3218.5</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>11</v>
       </c>
@@ -43997,7 +44040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>272</v>
       </c>
@@ -44027,7 +44070,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>273</v>
       </c>
@@ -44039,7 +44082,7 @@
         <v>1.204</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:G14" si="2">$S$8/1000</f>
+        <f t="shared" ref="E14:G15" si="2">$S$8/1000</f>
         <v>1.204</v>
       </c>
       <c r="F14">
@@ -44054,57 +44097,103 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C15" t="s">
         <v>276</v>
       </c>
       <c r="D15">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16">
         <f>$T$6/1000</f>
         <v>1.016</v>
       </c>
-      <c r="E15">
-        <f t="shared" ref="E15:G15" si="3">$T$6/1000</f>
+      <c r="E16">
+        <f t="shared" ref="E16:G16" si="3">$T$6/1000</f>
         <v>1.016</v>
       </c>
-      <c r="F15">
+      <c r="F16">
         <f t="shared" si="3"/>
         <v>1.016</v>
       </c>
-      <c r="G15">
+      <c r="G16">
         <f t="shared" si="3"/>
         <v>1.016</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>275</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>276</v>
       </c>
-      <c r="D16">
+      <c r="D17">
         <f>$R$8/1000</f>
         <v>0.99850000000000005</v>
       </c>
-      <c r="E16">
-        <f t="shared" ref="E16:G16" si="4">$R$8/1000</f>
+      <c r="E17">
+        <f t="shared" ref="E17:G18" si="4">$R$8/1000</f>
         <v>0.99850000000000005</v>
       </c>
-      <c r="F16">
+      <c r="F17">
         <f t="shared" si="4"/>
         <v>0.99850000000000005</v>
       </c>
-      <c r="G16">
+      <c r="G17">
         <f t="shared" si="4"/>
         <v>0.99850000000000005</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>279</v>
+      </c>
+      <c r="C18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D18">
+        <v>0.63</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
         <v>20</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1F87DB-9AFF-4FE8-BCD7-C941AFC48C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586D1570-E0D0-49FE-8616-CB6328F04A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -1017,21 +1017,21 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -44036,7 +44036,13 @@
       <c r="G12">
         <v>2040</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12">
+        <v>2045</v>
+      </c>
+      <c r="I12">
+        <v>2050</v>
+      </c>
+      <c r="J12" t="s">
         <v>2</v>
       </c>
     </row>
@@ -44052,7 +44058,7 @@
         <v>1.016</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E13:G13" si="1">$T$6/1000</f>
+        <f t="shared" ref="E13:I18" si="1">$T$6/1000</f>
         <v>1.016</v>
       </c>
       <c r="F13">
@@ -44063,10 +44069,18 @@
         <f t="shared" si="1"/>
         <v>1.016</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>1.016</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>1.016</v>
+      </c>
+      <c r="J13" t="s">
         <v>20</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>259</v>
       </c>
     </row>
@@ -44082,7 +44096,7 @@
         <v>1.204</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:G15" si="2">$S$8/1000</f>
+        <f t="shared" ref="E14:I15" si="2">$S$8/1000</f>
         <v>1.204</v>
       </c>
       <c r="F14">
@@ -44093,7 +44107,15 @@
         <f t="shared" si="2"/>
         <v>1.204</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>1.204</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>1.204</v>
+      </c>
+      <c r="J14" t="s">
         <v>20</v>
       </c>
     </row>
@@ -44116,7 +44138,13 @@
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
         <v>20</v>
       </c>
     </row>
@@ -44132,7 +44160,7 @@
         <v>1.016</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16:G16" si="3">$T$6/1000</f>
+        <f t="shared" ref="E16:I16" si="3">$T$6/1000</f>
         <v>1.016</v>
       </c>
       <c r="F16">
@@ -44143,11 +44171,19 @@
         <f t="shared" si="3"/>
         <v>1.016</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16">
+        <f t="shared" si="3"/>
+        <v>1.016</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="3"/>
+        <v>1.016</v>
+      </c>
+      <c r="J16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>275</v>
       </c>
@@ -44159,7 +44195,7 @@
         <v>0.99850000000000005</v>
       </c>
       <c r="E17">
-        <f t="shared" ref="E17:G18" si="4">$R$8/1000</f>
+        <f t="shared" ref="E17:I18" si="4">$R$8/1000</f>
         <v>0.99850000000000005</v>
       </c>
       <c r="F17">
@@ -44170,11 +44206,19 @@
         <f t="shared" si="4"/>
         <v>0.99850000000000005</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17">
+        <f t="shared" si="4"/>
+        <v>0.99850000000000005</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="4"/>
+        <v>0.99850000000000005</v>
+      </c>
+      <c r="J17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>279</v>
       </c>
@@ -44193,7 +44237,13 @@
       <c r="G18">
         <v>0</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
         <v>20</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586D1570-E0D0-49FE-8616-CB6328F04A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDA7066-71A2-46B3-A294-95CB46E1FFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="trade" sheetId="2" r:id="rId5"/>
     <sheet name="fuel_costs" sheetId="3" r:id="rId6"/>
     <sheet name="constraints" sheetId="7" r:id="rId7"/>
+    <sheet name="grids" sheetId="8" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9935" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9959" uniqueCount="303">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -914,6 +915,75 @@
   <si>
     <t>Trd_electricity export_ru</t>
   </si>
+  <si>
+    <t>~TFM_INS-AT</t>
+  </si>
+  <si>
+    <t>pasti</t>
+  </si>
+  <si>
+    <t>ncap_cost</t>
+  </si>
+  <si>
+    <t>efficiency</t>
+  </si>
+  <si>
+    <t>g_arukula_balti</t>
+  </si>
+  <si>
+    <t>g_arukula_harku</t>
+  </si>
+  <si>
+    <t>g_harku_lihula</t>
+  </si>
+  <si>
+    <t>g_lihula_sindi</t>
+  </si>
+  <si>
+    <t>g_balti_pussi</t>
+  </si>
+  <si>
+    <t>g_viru_balti</t>
+  </si>
+  <si>
+    <t>g_kiisa_harku</t>
+  </si>
+  <si>
+    <t>g_paide_kiisa</t>
+  </si>
+  <si>
+    <t>g_rakvere_kiisa</t>
+  </si>
+  <si>
+    <t>g_kilingi_nomme_sindi</t>
+  </si>
+  <si>
+    <t>g_tsirguliina_mustvee</t>
+  </si>
+  <si>
+    <t>g_mustvee_viru</t>
+  </si>
+  <si>
+    <t>g_paide_sopi</t>
+  </si>
+  <si>
+    <t>g_paide_viru</t>
+  </si>
+  <si>
+    <t>g_pussi_rakvere</t>
+  </si>
+  <si>
+    <t>g_viru_pussi</t>
+  </si>
+  <si>
+    <t>g_sopi_sindi</t>
+  </si>
+  <si>
+    <t>g_kilingi_nomme_tartu</t>
+  </si>
+  <si>
+    <t>g_tartu_pussi</t>
+  </si>
 </sst>
 </file>
 
@@ -44058,7 +44128,7 @@
         <v>1.016</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E13:I18" si="1">$T$6/1000</f>
+        <f t="shared" ref="E13:I13" si="1">$T$6/1000</f>
         <v>1.016</v>
       </c>
       <c r="F13">
@@ -44096,7 +44166,7 @@
         <v>1.204</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:I15" si="2">$S$8/1000</f>
+        <f t="shared" ref="E14:I14" si="2">$S$8/1000</f>
         <v>1.204</v>
       </c>
       <c r="F14">
@@ -44195,7 +44265,7 @@
         <v>0.99850000000000005</v>
       </c>
       <c r="E17">
-        <f t="shared" ref="E17:I18" si="4">$R$8/1000</f>
+        <f t="shared" ref="E17:I17" si="4">$R$8/1000</f>
         <v>0.99850000000000005</v>
       </c>
       <c r="F17">
@@ -44714,4 +44784,302 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A2DF39-3B67-43CD-A73F-8B3848EF882D}">
+  <dimension ref="A3:D23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5">
+        <v>1.106001</v>
+      </c>
+      <c r="C5">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D5">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B6">
+        <v>1.106001</v>
+      </c>
+      <c r="C6">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D6">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B7">
+        <v>1.106001</v>
+      </c>
+      <c r="C7">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D7">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8">
+        <v>1.106001</v>
+      </c>
+      <c r="C8">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D8">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>288</v>
+      </c>
+      <c r="B9">
+        <v>1.106001</v>
+      </c>
+      <c r="C9">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D9">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10">
+        <v>1.106001</v>
+      </c>
+      <c r="C10">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D10">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11">
+        <v>1.106001</v>
+      </c>
+      <c r="C11">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D11">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12">
+        <v>1.106001</v>
+      </c>
+      <c r="C12">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D12">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>292</v>
+      </c>
+      <c r="B13">
+        <v>1.106001</v>
+      </c>
+      <c r="C13">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D13">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B14">
+        <v>1.106001</v>
+      </c>
+      <c r="C14">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D14">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B15">
+        <v>1.106001</v>
+      </c>
+      <c r="C15">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D15">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>295</v>
+      </c>
+      <c r="B16">
+        <v>1.106001</v>
+      </c>
+      <c r="C16">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D16">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17">
+        <v>1.106001</v>
+      </c>
+      <c r="C17">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D17">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B18">
+        <v>1.106001</v>
+      </c>
+      <c r="C18">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D18">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>298</v>
+      </c>
+      <c r="B19">
+        <v>1.106001</v>
+      </c>
+      <c r="C19">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D19">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>299</v>
+      </c>
+      <c r="B20">
+        <v>1.106001</v>
+      </c>
+      <c r="C20">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D20">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>300</v>
+      </c>
+      <c r="B21">
+        <v>1.106001</v>
+      </c>
+      <c r="C21">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D21">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>301</v>
+      </c>
+      <c r="B22">
+        <v>1.106001</v>
+      </c>
+      <c r="C22">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D22">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>302</v>
+      </c>
+      <c r="B23">
+        <v>1.106001</v>
+      </c>
+      <c r="C23">
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D23">
+        <v>0.99885999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDA7066-71A2-46B3-A294-95CB46E1FFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FBB88D-F6E8-4D7C-960E-E77CF0765E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,9 @@
     <sheet name="trade" sheetId="2" r:id="rId5"/>
     <sheet name="fuel_costs" sheetId="3" r:id="rId6"/>
     <sheet name="constraints" sheetId="7" r:id="rId7"/>
-    <sheet name="grids" sheetId="8" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9959" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9935" uniqueCount="280">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -915,75 +914,6 @@
   <si>
     <t>Trd_electricity export_ru</t>
   </si>
-  <si>
-    <t>~TFM_INS-AT</t>
-  </si>
-  <si>
-    <t>pasti</t>
-  </si>
-  <si>
-    <t>ncap_cost</t>
-  </si>
-  <si>
-    <t>efficiency</t>
-  </si>
-  <si>
-    <t>g_arukula_balti</t>
-  </si>
-  <si>
-    <t>g_arukula_harku</t>
-  </si>
-  <si>
-    <t>g_harku_lihula</t>
-  </si>
-  <si>
-    <t>g_lihula_sindi</t>
-  </si>
-  <si>
-    <t>g_balti_pussi</t>
-  </si>
-  <si>
-    <t>g_viru_balti</t>
-  </si>
-  <si>
-    <t>g_kiisa_harku</t>
-  </si>
-  <si>
-    <t>g_paide_kiisa</t>
-  </si>
-  <si>
-    <t>g_rakvere_kiisa</t>
-  </si>
-  <si>
-    <t>g_kilingi_nomme_sindi</t>
-  </si>
-  <si>
-    <t>g_tsirguliina_mustvee</t>
-  </si>
-  <si>
-    <t>g_mustvee_viru</t>
-  </si>
-  <si>
-    <t>g_paide_sopi</t>
-  </si>
-  <si>
-    <t>g_paide_viru</t>
-  </si>
-  <si>
-    <t>g_pussi_rakvere</t>
-  </si>
-  <si>
-    <t>g_viru_pussi</t>
-  </si>
-  <si>
-    <t>g_sopi_sindi</t>
-  </si>
-  <si>
-    <t>g_kilingi_nomme_tartu</t>
-  </si>
-  <si>
-    <t>g_tartu_pussi</t>
-  </si>
 </sst>
 </file>
 
@@ -1389,22 +1319,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:W22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.35">
       <c r="N3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -1433,7 +1363,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -1486,7 +1416,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>67</v>
       </c>
@@ -1516,7 +1446,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -1546,7 +1476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -1576,7 +1506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -1609,7 +1539,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.35">
       <c r="M10" t="s">
         <v>67</v>
       </c>
@@ -1620,7 +1550,7 @@
         <v>0.39600000000000002</v>
       </c>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.35">
       <c r="M11" t="s">
         <v>5</v>
       </c>
@@ -1631,7 +1561,7 @@
         <v>0.316</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -1645,7 +1575,7 @@
         <v>0.27800000000000002</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -1680,7 +1610,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>3</v>
       </c>
@@ -1706,7 +1636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>68</v>
       </c>
@@ -1714,7 +1644,7 @@
         <v>9.950000000000081E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>2</v>
       </c>
@@ -1737,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>72</v>
       </c>
@@ -1751,7 +1681,7 @@
         <v>338.40000000000003</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>72</v>
       </c>
@@ -1765,7 +1695,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>72</v>
       </c>
@@ -1779,7 +1709,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>77</v>
       </c>
@@ -1802,25 +1732,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B64E1E-DC66-450D-AA2A-D1B01A72BCA4}">
   <dimension ref="A1:AN962"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="44.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.5703125" customWidth="1"/>
-    <col min="27" max="27" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.54296875" customWidth="1"/>
+    <col min="27" max="27" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
         <v>80</v>
       </c>
@@ -1846,7 +1776,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -1944,7 +1874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>IFERROR(IF([1]Veda!#REF!=A2,"ok","x"),"")</f>
         <v/>
@@ -2043,7 +1973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>136</v>
       </c>
@@ -2132,7 +2062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>138</v>
       </c>
@@ -2221,7 +2151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>140</v>
       </c>
@@ -2310,7 +2240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>142</v>
       </c>
@@ -2399,7 +2329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>144</v>
       </c>
@@ -2488,7 +2418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>146</v>
       </c>
@@ -2577,7 +2507,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
         <v>148</v>
       </c>
@@ -2666,7 +2596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
         <v>150</v>
       </c>
@@ -2749,7 +2679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>151</v>
       </c>
@@ -2832,7 +2762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>152</v>
       </c>
@@ -2915,7 +2845,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>153</v>
       </c>
@@ -2998,7 +2928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
       <c r="I15" t="s">
         <v>33</v>
       </c>
@@ -3078,7 +3008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
       <c r="I16" t="s">
         <v>33</v>
       </c>
@@ -3158,7 +3088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I17" t="s">
         <v>33</v>
       </c>
@@ -3238,7 +3168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="18" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I18" t="s">
         <v>33</v>
       </c>
@@ -3318,7 +3248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I19" t="s">
         <v>33</v>
       </c>
@@ -3398,7 +3328,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="20" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I20" t="s">
         <v>33</v>
       </c>
@@ -3478,7 +3408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="21" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I21" t="s">
         <v>33</v>
       </c>
@@ -3558,7 +3488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I22" t="s">
         <v>33</v>
       </c>
@@ -3638,7 +3568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="23" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I23" t="s">
         <v>33</v>
       </c>
@@ -3718,7 +3648,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="24" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I24" t="s">
         <v>33</v>
       </c>
@@ -3798,7 +3728,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="25" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I25" t="s">
         <v>33</v>
       </c>
@@ -3878,7 +3808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="26" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I26" t="s">
         <v>33</v>
       </c>
@@ -3958,7 +3888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="27" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I27" t="s">
         <v>33</v>
       </c>
@@ -4038,7 +3968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="28" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I28" t="s">
         <v>33</v>
       </c>
@@ -4118,7 +4048,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="29" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I29" t="s">
         <v>33</v>
       </c>
@@ -4198,7 +4128,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="30" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I30" t="s">
         <v>33</v>
       </c>
@@ -4278,7 +4208,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I31" t="s">
         <v>33</v>
       </c>
@@ -4358,7 +4288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I32" t="s">
         <v>33</v>
       </c>
@@ -4438,7 +4368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I33" t="s">
         <v>33</v>
       </c>
@@ -4518,7 +4448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I34" t="s">
         <v>33</v>
       </c>
@@ -4598,7 +4528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I35" t="s">
         <v>33</v>
       </c>
@@ -4678,7 +4608,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I36" t="s">
         <v>33</v>
       </c>
@@ -4758,7 +4688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I37" t="s">
         <v>33</v>
       </c>
@@ -4838,7 +4768,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I38" t="s">
         <v>33</v>
       </c>
@@ -4918,7 +4848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I39" t="s">
         <v>33</v>
       </c>
@@ -4986,7 +4916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I40" t="s">
         <v>33</v>
       </c>
@@ -5054,7 +4984,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I41" t="s">
         <v>33</v>
       </c>
@@ -5122,7 +5052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I42" t="s">
         <v>33</v>
       </c>
@@ -5190,7 +5120,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="43" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I43" t="s">
         <v>33</v>
       </c>
@@ -5258,7 +5188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="44" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I44" t="s">
         <v>33</v>
       </c>
@@ -5326,7 +5256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="45" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I45" t="s">
         <v>33</v>
       </c>
@@ -5394,7 +5324,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="46" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I46" t="s">
         <v>33</v>
       </c>
@@ -5462,7 +5392,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="47" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I47" t="s">
         <v>33</v>
       </c>
@@ -5530,7 +5460,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="48" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I48" t="s">
         <v>33</v>
       </c>
@@ -5598,7 +5528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="49" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I49" t="s">
         <v>33</v>
       </c>
@@ -5666,7 +5596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="50" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I50" t="s">
         <v>33</v>
       </c>
@@ -5734,7 +5664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="51" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I51" t="s">
         <v>33</v>
       </c>
@@ -5802,7 +5732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="52" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I52" t="s">
         <v>33</v>
       </c>
@@ -5870,7 +5800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="53" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I53" t="s">
         <v>33</v>
       </c>
@@ -5938,7 +5868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="54" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I54" t="s">
         <v>33</v>
       </c>
@@ -6006,7 +5936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="55" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I55" t="s">
         <v>33</v>
       </c>
@@ -6074,7 +6004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="56" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I56" t="s">
         <v>33</v>
       </c>
@@ -6142,7 +6072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="57" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I57" t="s">
         <v>33</v>
       </c>
@@ -6210,7 +6140,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="58" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I58" t="s">
         <v>33</v>
       </c>
@@ -6278,7 +6208,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="59" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I59" t="s">
         <v>33</v>
       </c>
@@ -6346,7 +6276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="60" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I60" t="s">
         <v>33</v>
       </c>
@@ -6414,7 +6344,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="61" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I61" t="s">
         <v>33</v>
       </c>
@@ -6482,7 +6412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="62" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I62" t="s">
         <v>33</v>
       </c>
@@ -6550,7 +6480,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="63" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I63" t="s">
         <v>33</v>
       </c>
@@ -6618,7 +6548,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="64" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I64" t="s">
         <v>33</v>
       </c>
@@ -6686,7 +6616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="65" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I65" t="s">
         <v>33</v>
       </c>
@@ -6754,7 +6684,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="66" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I66" t="s">
         <v>33</v>
       </c>
@@ -6822,7 +6752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="67" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I67" t="s">
         <v>33</v>
       </c>
@@ -6890,7 +6820,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="68" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I68" t="s">
         <v>33</v>
       </c>
@@ -6958,7 +6888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="69" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I69" t="s">
         <v>33</v>
       </c>
@@ -7026,7 +6956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="70" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I70" t="s">
         <v>33</v>
       </c>
@@ -7094,7 +7024,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="71" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I71" t="s">
         <v>33</v>
       </c>
@@ -7162,7 +7092,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="72" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I72" t="s">
         <v>33</v>
       </c>
@@ -7230,7 +7160,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="73" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I73" t="s">
         <v>33</v>
       </c>
@@ -7298,7 +7228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="74" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I74" t="s">
         <v>33</v>
       </c>
@@ -7366,7 +7296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="75" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I75" t="s">
         <v>33</v>
       </c>
@@ -7434,7 +7364,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="76" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I76" t="s">
         <v>33</v>
       </c>
@@ -7502,7 +7432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="77" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I77" t="s">
         <v>33</v>
       </c>
@@ -7570,7 +7500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="78" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I78" t="s">
         <v>33</v>
       </c>
@@ -7638,7 +7568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="79" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I79" t="s">
         <v>33</v>
       </c>
@@ -7706,7 +7636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="80" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I80" t="s">
         <v>33</v>
       </c>
@@ -7774,7 +7704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="81" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I81" t="s">
         <v>33</v>
       </c>
@@ -7842,7 +7772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="82" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I82" t="s">
         <v>33</v>
       </c>
@@ -7910,7 +7840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="83" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I83" t="s">
         <v>33</v>
       </c>
@@ -7978,7 +7908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="84" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I84" t="s">
         <v>33</v>
       </c>
@@ -8046,7 +7976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="85" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I85" t="s">
         <v>33</v>
       </c>
@@ -8114,7 +8044,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="86" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I86" t="s">
         <v>33</v>
       </c>
@@ -8182,7 +8112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="87" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I87" t="s">
         <v>33</v>
       </c>
@@ -8250,7 +8180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="88" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I88" t="s">
         <v>33</v>
       </c>
@@ -8318,7 +8248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="89" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I89" t="s">
         <v>33</v>
       </c>
@@ -8386,7 +8316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="90" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I90" t="s">
         <v>33</v>
       </c>
@@ -8454,7 +8384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="91" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I91" t="s">
         <v>33</v>
       </c>
@@ -8522,7 +8452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="92" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I92" t="s">
         <v>33</v>
       </c>
@@ -8590,7 +8520,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="93" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I93" t="s">
         <v>33</v>
       </c>
@@ -8658,7 +8588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="94" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I94" t="s">
         <v>33</v>
       </c>
@@ -8726,7 +8656,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="95" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I95" t="s">
         <v>33</v>
       </c>
@@ -8794,7 +8724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="96" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I96" t="s">
         <v>33</v>
       </c>
@@ -8862,7 +8792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="97" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I97" t="s">
         <v>33</v>
       </c>
@@ -8930,7 +8860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="98" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I98" t="s">
         <v>33</v>
       </c>
@@ -8998,7 +8928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="99" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I99" t="s">
         <v>39</v>
       </c>
@@ -9045,7 +8975,7 @@
         <v>1.7573439583804459E-2</v>
       </c>
     </row>
-    <row r="100" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="100" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I100" t="s">
         <v>39</v>
       </c>
@@ -9092,7 +9022,7 @@
         <v>3.549030522775862E-3</v>
       </c>
     </row>
-    <row r="101" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="101" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I101" t="s">
         <v>39</v>
       </c>
@@ -9139,7 +9069,7 @@
         <v>3.2008138253697617E-2</v>
       </c>
     </row>
-    <row r="102" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="102" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I102" t="s">
         <v>39</v>
       </c>
@@ -9186,7 +9116,7 @@
         <v>3.5595926097493078E-3</v>
       </c>
     </row>
-    <row r="103" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="103" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I103" t="s">
         <v>39</v>
       </c>
@@ -9233,7 +9163,7 @@
         <v>1.0678471251817045E-2</v>
       </c>
     </row>
-    <row r="104" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="104" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I104" t="s">
         <v>39</v>
       </c>
@@ -9280,7 +9210,7 @@
         <v>3.5562894851714701E-3</v>
       </c>
     </row>
-    <row r="105" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="105" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I105" t="s">
         <v>39</v>
       </c>
@@ -9327,7 +9257,7 @@
         <v>3.5440857255036491E-3</v>
       </c>
     </row>
-    <row r="106" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="106" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I106" t="s">
         <v>39</v>
       </c>
@@ -9374,7 +9304,7 @@
         <v>1.0554198606771802E-2</v>
       </c>
     </row>
-    <row r="107" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="107" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I107" t="s">
         <v>39</v>
       </c>
@@ -9421,7 +9351,7 @@
         <v>1.5916331913035826E-2</v>
       </c>
     </row>
-    <row r="108" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="108" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I108" t="s">
         <v>39</v>
       </c>
@@ -9468,7 +9398,7 @@
         <v>3.2085184733168996E-3</v>
       </c>
     </row>
-    <row r="109" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="109" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I109" t="s">
         <v>39</v>
       </c>
@@ -9515,7 +9445,7 @@
         <v>2.8854869593476187E-2</v>
       </c>
     </row>
-    <row r="110" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="110" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I110" t="s">
         <v>39</v>
       </c>
@@ -9562,7 +9492,7 @@
         <v>3.2092305241240983E-3</v>
       </c>
     </row>
-    <row r="111" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="111" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I111" t="s">
         <v>39</v>
       </c>
@@ -9609,7 +9539,7 @@
         <v>9.6277410203450178E-3</v>
       </c>
     </row>
-    <row r="112" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="112" spans="9:40" x14ac:dyDescent="0.35">
       <c r="I112" t="s">
         <v>39</v>
       </c>
@@ -9656,7 +9586,7 @@
         <v>3.2091711865568314E-3</v>
       </c>
     </row>
-    <row r="113" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="113" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I113" t="s">
         <v>39</v>
       </c>
@@ -9703,7 +9633,7 @@
         <v>3.1953059750055479E-3</v>
       </c>
     </row>
-    <row r="114" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="114" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I114" t="s">
         <v>39</v>
       </c>
@@ -9750,7 +9680,7 @@
         <v>9.546962812106154E-3</v>
       </c>
     </row>
-    <row r="115" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="115" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I115" t="s">
         <v>39</v>
       </c>
@@ -9797,7 +9727,7 @@
         <v>1.7589283950463944E-2</v>
       </c>
     </row>
-    <row r="116" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="116" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I116" t="s">
         <v>39</v>
       </c>
@@ -9844,7 +9774,7 @@
         <v>3.5536709677759697E-3</v>
       </c>
     </row>
-    <row r="117" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="117" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I117" t="s">
         <v>39</v>
       </c>
@@ -9891,7 +9821,7 @@
         <v>3.2007396781346641E-2</v>
       </c>
     </row>
-    <row r="118" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="118" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I118" t="s">
         <v>39</v>
       </c>
@@ -9938,7 +9868,7 @@
         <v>3.5703744929615035E-3</v>
       </c>
     </row>
-    <row r="119" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="119" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I119" t="s">
         <v>39</v>
       </c>
@@ -9985,7 +9915,7 @@
         <v>1.0713378306440639E-2</v>
       </c>
     </row>
-    <row r="120" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="120" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I120" t="s">
         <v>39</v>
       </c>
@@ -10032,7 +9962,7 @@
         <v>3.5532852735887369E-3</v>
       </c>
     </row>
-    <row r="121" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="121" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I121" t="s">
         <v>39</v>
       </c>
@@ -10079,7 +10009,7 @@
         <v>3.5378871748830676E-3</v>
       </c>
     </row>
-    <row r="122" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="122" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I122" t="s">
         <v>39</v>
       </c>
@@ -10126,7 +10056,7 @@
         <v>1.0542822358927487E-2</v>
       </c>
     </row>
-    <row r="123" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="123" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I123" t="s">
         <v>39</v>
       </c>
@@ -10173,7 +10103,7 @@
         <v>1.705835928247789E-2</v>
       </c>
     </row>
-    <row r="124" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="124" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I124" t="s">
         <v>39</v>
       </c>
@@ -10220,7 +10150,7 @@
         <v>3.4402943210260521E-3</v>
       </c>
     </row>
-    <row r="125" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="125" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I125" t="s">
         <v>39</v>
       </c>
@@ -10267,7 +10197,7 @@
         <v>3.0962362090992686E-2</v>
       </c>
     </row>
-    <row r="126" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="126" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I126" t="s">
         <v>39</v>
       </c>
@@ -10314,7 +10244,7 @@
         <v>3.4417678706131715E-3</v>
       </c>
     </row>
-    <row r="127" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="127" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I127" t="s">
         <v>39</v>
       </c>
@@ -10361,7 +10291,7 @@
         <v>1.0311893321637275E-2</v>
       </c>
     </row>
-    <row r="128" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="128" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I128" t="s">
         <v>39</v>
       </c>
@@ -10408,7 +10338,7 @@
         <v>3.4169054299284874E-3</v>
       </c>
     </row>
-    <row r="129" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I129" t="s">
         <v>39</v>
       </c>
@@ -10455,7 +10385,7 @@
         <v>3.4056906297151093E-3</v>
       </c>
     </row>
-    <row r="130" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I130" t="s">
         <v>39</v>
       </c>
@@ -10502,7 +10432,7 @@
         <v>1.0184624129445071E-2</v>
       </c>
     </row>
-    <row r="131" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I131" t="s">
         <v>39</v>
       </c>
@@ -10549,7 +10479,7 @@
         <v>1.7469370144214159E-2</v>
       </c>
     </row>
-    <row r="132" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="132" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I132" t="s">
         <v>39</v>
       </c>
@@ -10596,7 +10526,7 @@
         <v>3.5474934325437947E-3</v>
       </c>
     </row>
-    <row r="133" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="133" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I133" t="s">
         <v>39</v>
       </c>
@@ -10643,7 +10573,7 @@
         <v>3.2073292633235329E-2</v>
       </c>
     </row>
-    <row r="134" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="134" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I134" t="s">
         <v>39</v>
       </c>
@@ -10690,7 +10620,7 @@
         <v>3.5605180285588024E-3</v>
       </c>
     </row>
-    <row r="135" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="135" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I135" t="s">
         <v>39</v>
       </c>
@@ -10737,7 +10667,7 @@
         <v>1.0671268907350207E-2</v>
       </c>
     </row>
-    <row r="136" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="136" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I136" t="s">
         <v>39</v>
       </c>
@@ -10784,7 +10714,7 @@
         <v>3.5436760490496462E-3</v>
       </c>
     </row>
-    <row r="137" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="137" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I137" t="s">
         <v>39</v>
       </c>
@@ -10831,7 +10761,7 @@
         <v>3.5327974950507793E-3</v>
       </c>
     </row>
-    <row r="138" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="138" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I138" t="s">
         <v>39</v>
       </c>
@@ -10878,7 +10808,7 @@
         <v>1.0474465975916149E-2</v>
       </c>
     </row>
-    <row r="139" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="139" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I139" t="s">
         <v>39</v>
       </c>
@@ -10925,7 +10855,7 @@
         <v>1.6839558802278737E-2</v>
       </c>
     </row>
-    <row r="140" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="140" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I140" t="s">
         <v>39</v>
       </c>
@@ -10972,7 +10902,7 @@
         <v>3.4281868612851089E-3</v>
       </c>
     </row>
-    <row r="141" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="141" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I141" t="s">
         <v>39</v>
       </c>
@@ -11019,7 +10949,7 @@
         <v>3.1088045363079762E-2</v>
       </c>
     </row>
-    <row r="142" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="142" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I142" t="s">
         <v>39</v>
       </c>
@@ -11066,7 +10996,7 @@
         <v>3.4538998071006136E-3</v>
       </c>
     </row>
-    <row r="143" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="143" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I143" t="s">
         <v>39</v>
       </c>
@@ -11113,7 +11043,7 @@
         <v>1.0343077314774688E-2</v>
       </c>
     </row>
-    <row r="144" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="144" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I144" t="s">
         <v>39</v>
       </c>
@@ -11160,7 +11090,7 @@
         <v>3.437265509076891E-3</v>
       </c>
     </row>
-    <row r="145" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="145" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I145" t="s">
         <v>39</v>
       </c>
@@ -11207,7 +11137,7 @@
         <v>3.419078544709693E-3</v>
       </c>
     </row>
-    <row r="146" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="146" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I146" t="s">
         <v>39</v>
       </c>
@@ -11254,7 +11184,7 @@
         <v>1.0113025566482275E-2</v>
       </c>
     </row>
-    <row r="147" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="147" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I147" t="s">
         <v>39</v>
       </c>
@@ -11301,7 +11231,7 @@
         <v>1.7390991398851634E-2</v>
       </c>
     </row>
-    <row r="148" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="148" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I148" t="s">
         <v>39</v>
       </c>
@@ -11348,7 +11278,7 @@
         <v>3.5422986757694718E-3</v>
       </c>
     </row>
-    <row r="149" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="149" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I149" t="s">
         <v>39</v>
       </c>
@@ -11395,7 +11325,7 @@
         <v>3.2140319607500037E-2</v>
       </c>
     </row>
-    <row r="150" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="150" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I150" t="s">
         <v>39</v>
       </c>
@@ -11442,7 +11372,7 @@
         <v>3.5716509923773253E-3</v>
       </c>
     </row>
-    <row r="151" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="151" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I151" t="s">
         <v>39</v>
       </c>
@@ -11489,7 +11419,7 @@
         <v>1.0693433219403307E-2</v>
       </c>
     </row>
-    <row r="152" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="152" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I152" t="s">
         <v>39</v>
       </c>
@@ -11536,7 +11466,7 @@
         <v>3.5532860153083276E-3</v>
       </c>
     </row>
-    <row r="153" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="153" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I153" t="s">
         <v>39</v>
       </c>
@@ -11583,7 +11513,7 @@
         <v>3.5322607373068802E-3</v>
       </c>
     </row>
-    <row r="154" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="154" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I154" t="s">
         <v>39</v>
       </c>
@@ -11630,7 +11560,7 @@
         <v>1.0442979237565745E-2</v>
       </c>
     </row>
-    <row r="155" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="155" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I155" t="s">
         <v>39</v>
       </c>
@@ -11677,7 +11607,7 @@
         <v>1.7403901028330063E-2</v>
       </c>
     </row>
-    <row r="156" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="156" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I156" t="s">
         <v>39</v>
       </c>
@@ -11724,7 +11654,7 @@
         <v>3.5416743951138551E-3</v>
       </c>
     </row>
-    <row r="157" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="157" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I157" t="s">
         <v>39</v>
       </c>
@@ -11771,7 +11701,7 @@
         <v>3.212440601367874E-2</v>
       </c>
     </row>
-    <row r="158" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="158" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I158" t="s">
         <v>39</v>
       </c>
@@ -11818,7 +11748,7 @@
         <v>3.5695432725400445E-3</v>
       </c>
     </row>
-    <row r="159" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="159" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I159" t="s">
         <v>39</v>
       </c>
@@ -11865,7 +11795,7 @@
         <v>1.0686645248947878E-2</v>
       </c>
     </row>
-    <row r="160" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="160" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I160" t="s">
         <v>39</v>
       </c>
@@ -11912,7 +11842,7 @@
         <v>3.5494575060203174E-3</v>
       </c>
     </row>
-    <row r="161" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="161" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I161" t="s">
         <v>39</v>
       </c>
@@ -11959,7 +11889,7 @@
         <v>3.5336737131274154E-3</v>
       </c>
     </row>
-    <row r="162" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="162" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I162" t="s">
         <v>39</v>
       </c>
@@ -12006,7 +11936,7 @@
         <v>1.045090698379242E-2</v>
       </c>
     </row>
-    <row r="163" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="163" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I163" t="s">
         <v>39</v>
       </c>
@@ -12053,7 +11983,7 @@
         <v>1.6902954811906457E-2</v>
       </c>
     </row>
-    <row r="164" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="164" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I164" t="s">
         <v>39</v>
       </c>
@@ -12100,7 +12030,7 @@
         <v>3.4320663019850226E-3</v>
       </c>
     </row>
-    <row r="165" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="165" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I165" t="s">
         <v>39</v>
       </c>
@@ -12147,7 +12077,7 @@
         <v>3.1030225601335913E-2</v>
       </c>
     </row>
-    <row r="166" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="166" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I166" t="s">
         <v>39</v>
       </c>
@@ -12194,7 +12124,7 @@
         <v>3.4455655985381629E-3</v>
       </c>
     </row>
-    <row r="167" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="167" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I167" t="s">
         <v>39</v>
       </c>
@@ -12241,7 +12171,7 @@
         <v>1.0328715892817138E-2</v>
       </c>
     </row>
-    <row r="168" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="168" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I168" t="s">
         <v>39</v>
       </c>
@@ -12288,7 +12218,7 @@
         <v>3.4291983195671393E-3</v>
       </c>
     </row>
-    <row r="169" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="169" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I169" t="s">
         <v>39</v>
       </c>
@@ -12335,7 +12265,7 @@
         <v>3.4192691666445375E-3</v>
       </c>
     </row>
-    <row r="170" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="170" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I170" t="s">
         <v>39</v>
       </c>
@@ -12382,7 +12312,7 @@
         <v>1.0144235396185435E-2</v>
       </c>
     </row>
-    <row r="171" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="171" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I171" t="s">
         <v>39</v>
       </c>
@@ -12429,7 +12359,7 @@
         <v>1.7518031276070344E-2</v>
       </c>
     </row>
-    <row r="172" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="172" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I172" t="s">
         <v>39</v>
       </c>
@@ -12476,7 +12406,7 @@
         <v>3.5419323899115326E-3</v>
       </c>
     </row>
-    <row r="173" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="173" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I173" t="s">
         <v>39</v>
       </c>
@@ -12523,7 +12453,7 @@
         <v>3.2027367210469997E-2</v>
       </c>
     </row>
-    <row r="174" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="174" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I174" t="s">
         <v>39</v>
       </c>
@@ -12570,7 +12500,7 @@
         <v>3.5604753796823299E-3</v>
       </c>
     </row>
-    <row r="175" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="175" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I175" t="s">
         <v>39</v>
       </c>
@@ -12617,7 +12547,7 @@
         <v>1.0677104386231075E-2</v>
       </c>
     </row>
-    <row r="176" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="176" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I176" t="s">
         <v>39</v>
       </c>
@@ -12664,7 +12594,7 @@
         <v>3.5475892379909441E-3</v>
       </c>
     </row>
-    <row r="177" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="177" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I177" t="s">
         <v>39</v>
       </c>
@@ -12711,7 +12641,7 @@
         <v>3.5309648295617654E-3</v>
       </c>
     </row>
-    <row r="178" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="178" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I178" t="s">
         <v>39</v>
       </c>
@@ -12758,7 +12688,7 @@
         <v>1.0500941038611234E-2</v>
       </c>
     </row>
-    <row r="179" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="179" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I179" t="s">
         <v>39</v>
       </c>
@@ -12805,7 +12735,7 @@
         <v>1.6968870813844024E-2</v>
       </c>
     </row>
-    <row r="180" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="180" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I180" t="s">
         <v>39</v>
       </c>
@@ -12852,7 +12782,7 @@
         <v>3.4287378353211649E-3</v>
       </c>
     </row>
-    <row r="181" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="181" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I181" t="s">
         <v>39</v>
       </c>
@@ -12899,7 +12829,7 @@
         <v>3.095718043793113E-2</v>
       </c>
     </row>
-    <row r="182" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="182" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I182" t="s">
         <v>39</v>
       </c>
@@ -12946,7 +12876,7 @@
         <v>3.4444425114577111E-3</v>
       </c>
     </row>
-    <row r="183" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="183" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I183" t="s">
         <v>39</v>
       </c>
@@ -12993,7 +12923,7 @@
         <v>1.0328976112773587E-2</v>
       </c>
     </row>
-    <row r="184" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="184" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I184" t="s">
         <v>39</v>
       </c>
@@ -13040,7 +12970,7 @@
         <v>3.4392801431055216E-3</v>
       </c>
     </row>
-    <row r="185" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="185" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I185" t="s">
         <v>39</v>
       </c>
@@ -13087,7 +13017,7 @@
         <v>3.4253852627706047E-3</v>
       </c>
     </row>
-    <row r="186" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="186" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I186" t="s">
         <v>39</v>
       </c>
@@ -13134,7 +13064,7 @@
         <v>1.0200688292343307E-2</v>
       </c>
     </row>
-    <row r="187" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="187" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I187" t="s">
         <v>39</v>
       </c>
@@ -13181,7 +13111,7 @@
         <v>1.7564166852719741E-2</v>
       </c>
     </row>
-    <row r="188" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="188" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I188" t="s">
         <v>39</v>
       </c>
@@ -13228,7 +13158,7 @@
         <v>3.5520515466693206E-3</v>
       </c>
     </row>
-    <row r="189" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="189" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I189" t="s">
         <v>39</v>
       </c>
@@ -13275,7 +13205,7 @@
         <v>3.1997658003119024E-2</v>
       </c>
     </row>
-    <row r="190" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="190" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I190" t="s">
         <v>39</v>
       </c>
@@ -13322,7 +13252,7 @@
         <v>3.5585490102850075E-3</v>
       </c>
     </row>
-    <row r="191" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="191" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I191" t="s">
         <v>39</v>
       </c>
@@ -13369,7 +13299,7 @@
         <v>1.0670949473446422E-2</v>
       </c>
     </row>
-    <row r="192" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="192" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I192" t="s">
         <v>39</v>
       </c>
@@ -13416,7 +13346,7 @@
         <v>3.5476902354752288E-3</v>
       </c>
     </row>
-    <row r="193" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="193" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I193" t="s">
         <v>39</v>
       </c>
@@ -13463,7 +13393,7 @@
         <v>3.5329448500094913E-3</v>
       </c>
     </row>
-    <row r="194" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="194" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I194" t="s">
         <v>39</v>
       </c>
@@ -13510,7 +13440,7 @@
         <v>1.0541969381398029E-2</v>
       </c>
     </row>
-    <row r="195" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="195" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I195" t="s">
         <v>42</v>
       </c>
@@ -13557,7 +13487,7 @@
         <v>1.8478957293394084E-2</v>
       </c>
     </row>
-    <row r="196" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="196" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I196" t="s">
         <v>42</v>
       </c>
@@ -13604,7 +13534,7 @@
         <v>4.1712445978343074E-3</v>
       </c>
     </row>
-    <row r="197" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="197" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I197" t="s">
         <v>42</v>
       </c>
@@ -13651,7 +13581,7 @@
         <v>3.8466887803889016E-2</v>
       </c>
     </row>
-    <row r="198" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="198" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I198" t="s">
         <v>42</v>
       </c>
@@ -13698,7 +13628,7 @@
         <v>4.3174704668137642E-3</v>
       </c>
     </row>
-    <row r="199" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="199" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I199" t="s">
         <v>42</v>
       </c>
@@ -13745,7 +13675,7 @@
         <v>1.2948167016603873E-2</v>
       </c>
     </row>
-    <row r="200" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="200" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I200" t="s">
         <v>42</v>
       </c>
@@ -13792,7 +13722,7 @@
         <v>4.2717406538557694E-3</v>
       </c>
     </row>
-    <row r="201" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="201" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I201" t="s">
         <v>42</v>
       </c>
@@ -13839,7 +13769,7 @@
         <v>4.1027867940049735E-3</v>
       </c>
     </row>
-    <row r="202" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="202" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I202" t="s">
         <v>42</v>
       </c>
@@ -13886,7 +13816,7 @@
         <v>1.1227685490765055E-2</v>
       </c>
     </row>
-    <row r="203" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="203" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I203" t="s">
         <v>42</v>
       </c>
@@ -13933,7 +13863,7 @@
         <v>1.6569501564808842E-2</v>
       </c>
     </row>
-    <row r="204" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="204" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I204" t="s">
         <v>42</v>
       </c>
@@ -13980,7 +13910,7 @@
         <v>3.6635006255574106E-3</v>
       </c>
     </row>
-    <row r="205" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="205" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I205" t="s">
         <v>42</v>
       </c>
@@ -14027,7 +13957,7 @@
         <v>3.2669743630736992E-2</v>
       </c>
     </row>
-    <row r="206" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="206" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I206" t="s">
         <v>42</v>
       </c>
@@ -14074,7 +14004,7 @@
         <v>3.6733585493088348E-3</v>
       </c>
     </row>
-    <row r="207" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="207" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I207" t="s">
         <v>42</v>
       </c>
@@ -14121,7 +14051,7 @@
         <v>1.10207602259648E-2</v>
       </c>
     </row>
-    <row r="208" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="208" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I208" t="s">
         <v>42</v>
       </c>
@@ -14168,7 +14098,7 @@
         <v>3.6725370556628832E-3</v>
       </c>
     </row>
-    <row r="209" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="209" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I209" t="s">
         <v>42</v>
       </c>
@@ -14215,7 +14145,7 @@
         <v>3.4805813737254308E-3</v>
       </c>
     </row>
-    <row r="210" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="210" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I210" t="s">
         <v>42</v>
       </c>
@@ -14262,7 +14192,7 @@
         <v>9.9024335426087986E-3</v>
       </c>
     </row>
-    <row r="211" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="211" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I211" t="s">
         <v>42</v>
       </c>
@@ -14309,7 +14239,7 @@
         <v>1.989855025272743E-2</v>
       </c>
     </row>
-    <row r="212" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="212" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I212" t="s">
         <v>42</v>
       </c>
@@ -14356,7 +14286,7 @@
         <v>4.4755362321205862E-3</v>
       </c>
     </row>
-    <row r="213" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="213" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I213" t="s">
         <v>42</v>
       </c>
@@ -14403,7 +14333,7 @@
         <v>4.0617049230748568E-2</v>
       </c>
     </row>
-    <row r="214" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="214" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I214" t="s">
         <v>42</v>
       </c>
@@ -14450,7 +14380,7 @@
         <v>4.7067866934560757E-3</v>
       </c>
     </row>
-    <row r="215" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="215" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I215" t="s">
         <v>42</v>
       </c>
@@ -14497,7 +14427,7 @@
         <v>1.4151576838914404E-2</v>
       </c>
     </row>
-    <row r="216" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="216" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I216" t="s">
         <v>42</v>
       </c>
@@ -14544,7 +14474,7 @@
         <v>4.4701965234218979E-3</v>
       </c>
     </row>
-    <row r="217" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="217" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I217" t="s">
         <v>42</v>
       </c>
@@ -14591,7 +14521,7 @@
         <v>4.2570189222973518E-3</v>
       </c>
     </row>
-    <row r="218" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="218" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I218" t="s">
         <v>42</v>
       </c>
@@ -14638,7 +14568,7 @@
         <v>1.1790330269233018E-2</v>
       </c>
     </row>
-    <row r="219" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="219" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I219" t="s">
         <v>42</v>
       </c>
@@ -14685,7 +14615,7 @@
         <v>1.7030278920719268E-2</v>
       </c>
     </row>
-    <row r="220" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="220" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I220" t="s">
         <v>42</v>
       </c>
@@ -14732,7 +14662,7 @@
         <v>3.8023169358295701E-3</v>
       </c>
     </row>
-    <row r="221" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="221" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I221" t="s">
         <v>42</v>
       </c>
@@ -14779,7 +14709,7 @@
         <v>3.4216881869844028E-2</v>
       </c>
     </row>
-    <row r="222" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="222" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I222" t="s">
         <v>42</v>
       </c>
@@ -14826,7 +14756,7 @@
         <v>3.8227173613707113E-3</v>
       </c>
     </row>
-    <row r="223" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="223" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I223" t="s">
         <v>42</v>
       </c>
@@ -14873,7 +14803,7 @@
         <v>1.128249452012698E-2</v>
       </c>
     </row>
-    <row r="224" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="224" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I224" t="s">
         <v>42</v>
       </c>
@@ -14920,7 +14850,7 @@
         <v>3.4785115237168209E-3</v>
       </c>
     </row>
-    <row r="225" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="225" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I225" t="s">
         <v>42</v>
       </c>
@@ -14967,7 +14897,7 @@
         <v>3.3232492246318916E-3</v>
       </c>
     </row>
-    <row r="226" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="226" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I226" t="s">
         <v>42</v>
       </c>
@@ -15014,7 +14944,7 @@
         <v>9.5205275651675855E-3</v>
       </c>
     </row>
-    <row r="227" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="227" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I227" t="s">
         <v>42</v>
       </c>
@@ -15061,7 +14991,7 @@
         <v>1.3014575346651859E-2</v>
       </c>
     </row>
-    <row r="228" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="228" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I228" t="s">
         <v>42</v>
       </c>
@@ -15108,7 +15038,7 @@
         <v>3.3452441109341371E-3</v>
       </c>
     </row>
-    <row r="229" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="229" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I229" t="s">
         <v>42</v>
       </c>
@@ -15155,7 +15085,7 @@
         <v>3.2126428380157265E-2</v>
       </c>
     </row>
-    <row r="230" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="230" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I230" t="s">
         <v>42</v>
       </c>
@@ -15202,7 +15132,7 @@
         <v>3.5255619662206026E-3</v>
       </c>
     </row>
-    <row r="231" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="231" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I231" t="s">
         <v>42</v>
       </c>
@@ -15249,7 +15179,7 @@
         <v>1.0434293666696794E-2</v>
       </c>
     </row>
-    <row r="232" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="232" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I232" t="s">
         <v>42</v>
       </c>
@@ -15296,7 +15226,7 @@
         <v>3.2923946863778913E-3</v>
       </c>
     </row>
-    <row r="233" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="233" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I233" t="s">
         <v>42</v>
       </c>
@@ -15343,7 +15273,7 @@
         <v>3.1417875179533565E-3</v>
       </c>
     </row>
-    <row r="234" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="234" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I234" t="s">
         <v>42</v>
       </c>
@@ -15390,7 +15320,7 @@
         <v>7.7096730742893041E-3</v>
       </c>
     </row>
-    <row r="235" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="235" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I235" t="s">
         <v>42</v>
       </c>
@@ -15437,7 +15367,7 @@
         <v>1.1331637101402961E-2</v>
       </c>
     </row>
-    <row r="236" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="236" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I236" t="s">
         <v>42</v>
       </c>
@@ -15484,7 +15414,7 @@
         <v>3.1008006658386411E-3</v>
       </c>
     </row>
-    <row r="237" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="237" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I237" t="s">
         <v>42</v>
       </c>
@@ -15531,7 +15461,7 @@
         <v>3.1151832062842878E-2</v>
       </c>
     </row>
-    <row r="238" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="238" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I238" t="s">
         <v>42</v>
       </c>
@@ -15578,7 +15508,7 @@
         <v>3.4567812457511771E-3</v>
       </c>
     </row>
-    <row r="239" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="239" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I239" t="s">
         <v>42</v>
       </c>
@@ -15625,7 +15555,7 @@
         <v>1.0112531648032261E-2</v>
       </c>
     </row>
-    <row r="240" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="240" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I240" t="s">
         <v>42</v>
       </c>
@@ -15672,7 +15602,7 @@
         <v>3.226489193669298E-3</v>
       </c>
     </row>
-    <row r="241" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="241" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I241" t="s">
         <v>42</v>
       </c>
@@ -15719,7 +15649,7 @@
         <v>2.9747013911850077E-3</v>
       </c>
     </row>
-    <row r="242" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="242" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I242" t="s">
         <v>42</v>
       </c>
@@ -15766,7 +15696,7 @@
         <v>6.927600782676329E-3</v>
       </c>
     </row>
-    <row r="243" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="243" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I243" t="s">
         <v>42</v>
       </c>
@@ -15813,7 +15743,7 @@
         <v>1.1777936364459845E-2</v>
       </c>
     </row>
-    <row r="244" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="244" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I244" t="s">
         <v>42</v>
       </c>
@@ -15860,7 +15790,7 @@
         <v>3.2430194754923905E-3</v>
       </c>
     </row>
-    <row r="245" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="245" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I245" t="s">
         <v>42</v>
       </c>
@@ -15907,7 +15837,7 @@
         <v>3.2781620727294521E-2</v>
       </c>
     </row>
-    <row r="246" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="246" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I246" t="s">
         <v>42</v>
       </c>
@@ -15954,7 +15884,7 @@
         <v>3.6493849990233166E-3</v>
       </c>
     </row>
-    <row r="247" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="247" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I247" t="s">
         <v>42</v>
       </c>
@@ -16001,7 +15931,7 @@
         <v>1.0650226634804688E-2</v>
       </c>
     </row>
-    <row r="248" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="248" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I248" t="s">
         <v>42</v>
       </c>
@@ -16048,7 +15978,7 @@
         <v>3.3951327156011707E-3</v>
       </c>
     </row>
-    <row r="249" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="249" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I249" t="s">
         <v>42</v>
       </c>
@@ -16095,7 +16025,7 @@
         <v>3.1040501337188425E-3</v>
       </c>
     </row>
-    <row r="250" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="250" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I250" t="s">
         <v>42</v>
       </c>
@@ -16142,7 +16072,7 @@
         <v>7.1828388708489264E-3</v>
       </c>
     </row>
-    <row r="251" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="251" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I251" t="s">
         <v>42</v>
       </c>
@@ -16189,7 +16119,7 @@
         <v>1.1769034568936449E-2</v>
       </c>
     </row>
-    <row r="252" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="252" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I252" t="s">
         <v>42</v>
       </c>
@@ -16236,7 +16166,7 @@
         <v>3.1968510763847715E-3</v>
       </c>
     </row>
-    <row r="253" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="253" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I253" t="s">
         <v>42</v>
       </c>
@@ -16283,7 +16213,7 @@
         <v>3.2223575987753272E-2</v>
       </c>
     </row>
-    <row r="254" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="254" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I254" t="s">
         <v>42</v>
       </c>
@@ -16330,7 +16260,7 @@
         <v>3.5826792587668973E-3</v>
       </c>
     </row>
-    <row r="255" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="255" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I255" t="s">
         <v>42</v>
       </c>
@@ -16377,7 +16307,7 @@
         <v>1.0443674380475474E-2</v>
       </c>
     </row>
-    <row r="256" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="256" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I256" t="s">
         <v>42</v>
       </c>
@@ -16424,7 +16354,7 @@
         <v>3.3046036596121428E-3</v>
       </c>
     </row>
-    <row r="257" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="257" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I257" t="s">
         <v>42</v>
       </c>
@@ -16471,7 +16401,7 @@
         <v>3.0860863497889088E-3</v>
       </c>
     </row>
-    <row r="258" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="258" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I258" t="s">
         <v>42</v>
       </c>
@@ -16518,7 +16448,7 @@
         <v>7.1800170407158078E-3</v>
       </c>
     </row>
-    <row r="259" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="259" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I259" t="s">
         <v>42</v>
       </c>
@@ -16565,7 +16495,7 @@
         <v>1.2479406550232053E-2</v>
       </c>
     </row>
-    <row r="260" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="260" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I260" t="s">
         <v>42</v>
       </c>
@@ -16612,7 +16542,7 @@
         <v>3.2085270479097765E-3</v>
       </c>
     </row>
-    <row r="261" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="261" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I261" t="s">
         <v>42</v>
       </c>
@@ -16659,7 +16589,7 @@
         <v>3.083751184846777E-2</v>
       </c>
     </row>
-    <row r="262" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="262" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I262" t="s">
         <v>42</v>
       </c>
@@ -16706,7 +16636,7 @@
         <v>3.3954168523638584E-3</v>
       </c>
     </row>
-    <row r="263" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="263" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I263" t="s">
         <v>42</v>
       </c>
@@ -16753,7 +16683,7 @@
         <v>1.0075759661711028E-2</v>
       </c>
     </row>
-    <row r="264" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="264" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I264" t="s">
         <v>42</v>
       </c>
@@ -16800,7 +16730,7 @@
         <v>3.168821521688763E-3</v>
       </c>
     </row>
-    <row r="265" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="265" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I265" t="s">
         <v>42</v>
       </c>
@@ -16847,7 +16777,7 @@
         <v>3.0313582515994601E-3</v>
       </c>
     </row>
-    <row r="266" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="266" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I266" t="s">
         <v>42</v>
       </c>
@@ -16894,7 +16824,7 @@
         <v>7.52173591644624E-3</v>
       </c>
     </row>
-    <row r="267" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="267" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I267" t="s">
         <v>42</v>
       </c>
@@ -16941,7 +16871,7 @@
         <v>1.4531792155247624E-2</v>
       </c>
     </row>
-    <row r="268" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="268" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I268" t="s">
         <v>42</v>
       </c>
@@ -16988,7 +16918,7 @@
         <v>3.4369611769699262E-3</v>
       </c>
     </row>
-    <row r="269" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="269" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I269" t="s">
         <v>42</v>
       </c>
@@ -17035,7 +16965,7 @@
         <v>3.3008975782873033E-2</v>
       </c>
     </row>
-    <row r="270" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="270" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I270" t="s">
         <v>42</v>
       </c>
@@ -17082,7 +17012,7 @@
         <v>3.6936779413299283E-3</v>
       </c>
     </row>
-    <row r="271" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="271" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I271" t="s">
         <v>42</v>
       </c>
@@ -17129,7 +17059,7 @@
         <v>1.1021201703442948E-2</v>
       </c>
     </row>
-    <row r="272" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="272" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I272" t="s">
         <v>42</v>
       </c>
@@ -17176,7 +17106,7 @@
         <v>3.5152769045506843E-3</v>
       </c>
     </row>
-    <row r="273" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="273" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I273" t="s">
         <v>42</v>
       </c>
@@ -17223,7 +17153,7 @@
         <v>3.2851217680764633E-3</v>
       </c>
     </row>
-    <row r="274" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="274" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I274" t="s">
         <v>42</v>
       </c>
@@ -17270,7 +17200,7 @@
         <v>8.5823239842190962E-3</v>
       </c>
     </row>
-    <row r="275" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="275" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I275" t="s">
         <v>42</v>
       </c>
@@ -17317,7 +17247,7 @@
         <v>1.5033124372636795E-2</v>
       </c>
     </row>
-    <row r="276" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="276" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I276" t="s">
         <v>42</v>
       </c>
@@ -17364,7 +17294,7 @@
         <v>3.4906763138438132E-3</v>
       </c>
     </row>
-    <row r="277" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="277" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I277" t="s">
         <v>42</v>
       </c>
@@ -17411,7 +17341,7 @@
         <v>3.2780313939305285E-2</v>
       </c>
     </row>
-    <row r="278" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="278" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I278" t="s">
         <v>42</v>
       </c>
@@ -17458,7 +17388,7 @@
         <v>3.7080982988057778E-3</v>
       </c>
     </row>
-    <row r="279" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="279" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I279" t="s">
         <v>42</v>
       </c>
@@ -17505,7 +17435,7 @@
         <v>1.1064052029047521E-2</v>
       </c>
     </row>
-    <row r="280" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="280" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I280" t="s">
         <v>42</v>
       </c>
@@ -17552,7 +17482,7 @@
         <v>3.6366283516079531E-3</v>
       </c>
     </row>
-    <row r="281" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="281" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I281" t="s">
         <v>42</v>
       </c>
@@ -17599,7 +17529,7 @@
         <v>3.4442619228475251E-3</v>
       </c>
     </row>
-    <row r="282" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="282" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I282" t="s">
         <v>42</v>
       </c>
@@ -17646,7 +17576,7 @@
         <v>9.2879827664992809E-3</v>
       </c>
     </row>
-    <row r="283" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="283" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I283" t="s">
         <v>42</v>
       </c>
@@ -17693,7 +17623,7 @@
         <v>1.6818171731056177E-2</v>
       </c>
     </row>
-    <row r="284" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="284" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I284" t="s">
         <v>42</v>
       </c>
@@ -17740,7 +17670,7 @@
         <v>3.9065868799424489E-3</v>
       </c>
     </row>
-    <row r="285" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="285" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I285" t="s">
         <v>42</v>
       </c>
@@ -17787,7 +17717,7 @@
         <v>3.5563456793290427E-2</v>
       </c>
     </row>
-    <row r="286" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="286" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I286" t="s">
         <v>42</v>
       </c>
@@ -17834,7 +17764,7 @@
         <v>3.9965404341741938E-3</v>
       </c>
     </row>
-    <row r="287" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="287" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I287" t="s">
         <v>42</v>
       </c>
@@ -17881,7 +17811,7 @@
         <v>1.1924586388884714E-2</v>
       </c>
     </row>
-    <row r="288" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="288" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I288" t="s">
         <v>42</v>
       </c>
@@ -17928,7 +17858,7 @@
         <v>3.8462070969649763E-3</v>
       </c>
     </row>
-    <row r="289" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="289" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I289" t="s">
         <v>42</v>
       </c>
@@ -17975,7 +17905,7 @@
         <v>3.6420659259459023E-3</v>
       </c>
     </row>
-    <row r="290" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="290" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I290" t="s">
         <v>42</v>
       </c>
@@ -18022,7 +17952,7 @@
         <v>1.0138933033800368E-2</v>
       </c>
     </row>
-    <row r="291" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="291" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I291" t="s">
         <v>45</v>
       </c>
@@ -18060,7 +17990,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="292" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="292" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I292" t="s">
         <v>45</v>
       </c>
@@ -18098,7 +18028,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="293" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="293" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I293" t="s">
         <v>45</v>
       </c>
@@ -18136,7 +18066,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="294" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="294" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I294" t="s">
         <v>45</v>
       </c>
@@ -18174,7 +18104,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="295" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="295" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I295" t="s">
         <v>45</v>
       </c>
@@ -18212,7 +18142,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="296" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="296" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I296" t="s">
         <v>45</v>
       </c>
@@ -18250,7 +18180,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="297" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="297" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I297" t="s">
         <v>45</v>
       </c>
@@ -18288,7 +18218,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="298" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="298" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I298" t="s">
         <v>45</v>
       </c>
@@ -18326,7 +18256,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="299" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="299" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I299" t="s">
         <v>45</v>
       </c>
@@ -18364,7 +18294,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="300" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="300" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I300" t="s">
         <v>45</v>
       </c>
@@ -18402,7 +18332,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="301" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="301" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I301" t="s">
         <v>45</v>
       </c>
@@ -18440,7 +18370,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="302" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="302" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I302" t="s">
         <v>45</v>
       </c>
@@ -18478,7 +18408,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="303" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="303" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I303" t="s">
         <v>45</v>
       </c>
@@ -18516,7 +18446,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="304" spans="9:26" x14ac:dyDescent="0.25">
+    <row r="304" spans="9:26" x14ac:dyDescent="0.35">
       <c r="I304" t="s">
         <v>45</v>
       </c>
@@ -18554,7 +18484,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="305" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="305" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I305" t="s">
         <v>45</v>
       </c>
@@ -18592,7 +18522,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="306" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="306" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I306" t="s">
         <v>45</v>
       </c>
@@ -18630,7 +18560,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="307" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="307" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I307" t="s">
         <v>45</v>
       </c>
@@ -18668,7 +18598,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="308" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="308" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I308" t="s">
         <v>45</v>
       </c>
@@ -18706,7 +18636,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="309" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="309" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I309" t="s">
         <v>45</v>
       </c>
@@ -18744,7 +18674,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="310" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="310" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I310" t="s">
         <v>45</v>
       </c>
@@ -18782,7 +18712,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="311" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="311" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I311" t="s">
         <v>45</v>
       </c>
@@ -18820,7 +18750,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="312" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="312" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I312" t="s">
         <v>45</v>
       </c>
@@ -18858,7 +18788,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="313" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="313" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I313" t="s">
         <v>45</v>
       </c>
@@ -18896,7 +18826,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="314" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="314" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I314" t="s">
         <v>45</v>
       </c>
@@ -18934,7 +18864,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="315" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="315" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I315" t="s">
         <v>45</v>
       </c>
@@ -18972,7 +18902,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="316" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="316" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I316" t="s">
         <v>45</v>
       </c>
@@ -19010,7 +18940,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="317" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="317" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I317" t="s">
         <v>45</v>
       </c>
@@ -19048,7 +18978,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="318" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="318" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I318" t="s">
         <v>45</v>
       </c>
@@ -19086,7 +19016,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="319" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="319" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I319" t="s">
         <v>45</v>
       </c>
@@ -19124,7 +19054,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="320" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="320" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I320" t="s">
         <v>45</v>
       </c>
@@ -19162,7 +19092,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="321" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="321" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I321" t="s">
         <v>45</v>
       </c>
@@ -19200,7 +19130,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="322" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="322" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I322" t="s">
         <v>45</v>
       </c>
@@ -19238,7 +19168,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="323" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="323" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I323" t="s">
         <v>45</v>
       </c>
@@ -19276,7 +19206,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="324" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="324" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I324" t="s">
         <v>45</v>
       </c>
@@ -19314,7 +19244,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="325" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="325" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I325" t="s">
         <v>45</v>
       </c>
@@ -19352,7 +19282,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="326" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="326" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I326" t="s">
         <v>45</v>
       </c>
@@ -19390,7 +19320,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="327" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="327" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I327" t="s">
         <v>45</v>
       </c>
@@ -19428,7 +19358,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="328" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="328" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I328" t="s">
         <v>45</v>
       </c>
@@ -19466,7 +19396,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="329" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="329" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I329" t="s">
         <v>45</v>
       </c>
@@ -19504,7 +19434,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="330" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="330" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I330" t="s">
         <v>45</v>
       </c>
@@ -19542,7 +19472,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="331" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="331" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I331" t="s">
         <v>45</v>
       </c>
@@ -19580,7 +19510,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="332" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="332" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I332" t="s">
         <v>45</v>
       </c>
@@ -19618,7 +19548,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="333" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="333" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I333" t="s">
         <v>45</v>
       </c>
@@ -19656,7 +19586,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="334" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="334" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I334" t="s">
         <v>45</v>
       </c>
@@ -19694,7 +19624,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="335" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="335" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I335" t="s">
         <v>45</v>
       </c>
@@ -19732,7 +19662,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="336" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="336" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I336" t="s">
         <v>45</v>
       </c>
@@ -19770,7 +19700,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="337" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="337" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I337" t="s">
         <v>45</v>
       </c>
@@ -19808,7 +19738,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="338" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="338" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I338" t="s">
         <v>45</v>
       </c>
@@ -19846,7 +19776,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="339" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="339" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I339" t="s">
         <v>45</v>
       </c>
@@ -19884,7 +19814,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="340" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="340" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I340" t="s">
         <v>45</v>
       </c>
@@ -19922,7 +19852,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="341" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="341" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I341" t="s">
         <v>45</v>
       </c>
@@ -19960,7 +19890,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="342" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="342" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I342" t="s">
         <v>45</v>
       </c>
@@ -19998,7 +19928,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="343" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="343" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I343" t="s">
         <v>45</v>
       </c>
@@ -20036,7 +19966,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="344" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="344" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I344" t="s">
         <v>45</v>
       </c>
@@ -20074,7 +20004,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="345" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="345" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I345" t="s">
         <v>45</v>
       </c>
@@ -20112,7 +20042,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="346" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="346" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I346" t="s">
         <v>45</v>
       </c>
@@ -20150,7 +20080,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="347" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="347" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I347" t="s">
         <v>45</v>
       </c>
@@ -20188,7 +20118,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="348" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="348" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I348" t="s">
         <v>45</v>
       </c>
@@ -20226,7 +20156,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="349" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="349" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I349" t="s">
         <v>45</v>
       </c>
@@ -20264,7 +20194,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="350" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="350" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I350" t="s">
         <v>45</v>
       </c>
@@ -20302,7 +20232,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="351" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="351" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I351" t="s">
         <v>45</v>
       </c>
@@ -20340,7 +20270,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="352" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="352" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I352" t="s">
         <v>45</v>
       </c>
@@ -20378,7 +20308,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="353" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="353" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I353" t="s">
         <v>45</v>
       </c>
@@ -20416,7 +20346,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="354" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="354" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I354" t="s">
         <v>45</v>
       </c>
@@ -20454,7 +20384,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="355" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="355" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I355" t="s">
         <v>45</v>
       </c>
@@ -20492,7 +20422,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="356" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="356" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I356" t="s">
         <v>45</v>
       </c>
@@ -20530,7 +20460,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="357" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="357" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I357" t="s">
         <v>45</v>
       </c>
@@ -20568,7 +20498,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="358" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="358" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I358" t="s">
         <v>45</v>
       </c>
@@ -20606,7 +20536,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="359" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="359" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I359" t="s">
         <v>45</v>
       </c>
@@ -20644,7 +20574,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="360" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="360" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I360" t="s">
         <v>45</v>
       </c>
@@ -20682,7 +20612,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="361" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="361" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I361" t="s">
         <v>45</v>
       </c>
@@ -20720,7 +20650,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="362" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="362" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I362" t="s">
         <v>45</v>
       </c>
@@ -20758,7 +20688,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="363" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="363" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I363" t="s">
         <v>45</v>
       </c>
@@ -20796,7 +20726,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="364" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="364" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I364" t="s">
         <v>45</v>
       </c>
@@ -20834,7 +20764,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="365" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="365" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I365" t="s">
         <v>45</v>
       </c>
@@ -20872,7 +20802,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="366" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="366" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I366" t="s">
         <v>45</v>
       </c>
@@ -20910,7 +20840,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="367" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="367" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I367" t="s">
         <v>45</v>
       </c>
@@ -20948,7 +20878,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="368" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="368" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I368" t="s">
         <v>45</v>
       </c>
@@ -20986,7 +20916,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="369" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="369" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I369" t="s">
         <v>45</v>
       </c>
@@ -21024,7 +20954,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="370" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="370" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I370" t="s">
         <v>45</v>
       </c>
@@ -21062,7 +20992,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="371" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="371" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I371" t="s">
         <v>45</v>
       </c>
@@ -21100,7 +21030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="372" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="372" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I372" t="s">
         <v>45</v>
       </c>
@@ -21138,7 +21068,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="373" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="373" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I373" t="s">
         <v>45</v>
       </c>
@@ -21176,7 +21106,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="374" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="374" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I374" t="s">
         <v>45</v>
       </c>
@@ -21214,7 +21144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="375" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="375" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I375" t="s">
         <v>45</v>
       </c>
@@ -21252,7 +21182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="376" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="376" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I376" t="s">
         <v>45</v>
       </c>
@@ -21290,7 +21220,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="377" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="377" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I377" t="s">
         <v>45</v>
       </c>
@@ -21328,7 +21258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="378" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="378" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I378" t="s">
         <v>45</v>
       </c>
@@ -21366,7 +21296,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="379" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="379" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I379" t="s">
         <v>45</v>
       </c>
@@ -21404,7 +21334,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="380" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="380" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I380" t="s">
         <v>45</v>
       </c>
@@ -21442,7 +21372,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="381" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="381" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I381" t="s">
         <v>45</v>
       </c>
@@ -21480,7 +21410,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="382" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="382" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I382" t="s">
         <v>45</v>
       </c>
@@ -21518,7 +21448,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="383" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="383" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I383" t="s">
         <v>45</v>
       </c>
@@ -21556,7 +21486,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="384" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="384" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I384" t="s">
         <v>45</v>
       </c>
@@ -21594,7 +21524,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="385" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="385" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I385" t="s">
         <v>45</v>
       </c>
@@ -21632,7 +21562,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="386" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="386" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I386" t="s">
         <v>45</v>
       </c>
@@ -21670,7 +21600,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="387" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="387" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I387" t="s">
         <v>48</v>
       </c>
@@ -21708,7 +21638,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="388" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="388" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I388" t="s">
         <v>48</v>
       </c>
@@ -21746,7 +21676,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="389" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="389" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I389" t="s">
         <v>48</v>
       </c>
@@ -21784,7 +21714,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="390" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="390" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I390" t="s">
         <v>48</v>
       </c>
@@ -21822,7 +21752,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="391" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="391" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I391" t="s">
         <v>48</v>
       </c>
@@ -21860,7 +21790,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="392" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="392" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I392" t="s">
         <v>48</v>
       </c>
@@ -21898,7 +21828,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="393" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="393" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I393" t="s">
         <v>48</v>
       </c>
@@ -21936,7 +21866,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="394" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="394" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I394" t="s">
         <v>48</v>
       </c>
@@ -21974,7 +21904,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="395" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="395" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I395" t="s">
         <v>48</v>
       </c>
@@ -22012,7 +21942,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="396" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="396" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I396" t="s">
         <v>48</v>
       </c>
@@ -22050,7 +21980,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="397" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="397" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I397" t="s">
         <v>48</v>
       </c>
@@ -22088,7 +22018,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="398" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="398" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I398" t="s">
         <v>48</v>
       </c>
@@ -22126,7 +22056,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="399" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="399" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I399" t="s">
         <v>48</v>
       </c>
@@ -22164,7 +22094,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="400" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="400" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I400" t="s">
         <v>48</v>
       </c>
@@ -22202,7 +22132,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="401" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="401" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I401" t="s">
         <v>48</v>
       </c>
@@ -22240,7 +22170,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="402" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="402" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I402" t="s">
         <v>48</v>
       </c>
@@ -22278,7 +22208,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="403" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="403" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I403" t="s">
         <v>48</v>
       </c>
@@ -22316,7 +22246,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="404" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="404" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I404" t="s">
         <v>48</v>
       </c>
@@ -22354,7 +22284,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="405" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="405" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I405" t="s">
         <v>48</v>
       </c>
@@ -22392,7 +22322,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="406" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="406" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I406" t="s">
         <v>48</v>
       </c>
@@ -22430,7 +22360,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="407" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="407" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I407" t="s">
         <v>48</v>
       </c>
@@ -22468,7 +22398,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="408" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="408" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I408" t="s">
         <v>48</v>
       </c>
@@ -22506,7 +22436,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="409" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="409" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I409" t="s">
         <v>48</v>
       </c>
@@ -22544,7 +22474,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="410" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="410" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I410" t="s">
         <v>48</v>
       </c>
@@ -22582,7 +22512,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="411" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="411" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I411" t="s">
         <v>48</v>
       </c>
@@ -22620,7 +22550,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="412" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="412" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I412" t="s">
         <v>48</v>
       </c>
@@ -22658,7 +22588,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="413" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="413" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I413" t="s">
         <v>48</v>
       </c>
@@ -22696,7 +22626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="414" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="414" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I414" t="s">
         <v>48</v>
       </c>
@@ -22734,7 +22664,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="415" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="415" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I415" t="s">
         <v>48</v>
       </c>
@@ -22772,7 +22702,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="416" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="416" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I416" t="s">
         <v>48</v>
       </c>
@@ -22810,7 +22740,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="417" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="417" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I417" t="s">
         <v>48</v>
       </c>
@@ -22848,7 +22778,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="418" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="418" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I418" t="s">
         <v>48</v>
       </c>
@@ -22886,7 +22816,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="419" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="419" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I419" t="s">
         <v>48</v>
       </c>
@@ -22924,7 +22854,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="420" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="420" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I420" t="s">
         <v>48</v>
       </c>
@@ -22962,7 +22892,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="421" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="421" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I421" t="s">
         <v>48</v>
       </c>
@@ -23000,7 +22930,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="422" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="422" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I422" t="s">
         <v>48</v>
       </c>
@@ -23038,7 +22968,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="423" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="423" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I423" t="s">
         <v>48</v>
       </c>
@@ -23076,7 +23006,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="424" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="424" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I424" t="s">
         <v>48</v>
       </c>
@@ -23114,7 +23044,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="425" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="425" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I425" t="s">
         <v>48</v>
       </c>
@@ -23152,7 +23082,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="426" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="426" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I426" t="s">
         <v>48</v>
       </c>
@@ -23190,7 +23120,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="427" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="427" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I427" t="s">
         <v>48</v>
       </c>
@@ -23228,7 +23158,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="428" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="428" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I428" t="s">
         <v>48</v>
       </c>
@@ -23266,7 +23196,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="429" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="429" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I429" t="s">
         <v>48</v>
       </c>
@@ -23304,7 +23234,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="430" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="430" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I430" t="s">
         <v>48</v>
       </c>
@@ -23342,7 +23272,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="431" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="431" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I431" t="s">
         <v>48</v>
       </c>
@@ -23380,7 +23310,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="432" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="432" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I432" t="s">
         <v>48</v>
       </c>
@@ -23418,7 +23348,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="433" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="433" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I433" t="s">
         <v>48</v>
       </c>
@@ -23456,7 +23386,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="434" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="434" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I434" t="s">
         <v>48</v>
       </c>
@@ -23494,7 +23424,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="435" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="435" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I435" t="s">
         <v>48</v>
       </c>
@@ -23532,7 +23462,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="436" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="436" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I436" t="s">
         <v>48</v>
       </c>
@@ -23570,7 +23500,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="437" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="437" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I437" t="s">
         <v>48</v>
       </c>
@@ -23608,7 +23538,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="438" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="438" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I438" t="s">
         <v>48</v>
       </c>
@@ -23646,7 +23576,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="439" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="439" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I439" t="s">
         <v>48</v>
       </c>
@@ -23684,7 +23614,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="440" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="440" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I440" t="s">
         <v>48</v>
       </c>
@@ -23722,7 +23652,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="441" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="441" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I441" t="s">
         <v>48</v>
       </c>
@@ -23760,7 +23690,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="442" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="442" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I442" t="s">
         <v>48</v>
       </c>
@@ -23798,7 +23728,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="443" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="443" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I443" t="s">
         <v>48</v>
       </c>
@@ -23836,7 +23766,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="444" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="444" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I444" t="s">
         <v>48</v>
       </c>
@@ -23874,7 +23804,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="445" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="445" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I445" t="s">
         <v>48</v>
       </c>
@@ -23912,7 +23842,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="446" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="446" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I446" t="s">
         <v>48</v>
       </c>
@@ -23950,7 +23880,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="447" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="447" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I447" t="s">
         <v>48</v>
       </c>
@@ -23988,7 +23918,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="448" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="448" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I448" t="s">
         <v>48</v>
       </c>
@@ -24026,7 +23956,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="449" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="449" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I449" t="s">
         <v>48</v>
       </c>
@@ -24064,7 +23994,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="450" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="450" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I450" t="s">
         <v>48</v>
       </c>
@@ -24102,7 +24032,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="451" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="451" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I451" t="s">
         <v>48</v>
       </c>
@@ -24140,7 +24070,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="452" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="452" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I452" t="s">
         <v>48</v>
       </c>
@@ -24178,7 +24108,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="453" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="453" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I453" t="s">
         <v>48</v>
       </c>
@@ -24216,7 +24146,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="454" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="454" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I454" t="s">
         <v>48</v>
       </c>
@@ -24254,7 +24184,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="455" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="455" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I455" t="s">
         <v>48</v>
       </c>
@@ -24292,7 +24222,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="456" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="456" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I456" t="s">
         <v>48</v>
       </c>
@@ -24330,7 +24260,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="457" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="457" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I457" t="s">
         <v>48</v>
       </c>
@@ -24368,7 +24298,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="458" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="458" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I458" t="s">
         <v>48</v>
       </c>
@@ -24406,7 +24336,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="459" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="459" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I459" t="s">
         <v>48</v>
       </c>
@@ -24444,7 +24374,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="460" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="460" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I460" t="s">
         <v>48</v>
       </c>
@@ -24482,7 +24412,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="461" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="461" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I461" t="s">
         <v>48</v>
       </c>
@@ -24520,7 +24450,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="462" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="462" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I462" t="s">
         <v>48</v>
       </c>
@@ -24558,7 +24488,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="463" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="463" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I463" t="s">
         <v>48</v>
       </c>
@@ -24596,7 +24526,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="464" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="464" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I464" t="s">
         <v>48</v>
       </c>
@@ -24634,7 +24564,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="465" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="465" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I465" t="s">
         <v>48</v>
       </c>
@@ -24672,7 +24602,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="466" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="466" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I466" t="s">
         <v>48</v>
       </c>
@@ -24710,7 +24640,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="467" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="467" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I467" t="s">
         <v>48</v>
       </c>
@@ -24748,7 +24678,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="468" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="468" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I468" t="s">
         <v>48</v>
       </c>
@@ -24786,7 +24716,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="469" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="469" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I469" t="s">
         <v>48</v>
       </c>
@@ -24824,7 +24754,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="470" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="470" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I470" t="s">
         <v>48</v>
       </c>
@@ -24862,7 +24792,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="471" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="471" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I471" t="s">
         <v>48</v>
       </c>
@@ -24900,7 +24830,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="472" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="472" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I472" t="s">
         <v>48</v>
       </c>
@@ -24938,7 +24868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="473" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="473" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I473" t="s">
         <v>48</v>
       </c>
@@ -24976,7 +24906,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="474" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="474" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I474" t="s">
         <v>48</v>
       </c>
@@ -25014,7 +24944,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="475" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="475" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I475" t="s">
         <v>48</v>
       </c>
@@ -25052,7 +24982,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="476" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="476" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I476" t="s">
         <v>48</v>
       </c>
@@ -25090,7 +25020,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="477" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="477" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I477" t="s">
         <v>48</v>
       </c>
@@ -25128,7 +25058,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="478" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="478" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I478" t="s">
         <v>48</v>
       </c>
@@ -25166,7 +25096,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="479" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="479" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I479" t="s">
         <v>48</v>
       </c>
@@ -25204,7 +25134,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="480" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="480" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I480" t="s">
         <v>48</v>
       </c>
@@ -25242,7 +25172,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="481" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="481" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I481" t="s">
         <v>48</v>
       </c>
@@ -25280,7 +25210,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="482" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="482" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I482" t="s">
         <v>48</v>
       </c>
@@ -25318,7 +25248,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="483" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="483" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I483" t="s">
         <v>51</v>
       </c>
@@ -25356,7 +25286,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="484" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="484" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I484" t="s">
         <v>51</v>
       </c>
@@ -25394,7 +25324,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="485" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="485" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I485" t="s">
         <v>51</v>
       </c>
@@ -25432,7 +25362,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="486" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="486" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I486" t="s">
         <v>51</v>
       </c>
@@ -25470,7 +25400,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="487" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="487" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I487" t="s">
         <v>51</v>
       </c>
@@ -25508,7 +25438,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="488" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="488" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I488" t="s">
         <v>51</v>
       </c>
@@ -25546,7 +25476,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="489" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="489" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I489" t="s">
         <v>51</v>
       </c>
@@ -25584,7 +25514,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="490" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="490" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I490" t="s">
         <v>51</v>
       </c>
@@ -25622,7 +25552,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="491" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="491" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I491" t="s">
         <v>51</v>
       </c>
@@ -25660,7 +25590,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="492" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="492" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I492" t="s">
         <v>51</v>
       </c>
@@ -25698,7 +25628,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="493" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="493" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I493" t="s">
         <v>51</v>
       </c>
@@ -25736,7 +25666,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="494" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="494" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I494" t="s">
         <v>51</v>
       </c>
@@ -25774,7 +25704,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="495" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="495" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I495" t="s">
         <v>51</v>
       </c>
@@ -25812,7 +25742,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="496" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="496" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I496" t="s">
         <v>51</v>
       </c>
@@ -25850,7 +25780,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="497" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="497" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I497" t="s">
         <v>51</v>
       </c>
@@ -25888,7 +25818,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="498" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="498" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I498" t="s">
         <v>51</v>
       </c>
@@ -25926,7 +25856,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="499" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="499" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I499" t="s">
         <v>51</v>
       </c>
@@ -25964,7 +25894,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="500" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="500" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I500" t="s">
         <v>51</v>
       </c>
@@ -26002,7 +25932,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="501" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="501" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I501" t="s">
         <v>51</v>
       </c>
@@ -26040,7 +25970,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="502" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="502" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I502" t="s">
         <v>51</v>
       </c>
@@ -26078,7 +26008,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="503" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="503" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I503" t="s">
         <v>51</v>
       </c>
@@ -26116,7 +26046,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="504" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="504" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I504" t="s">
         <v>51</v>
       </c>
@@ -26154,7 +26084,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="505" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="505" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I505" t="s">
         <v>51</v>
       </c>
@@ -26192,7 +26122,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="506" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="506" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I506" t="s">
         <v>51</v>
       </c>
@@ -26230,7 +26160,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="507" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="507" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I507" t="s">
         <v>51</v>
       </c>
@@ -26268,7 +26198,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="508" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="508" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I508" t="s">
         <v>51</v>
       </c>
@@ -26306,7 +26236,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="509" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="509" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I509" t="s">
         <v>51</v>
       </c>
@@ -26344,7 +26274,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="510" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="510" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I510" t="s">
         <v>51</v>
       </c>
@@ -26382,7 +26312,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="511" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="511" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I511" t="s">
         <v>51</v>
       </c>
@@ -26420,7 +26350,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="512" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="512" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I512" t="s">
         <v>51</v>
       </c>
@@ -26458,7 +26388,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="513" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="513" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I513" t="s">
         <v>51</v>
       </c>
@@ -26496,7 +26426,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="514" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="514" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I514" t="s">
         <v>51</v>
       </c>
@@ -26534,7 +26464,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="515" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="515" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I515" t="s">
         <v>51</v>
       </c>
@@ -26572,7 +26502,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="516" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="516" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I516" t="s">
         <v>51</v>
       </c>
@@ -26610,7 +26540,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="517" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="517" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I517" t="s">
         <v>51</v>
       </c>
@@ -26648,7 +26578,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="518" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="518" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I518" t="s">
         <v>51</v>
       </c>
@@ -26686,7 +26616,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="519" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="519" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I519" t="s">
         <v>51</v>
       </c>
@@ -26724,7 +26654,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="520" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="520" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I520" t="s">
         <v>51</v>
       </c>
@@ -26762,7 +26692,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="521" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="521" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I521" t="s">
         <v>51</v>
       </c>
@@ -26800,7 +26730,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="522" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="522" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I522" t="s">
         <v>51</v>
       </c>
@@ -26838,7 +26768,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="523" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="523" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I523" t="s">
         <v>51</v>
       </c>
@@ -26876,7 +26806,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="524" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="524" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I524" t="s">
         <v>51</v>
       </c>
@@ -26914,7 +26844,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="525" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="525" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I525" t="s">
         <v>51</v>
       </c>
@@ -26952,7 +26882,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="526" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="526" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I526" t="s">
         <v>51</v>
       </c>
@@ -26990,7 +26920,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="527" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="527" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I527" t="s">
         <v>51</v>
       </c>
@@ -27028,7 +26958,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="528" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="528" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I528" t="s">
         <v>51</v>
       </c>
@@ -27066,7 +26996,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="529" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="529" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I529" t="s">
         <v>51</v>
       </c>
@@ -27104,7 +27034,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="530" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="530" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I530" t="s">
         <v>51</v>
       </c>
@@ -27142,7 +27072,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="531" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="531" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I531" t="s">
         <v>51</v>
       </c>
@@ -27180,7 +27110,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="532" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="532" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I532" t="s">
         <v>51</v>
       </c>
@@ -27218,7 +27148,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="533" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="533" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I533" t="s">
         <v>51</v>
       </c>
@@ -27256,7 +27186,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="534" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="534" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I534" t="s">
         <v>51</v>
       </c>
@@ -27294,7 +27224,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="535" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="535" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I535" t="s">
         <v>51</v>
       </c>
@@ -27332,7 +27262,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="536" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="536" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I536" t="s">
         <v>51</v>
       </c>
@@ -27370,7 +27300,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="537" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="537" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I537" t="s">
         <v>51</v>
       </c>
@@ -27408,7 +27338,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="538" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="538" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I538" t="s">
         <v>51</v>
       </c>
@@ -27446,7 +27376,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="539" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="539" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I539" t="s">
         <v>51</v>
       </c>
@@ -27484,7 +27414,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="540" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="540" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I540" t="s">
         <v>51</v>
       </c>
@@ -27522,7 +27452,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="541" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="541" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I541" t="s">
         <v>51</v>
       </c>
@@ -27560,7 +27490,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="542" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="542" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I542" t="s">
         <v>51</v>
       </c>
@@ -27598,7 +27528,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="543" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="543" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I543" t="s">
         <v>51</v>
       </c>
@@ -27636,7 +27566,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="544" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="544" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I544" t="s">
         <v>51</v>
       </c>
@@ -27674,7 +27604,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="545" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="545" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I545" t="s">
         <v>51</v>
       </c>
@@ -27712,7 +27642,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="546" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="546" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I546" t="s">
         <v>51</v>
       </c>
@@ -27750,7 +27680,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="547" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="547" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I547" t="s">
         <v>51</v>
       </c>
@@ -27788,7 +27718,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="548" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="548" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I548" t="s">
         <v>51</v>
       </c>
@@ -27826,7 +27756,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="549" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="549" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I549" t="s">
         <v>51</v>
       </c>
@@ -27864,7 +27794,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="550" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="550" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I550" t="s">
         <v>51</v>
       </c>
@@ -27902,7 +27832,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="551" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="551" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I551" t="s">
         <v>51</v>
       </c>
@@ -27940,7 +27870,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="552" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="552" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I552" t="s">
         <v>51</v>
       </c>
@@ -27978,7 +27908,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="553" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="553" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I553" t="s">
         <v>51</v>
       </c>
@@ -28016,7 +27946,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="554" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="554" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I554" t="s">
         <v>51</v>
       </c>
@@ -28054,7 +27984,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="555" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="555" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I555" t="s">
         <v>51</v>
       </c>
@@ -28092,7 +28022,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="556" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="556" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I556" t="s">
         <v>51</v>
       </c>
@@ -28130,7 +28060,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="557" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="557" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I557" t="s">
         <v>51</v>
       </c>
@@ -28168,7 +28098,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="558" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="558" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I558" t="s">
         <v>51</v>
       </c>
@@ -28206,7 +28136,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="559" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="559" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I559" t="s">
         <v>51</v>
       </c>
@@ -28244,7 +28174,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="560" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="560" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I560" t="s">
         <v>51</v>
       </c>
@@ -28282,7 +28212,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="561" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="561" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I561" t="s">
         <v>51</v>
       </c>
@@ -28320,7 +28250,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="562" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="562" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I562" t="s">
         <v>51</v>
       </c>
@@ -28358,7 +28288,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="563" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="563" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I563" t="s">
         <v>51</v>
       </c>
@@ -28396,7 +28326,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="564" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="564" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I564" t="s">
         <v>51</v>
       </c>
@@ -28434,7 +28364,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="565" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="565" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I565" t="s">
         <v>51</v>
       </c>
@@ -28472,7 +28402,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="566" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="566" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I566" t="s">
         <v>51</v>
       </c>
@@ -28510,7 +28440,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="567" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="567" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I567" t="s">
         <v>51</v>
       </c>
@@ -28548,7 +28478,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="568" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="568" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I568" t="s">
         <v>51</v>
       </c>
@@ -28586,7 +28516,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="569" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="569" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I569" t="s">
         <v>51</v>
       </c>
@@ -28624,7 +28554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="570" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="570" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I570" t="s">
         <v>51</v>
       </c>
@@ -28662,7 +28592,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="571" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="571" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I571" t="s">
         <v>51</v>
       </c>
@@ -28700,7 +28630,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="572" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="572" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I572" t="s">
         <v>51</v>
       </c>
@@ -28738,7 +28668,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="573" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="573" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I573" t="s">
         <v>51</v>
       </c>
@@ -28776,7 +28706,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="574" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="574" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I574" t="s">
         <v>51</v>
       </c>
@@ -28814,7 +28744,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="575" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="575" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I575" t="s">
         <v>51</v>
       </c>
@@ -28852,7 +28782,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="576" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="576" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I576" t="s">
         <v>51</v>
       </c>
@@ -28890,7 +28820,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="577" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="577" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I577" t="s">
         <v>51</v>
       </c>
@@ -28928,7 +28858,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="578" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="578" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I578" t="s">
         <v>51</v>
       </c>
@@ -28966,7 +28896,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="579" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="579" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I579" t="s">
         <v>54</v>
       </c>
@@ -29004,7 +28934,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="580" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="580" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I580" t="s">
         <v>54</v>
       </c>
@@ -29042,7 +28972,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="581" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="581" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I581" t="s">
         <v>54</v>
       </c>
@@ -29080,7 +29010,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="582" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="582" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I582" t="s">
         <v>54</v>
       </c>
@@ -29118,7 +29048,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="583" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="583" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I583" t="s">
         <v>54</v>
       </c>
@@ -29156,7 +29086,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="584" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="584" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I584" t="s">
         <v>54</v>
       </c>
@@ -29194,7 +29124,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="585" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="585" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I585" t="s">
         <v>54</v>
       </c>
@@ -29232,7 +29162,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="586" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="586" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I586" t="s">
         <v>54</v>
       </c>
@@ -29270,7 +29200,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="587" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="587" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I587" t="s">
         <v>54</v>
       </c>
@@ -29308,7 +29238,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="588" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="588" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I588" t="s">
         <v>54</v>
       </c>
@@ -29346,7 +29276,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="589" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="589" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I589" t="s">
         <v>54</v>
       </c>
@@ -29384,7 +29314,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="590" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="590" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I590" t="s">
         <v>54</v>
       </c>
@@ -29422,7 +29352,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="591" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="591" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I591" t="s">
         <v>54</v>
       </c>
@@ -29460,7 +29390,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="592" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="592" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I592" t="s">
         <v>54</v>
       </c>
@@ -29498,7 +29428,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="593" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="593" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I593" t="s">
         <v>54</v>
       </c>
@@ -29536,7 +29466,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="594" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="594" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I594" t="s">
         <v>54</v>
       </c>
@@ -29574,7 +29504,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="595" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="595" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I595" t="s">
         <v>54</v>
       </c>
@@ -29612,7 +29542,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="596" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="596" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I596" t="s">
         <v>54</v>
       </c>
@@ -29650,7 +29580,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="597" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="597" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I597" t="s">
         <v>54</v>
       </c>
@@ -29688,7 +29618,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="598" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="598" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I598" t="s">
         <v>54</v>
       </c>
@@ -29726,7 +29656,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="599" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="599" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I599" t="s">
         <v>54</v>
       </c>
@@ -29764,7 +29694,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="600" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="600" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I600" t="s">
         <v>54</v>
       </c>
@@ -29802,7 +29732,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="601" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="601" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I601" t="s">
         <v>54</v>
       </c>
@@ -29840,7 +29770,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="602" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="602" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I602" t="s">
         <v>54</v>
       </c>
@@ -29878,7 +29808,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="603" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="603" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I603" t="s">
         <v>54</v>
       </c>
@@ -29916,7 +29846,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="604" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="604" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I604" t="s">
         <v>54</v>
       </c>
@@ -29954,7 +29884,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="605" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="605" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I605" t="s">
         <v>54</v>
       </c>
@@ -29992,7 +29922,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="606" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="606" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I606" t="s">
         <v>54</v>
       </c>
@@ -30030,7 +29960,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="607" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="607" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I607" t="s">
         <v>54</v>
       </c>
@@ -30068,7 +29998,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="608" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="608" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I608" t="s">
         <v>54</v>
       </c>
@@ -30106,7 +30036,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="609" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="609" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I609" t="s">
         <v>54</v>
       </c>
@@ -30144,7 +30074,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="610" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="610" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I610" t="s">
         <v>54</v>
       </c>
@@ -30182,7 +30112,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="611" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="611" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I611" t="s">
         <v>54</v>
       </c>
@@ -30220,7 +30150,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="612" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="612" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I612" t="s">
         <v>54</v>
       </c>
@@ -30258,7 +30188,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="613" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="613" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I613" t="s">
         <v>54</v>
       </c>
@@ -30296,7 +30226,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="614" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="614" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I614" t="s">
         <v>54</v>
       </c>
@@ -30334,7 +30264,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="615" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="615" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I615" t="s">
         <v>54</v>
       </c>
@@ -30372,7 +30302,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="616" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="616" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I616" t="s">
         <v>54</v>
       </c>
@@ -30410,7 +30340,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="617" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="617" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I617" t="s">
         <v>54</v>
       </c>
@@ -30448,7 +30378,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="618" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="618" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I618" t="s">
         <v>54</v>
       </c>
@@ -30486,7 +30416,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="619" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="619" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I619" t="s">
         <v>54</v>
       </c>
@@ -30524,7 +30454,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="620" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="620" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I620" t="s">
         <v>54</v>
       </c>
@@ -30562,7 +30492,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="621" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="621" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I621" t="s">
         <v>54</v>
       </c>
@@ -30600,7 +30530,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="622" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="622" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I622" t="s">
         <v>54</v>
       </c>
@@ -30638,7 +30568,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="623" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="623" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I623" t="s">
         <v>54</v>
       </c>
@@ -30676,7 +30606,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="624" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="624" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I624" t="s">
         <v>54</v>
       </c>
@@ -30714,7 +30644,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="625" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="625" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I625" t="s">
         <v>54</v>
       </c>
@@ -30752,7 +30682,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="626" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="626" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I626" t="s">
         <v>54</v>
       </c>
@@ -30790,7 +30720,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="627" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="627" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I627" t="s">
         <v>54</v>
       </c>
@@ -30828,7 +30758,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="628" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="628" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I628" t="s">
         <v>54</v>
       </c>
@@ -30866,7 +30796,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="629" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="629" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I629" t="s">
         <v>54</v>
       </c>
@@ -30904,7 +30834,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="630" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="630" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I630" t="s">
         <v>54</v>
       </c>
@@ -30942,7 +30872,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="631" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="631" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I631" t="s">
         <v>54</v>
       </c>
@@ -30980,7 +30910,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="632" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="632" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I632" t="s">
         <v>54</v>
       </c>
@@ -31018,7 +30948,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="633" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="633" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I633" t="s">
         <v>54</v>
       </c>
@@ -31056,7 +30986,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="634" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="634" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I634" t="s">
         <v>54</v>
       </c>
@@ -31094,7 +31024,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="635" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="635" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I635" t="s">
         <v>54</v>
       </c>
@@ -31132,7 +31062,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="636" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="636" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I636" t="s">
         <v>54</v>
       </c>
@@ -31170,7 +31100,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="637" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="637" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I637" t="s">
         <v>54</v>
       </c>
@@ -31208,7 +31138,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="638" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="638" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I638" t="s">
         <v>54</v>
       </c>
@@ -31246,7 +31176,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="639" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="639" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I639" t="s">
         <v>54</v>
       </c>
@@ -31284,7 +31214,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="640" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="640" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I640" t="s">
         <v>54</v>
       </c>
@@ -31322,7 +31252,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="641" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="641" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I641" t="s">
         <v>54</v>
       </c>
@@ -31360,7 +31290,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="642" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="642" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I642" t="s">
         <v>54</v>
       </c>
@@ -31398,7 +31328,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="643" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="643" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I643" t="s">
         <v>54</v>
       </c>
@@ -31436,7 +31366,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="644" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="644" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I644" t="s">
         <v>54</v>
       </c>
@@ -31474,7 +31404,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="645" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="645" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I645" t="s">
         <v>54</v>
       </c>
@@ -31512,7 +31442,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="646" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="646" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I646" t="s">
         <v>54</v>
       </c>
@@ -31550,7 +31480,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="647" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="647" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I647" t="s">
         <v>54</v>
       </c>
@@ -31588,7 +31518,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="648" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="648" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I648" t="s">
         <v>54</v>
       </c>
@@ -31626,7 +31556,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="649" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="649" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I649" t="s">
         <v>54</v>
       </c>
@@ -31664,7 +31594,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="650" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="650" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I650" t="s">
         <v>54</v>
       </c>
@@ -31702,7 +31632,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="651" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="651" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I651" t="s">
         <v>54</v>
       </c>
@@ -31740,7 +31670,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="652" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="652" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I652" t="s">
         <v>54</v>
       </c>
@@ -31778,7 +31708,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="653" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="653" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I653" t="s">
         <v>54</v>
       </c>
@@ -31816,7 +31746,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="654" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="654" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I654" t="s">
         <v>54</v>
       </c>
@@ -31854,7 +31784,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="655" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="655" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I655" t="s">
         <v>54</v>
       </c>
@@ -31892,7 +31822,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="656" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="656" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I656" t="s">
         <v>54</v>
       </c>
@@ -31930,7 +31860,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="657" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="657" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I657" t="s">
         <v>54</v>
       </c>
@@ -31968,7 +31898,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="658" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="658" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I658" t="s">
         <v>54</v>
       </c>
@@ -32006,7 +31936,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="659" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="659" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I659" t="s">
         <v>54</v>
       </c>
@@ -32044,7 +31974,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="660" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="660" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I660" t="s">
         <v>54</v>
       </c>
@@ -32082,7 +32012,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="661" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="661" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I661" t="s">
         <v>54</v>
       </c>
@@ -32120,7 +32050,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="662" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="662" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I662" t="s">
         <v>54</v>
       </c>
@@ -32158,7 +32088,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="663" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="663" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I663" t="s">
         <v>54</v>
       </c>
@@ -32196,7 +32126,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="664" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="664" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I664" t="s">
         <v>54</v>
       </c>
@@ -32234,7 +32164,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="665" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="665" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I665" t="s">
         <v>54</v>
       </c>
@@ -32272,7 +32202,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="666" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="666" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I666" t="s">
         <v>54</v>
       </c>
@@ -32310,7 +32240,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="667" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="667" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I667" t="s">
         <v>54</v>
       </c>
@@ -32348,7 +32278,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="668" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="668" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I668" t="s">
         <v>54</v>
       </c>
@@ -32386,7 +32316,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="669" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="669" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I669" t="s">
         <v>54</v>
       </c>
@@ -32424,7 +32354,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="670" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="670" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I670" t="s">
         <v>54</v>
       </c>
@@ -32462,7 +32392,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="671" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="671" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I671" t="s">
         <v>54</v>
       </c>
@@ -32500,7 +32430,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="672" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="672" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I672" t="s">
         <v>54</v>
       </c>
@@ -32538,7 +32468,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="673" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="673" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I673" t="s">
         <v>54</v>
       </c>
@@ -32576,7 +32506,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="674" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="674" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I674" t="s">
         <v>54</v>
       </c>
@@ -32614,7 +32544,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="675" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="675" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I675" t="s">
         <v>57</v>
       </c>
@@ -32652,7 +32582,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="676" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="676" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I676" t="s">
         <v>57</v>
       </c>
@@ -32690,7 +32620,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="677" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="677" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I677" t="s">
         <v>57</v>
       </c>
@@ -32728,7 +32658,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="678" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="678" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I678" t="s">
         <v>57</v>
       </c>
@@ -32766,7 +32696,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="679" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="679" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I679" t="s">
         <v>57</v>
       </c>
@@ -32804,7 +32734,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="680" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="680" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I680" t="s">
         <v>57</v>
       </c>
@@ -32842,7 +32772,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="681" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="681" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I681" t="s">
         <v>57</v>
       </c>
@@ -32880,7 +32810,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="682" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="682" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I682" t="s">
         <v>57</v>
       </c>
@@ -32918,7 +32848,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="683" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="683" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I683" t="s">
         <v>57</v>
       </c>
@@ -32956,7 +32886,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="684" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="684" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I684" t="s">
         <v>57</v>
       </c>
@@ -32994,7 +32924,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="685" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="685" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I685" t="s">
         <v>57</v>
       </c>
@@ -33032,7 +32962,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="686" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="686" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I686" t="s">
         <v>57</v>
       </c>
@@ -33070,7 +33000,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="687" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="687" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I687" t="s">
         <v>57</v>
       </c>
@@ -33108,7 +33038,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="688" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="688" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I688" t="s">
         <v>57</v>
       </c>
@@ -33146,7 +33076,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="689" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="689" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I689" t="s">
         <v>57</v>
       </c>
@@ -33184,7 +33114,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="690" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="690" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I690" t="s">
         <v>57</v>
       </c>
@@ -33222,7 +33152,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="691" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="691" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I691" t="s">
         <v>57</v>
       </c>
@@ -33260,7 +33190,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="692" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="692" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I692" t="s">
         <v>57</v>
       </c>
@@ -33298,7 +33228,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="693" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="693" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I693" t="s">
         <v>57</v>
       </c>
@@ -33336,7 +33266,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="694" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="694" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I694" t="s">
         <v>57</v>
       </c>
@@ -33374,7 +33304,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="695" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="695" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I695" t="s">
         <v>57</v>
       </c>
@@ -33412,7 +33342,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="696" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="696" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I696" t="s">
         <v>57</v>
       </c>
@@ -33450,7 +33380,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="697" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="697" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I697" t="s">
         <v>57</v>
       </c>
@@ -33488,7 +33418,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="698" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="698" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I698" t="s">
         <v>57</v>
       </c>
@@ -33526,7 +33456,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="699" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="699" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I699" t="s">
         <v>57</v>
       </c>
@@ -33564,7 +33494,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="700" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="700" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I700" t="s">
         <v>57</v>
       </c>
@@ -33602,7 +33532,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="701" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="701" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I701" t="s">
         <v>57</v>
       </c>
@@ -33640,7 +33570,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="702" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="702" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I702" t="s">
         <v>57</v>
       </c>
@@ -33678,7 +33608,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="703" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="703" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I703" t="s">
         <v>57</v>
       </c>
@@ -33716,7 +33646,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="704" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="704" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I704" t="s">
         <v>57</v>
       </c>
@@ -33754,7 +33684,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="705" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="705" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I705" t="s">
         <v>57</v>
       </c>
@@ -33792,7 +33722,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="706" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="706" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I706" t="s">
         <v>57</v>
       </c>
@@ -33830,7 +33760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="707" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="707" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I707" t="s">
         <v>57</v>
       </c>
@@ -33868,7 +33798,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="708" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="708" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I708" t="s">
         <v>57</v>
       </c>
@@ -33906,7 +33836,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="709" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="709" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I709" t="s">
         <v>57</v>
       </c>
@@ -33944,7 +33874,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="710" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="710" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I710" t="s">
         <v>57</v>
       </c>
@@ -33982,7 +33912,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="711" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="711" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I711" t="s">
         <v>57</v>
       </c>
@@ -34020,7 +33950,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="712" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="712" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I712" t="s">
         <v>57</v>
       </c>
@@ -34058,7 +33988,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="713" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="713" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I713" t="s">
         <v>57</v>
       </c>
@@ -34096,7 +34026,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="714" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="714" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I714" t="s">
         <v>57</v>
       </c>
@@ -34134,7 +34064,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="715" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="715" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I715" t="s">
         <v>57</v>
       </c>
@@ -34172,7 +34102,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="716" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="716" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I716" t="s">
         <v>57</v>
       </c>
@@ -34210,7 +34140,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="717" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="717" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I717" t="s">
         <v>57</v>
       </c>
@@ -34248,7 +34178,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="718" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="718" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I718" t="s">
         <v>57</v>
       </c>
@@ -34286,7 +34216,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="719" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="719" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I719" t="s">
         <v>57</v>
       </c>
@@ -34324,7 +34254,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="720" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="720" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I720" t="s">
         <v>57</v>
       </c>
@@ -34362,7 +34292,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="721" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="721" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I721" t="s">
         <v>57</v>
       </c>
@@ -34400,7 +34330,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="722" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="722" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I722" t="s">
         <v>57</v>
       </c>
@@ -34438,7 +34368,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="723" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="723" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I723" t="s">
         <v>57</v>
       </c>
@@ -34476,7 +34406,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="724" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="724" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I724" t="s">
         <v>57</v>
       </c>
@@ -34514,7 +34444,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="725" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="725" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I725" t="s">
         <v>57</v>
       </c>
@@ -34552,7 +34482,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="726" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="726" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I726" t="s">
         <v>57</v>
       </c>
@@ -34590,7 +34520,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="727" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="727" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I727" t="s">
         <v>57</v>
       </c>
@@ -34628,7 +34558,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="728" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="728" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I728" t="s">
         <v>57</v>
       </c>
@@ -34666,7 +34596,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="729" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="729" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I729" t="s">
         <v>57</v>
       </c>
@@ -34704,7 +34634,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="730" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="730" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I730" t="s">
         <v>57</v>
       </c>
@@ -34742,7 +34672,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="731" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="731" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I731" t="s">
         <v>57</v>
       </c>
@@ -34780,7 +34710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="732" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="732" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I732" t="s">
         <v>57</v>
       </c>
@@ -34818,7 +34748,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="733" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="733" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I733" t="s">
         <v>57</v>
       </c>
@@ -34856,7 +34786,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="734" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="734" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I734" t="s">
         <v>57</v>
       </c>
@@ -34894,7 +34824,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="735" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="735" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I735" t="s">
         <v>57</v>
       </c>
@@ -34932,7 +34862,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="736" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="736" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I736" t="s">
         <v>57</v>
       </c>
@@ -34970,7 +34900,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="737" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="737" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I737" t="s">
         <v>57</v>
       </c>
@@ -35008,7 +34938,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="738" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="738" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I738" t="s">
         <v>57</v>
       </c>
@@ -35046,7 +34976,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="739" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="739" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I739" t="s">
         <v>57</v>
       </c>
@@ -35084,7 +35014,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="740" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="740" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I740" t="s">
         <v>57</v>
       </c>
@@ -35122,7 +35052,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="741" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="741" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I741" t="s">
         <v>57</v>
       </c>
@@ -35160,7 +35090,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="742" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="742" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I742" t="s">
         <v>57</v>
       </c>
@@ -35198,7 +35128,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="743" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="743" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I743" t="s">
         <v>57</v>
       </c>
@@ -35236,7 +35166,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="744" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="744" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I744" t="s">
         <v>57</v>
       </c>
@@ -35274,7 +35204,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="745" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="745" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I745" t="s">
         <v>57</v>
       </c>
@@ -35312,7 +35242,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="746" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="746" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I746" t="s">
         <v>57</v>
       </c>
@@ -35350,7 +35280,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="747" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="747" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I747" t="s">
         <v>57</v>
       </c>
@@ -35388,7 +35318,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="748" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="748" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I748" t="s">
         <v>57</v>
       </c>
@@ -35426,7 +35356,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="749" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="749" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I749" t="s">
         <v>57</v>
       </c>
@@ -35464,7 +35394,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="750" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="750" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I750" t="s">
         <v>57</v>
       </c>
@@ -35502,7 +35432,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="751" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="751" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I751" t="s">
         <v>57</v>
       </c>
@@ -35540,7 +35470,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="752" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="752" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I752" t="s">
         <v>57</v>
       </c>
@@ -35578,7 +35508,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="753" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="753" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I753" t="s">
         <v>57</v>
       </c>
@@ -35616,7 +35546,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="754" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="754" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I754" t="s">
         <v>57</v>
       </c>
@@ -35654,7 +35584,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="755" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="755" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I755" t="s">
         <v>57</v>
       </c>
@@ -35692,7 +35622,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="756" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="756" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I756" t="s">
         <v>57</v>
       </c>
@@ -35730,7 +35660,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="757" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="757" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I757" t="s">
         <v>57</v>
       </c>
@@ -35768,7 +35698,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="758" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="758" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I758" t="s">
         <v>57</v>
       </c>
@@ -35806,7 +35736,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="759" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="759" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I759" t="s">
         <v>57</v>
       </c>
@@ -35844,7 +35774,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="760" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="760" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I760" t="s">
         <v>57</v>
       </c>
@@ -35882,7 +35812,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="761" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="761" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I761" t="s">
         <v>57</v>
       </c>
@@ -35920,7 +35850,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="762" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="762" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I762" t="s">
         <v>57</v>
       </c>
@@ -35958,7 +35888,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="763" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="763" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I763" t="s">
         <v>57</v>
       </c>
@@ -35996,7 +35926,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="764" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="764" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I764" t="s">
         <v>57</v>
       </c>
@@ -36034,7 +35964,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="765" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="765" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I765" t="s">
         <v>57</v>
       </c>
@@ -36072,7 +36002,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="766" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="766" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I766" t="s">
         <v>57</v>
       </c>
@@ -36110,7 +36040,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="767" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="767" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I767" t="s">
         <v>57</v>
       </c>
@@ -36148,7 +36078,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="768" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="768" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I768" t="s">
         <v>57</v>
       </c>
@@ -36186,7 +36116,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="769" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="769" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I769" t="s">
         <v>57</v>
       </c>
@@ -36224,7 +36154,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="770" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="770" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I770" t="s">
         <v>57</v>
       </c>
@@ -36262,7 +36192,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="771" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="771" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I771" t="s">
         <v>60</v>
       </c>
@@ -36300,7 +36230,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="772" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="772" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I772" t="s">
         <v>60</v>
       </c>
@@ -36338,7 +36268,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="773" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="773" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I773" t="s">
         <v>60</v>
       </c>
@@ -36376,7 +36306,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="774" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="774" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I774" t="s">
         <v>60</v>
       </c>
@@ -36414,7 +36344,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="775" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="775" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I775" t="s">
         <v>60</v>
       </c>
@@ -36452,7 +36382,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="776" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="776" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I776" t="s">
         <v>60</v>
       </c>
@@ -36490,7 +36420,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="777" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="777" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I777" t="s">
         <v>60</v>
       </c>
@@ -36528,7 +36458,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="778" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="778" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I778" t="s">
         <v>60</v>
       </c>
@@ -36566,7 +36496,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="779" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="779" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I779" t="s">
         <v>60</v>
       </c>
@@ -36604,7 +36534,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="780" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="780" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I780" t="s">
         <v>60</v>
       </c>
@@ -36642,7 +36572,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="781" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="781" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I781" t="s">
         <v>60</v>
       </c>
@@ -36680,7 +36610,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="782" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="782" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I782" t="s">
         <v>60</v>
       </c>
@@ -36718,7 +36648,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="783" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="783" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I783" t="s">
         <v>60</v>
       </c>
@@ -36756,7 +36686,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="784" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="784" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I784" t="s">
         <v>60</v>
       </c>
@@ -36794,7 +36724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="785" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="785" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I785" t="s">
         <v>60</v>
       </c>
@@ -36832,7 +36762,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="786" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="786" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I786" t="s">
         <v>60</v>
       </c>
@@ -36870,7 +36800,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="787" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="787" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I787" t="s">
         <v>60</v>
       </c>
@@ -36908,7 +36838,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="788" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="788" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I788" t="s">
         <v>60</v>
       </c>
@@ -36946,7 +36876,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="789" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="789" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I789" t="s">
         <v>60</v>
       </c>
@@ -36984,7 +36914,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="790" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="790" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I790" t="s">
         <v>60</v>
       </c>
@@ -37022,7 +36952,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="791" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="791" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I791" t="s">
         <v>60</v>
       </c>
@@ -37060,7 +36990,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="792" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="792" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I792" t="s">
         <v>60</v>
       </c>
@@ -37098,7 +37028,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="793" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="793" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I793" t="s">
         <v>60</v>
       </c>
@@ -37136,7 +37066,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="794" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="794" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I794" t="s">
         <v>60</v>
       </c>
@@ -37174,7 +37104,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="795" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="795" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I795" t="s">
         <v>60</v>
       </c>
@@ -37212,7 +37142,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="796" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="796" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I796" t="s">
         <v>60</v>
       </c>
@@ -37250,7 +37180,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="797" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="797" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I797" t="s">
         <v>60</v>
       </c>
@@ -37288,7 +37218,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="798" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="798" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I798" t="s">
         <v>60</v>
       </c>
@@ -37326,7 +37256,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="799" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="799" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I799" t="s">
         <v>60</v>
       </c>
@@ -37364,7 +37294,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="800" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="800" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I800" t="s">
         <v>60</v>
       </c>
@@ -37402,7 +37332,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="801" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="801" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I801" t="s">
         <v>60</v>
       </c>
@@ -37440,7 +37370,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="802" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="802" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I802" t="s">
         <v>60</v>
       </c>
@@ -37478,7 +37408,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="803" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="803" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I803" t="s">
         <v>60</v>
       </c>
@@ -37516,7 +37446,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="804" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="804" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I804" t="s">
         <v>60</v>
       </c>
@@ -37554,7 +37484,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="805" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="805" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I805" t="s">
         <v>60</v>
       </c>
@@ -37592,7 +37522,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="806" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="806" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I806" t="s">
         <v>60</v>
       </c>
@@ -37630,7 +37560,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="807" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="807" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I807" t="s">
         <v>60</v>
       </c>
@@ -37668,7 +37598,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="808" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="808" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I808" t="s">
         <v>60</v>
       </c>
@@ -37706,7 +37636,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="809" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="809" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I809" t="s">
         <v>60</v>
       </c>
@@ -37744,7 +37674,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="810" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="810" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I810" t="s">
         <v>60</v>
       </c>
@@ -37782,7 +37712,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="811" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="811" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I811" t="s">
         <v>60</v>
       </c>
@@ -37820,7 +37750,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="812" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="812" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I812" t="s">
         <v>60</v>
       </c>
@@ -37858,7 +37788,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="813" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="813" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I813" t="s">
         <v>60</v>
       </c>
@@ -37896,7 +37826,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="814" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="814" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I814" t="s">
         <v>60</v>
       </c>
@@ -37934,7 +37864,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="815" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="815" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I815" t="s">
         <v>60</v>
       </c>
@@ -37972,7 +37902,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="816" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="816" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I816" t="s">
         <v>60</v>
       </c>
@@ -38010,7 +37940,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="817" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="817" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I817" t="s">
         <v>60</v>
       </c>
@@ -38048,7 +37978,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="818" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="818" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I818" t="s">
         <v>60</v>
       </c>
@@ -38086,7 +38016,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="819" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="819" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I819" t="s">
         <v>60</v>
       </c>
@@ -38124,7 +38054,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="820" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="820" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I820" t="s">
         <v>60</v>
       </c>
@@ -38162,7 +38092,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="821" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="821" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I821" t="s">
         <v>60</v>
       </c>
@@ -38200,7 +38130,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="822" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="822" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I822" t="s">
         <v>60</v>
       </c>
@@ -38238,7 +38168,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="823" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="823" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I823" t="s">
         <v>60</v>
       </c>
@@ -38276,7 +38206,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="824" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="824" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I824" t="s">
         <v>60</v>
       </c>
@@ -38314,7 +38244,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="825" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="825" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I825" t="s">
         <v>60</v>
       </c>
@@ -38352,7 +38282,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="826" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="826" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I826" t="s">
         <v>60</v>
       </c>
@@ -38390,7 +38320,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="827" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="827" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I827" t="s">
         <v>60</v>
       </c>
@@ -38428,7 +38358,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="828" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="828" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I828" t="s">
         <v>60</v>
       </c>
@@ -38466,7 +38396,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="829" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="829" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I829" t="s">
         <v>60</v>
       </c>
@@ -38504,7 +38434,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="830" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="830" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I830" t="s">
         <v>60</v>
       </c>
@@ -38542,7 +38472,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="831" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="831" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I831" t="s">
         <v>60</v>
       </c>
@@ -38580,7 +38510,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="832" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="832" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I832" t="s">
         <v>60</v>
       </c>
@@ -38618,7 +38548,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="833" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="833" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I833" t="s">
         <v>60</v>
       </c>
@@ -38656,7 +38586,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="834" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="834" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I834" t="s">
         <v>60</v>
       </c>
@@ -38694,7 +38624,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="835" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="835" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I835" t="s">
         <v>60</v>
       </c>
@@ -38732,7 +38662,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="836" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="836" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I836" t="s">
         <v>60</v>
       </c>
@@ -38770,7 +38700,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="837" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="837" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I837" t="s">
         <v>60</v>
       </c>
@@ -38808,7 +38738,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="838" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="838" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I838" t="s">
         <v>60</v>
       </c>
@@ -38846,7 +38776,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="839" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="839" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I839" t="s">
         <v>60</v>
       </c>
@@ -38884,7 +38814,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="840" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="840" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I840" t="s">
         <v>60</v>
       </c>
@@ -38922,7 +38852,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="841" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="841" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I841" t="s">
         <v>60</v>
       </c>
@@ -38960,7 +38890,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="842" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="842" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I842" t="s">
         <v>60</v>
       </c>
@@ -38998,7 +38928,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="843" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="843" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I843" t="s">
         <v>60</v>
       </c>
@@ -39036,7 +38966,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="844" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="844" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I844" t="s">
         <v>60</v>
       </c>
@@ -39074,7 +39004,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="845" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="845" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I845" t="s">
         <v>60</v>
       </c>
@@ -39112,7 +39042,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="846" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="846" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I846" t="s">
         <v>60</v>
       </c>
@@ -39150,7 +39080,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="847" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="847" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I847" t="s">
         <v>60</v>
       </c>
@@ -39188,7 +39118,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="848" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="848" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I848" t="s">
         <v>60</v>
       </c>
@@ -39226,7 +39156,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="849" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="849" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I849" t="s">
         <v>60</v>
       </c>
@@ -39264,7 +39194,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="850" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="850" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I850" t="s">
         <v>60</v>
       </c>
@@ -39302,7 +39232,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="851" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="851" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I851" t="s">
         <v>60</v>
       </c>
@@ -39340,7 +39270,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="852" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="852" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I852" t="s">
         <v>60</v>
       </c>
@@ -39378,7 +39308,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="853" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="853" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I853" t="s">
         <v>60</v>
       </c>
@@ -39416,7 +39346,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="854" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="854" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I854" t="s">
         <v>60</v>
       </c>
@@ -39454,7 +39384,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="855" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="855" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I855" t="s">
         <v>60</v>
       </c>
@@ -39492,7 +39422,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="856" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="856" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I856" t="s">
         <v>60</v>
       </c>
@@ -39530,7 +39460,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="857" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="857" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I857" t="s">
         <v>60</v>
       </c>
@@ -39568,7 +39498,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="858" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="858" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I858" t="s">
         <v>60</v>
       </c>
@@ -39606,7 +39536,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="859" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="859" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I859" t="s">
         <v>60</v>
       </c>
@@ -39644,7 +39574,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="860" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="860" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I860" t="s">
         <v>60</v>
       </c>
@@ -39682,7 +39612,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="861" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="861" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I861" t="s">
         <v>60</v>
       </c>
@@ -39720,7 +39650,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="862" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="862" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I862" t="s">
         <v>60</v>
       </c>
@@ -39758,7 +39688,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="863" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="863" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I863" t="s">
         <v>60</v>
       </c>
@@ -39796,7 +39726,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="864" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="864" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I864" t="s">
         <v>60</v>
       </c>
@@ -39834,7 +39764,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="865" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="865" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I865" t="s">
         <v>60</v>
       </c>
@@ -39872,7 +39802,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="866" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="866" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I866" t="s">
         <v>60</v>
       </c>
@@ -39910,7 +39840,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="867" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="867" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I867" t="s">
         <v>63</v>
       </c>
@@ -39948,7 +39878,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="868" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="868" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I868" t="s">
         <v>63</v>
       </c>
@@ -39986,7 +39916,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="869" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="869" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I869" t="s">
         <v>63</v>
       </c>
@@ -40024,7 +39954,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="870" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="870" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I870" t="s">
         <v>63</v>
       </c>
@@ -40062,7 +39992,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="871" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="871" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I871" t="s">
         <v>63</v>
       </c>
@@ -40100,7 +40030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="872" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="872" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I872" t="s">
         <v>63</v>
       </c>
@@ -40138,7 +40068,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="873" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="873" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I873" t="s">
         <v>63</v>
       </c>
@@ -40176,7 +40106,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="874" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="874" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I874" t="s">
         <v>63</v>
       </c>
@@ -40214,7 +40144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="875" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="875" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I875" t="s">
         <v>63</v>
       </c>
@@ -40252,7 +40182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="876" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="876" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I876" t="s">
         <v>63</v>
       </c>
@@ -40290,7 +40220,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="877" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="877" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I877" t="s">
         <v>63</v>
       </c>
@@ -40328,7 +40258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="878" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="878" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I878" t="s">
         <v>63</v>
       </c>
@@ -40366,7 +40296,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="879" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="879" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I879" t="s">
         <v>63</v>
       </c>
@@ -40404,7 +40334,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="880" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="880" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I880" t="s">
         <v>63</v>
       </c>
@@ -40442,7 +40372,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="881" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="881" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I881" t="s">
         <v>63</v>
       </c>
@@ -40480,7 +40410,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="882" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="882" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I882" t="s">
         <v>63</v>
       </c>
@@ -40518,7 +40448,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="883" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="883" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I883" t="s">
         <v>63</v>
       </c>
@@ -40556,7 +40486,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="884" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="884" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I884" t="s">
         <v>63</v>
       </c>
@@ -40594,7 +40524,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="885" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="885" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I885" t="s">
         <v>63</v>
       </c>
@@ -40632,7 +40562,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="886" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="886" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I886" t="s">
         <v>63</v>
       </c>
@@ -40670,7 +40600,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="887" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="887" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I887" t="s">
         <v>63</v>
       </c>
@@ -40708,7 +40638,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="888" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="888" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I888" t="s">
         <v>63</v>
       </c>
@@ -40746,7 +40676,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="889" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="889" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I889" t="s">
         <v>63</v>
       </c>
@@ -40784,7 +40714,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="890" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="890" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I890" t="s">
         <v>63</v>
       </c>
@@ -40822,7 +40752,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="891" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="891" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I891" t="s">
         <v>63</v>
       </c>
@@ -40860,7 +40790,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="892" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="892" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I892" t="s">
         <v>63</v>
       </c>
@@ -40898,7 +40828,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="893" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="893" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I893" t="s">
         <v>63</v>
       </c>
@@ -40936,7 +40866,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="894" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="894" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I894" t="s">
         <v>63</v>
       </c>
@@ -40974,7 +40904,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="895" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="895" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I895" t="s">
         <v>63</v>
       </c>
@@ -41012,7 +40942,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="896" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="896" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I896" t="s">
         <v>63</v>
       </c>
@@ -41050,7 +40980,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="897" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="897" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I897" t="s">
         <v>63</v>
       </c>
@@ -41088,7 +41018,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="898" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="898" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I898" t="s">
         <v>63</v>
       </c>
@@ -41126,7 +41056,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="899" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="899" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I899" t="s">
         <v>63</v>
       </c>
@@ -41164,7 +41094,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="900" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="900" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I900" t="s">
         <v>63</v>
       </c>
@@ -41202,7 +41132,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="901" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="901" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I901" t="s">
         <v>63</v>
       </c>
@@ -41240,7 +41170,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="902" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="902" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I902" t="s">
         <v>63</v>
       </c>
@@ -41278,7 +41208,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="903" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="903" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I903" t="s">
         <v>63</v>
       </c>
@@ -41316,7 +41246,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="904" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="904" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I904" t="s">
         <v>63</v>
       </c>
@@ -41354,7 +41284,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="905" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="905" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I905" t="s">
         <v>63</v>
       </c>
@@ -41392,7 +41322,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="906" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="906" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I906" t="s">
         <v>63</v>
       </c>
@@ -41430,7 +41360,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="907" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="907" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I907" t="s">
         <v>63</v>
       </c>
@@ -41468,7 +41398,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="908" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="908" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I908" t="s">
         <v>63</v>
       </c>
@@ -41506,7 +41436,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="909" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="909" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I909" t="s">
         <v>63</v>
       </c>
@@ -41544,7 +41474,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="910" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="910" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I910" t="s">
         <v>63</v>
       </c>
@@ -41582,7 +41512,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="911" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="911" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I911" t="s">
         <v>63</v>
       </c>
@@ -41620,7 +41550,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="912" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="912" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I912" t="s">
         <v>63</v>
       </c>
@@ -41658,7 +41588,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="913" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="913" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I913" t="s">
         <v>63</v>
       </c>
@@ -41696,7 +41626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="914" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="914" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I914" t="s">
         <v>63</v>
       </c>
@@ -41734,7 +41664,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="915" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="915" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I915" t="s">
         <v>63</v>
       </c>
@@ -41772,7 +41702,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="916" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="916" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I916" t="s">
         <v>63</v>
       </c>
@@ -41810,7 +41740,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="917" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="917" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I917" t="s">
         <v>63</v>
       </c>
@@ -41848,7 +41778,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="918" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="918" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I918" t="s">
         <v>63</v>
       </c>
@@ -41886,7 +41816,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="919" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="919" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I919" t="s">
         <v>63</v>
       </c>
@@ -41924,7 +41854,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="920" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="920" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I920" t="s">
         <v>63</v>
       </c>
@@ -41962,7 +41892,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="921" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="921" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I921" t="s">
         <v>63</v>
       </c>
@@ -42000,7 +41930,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="922" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="922" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I922" t="s">
         <v>63</v>
       </c>
@@ -42038,7 +41968,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="923" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="923" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I923" t="s">
         <v>63</v>
       </c>
@@ -42076,7 +42006,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="924" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="924" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I924" t="s">
         <v>63</v>
       </c>
@@ -42114,7 +42044,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="925" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="925" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I925" t="s">
         <v>63</v>
       </c>
@@ -42152,7 +42082,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="926" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="926" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I926" t="s">
         <v>63</v>
       </c>
@@ -42190,7 +42120,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="927" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="927" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I927" t="s">
         <v>63</v>
       </c>
@@ -42228,7 +42158,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="928" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="928" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I928" t="s">
         <v>63</v>
       </c>
@@ -42266,7 +42196,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="929" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="929" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I929" t="s">
         <v>63</v>
       </c>
@@ -42304,7 +42234,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="930" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="930" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I930" t="s">
         <v>63</v>
       </c>
@@ -42342,7 +42272,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="931" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="931" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I931" t="s">
         <v>63</v>
       </c>
@@ -42380,7 +42310,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="932" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="932" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I932" t="s">
         <v>63</v>
       </c>
@@ -42418,7 +42348,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="933" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="933" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I933" t="s">
         <v>63</v>
       </c>
@@ -42456,7 +42386,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="934" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="934" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I934" t="s">
         <v>63</v>
       </c>
@@ -42494,7 +42424,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="935" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="935" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I935" t="s">
         <v>63</v>
       </c>
@@ -42532,7 +42462,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="936" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="936" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I936" t="s">
         <v>63</v>
       </c>
@@ -42570,7 +42500,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="937" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="937" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I937" t="s">
         <v>63</v>
       </c>
@@ -42608,7 +42538,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="938" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="938" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I938" t="s">
         <v>63</v>
       </c>
@@ -42646,7 +42576,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="939" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="939" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I939" t="s">
         <v>63</v>
       </c>
@@ -42684,7 +42614,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="940" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="940" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I940" t="s">
         <v>63</v>
       </c>
@@ -42722,7 +42652,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="941" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="941" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I941" t="s">
         <v>63</v>
       </c>
@@ -42760,7 +42690,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="942" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="942" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I942" t="s">
         <v>63</v>
       </c>
@@ -42798,7 +42728,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="943" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="943" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I943" t="s">
         <v>63</v>
       </c>
@@ -42836,7 +42766,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="944" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="944" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I944" t="s">
         <v>63</v>
       </c>
@@ -42874,7 +42804,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="945" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="945" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I945" t="s">
         <v>63</v>
       </c>
@@ -42912,7 +42842,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="946" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="946" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I946" t="s">
         <v>63</v>
       </c>
@@ -42950,7 +42880,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="947" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="947" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I947" t="s">
         <v>63</v>
       </c>
@@ -42988,7 +42918,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="948" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="948" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I948" t="s">
         <v>63</v>
       </c>
@@ -43026,7 +42956,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="949" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="949" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I949" t="s">
         <v>63</v>
       </c>
@@ -43064,7 +42994,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="950" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="950" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I950" t="s">
         <v>63</v>
       </c>
@@ -43102,7 +43032,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="951" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="951" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I951" t="s">
         <v>63</v>
       </c>
@@ -43140,7 +43070,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="952" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="952" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I952" t="s">
         <v>63</v>
       </c>
@@ -43178,7 +43108,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="953" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="953" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I953" t="s">
         <v>63</v>
       </c>
@@ -43216,7 +43146,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="954" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="954" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I954" t="s">
         <v>63</v>
       </c>
@@ -43254,7 +43184,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="955" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="955" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I955" t="s">
         <v>63</v>
       </c>
@@ -43292,7 +43222,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="956" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="956" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I956" t="s">
         <v>63</v>
       </c>
@@ -43330,7 +43260,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="957" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="957" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I957" t="s">
         <v>63</v>
       </c>
@@ -43368,7 +43298,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="958" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="958" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I958" t="s">
         <v>63</v>
       </c>
@@ -43406,7 +43336,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="959" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="959" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I959" t="s">
         <v>63</v>
       </c>
@@ -43444,7 +43374,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="960" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="960" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I960" t="s">
         <v>63</v>
       </c>
@@ -43482,7 +43412,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="961" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="961" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I961" t="s">
         <v>63</v>
       </c>
@@ -43520,7 +43450,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="962" spans="9:22" x14ac:dyDescent="0.25">
+    <row r="962" spans="9:22" x14ac:dyDescent="0.35">
       <c r="I962" t="s">
         <v>63</v>
       </c>
@@ -43567,24 +43497,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0448EE0-6EB3-49B4-88D9-D0F0750B940D}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -43610,7 +43540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -43636,7 +43566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -43662,7 +43592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>95</v>
       </c>
@@ -43685,7 +43615,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -43711,7 +43641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -43745,19 +43675,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A318F2-D986-4B43-9E10-D5047049B529}">
   <dimension ref="A3:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -43768,7 +43698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>98</v>
       </c>
@@ -43779,17 +43709,17 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>119</v>
       </c>
@@ -43806,7 +43736,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>263</v>
       </c>
@@ -43820,7 +43750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>87</v>
       </c>
@@ -43828,7 +43758,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>265</v>
       </c>
@@ -43842,7 +43772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>267</v>
       </c>
@@ -43858,13 +43788,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0573AE-84FA-4F18-8D18-B7F3EC5B3273}">
   <dimension ref="B4:Y18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="43.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>277</v>
       </c>
@@ -43872,7 +43802,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -43928,7 +43858,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>272</v>
       </c>
@@ -43969,7 +43899,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>273</v>
       </c>
@@ -44010,7 +43940,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>274</v>
       </c>
@@ -44058,7 +43988,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>275</v>
       </c>
@@ -44082,12 +44012,12 @@
         <v>3218.5</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>11</v>
       </c>
@@ -44116,7 +44046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>272</v>
       </c>
@@ -44154,7 +44084,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>273</v>
       </c>
@@ -44189,7 +44119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>278</v>
       </c>
@@ -44218,7 +44148,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>274</v>
       </c>
@@ -44253,7 +44183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>275</v>
       </c>
@@ -44288,7 +44218,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>279</v>
       </c>
@@ -44328,31 +44258,31 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BDE16D-C995-4313-9FD3-ABCD01C0EB3D}">
   <dimension ref="B5:W20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>1</v>
       </c>
@@ -44378,7 +44308,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>15</v>
       </c>
@@ -44409,7 +44339,7 @@
         <v>35.819287365996651</v>
       </c>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -44440,7 +44370,7 @@
         <v>87.108237397170171</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -44466,7 +44396,7 @@
         <v>60.419999999999995</v>
       </c>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>18</v>
       </c>
@@ -44492,12 +44422,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.35">
       <c r="E13">
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.35">
       <c r="K16" t="s">
         <v>116</v>
       </c>
@@ -44532,7 +44462,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="11:23" x14ac:dyDescent="0.35">
       <c r="K17">
         <v>4.1840000000000002</v>
       </c>
@@ -44573,7 +44503,7 @@
         <v>46470588.235294119</v>
       </c>
     </row>
-    <row r="18" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="11:23" x14ac:dyDescent="0.35">
       <c r="P18" t="s">
         <v>107</v>
       </c>
@@ -44599,7 +44529,7 @@
         <v>35145058.821884029</v>
       </c>
     </row>
-    <row r="19" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="11:23" x14ac:dyDescent="0.35">
       <c r="P19" t="s">
         <v>108</v>
       </c>
@@ -44625,7 +44555,7 @@
         <v>96367112.810707465</v>
       </c>
     </row>
-    <row r="20" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="11:23" x14ac:dyDescent="0.35">
       <c r="S20" t="s">
         <v>117</v>
       </c>
@@ -44645,26 +44575,26 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1758F-E590-4DA8-B461-246947AA96DE}">
   <dimension ref="A2:I16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D5" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -44693,7 +44623,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -44713,7 +44643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>131</v>
       </c>
@@ -44727,7 +44657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>127</v>
       </c>
@@ -44744,7 +44674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>126</v>
       </c>
@@ -44767,7 +44697,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>127</v>
       </c>
@@ -44779,304 +44709,6 @@
       </c>
       <c r="G16">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A2DF39-3B67-43CD-A73F-8B3848EF882D}">
-  <dimension ref="A3:D23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B5">
-        <v>1.106001</v>
-      </c>
-      <c r="C5">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D5">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B6">
-        <v>1.106001</v>
-      </c>
-      <c r="C6">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D6">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B7">
-        <v>1.106001</v>
-      </c>
-      <c r="C7">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D7">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>287</v>
-      </c>
-      <c r="B8">
-        <v>1.106001</v>
-      </c>
-      <c r="C8">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D8">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>288</v>
-      </c>
-      <c r="B9">
-        <v>1.106001</v>
-      </c>
-      <c r="C9">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D9">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>289</v>
-      </c>
-      <c r="B10">
-        <v>1.106001</v>
-      </c>
-      <c r="C10">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D10">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>290</v>
-      </c>
-      <c r="B11">
-        <v>1.106001</v>
-      </c>
-      <c r="C11">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D11">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12">
-        <v>1.106001</v>
-      </c>
-      <c r="C12">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D12">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13">
-        <v>1.106001</v>
-      </c>
-      <c r="C13">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D13">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14">
-        <v>1.106001</v>
-      </c>
-      <c r="C14">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D14">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>294</v>
-      </c>
-      <c r="B15">
-        <v>1.106001</v>
-      </c>
-      <c r="C15">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D15">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>295</v>
-      </c>
-      <c r="B16">
-        <v>1.106001</v>
-      </c>
-      <c r="C16">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D16">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>296</v>
-      </c>
-      <c r="B17">
-        <v>1.106001</v>
-      </c>
-      <c r="C17">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D17">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>297</v>
-      </c>
-      <c r="B18">
-        <v>1.106001</v>
-      </c>
-      <c r="C18">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D18">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>298</v>
-      </c>
-      <c r="B19">
-        <v>1.106001</v>
-      </c>
-      <c r="C19">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D19">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>299</v>
-      </c>
-      <c r="B20">
-        <v>1.106001</v>
-      </c>
-      <c r="C20">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D20">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>300</v>
-      </c>
-      <c r="B21">
-        <v>1.106001</v>
-      </c>
-      <c r="C21">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D21">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>301</v>
-      </c>
-      <c r="B22">
-        <v>1.106001</v>
-      </c>
-      <c r="C22">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D22">
-        <v>0.99885999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>302</v>
-      </c>
-      <c r="B23">
-        <v>1.106001</v>
-      </c>
-      <c r="C23">
-        <v>20.900000000000002</v>
-      </c>
-      <c r="D23">
-        <v>0.99885999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92C852F-A98A-483E-86C2-D3FE1562D90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5844505-75F8-445B-9F2C-AA75094ABD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9971" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9957" uniqueCount="295">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -903,12 +903,6 @@
     <t>fx</t>
   </si>
   <si>
-    <t>Trd_electricity import_ru</t>
-  </si>
-  <si>
-    <t>Trd_electricity export_ru</t>
-  </si>
-  <si>
     <t>2022</t>
   </si>
   <si>
@@ -948,12 +942,6 @@
     <t>Import capacity to Latvia interconnector in GW</t>
   </si>
   <si>
-    <t>Trd_elc_imp_ru</t>
-  </si>
-  <si>
-    <t>Russia imports disabled after 2022/2025 in current assumptions</t>
-  </si>
-  <si>
     <t>Trd_elc_exp_fi</t>
   </si>
   <si>
@@ -964,12 +952,6 @@
   </si>
   <si>
     <t>Export capacity to Latvia interconnector in GW</t>
-  </si>
-  <si>
-    <t>Trd_elc_exp_ru</t>
-  </si>
-  <si>
-    <t>Russia exports disabled after 2022 in current assumptions</t>
   </si>
   <si>
     <t>lo</t>
@@ -43850,7 +43832,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0573AE-84FA-4F18-8D18-B7F3EC5B3273}">
-  <dimension ref="B4:Y28"/>
+  <dimension ref="B4:Y24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
@@ -43935,7 +43917,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q6" t="s">
         <v>255</v>
@@ -43976,7 +43958,7 @@
         <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q7" t="s">
         <v>256</v>
@@ -44017,7 +43999,7 @@
         <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q8" t="s">
         <v>257</v>
@@ -44065,7 +44047,7 @@
         <v>13</v>
       </c>
       <c r="K9" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q9" t="s">
         <v>259</v>
@@ -44077,7 +44059,7 @@
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.35">
@@ -44184,28 +44166,34 @@
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C15" t="s">
         <v>275</v>
       </c>
       <c r="D15">
-        <v>0.63500000000000001</v>
+        <f>$T$6/1000</f>
+        <v>1.016</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="3">$T$6/1000</f>
+        <v>1.016</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1.016</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1.016</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1.016</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1.016</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
@@ -44213,146 +44201,152 @@
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C16" t="s">
         <v>275</v>
       </c>
       <c r="D16">
-        <f>$T$6/1000</f>
-        <v>1.016</v>
+        <f>$R$8/1000</f>
+        <v>0.99850000000000005</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16:I16" si="3">$T$6/1000</f>
-        <v>1.016</v>
+        <f t="shared" ref="E16:I16" si="4">$R$8/1000</f>
+        <v>0.99850000000000005</v>
       </c>
       <c r="F16">
-        <f t="shared" si="3"/>
-        <v>1.016</v>
+        <f t="shared" si="4"/>
+        <v>0.99850000000000005</v>
       </c>
       <c r="G16">
-        <f t="shared" si="3"/>
-        <v>1.016</v>
+        <f t="shared" si="4"/>
+        <v>0.99850000000000005</v>
       </c>
       <c r="H16">
-        <f t="shared" si="3"/>
-        <v>1.016</v>
+        <f t="shared" si="4"/>
+        <v>0.99850000000000005</v>
       </c>
       <c r="I16">
-        <f t="shared" si="3"/>
-        <v>1.016</v>
+        <f t="shared" si="4"/>
+        <v>0.99850000000000005</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>274</v>
-      </c>
-      <c r="C17" t="s">
-        <v>275</v>
-      </c>
-      <c r="D17">
-        <f>$R$8/1000</f>
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ref="E17:I17" si="4">$R$8/1000</f>
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="4"/>
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="4"/>
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="4"/>
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="4"/>
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="J17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B18" t="s">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20" t="s">
         <v>277</v>
       </c>
-      <c r="C18" t="s">
-        <v>275</v>
-      </c>
-      <c r="D18">
-        <v>0.63</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
-        <v>19</v>
+      <c r="E20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F20" t="s">
+        <v>279</v>
+      </c>
+      <c r="G20" t="s">
+        <v>280</v>
+      </c>
+      <c r="H20" t="s">
+        <v>281</v>
+      </c>
+      <c r="I20" t="s">
+        <v>282</v>
+      </c>
+      <c r="J20" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>0</v>
+        <v>284</v>
+      </c>
+      <c r="C21">
+        <v>1.016</v>
+      </c>
+      <c r="D21">
+        <v>1.016</v>
+      </c>
+      <c r="E21">
+        <v>1.016</v>
+      </c>
+      <c r="F21">
+        <v>1.016</v>
+      </c>
+      <c r="G21">
+        <v>1.016</v>
+      </c>
+      <c r="H21">
+        <v>1.016</v>
+      </c>
+      <c r="I21">
+        <v>1.016</v>
+      </c>
+      <c r="J21" t="s">
+        <v>285</v>
+      </c>
+      <c r="K21" t="s">
+        <v>131</v>
+      </c>
+      <c r="L21" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" t="s">
-        <v>278</v>
-      </c>
-      <c r="D22" t="s">
-        <v>279</v>
-      </c>
-      <c r="E22" t="s">
-        <v>280</v>
-      </c>
-      <c r="F22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G22" t="s">
-        <v>282</v>
-      </c>
-      <c r="H22" t="s">
-        <v>283</v>
-      </c>
-      <c r="I22" t="s">
-        <v>284</v>
+        <v>287</v>
+      </c>
+      <c r="C22">
+        <v>1.204</v>
+      </c>
+      <c r="D22">
+        <v>1.204</v>
+      </c>
+      <c r="E22">
+        <v>1.204</v>
+      </c>
+      <c r="F22">
+        <v>1.204</v>
+      </c>
+      <c r="G22">
+        <v>1.204</v>
+      </c>
+      <c r="H22">
+        <v>1.204</v>
+      </c>
+      <c r="I22">
+        <v>1.204</v>
       </c>
       <c r="J22" t="s">
-        <v>2</v>
+        <v>285</v>
       </c>
       <c r="K22" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C23">
         <v>1.016</v>
@@ -44376,188 +44370,48 @@
         <v>1.016</v>
       </c>
       <c r="J23" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K23" t="s">
         <v>131</v>
       </c>
       <c r="L23" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C24">
-        <v>1.204</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="D24">
-        <v>1.204</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="E24">
-        <v>1.204</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="F24">
-        <v>1.204</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="G24">
-        <v>1.204</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="H24">
-        <v>1.204</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="I24">
-        <v>1.204</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="J24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K24" t="s">
         <v>131</v>
       </c>
       <c r="L24" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
-        <v>291</v>
-      </c>
-      <c r="C25">
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>287</v>
-      </c>
-      <c r="K25" t="s">
-        <v>131</v>
-      </c>
-      <c r="L25" t="s">
         <v>292</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B26" t="s">
-        <v>293</v>
-      </c>
-      <c r="C26">
-        <v>1.016</v>
-      </c>
-      <c r="D26">
-        <v>1.016</v>
-      </c>
-      <c r="E26">
-        <v>1.016</v>
-      </c>
-      <c r="F26">
-        <v>1.016</v>
-      </c>
-      <c r="G26">
-        <v>1.016</v>
-      </c>
-      <c r="H26">
-        <v>1.016</v>
-      </c>
-      <c r="I26">
-        <v>1.016</v>
-      </c>
-      <c r="J26" t="s">
-        <v>287</v>
-      </c>
-      <c r="K26" t="s">
-        <v>131</v>
-      </c>
-      <c r="L26" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>295</v>
-      </c>
-      <c r="C27">
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="D27">
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="E27">
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="F27">
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="G27">
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="H27">
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="I27">
-        <v>0.99850000000000005</v>
-      </c>
-      <c r="J27" t="s">
-        <v>287</v>
-      </c>
-      <c r="K27" t="s">
-        <v>131</v>
-      </c>
-      <c r="L27" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>297</v>
-      </c>
-      <c r="C28">
-        <v>0.63</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28" t="s">
-        <v>287</v>
-      </c>
-      <c r="K28" t="s">
-        <v>131</v>
-      </c>
-      <c r="L28" t="s">
-        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5844505-75F8-445B-9F2C-AA75094ABD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF00A2D3-77D7-4570-83E4-0DFD30B0E1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,8 @@
     <sheet name="build rates" sheetId="5" r:id="rId3"/>
     <sheet name="necessary_for_some_reason" sheetId="6" r:id="rId4"/>
     <sheet name="trade" sheetId="2" r:id="rId5"/>
-    <sheet name="fuel_costs" sheetId="3" r:id="rId6"/>
-    <sheet name="constraints" sheetId="7" r:id="rId7"/>
+    <sheet name="constraints" sheetId="7" r:id="rId6"/>
+    <sheet name="fuel_costs" sheetId="3" r:id="rId7"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId8"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9957" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9957" uniqueCount="296">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -959,6 +959,9 @@
   <si>
     <t>tfm_ins-ts</t>
   </si>
+  <si>
+    <t>up</t>
+  </si>
 </sst>
 </file>
 
@@ -43954,11 +43957,23 @@
       <c r="D7">
         <v>0</v>
       </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
       <c r="J7" t="s">
         <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q7" t="s">
         <v>256</v>
@@ -44423,6 +44438,150 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1758F-E590-4DA8-B461-246947AA96DE}">
+  <dimension ref="A2:I16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7">
+        <v>2050</v>
+      </c>
+      <c r="E7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14">
+        <v>2030</v>
+      </c>
+      <c r="E14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15">
+        <v>2035</v>
+      </c>
+      <c r="E15" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>2.1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BDE16D-C995-4313-9FD3-ABCD01C0EB3D}">
   <dimension ref="B5:W20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -44737,148 +44896,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1758F-E590-4DA8-B461-246947AA96DE}">
-  <dimension ref="A2:I16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7">
-        <v>2050</v>
-      </c>
-      <c r="E7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>131</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14">
-        <v>2030</v>
-      </c>
-      <c r="E14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15">
-        <v>2035</v>
-      </c>
-      <c r="E15" t="s">
-        <v>127</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>2.1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7EAA00-52F5-4FFE-B832-20E21232147A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78294755-A798-438E-8A18-62F814A76FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -43969,6 +43969,9 @@
       <c r="H7">
         <v>0</v>
       </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
       <c r="J7" t="s">
         <v>13</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78294755-A798-438E-8A18-62F814A76FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A387F6-67F8-47ED-A0FC-3ED57372EE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44061,6 +44061,21 @@
       <c r="D9">
         <v>1.64</v>
       </c>
+      <c r="E9">
+        <v>1.64</v>
+      </c>
+      <c r="F9">
+        <v>1.64</v>
+      </c>
+      <c r="G9">
+        <v>1.64</v>
+      </c>
+      <c r="H9">
+        <v>1.64</v>
+      </c>
+      <c r="I9">
+        <v>1.64</v>
+      </c>
       <c r="J9" t="s">
         <v>13</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A387F6-67F8-47ED-A0FC-3ED57372EE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC093415-0638-4CAF-A794-A8C22FBA62C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43846,6 +43846,9 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
+      <c r="E4">
+        <v>0.04</v>
+      </c>
       <c r="X4">
         <v>2022</v>
       </c>
@@ -43916,11 +43919,31 @@
       <c r="D6">
         <v>4.68</v>
       </c>
+      <c r="E6">
+        <f>D6-(D6*$E$4)</f>
+        <v>4.4927999999999999</v>
+      </c>
+      <c r="F6">
+        <f t="shared" ref="F6:I6" si="0">E6-(E6*$E$4)</f>
+        <v>4.3130879999999996</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>4.1405644799999992</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>3.9749419007999993</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>3.8159442247679993</v>
+      </c>
       <c r="J6" t="s">
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q6" t="s">
         <v>254</v>
@@ -44027,27 +44050,27 @@
         <v>998.5</v>
       </c>
       <c r="S8">
-        <f t="shared" ref="S8:Y8" si="0">SUM(S6:S7)/COUNT(S6:S7)</f>
+        <f t="shared" ref="S8:Y8" si="1">SUM(S6:S7)/COUNT(S6:S7)</f>
         <v>1204</v>
       </c>
       <c r="T8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1016</v>
       </c>
       <c r="U8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>630</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>635</v>
       </c>
     </row>
@@ -44136,23 +44159,23 @@
         <v>1.016</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E13:I13" si="1">$T$6/1000</f>
+        <f t="shared" ref="E13:I13" si="2">$T$6/1000</f>
         <v>1.016</v>
       </c>
       <c r="F13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.016</v>
       </c>
       <c r="G13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.016</v>
       </c>
       <c r="H13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.016</v>
       </c>
       <c r="I13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.016</v>
       </c>
       <c r="J13" t="s">
@@ -44174,23 +44197,23 @@
         <v>1.204</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:I14" si="2">$S$8/1000</f>
+        <f t="shared" ref="E14:I14" si="3">$S$8/1000</f>
         <v>1.204</v>
       </c>
       <c r="F14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.204</v>
       </c>
       <c r="G14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.204</v>
       </c>
       <c r="H14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.204</v>
       </c>
       <c r="I14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.204</v>
       </c>
       <c r="J14" t="s">
@@ -44209,23 +44232,23 @@
         <v>1.016</v>
       </c>
       <c r="E15">
-        <f t="shared" ref="E15:I15" si="3">$T$6/1000</f>
+        <f t="shared" ref="E15:I15" si="4">$T$6/1000</f>
         <v>1.016</v>
       </c>
       <c r="F15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.016</v>
       </c>
       <c r="G15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.016</v>
       </c>
       <c r="H15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.016</v>
       </c>
       <c r="I15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.016</v>
       </c>
       <c r="J15" t="s">
@@ -44244,23 +44267,23 @@
         <v>0.99850000000000005</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16:I16" si="4">$R$8/1000</f>
+        <f t="shared" ref="E16:I16" si="5">$R$8/1000</f>
         <v>0.99850000000000005</v>
       </c>
       <c r="F16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.99850000000000005</v>
       </c>
       <c r="G16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.99850000000000005</v>
       </c>
       <c r="H16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.99850000000000005</v>
       </c>
       <c r="I16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.99850000000000005</v>
       </c>
       <c r="J16" t="s">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EB8F3B-0BC2-481D-9E4A-C641D9DC2DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5F7983-B2B0-49C9-8A31-BAB9DE9B3327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6213" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6213" uniqueCount="284">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -923,6 +923,9 @@
   <si>
     <t>e_wof_parnu_laht</t>
   </si>
+  <si>
+    <t>TFM_DINS-AT</t>
+  </si>
 </sst>
 </file>
 
@@ -1560,6 +1563,10 @@
       </c>
     </row>
     <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>SUM(C6:C9)</f>
+        <v>8.4914999999999985</v>
+      </c>
       <c r="M11" t="s">
         <v>5</v>
       </c>
@@ -1776,7 +1783,7 @@
         <v>50</v>
       </c>
       <c r="AB1" t="s">
-        <v>50</v>
+        <v>283</v>
       </c>
       <c r="AF1" t="s">
         <v>68</v>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5F7983-B2B0-49C9-8A31-BAB9DE9B3327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB83B1D-AEBC-4C9C-ADF0-A3952AE3607A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6213" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6506" uniqueCount="287">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -926,6 +926,15 @@
   <si>
     <t>TFM_DINS-AT</t>
   </si>
+  <si>
+    <t>Timeslice</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>NCAP_AFC</t>
+  </si>
 </sst>
 </file>
 
@@ -1029,21 +1038,21 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1747,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B64E1E-DC66-450D-AA2A-D1B01A72BCA4}">
-  <dimension ref="A1:AN962"/>
+  <dimension ref="A1:AW962"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.42578125" bestFit="1" customWidth="1"/>
@@ -1764,9 +1773,13 @@
     <col min="36" max="36" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="12" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>49</v>
       </c>
@@ -1791,8 +1804,11 @@
       <c r="AK1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -1889,8 +1905,20 @@
       <c r="AN2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ2" t="s">
+        <v>284</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>285</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>IFERROR(IF([1]Veda!#REF!=A2,"ok","x"),"")</f>
         <v/>
@@ -1988,8 +2016,24 @@
       <c r="AN3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT3">
+        <f>350/$AV$3</f>
+        <v>0.34448818897637795</v>
+      </c>
+      <c r="AV3">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>104</v>
       </c>
@@ -2077,8 +2121,21 @@
       <c r="AN4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" ref="AT4:AT24" si="0">350/$AV$3</f>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>106</v>
       </c>
@@ -2166,8 +2223,21 @@
       <c r="AN5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>108</v>
       </c>
@@ -2255,8 +2325,21 @@
       <c r="AN6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>110</v>
       </c>
@@ -2344,8 +2427,21 @@
       <c r="AN7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>112</v>
       </c>
@@ -2433,8 +2529,21 @@
       <c r="AN8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>114</v>
       </c>
@@ -2522,8 +2631,21 @@
       <c r="AN9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>116</v>
       </c>
@@ -2611,8 +2733,21 @@
       <c r="AN10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>118</v>
       </c>
@@ -2694,8 +2829,21 @@
       <c r="AN11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>119</v>
       </c>
@@ -2777,8 +2925,21 @@
       <c r="AN12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ12" t="s">
+        <v>131</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT12">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>120</v>
       </c>
@@ -2860,8 +3021,21 @@
       <c r="AN13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ13" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT13">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>121</v>
       </c>
@@ -2943,8 +3117,21 @@
       <c r="AN14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
         <v>266</v>
       </c>
@@ -3023,8 +3210,21 @@
       <c r="AN15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AQ15" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT15">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="I16" t="s">
         <v>266</v>
       </c>
@@ -3103,8 +3303,21 @@
       <c r="AN16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ16" t="s">
+        <v>135</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT16">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="17" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I17" t="s">
         <v>266</v>
       </c>
@@ -3183,8 +3396,21 @@
       <c r="AN17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ17" t="s">
+        <v>136</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT17">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="18" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I18" t="s">
         <v>266</v>
       </c>
@@ -3263,8 +3489,21 @@
       <c r="AN18" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ18" t="s">
+        <v>137</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT18">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="19" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I19" t="s">
         <v>266</v>
       </c>
@@ -3343,8 +3582,21 @@
       <c r="AN19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT19">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="20" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
         <v>266</v>
       </c>
@@ -3423,8 +3675,21 @@
       <c r="AN20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ20" t="s">
+        <v>139</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT20">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="21" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
         <v>266</v>
       </c>
@@ -3503,8 +3768,21 @@
       <c r="AN21" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT21">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="22" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
         <v>266</v>
       </c>
@@ -3583,8 +3861,21 @@
       <c r="AN22" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ22" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT22">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="23" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I23" t="s">
         <v>266</v>
       </c>
@@ -3663,8 +3954,21 @@
       <c r="AN23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ23" t="s">
+        <v>142</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT23">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="24" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
         <v>266</v>
       </c>
@@ -3743,8 +4047,21 @@
       <c r="AN24" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ24" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT24">
+        <f t="shared" si="0"/>
+        <v>0.34448818897637795</v>
+      </c>
+    </row>
+    <row r="25" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I25" t="s">
         <v>266</v>
       </c>
@@ -3823,8 +4140,24 @@
       <c r="AN25" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ25" t="s">
+        <v>144</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT25">
+        <v>0.79</v>
+      </c>
+      <c r="AW25" s="2">
+        <f ca="1">RANDBETWEEN(70,95)/100</f>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="26" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I26" t="s">
         <v>266</v>
       </c>
@@ -3903,8 +4236,24 @@
       <c r="AN26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ26" t="s">
+        <v>145</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT26">
+        <v>0.85</v>
+      </c>
+      <c r="AW26" s="2">
+        <f t="shared" ref="AW26:AW89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="27" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
         <v>266</v>
       </c>
@@ -3983,8 +4332,24 @@
       <c r="AN27" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ27" t="s">
+        <v>146</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS27" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT27">
+        <v>0.72</v>
+      </c>
+      <c r="AW27" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="28" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I28" t="s">
         <v>266</v>
       </c>
@@ -4063,8 +4428,24 @@
       <c r="AN28" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ28" t="s">
+        <v>147</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS28" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT28">
+        <v>0.79</v>
+      </c>
+      <c r="AW28" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="29" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I29" t="s">
         <v>266</v>
       </c>
@@ -4143,8 +4524,24 @@
       <c r="AN29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ29" t="s">
+        <v>148</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT29">
+        <v>0.83</v>
+      </c>
+      <c r="AW29" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="30" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I30" t="s">
         <v>266</v>
       </c>
@@ -4223,8 +4620,24 @@
       <c r="AN30" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ30" t="s">
+        <v>149</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT30">
+        <v>0.77</v>
+      </c>
+      <c r="AW30" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="31" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I31" t="s">
         <v>266</v>
       </c>
@@ -4303,8 +4716,24 @@
       <c r="AN31" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ31" t="s">
+        <v>150</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS31" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT31">
+        <v>0.74</v>
+      </c>
+      <c r="AW31" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="32" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I32" t="s">
         <v>266</v>
       </c>
@@ -4383,8 +4812,24 @@
       <c r="AN32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ32" t="s">
+        <v>151</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS32" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT32">
+        <v>0.87</v>
+      </c>
+      <c r="AW32" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="33" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I33" t="s">
         <v>266</v>
       </c>
@@ -4463,8 +4908,24 @@
       <c r="AN33" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ33" t="s">
+        <v>152</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS33" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT33">
+        <v>0.71</v>
+      </c>
+      <c r="AW33" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="34" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I34" t="s">
         <v>266</v>
       </c>
@@ -4543,8 +5004,24 @@
       <c r="AN34" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ34" t="s">
+        <v>153</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS34" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT34">
+        <v>0.88</v>
+      </c>
+      <c r="AW34" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="35" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I35" t="s">
         <v>266</v>
       </c>
@@ -4623,8 +5100,24 @@
       <c r="AN35" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ35" t="s">
+        <v>154</v>
+      </c>
+      <c r="AR35" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS35" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT35">
+        <v>0.74</v>
+      </c>
+      <c r="AW35" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="36" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I36" t="s">
         <v>266</v>
       </c>
@@ -4703,8 +5196,24 @@
       <c r="AN36" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ36" t="s">
+        <v>155</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS36" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT36">
+        <v>0.92</v>
+      </c>
+      <c r="AW36" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="37" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I37" t="s">
         <v>266</v>
       </c>
@@ -4783,8 +5292,24 @@
       <c r="AN37" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="38" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ37" t="s">
+        <v>156</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS37" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT37">
+        <v>0.73</v>
+      </c>
+      <c r="AW37" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="38" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I38" t="s">
         <v>266</v>
       </c>
@@ -4863,8 +5388,24 @@
       <c r="AN38" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ38" t="s">
+        <v>157</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS38" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT38">
+        <v>0.89</v>
+      </c>
+      <c r="AW38" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="39" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I39" t="s">
         <v>266</v>
       </c>
@@ -4931,8 +5472,24 @@
       <c r="AN39" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ39" t="s">
+        <v>158</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS39" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT39">
+        <v>0.72</v>
+      </c>
+      <c r="AW39" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="40" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I40" t="s">
         <v>266</v>
       </c>
@@ -4999,8 +5556,24 @@
       <c r="AN40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ40" t="s">
+        <v>159</v>
+      </c>
+      <c r="AR40" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS40" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT40">
+        <v>0.81</v>
+      </c>
+      <c r="AW40" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="41" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I41" t="s">
         <v>266</v>
       </c>
@@ -5067,8 +5640,24 @@
       <c r="AN41" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ41" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR41" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS41" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT41">
+        <v>0.78</v>
+      </c>
+      <c r="AW41" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="42" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I42" t="s">
         <v>266</v>
       </c>
@@ -5135,8 +5724,24 @@
       <c r="AN42" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ42" t="s">
+        <v>161</v>
+      </c>
+      <c r="AR42" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS42" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT42">
+        <v>0.79</v>
+      </c>
+      <c r="AW42" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="43" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I43" t="s">
         <v>266</v>
       </c>
@@ -5203,8 +5808,24 @@
       <c r="AN43" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ43" t="s">
+        <v>162</v>
+      </c>
+      <c r="AR43" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS43" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT43">
+        <v>0.87</v>
+      </c>
+      <c r="AW43" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="44" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I44" t="s">
         <v>266</v>
       </c>
@@ -5271,8 +5892,24 @@
       <c r="AN44" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ44" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR44" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS44" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT44">
+        <v>0.7</v>
+      </c>
+      <c r="AW44" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="45" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I45" t="s">
         <v>266</v>
       </c>
@@ -5339,8 +5976,24 @@
       <c r="AN45" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ45" t="s">
+        <v>164</v>
+      </c>
+      <c r="AR45" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS45" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT45">
+        <v>0.8</v>
+      </c>
+      <c r="AW45" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="46" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I46" t="s">
         <v>266</v>
       </c>
@@ -5407,8 +6060,24 @@
       <c r="AN46" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ46" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR46" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS46" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT46">
+        <v>0.95</v>
+      </c>
+      <c r="AW46" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="47" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I47" t="s">
         <v>266</v>
       </c>
@@ -5475,8 +6144,24 @@
       <c r="AN47" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ47" t="s">
+        <v>166</v>
+      </c>
+      <c r="AR47" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS47" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT47">
+        <v>0.87</v>
+      </c>
+      <c r="AW47" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="48" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I48" t="s">
         <v>266</v>
       </c>
@@ -5543,8 +6228,24 @@
       <c r="AN48" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ48" t="s">
+        <v>167</v>
+      </c>
+      <c r="AR48" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS48" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT48">
+        <v>0.84</v>
+      </c>
+      <c r="AW48" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="49" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I49" t="s">
         <v>266</v>
       </c>
@@ -5611,8 +6312,24 @@
       <c r="AN49" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ49" t="s">
+        <v>168</v>
+      </c>
+      <c r="AR49" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS49" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT49">
+        <v>0.74</v>
+      </c>
+      <c r="AW49" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="50" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I50" t="s">
         <v>266</v>
       </c>
@@ -5679,8 +6396,24 @@
       <c r="AN50" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="51" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ50" t="s">
+        <v>169</v>
+      </c>
+      <c r="AR50" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS50" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT50">
+        <v>0.89</v>
+      </c>
+      <c r="AW50" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="51" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I51" t="s">
         <v>266</v>
       </c>
@@ -5747,8 +6480,24 @@
       <c r="AN51" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ51" t="s">
+        <v>170</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS51" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT51">
+        <v>0.73</v>
+      </c>
+      <c r="AW51" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="52" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I52" t="s">
         <v>266</v>
       </c>
@@ -5815,8 +6564,24 @@
       <c r="AN52" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ52" t="s">
+        <v>171</v>
+      </c>
+      <c r="AR52" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT52">
+        <v>0.91</v>
+      </c>
+      <c r="AW52" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="53" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I53" t="s">
         <v>266</v>
       </c>
@@ -5883,8 +6648,24 @@
       <c r="AN53" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="54" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ53" t="s">
+        <v>172</v>
+      </c>
+      <c r="AR53" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS53" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT53">
+        <v>0.9</v>
+      </c>
+      <c r="AW53" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="54" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I54" t="s">
         <v>266</v>
       </c>
@@ -5951,8 +6732,24 @@
       <c r="AN54" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ54" t="s">
+        <v>173</v>
+      </c>
+      <c r="AR54" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS54" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT54">
+        <v>0.88</v>
+      </c>
+      <c r="AW54" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="55" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I55" t="s">
         <v>266</v>
       </c>
@@ -6019,8 +6816,24 @@
       <c r="AN55" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="56" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ55" t="s">
+        <v>174</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS55" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT55">
+        <v>0.78</v>
+      </c>
+      <c r="AW55" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="56" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I56" t="s">
         <v>266</v>
       </c>
@@ -6087,8 +6900,24 @@
       <c r="AN56" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="57" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ56" t="s">
+        <v>175</v>
+      </c>
+      <c r="AR56" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS56" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT56">
+        <v>0.78</v>
+      </c>
+      <c r="AW56" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="57" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I57" t="s">
         <v>266</v>
       </c>
@@ -6155,8 +6984,24 @@
       <c r="AN57" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ57" t="s">
+        <v>176</v>
+      </c>
+      <c r="AR57" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS57" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT57">
+        <v>0.8</v>
+      </c>
+      <c r="AW57" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="58" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I58" t="s">
         <v>266</v>
       </c>
@@ -6223,8 +7068,24 @@
       <c r="AN58" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ58" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR58" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS58" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT58">
+        <v>0.7</v>
+      </c>
+      <c r="AW58" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="59" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I59" t="s">
         <v>266</v>
       </c>
@@ -6291,8 +7152,24 @@
       <c r="AN59" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ59" t="s">
+        <v>178</v>
+      </c>
+      <c r="AR59" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS59" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT59">
+        <v>0.84</v>
+      </c>
+      <c r="AW59" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="60" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I60" t="s">
         <v>266</v>
       </c>
@@ -6359,8 +7236,24 @@
       <c r="AN60" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ60" t="s">
+        <v>179</v>
+      </c>
+      <c r="AR60" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS60" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT60">
+        <v>0.86</v>
+      </c>
+      <c r="AW60" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="61" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I61" t="s">
         <v>266</v>
       </c>
@@ -6427,8 +7320,24 @@
       <c r="AN61" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="62" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ61" t="s">
+        <v>180</v>
+      </c>
+      <c r="AR61" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS61" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT61">
+        <v>0.92</v>
+      </c>
+      <c r="AW61" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="62" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I62" t="s">
         <v>266</v>
       </c>
@@ -6495,8 +7404,24 @@
       <c r="AN62" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ62" t="s">
+        <v>181</v>
+      </c>
+      <c r="AR62" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS62" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT62">
+        <v>0.87</v>
+      </c>
+      <c r="AW62" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="63" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I63" t="s">
         <v>266</v>
       </c>
@@ -6563,8 +7488,24 @@
       <c r="AN63" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="64" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ63" t="s">
+        <v>182</v>
+      </c>
+      <c r="AR63" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS63" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT63">
+        <v>0.86</v>
+      </c>
+      <c r="AW63" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="64" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I64" t="s">
         <v>266</v>
       </c>
@@ -6631,8 +7572,24 @@
       <c r="AN64" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="65" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ64" t="s">
+        <v>183</v>
+      </c>
+      <c r="AR64" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS64" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT64">
+        <v>0.81</v>
+      </c>
+      <c r="AW64" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="65" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I65" t="s">
         <v>266</v>
       </c>
@@ -6699,8 +7656,24 @@
       <c r="AN65" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ65" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR65" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS65" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT65">
+        <v>0.84</v>
+      </c>
+      <c r="AW65" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="66" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I66" t="s">
         <v>266</v>
       </c>
@@ -6767,8 +7740,24 @@
       <c r="AN66" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ66" t="s">
+        <v>185</v>
+      </c>
+      <c r="AR66" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS66" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT66">
+        <v>0.8</v>
+      </c>
+      <c r="AW66" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="67" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I67" t="s">
         <v>266</v>
       </c>
@@ -6835,8 +7824,24 @@
       <c r="AN67" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="68" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ67" t="s">
+        <v>186</v>
+      </c>
+      <c r="AR67" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS67" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT67">
+        <v>0.83</v>
+      </c>
+      <c r="AW67" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="68" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I68" t="s">
         <v>266</v>
       </c>
@@ -6903,8 +7908,24 @@
       <c r="AN68" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="69" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AR68" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS68" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT68">
+        <v>0.84</v>
+      </c>
+      <c r="AW68" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="69" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I69" t="s">
         <v>266</v>
       </c>
@@ -6971,8 +7992,24 @@
       <c r="AN69" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="70" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ69" t="s">
+        <v>188</v>
+      </c>
+      <c r="AR69" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS69" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT69">
+        <v>0.78</v>
+      </c>
+      <c r="AW69" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="70" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I70" t="s">
         <v>266</v>
       </c>
@@ -7039,8 +8076,24 @@
       <c r="AN70" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="71" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ70" t="s">
+        <v>189</v>
+      </c>
+      <c r="AR70" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS70" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT70">
+        <v>0.86</v>
+      </c>
+      <c r="AW70" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="71" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I71" t="s">
         <v>266</v>
       </c>
@@ -7107,8 +8160,24 @@
       <c r="AN71" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="72" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ71" t="s">
+        <v>190</v>
+      </c>
+      <c r="AR71" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS71" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT71">
+        <v>0.79</v>
+      </c>
+      <c r="AW71" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="72" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I72" t="s">
         <v>266</v>
       </c>
@@ -7175,8 +8244,24 @@
       <c r="AN72" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ72" t="s">
+        <v>191</v>
+      </c>
+      <c r="AR72" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS72" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT72">
+        <v>0.88</v>
+      </c>
+      <c r="AW72" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="73" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I73" t="s">
         <v>266</v>
       </c>
@@ -7243,8 +8328,24 @@
       <c r="AN73" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="74" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ73" t="s">
+        <v>192</v>
+      </c>
+      <c r="AR73" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS73" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT73">
+        <v>0.9</v>
+      </c>
+      <c r="AW73" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="74" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I74" t="s">
         <v>266</v>
       </c>
@@ -7311,8 +8412,24 @@
       <c r="AN74" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="75" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ74" t="s">
+        <v>193</v>
+      </c>
+      <c r="AR74" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS74" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT74">
+        <v>0.79</v>
+      </c>
+      <c r="AW74" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="75" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I75" t="s">
         <v>266</v>
       </c>
@@ -7379,8 +8496,24 @@
       <c r="AN75" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="76" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ75" t="s">
+        <v>194</v>
+      </c>
+      <c r="AR75" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS75" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT75">
+        <v>0.85</v>
+      </c>
+      <c r="AW75" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="76" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I76" t="s">
         <v>266</v>
       </c>
@@ -7447,8 +8580,24 @@
       <c r="AN76" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ76" t="s">
+        <v>195</v>
+      </c>
+      <c r="AR76" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS76" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT76">
+        <v>0.78</v>
+      </c>
+      <c r="AW76" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="77" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I77" t="s">
         <v>266</v>
       </c>
@@ -7515,8 +8664,24 @@
       <c r="AN77" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="78" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ77" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR77" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS77" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT77">
+        <v>0.85</v>
+      </c>
+      <c r="AW77" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="78" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I78" t="s">
         <v>266</v>
       </c>
@@ -7583,8 +8748,24 @@
       <c r="AN78" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="79" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ78" t="s">
+        <v>197</v>
+      </c>
+      <c r="AR78" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS78" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT78">
+        <v>0.94</v>
+      </c>
+      <c r="AW78" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="79" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I79" t="s">
         <v>266</v>
       </c>
@@ -7651,8 +8832,24 @@
       <c r="AN79" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="80" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ79" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR79" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS79" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT79">
+        <v>0.88</v>
+      </c>
+      <c r="AW79" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="80" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I80" t="s">
         <v>266</v>
       </c>
@@ -7719,8 +8916,24 @@
       <c r="AN80" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="81" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ80" t="s">
+        <v>199</v>
+      </c>
+      <c r="AR80" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS80" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT80">
+        <v>0.94</v>
+      </c>
+      <c r="AW80" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="81" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I81" t="s">
         <v>266</v>
       </c>
@@ -7787,8 +9000,24 @@
       <c r="AN81" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="82" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ81" t="s">
+        <v>200</v>
+      </c>
+      <c r="AR81" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS81" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT81">
+        <v>0.89</v>
+      </c>
+      <c r="AW81" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="82" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I82" t="s">
         <v>266</v>
       </c>
@@ -7855,8 +9084,24 @@
       <c r="AN82" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="83" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ82" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR82" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS82" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT82">
+        <v>0.91</v>
+      </c>
+      <c r="AW82" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="83" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I83" t="s">
         <v>266</v>
       </c>
@@ -7923,8 +9168,24 @@
       <c r="AN83" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ83" t="s">
+        <v>202</v>
+      </c>
+      <c r="AR83" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS83" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT83">
+        <v>0.85</v>
+      </c>
+      <c r="AW83" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="84" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I84" t="s">
         <v>266</v>
       </c>
@@ -7991,8 +9252,24 @@
       <c r="AN84" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="85" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ84" t="s">
+        <v>203</v>
+      </c>
+      <c r="AR84" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS84" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT84">
+        <v>0.81</v>
+      </c>
+      <c r="AW84" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="85" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I85" t="s">
         <v>266</v>
       </c>
@@ -8059,8 +9336,24 @@
       <c r="AN85" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="86" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ85" t="s">
+        <v>204</v>
+      </c>
+      <c r="AR85" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS85" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT85">
+        <v>0.93</v>
+      </c>
+      <c r="AW85" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="86" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I86" t="s">
         <v>266</v>
       </c>
@@ -8127,8 +9420,24 @@
       <c r="AN86" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="87" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ86" t="s">
+        <v>205</v>
+      </c>
+      <c r="AR86" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS86" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT86">
+        <v>0.84</v>
+      </c>
+      <c r="AW86" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="87" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I87" t="s">
         <v>266</v>
       </c>
@@ -8195,8 +9504,24 @@
       <c r="AN87" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="88" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ87" t="s">
+        <v>206</v>
+      </c>
+      <c r="AR87" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS87" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT87">
+        <v>0.8</v>
+      </c>
+      <c r="AW87" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="88" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I88" t="s">
         <v>266</v>
       </c>
@@ -8263,8 +9588,24 @@
       <c r="AN88" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="89" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ88" t="s">
+        <v>207</v>
+      </c>
+      <c r="AR88" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS88" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT88">
+        <v>0.87</v>
+      </c>
+      <c r="AW88" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="89" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I89" t="s">
         <v>266</v>
       </c>
@@ -8331,8 +9672,24 @@
       <c r="AN89" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ89" t="s">
+        <v>208</v>
+      </c>
+      <c r="AR89" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS89" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT89">
+        <v>0.75</v>
+      </c>
+      <c r="AW89" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="90" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I90" t="s">
         <v>266</v>
       </c>
@@ -8399,8 +9756,24 @@
       <c r="AN90" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ90" t="s">
+        <v>209</v>
+      </c>
+      <c r="AR90" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS90" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT90">
+        <v>0.94</v>
+      </c>
+      <c r="AW90" s="2">
+        <f t="shared" ref="AW90:AW98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="91" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I91" t="s">
         <v>266</v>
       </c>
@@ -8467,8 +9840,24 @@
       <c r="AN91" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ91" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR91" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS91" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT91">
+        <v>0.8</v>
+      </c>
+      <c r="AW91" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="92" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I92" t="s">
         <v>266</v>
       </c>
@@ -8535,8 +9924,24 @@
       <c r="AN92" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="93" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ92" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR92" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS92" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT92">
+        <v>0.7</v>
+      </c>
+      <c r="AW92" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="93" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I93" t="s">
         <v>266</v>
       </c>
@@ -8603,8 +10008,24 @@
       <c r="AN93" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="94" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ93" t="s">
+        <v>212</v>
+      </c>
+      <c r="AR93" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS93" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT93">
+        <v>0.82</v>
+      </c>
+      <c r="AW93" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="94" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I94" t="s">
         <v>266</v>
       </c>
@@ -8671,8 +10092,24 @@
       <c r="AN94" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ94" t="s">
+        <v>213</v>
+      </c>
+      <c r="AR94" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS94" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT94">
+        <v>0.95</v>
+      </c>
+      <c r="AW94" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="95" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I95" t="s">
         <v>266</v>
       </c>
@@ -8739,8 +10176,24 @@
       <c r="AN95" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="96" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ95" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR95" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS95" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT95">
+        <v>0.76</v>
+      </c>
+      <c r="AW95" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="96" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I96" t="s">
         <v>266</v>
       </c>
@@ -8807,8 +10260,24 @@
       <c r="AN96" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="97" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ96" t="s">
+        <v>215</v>
+      </c>
+      <c r="AR96" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS96" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT96">
+        <v>0.93</v>
+      </c>
+      <c r="AW96" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="97" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I97" t="s">
         <v>266</v>
       </c>
@@ -8875,8 +10344,24 @@
       <c r="AN97" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="98" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ97" t="s">
+        <v>216</v>
+      </c>
+      <c r="AR97" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS97" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT97">
+        <v>0.89</v>
+      </c>
+      <c r="AW97" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="98" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I98" t="s">
         <v>266</v>
       </c>
@@ -8943,8 +10428,24 @@
       <c r="AN98" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="99" spans="9:40" x14ac:dyDescent="0.25">
+      <c r="AQ98" t="s">
+        <v>217</v>
+      </c>
+      <c r="AR98" t="s">
+        <v>286</v>
+      </c>
+      <c r="AS98" t="s">
+        <v>240</v>
+      </c>
+      <c r="AT98">
+        <v>0.79</v>
+      </c>
+      <c r="AW98" s="2">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="99" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I99" t="s">
         <v>267</v>
       </c>
@@ -8979,7 +10480,7 @@
         <v>1.7573439583804459E-2</v>
       </c>
     </row>
-    <row r="100" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="100" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I100" t="s">
         <v>267</v>
       </c>
@@ -9014,7 +10515,7 @@
         <v>3.549030522775862E-3</v>
       </c>
     </row>
-    <row r="101" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="101" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I101" t="s">
         <v>267</v>
       </c>
@@ -9049,7 +10550,7 @@
         <v>3.2008138253697617E-2</v>
       </c>
     </row>
-    <row r="102" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="102" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I102" t="s">
         <v>267</v>
       </c>
@@ -9084,7 +10585,7 @@
         <v>3.5595926097493078E-3</v>
       </c>
     </row>
-    <row r="103" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="103" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I103" t="s">
         <v>267</v>
       </c>
@@ -9119,7 +10620,7 @@
         <v>1.0678471251817045E-2</v>
       </c>
     </row>
-    <row r="104" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="104" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I104" t="s">
         <v>267</v>
       </c>
@@ -9154,7 +10655,7 @@
         <v>3.5562894851714701E-3</v>
       </c>
     </row>
-    <row r="105" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="105" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I105" t="s">
         <v>267</v>
       </c>
@@ -9189,7 +10690,7 @@
         <v>3.5440857255036491E-3</v>
       </c>
     </row>
-    <row r="106" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="106" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I106" t="s">
         <v>267</v>
       </c>
@@ -9224,7 +10725,7 @@
         <v>1.0554198606771802E-2</v>
       </c>
     </row>
-    <row r="107" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="107" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I107" t="s">
         <v>267</v>
       </c>
@@ -9259,7 +10760,7 @@
         <v>1.5916331913035826E-2</v>
       </c>
     </row>
-    <row r="108" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="108" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I108" t="s">
         <v>267</v>
       </c>
@@ -9294,7 +10795,7 @@
         <v>3.2085184733168996E-3</v>
       </c>
     </row>
-    <row r="109" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="109" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I109" t="s">
         <v>267</v>
       </c>
@@ -9329,7 +10830,7 @@
         <v>2.8854869593476187E-2</v>
       </c>
     </row>
-    <row r="110" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="110" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I110" t="s">
         <v>267</v>
       </c>
@@ -9364,7 +10865,7 @@
         <v>3.2092305241240983E-3</v>
       </c>
     </row>
-    <row r="111" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="111" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I111" t="s">
         <v>267</v>
       </c>
@@ -9399,7 +10900,7 @@
         <v>9.6277410203450178E-3</v>
       </c>
     </row>
-    <row r="112" spans="9:40" x14ac:dyDescent="0.25">
+    <row r="112" spans="9:49" x14ac:dyDescent="0.25">
       <c r="I112" t="s">
         <v>267</v>
       </c>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9CC119-1370-435C-8465-A7FDBBCFAFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AX32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="33" spans="9:50" x14ac:dyDescent="0.25">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9CC119-1370-435C-8465-A7FDBBCFAFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74514E36-3DC2-4A49-BE9A-99A6879CE805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.72</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AX32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="33" spans="9:50" x14ac:dyDescent="0.25">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AX37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="38" spans="9:50" x14ac:dyDescent="0.25">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">
@@ -37007,7 +37007,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0448EE0-6EB3-49B4-88D9-D0F0750B940D}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -37015,17 +37015,17 @@
     <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -37048,133 +37048,148 @@
         <v>2040</v>
       </c>
       <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2045</v>
+      </c>
+      <c r="I4">
+        <v>2050</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>0.5</v>
       </c>
-      <c r="F5">
-        <v>0.2</v>
-      </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6">
-        <v>0.1</v>
-      </c>
-      <c r="F6">
-        <v>0.05</v>
-      </c>
-      <c r="G6">
-        <v>1E-3</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
       </c>
       <c r="E9">
+        <v>0.5</v>
+      </c>
+      <c r="F9">
+        <v>0.2</v>
+      </c>
+      <c r="G9">
+        <v>0.1</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10">
+        <v>0.1</v>
+      </c>
+      <c r="F10">
+        <v>0.05</v>
+      </c>
+      <c r="G10">
+        <v>1E-3</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <v>4</v>
       </c>
     </row>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74514E36-3DC2-4A49-BE9A-99A6879CE805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF97E107-38E0-4FAF-872A-94C3F37A3AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AX37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="38" spans="9:50" x14ac:dyDescent="0.25">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">
@@ -37071,7 +37071,7 @@
         <v>56</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
         <v>0.5</v>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF97E107-38E0-4FAF-872A-94C3F37A3AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24C6110-D4E1-4093-94CD-5BA92C467ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AX32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="33" spans="9:50" x14ac:dyDescent="0.25">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AX37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38" spans="9:50" x14ac:dyDescent="0.25">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">
@@ -37007,7 +37007,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0448EE0-6EB3-49B4-88D9-D0F0750B940D}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -37071,16 +37071,16 @@
         <v>56</v>
       </c>
       <c r="E5">
+        <v>0.35</v>
+      </c>
+      <c r="F5">
+        <v>0.35</v>
+      </c>
+      <c r="G5">
         <v>0.5</v>
       </c>
-      <c r="F5">
-        <v>0.5</v>
-      </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.8</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -37191,6 +37191,27 @@
       </c>
       <c r="J13">
         <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P19">
+        <v>3.5</v>
+      </c>
+      <c r="Q19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P20">
+        <v>0.5</v>
+      </c>
+      <c r="R20">
+        <f>P19/P20</f>
+        <v>7</v>
+      </c>
+      <c r="S20">
+        <f>1/(Q19/P19)</f>
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24C6110-D4E1-4093-94CD-5BA92C467ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8B2293-D976-469A-8FF3-BEFE6A33D914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -936,9 +936,6 @@
     <t>Limtype</t>
   </si>
   <si>
-    <t>~UC_T: uc_rhsrt</t>
-  </si>
-  <si>
     <t>elc_spv_voru</t>
   </si>
   <si>
@@ -952,6 +949,9 @@
   </si>
   <si>
     <t>elc_spv_hiiu</t>
+  </si>
+  <si>
+    <t>UC_T: uc_rhsrt</t>
   </si>
 </sst>
 </file>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AX32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33" spans="9:50" x14ac:dyDescent="0.25">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AX37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="38" spans="9:50" x14ac:dyDescent="0.25">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.94</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.94</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">
@@ -30351,7 +30351,7 @@
     </row>
     <row r="963" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I963" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J963" t="s">
         <v>123</v>
@@ -30365,7 +30365,7 @@
     </row>
     <row r="964" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I964" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J964" t="s">
         <v>124</v>
@@ -30379,7 +30379,7 @@
     </row>
     <row r="965" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I965" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J965" t="s">
         <v>125</v>
@@ -30393,7 +30393,7 @@
     </row>
     <row r="966" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I966" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J966" t="s">
         <v>126</v>
@@ -30407,7 +30407,7 @@
     </row>
     <row r="967" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I967" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J967" t="s">
         <v>127</v>
@@ -30421,7 +30421,7 @@
     </row>
     <row r="968" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I968" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J968" t="s">
         <v>128</v>
@@ -30435,7 +30435,7 @@
     </row>
     <row r="969" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I969" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J969" t="s">
         <v>129</v>
@@ -30449,7 +30449,7 @@
     </row>
     <row r="970" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I970" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J970" t="s">
         <v>130</v>
@@ -30463,7 +30463,7 @@
     </row>
     <row r="971" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I971" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J971" t="s">
         <v>131</v>
@@ -30477,7 +30477,7 @@
     </row>
     <row r="972" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I972" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J972" t="s">
         <v>132</v>
@@ -30491,7 +30491,7 @@
     </row>
     <row r="973" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I973" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J973" t="s">
         <v>133</v>
@@ -30505,7 +30505,7 @@
     </row>
     <row r="974" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I974" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J974" t="s">
         <v>134</v>
@@ -30519,7 +30519,7 @@
     </row>
     <row r="975" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I975" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J975" t="s">
         <v>135</v>
@@ -30533,7 +30533,7 @@
     </row>
     <row r="976" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I976" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J976" t="s">
         <v>136</v>
@@ -30547,7 +30547,7 @@
     </row>
     <row r="977" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I977" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J977" t="s">
         <v>137</v>
@@ -30561,7 +30561,7 @@
     </row>
     <row r="978" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I978" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J978" t="s">
         <v>138</v>
@@ -30575,7 +30575,7 @@
     </row>
     <row r="979" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I979" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J979" t="s">
         <v>139</v>
@@ -30589,7 +30589,7 @@
     </row>
     <row r="980" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I980" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J980" t="s">
         <v>140</v>
@@ -30603,7 +30603,7 @@
     </row>
     <row r="981" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I981" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J981" t="s">
         <v>141</v>
@@ -30617,7 +30617,7 @@
     </row>
     <row r="982" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I982" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J982" t="s">
         <v>142</v>
@@ -30631,7 +30631,7 @@
     </row>
     <row r="983" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I983" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J983" t="s">
         <v>143</v>
@@ -30645,7 +30645,7 @@
     </row>
     <row r="984" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I984" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J984" t="s">
         <v>144</v>
@@ -30659,7 +30659,7 @@
     </row>
     <row r="985" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I985" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J985" t="s">
         <v>145</v>
@@ -30673,7 +30673,7 @@
     </row>
     <row r="986" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I986" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J986" t="s">
         <v>146</v>
@@ -30687,7 +30687,7 @@
     </row>
     <row r="987" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I987" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J987" t="s">
         <v>147</v>
@@ -30701,7 +30701,7 @@
     </row>
     <row r="988" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I988" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J988" t="s">
         <v>148</v>
@@ -30715,7 +30715,7 @@
     </row>
     <row r="989" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I989" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J989" t="s">
         <v>149</v>
@@ -30729,7 +30729,7 @@
     </row>
     <row r="990" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I990" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J990" t="s">
         <v>150</v>
@@ -30743,7 +30743,7 @@
     </row>
     <row r="991" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I991" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J991" t="s">
         <v>151</v>
@@ -30757,7 +30757,7 @@
     </row>
     <row r="992" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I992" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J992" t="s">
         <v>152</v>
@@ -30771,7 +30771,7 @@
     </row>
     <row r="993" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I993" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J993" t="s">
         <v>153</v>
@@ -30785,7 +30785,7 @@
     </row>
     <row r="994" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I994" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J994" t="s">
         <v>154</v>
@@ -30799,7 +30799,7 @@
     </row>
     <row r="995" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I995" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J995" t="s">
         <v>155</v>
@@ -30813,7 +30813,7 @@
     </row>
     <row r="996" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I996" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J996" t="s">
         <v>156</v>
@@ -30827,7 +30827,7 @@
     </row>
     <row r="997" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I997" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J997" t="s">
         <v>157</v>
@@ -30841,7 +30841,7 @@
     </row>
     <row r="998" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I998" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J998" t="s">
         <v>158</v>
@@ -30855,7 +30855,7 @@
     </row>
     <row r="999" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I999" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J999" t="s">
         <v>159</v>
@@ -30869,7 +30869,7 @@
     </row>
     <row r="1000" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1000" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1000" t="s">
         <v>160</v>
@@ -30883,7 +30883,7 @@
     </row>
     <row r="1001" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1001" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1001" t="s">
         <v>161</v>
@@ -30897,7 +30897,7 @@
     </row>
     <row r="1002" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1002" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1002" t="s">
         <v>162</v>
@@ -30911,7 +30911,7 @@
     </row>
     <row r="1003" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1003" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1003" t="s">
         <v>163</v>
@@ -30925,7 +30925,7 @@
     </row>
     <row r="1004" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1004" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1004" t="s">
         <v>164</v>
@@ -30939,7 +30939,7 @@
     </row>
     <row r="1005" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1005" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1005" t="s">
         <v>165</v>
@@ -30953,7 +30953,7 @@
     </row>
     <row r="1006" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1006" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1006" t="s">
         <v>166</v>
@@ -30967,7 +30967,7 @@
     </row>
     <row r="1007" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1007" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1007" t="s">
         <v>167</v>
@@ -30981,7 +30981,7 @@
     </row>
     <row r="1008" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1008" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1008" t="s">
         <v>168</v>
@@ -30995,7 +30995,7 @@
     </row>
     <row r="1009" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1009" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1009" t="s">
         <v>169</v>
@@ -31009,7 +31009,7 @@
     </row>
     <row r="1010" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1010" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1010" t="s">
         <v>170</v>
@@ -31023,7 +31023,7 @@
     </row>
     <row r="1011" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1011" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1011" t="s">
         <v>171</v>
@@ -31037,7 +31037,7 @@
     </row>
     <row r="1012" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1012" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1012" t="s">
         <v>172</v>
@@ -31051,7 +31051,7 @@
     </row>
     <row r="1013" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1013" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1013" t="s">
         <v>173</v>
@@ -31065,7 +31065,7 @@
     </row>
     <row r="1014" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1014" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1014" t="s">
         <v>174</v>
@@ -31079,7 +31079,7 @@
     </row>
     <row r="1015" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1015" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1015" t="s">
         <v>175</v>
@@ -31093,7 +31093,7 @@
     </row>
     <row r="1016" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1016" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1016" t="s">
         <v>176</v>
@@ -31107,7 +31107,7 @@
     </row>
     <row r="1017" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1017" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1017" t="s">
         <v>177</v>
@@ -31121,7 +31121,7 @@
     </row>
     <row r="1018" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1018" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1018" t="s">
         <v>178</v>
@@ -31135,7 +31135,7 @@
     </row>
     <row r="1019" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1019" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1019" t="s">
         <v>179</v>
@@ -31149,7 +31149,7 @@
     </row>
     <row r="1020" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1020" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1020" t="s">
         <v>180</v>
@@ -31163,7 +31163,7 @@
     </row>
     <row r="1021" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1021" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1021" t="s">
         <v>181</v>
@@ -31177,7 +31177,7 @@
     </row>
     <row r="1022" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1022" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1022" t="s">
         <v>182</v>
@@ -31191,7 +31191,7 @@
     </row>
     <row r="1023" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1023" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1023" t="s">
         <v>183</v>
@@ -31205,7 +31205,7 @@
     </row>
     <row r="1024" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1024" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1024" t="s">
         <v>184</v>
@@ -31219,7 +31219,7 @@
     </row>
     <row r="1025" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1025" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1025" t="s">
         <v>185</v>
@@ -31233,7 +31233,7 @@
     </row>
     <row r="1026" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1026" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1026" t="s">
         <v>186</v>
@@ -31247,7 +31247,7 @@
     </row>
     <row r="1027" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1027" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1027" t="s">
         <v>187</v>
@@ -31261,7 +31261,7 @@
     </row>
     <row r="1028" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1028" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1028" t="s">
         <v>188</v>
@@ -31275,7 +31275,7 @@
     </row>
     <row r="1029" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1029" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1029" t="s">
         <v>189</v>
@@ -31289,7 +31289,7 @@
     </row>
     <row r="1030" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1030" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1030" t="s">
         <v>190</v>
@@ -31303,7 +31303,7 @@
     </row>
     <row r="1031" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1031" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1031" t="s">
         <v>191</v>
@@ -31317,7 +31317,7 @@
     </row>
     <row r="1032" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1032" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1032" t="s">
         <v>192</v>
@@ -31331,7 +31331,7 @@
     </row>
     <row r="1033" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1033" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1033" t="s">
         <v>193</v>
@@ -31345,7 +31345,7 @@
     </row>
     <row r="1034" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1034" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1034" t="s">
         <v>194</v>
@@ -31359,7 +31359,7 @@
     </row>
     <row r="1035" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1035" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1035" t="s">
         <v>195</v>
@@ -31373,7 +31373,7 @@
     </row>
     <row r="1036" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1036" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1036" t="s">
         <v>196</v>
@@ -31387,7 +31387,7 @@
     </row>
     <row r="1037" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1037" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1037" t="s">
         <v>197</v>
@@ -31401,7 +31401,7 @@
     </row>
     <row r="1038" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1038" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1038" t="s">
         <v>198</v>
@@ -31415,7 +31415,7 @@
     </row>
     <row r="1039" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1039" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1039" t="s">
         <v>199</v>
@@ -31429,7 +31429,7 @@
     </row>
     <row r="1040" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1040" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1040" t="s">
         <v>200</v>
@@ -31443,7 +31443,7 @@
     </row>
     <row r="1041" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1041" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1041" t="s">
         <v>201</v>
@@ -31457,7 +31457,7 @@
     </row>
     <row r="1042" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1042" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1042" t="s">
         <v>202</v>
@@ -31471,7 +31471,7 @@
     </row>
     <row r="1043" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1043" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1043" t="s">
         <v>203</v>
@@ -31485,7 +31485,7 @@
     </row>
     <row r="1044" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1044" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1044" t="s">
         <v>204</v>
@@ -31499,7 +31499,7 @@
     </row>
     <row r="1045" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1045" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1045" t="s">
         <v>205</v>
@@ -31513,7 +31513,7 @@
     </row>
     <row r="1046" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1046" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1046" t="s">
         <v>206</v>
@@ -31527,7 +31527,7 @@
     </row>
     <row r="1047" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1047" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1047" t="s">
         <v>207</v>
@@ -31541,7 +31541,7 @@
     </row>
     <row r="1048" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1048" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1048" t="s">
         <v>208</v>
@@ -31555,7 +31555,7 @@
     </row>
     <row r="1049" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1049" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1049" t="s">
         <v>209</v>
@@ -31569,7 +31569,7 @@
     </row>
     <row r="1050" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1050" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1050" t="s">
         <v>210</v>
@@ -31583,7 +31583,7 @@
     </row>
     <row r="1051" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1051" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1051" t="s">
         <v>211</v>
@@ -31597,7 +31597,7 @@
     </row>
     <row r="1052" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1052" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1052" t="s">
         <v>212</v>
@@ -31611,7 +31611,7 @@
     </row>
     <row r="1053" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1053" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1053" t="s">
         <v>213</v>
@@ -31625,7 +31625,7 @@
     </row>
     <row r="1054" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1054" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1054" t="s">
         <v>214</v>
@@ -31639,7 +31639,7 @@
     </row>
     <row r="1055" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1055" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1055" t="s">
         <v>215</v>
@@ -31653,7 +31653,7 @@
     </row>
     <row r="1056" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1056" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1056" t="s">
         <v>216</v>
@@ -31667,7 +31667,7 @@
     </row>
     <row r="1057" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1057" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J1057" t="s">
         <v>217</v>
@@ -31681,7 +31681,7 @@
     </row>
     <row r="1058" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1058" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1058" t="s">
         <v>123</v>
@@ -31695,7 +31695,7 @@
     </row>
     <row r="1059" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1059" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1059" t="s">
         <v>124</v>
@@ -31709,7 +31709,7 @@
     </row>
     <row r="1060" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1060" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1060" t="s">
         <v>125</v>
@@ -31723,7 +31723,7 @@
     </row>
     <row r="1061" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1061" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1061" t="s">
         <v>126</v>
@@ -31737,7 +31737,7 @@
     </row>
     <row r="1062" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1062" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1062" t="s">
         <v>127</v>
@@ -31751,7 +31751,7 @@
     </row>
     <row r="1063" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1063" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1063" t="s">
         <v>128</v>
@@ -31765,7 +31765,7 @@
     </row>
     <row r="1064" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1064" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1064" t="s">
         <v>129</v>
@@ -31779,7 +31779,7 @@
     </row>
     <row r="1065" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1065" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1065" t="s">
         <v>130</v>
@@ -31793,7 +31793,7 @@
     </row>
     <row r="1066" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1066" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1066" t="s">
         <v>131</v>
@@ -31807,7 +31807,7 @@
     </row>
     <row r="1067" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1067" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1067" t="s">
         <v>132</v>
@@ -31821,7 +31821,7 @@
     </row>
     <row r="1068" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1068" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1068" t="s">
         <v>133</v>
@@ -31835,7 +31835,7 @@
     </row>
     <row r="1069" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1069" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1069" t="s">
         <v>134</v>
@@ -31849,7 +31849,7 @@
     </row>
     <row r="1070" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1070" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1070" t="s">
         <v>135</v>
@@ -31863,7 +31863,7 @@
     </row>
     <row r="1071" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1071" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1071" t="s">
         <v>136</v>
@@ -31877,7 +31877,7 @@
     </row>
     <row r="1072" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1072" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1072" t="s">
         <v>137</v>
@@ -31891,7 +31891,7 @@
     </row>
     <row r="1073" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1073" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1073" t="s">
         <v>138</v>
@@ -31905,7 +31905,7 @@
     </row>
     <row r="1074" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1074" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1074" t="s">
         <v>139</v>
@@ -31919,7 +31919,7 @@
     </row>
     <row r="1075" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1075" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1075" t="s">
         <v>140</v>
@@ -31933,7 +31933,7 @@
     </row>
     <row r="1076" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1076" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1076" t="s">
         <v>141</v>
@@ -31947,7 +31947,7 @@
     </row>
     <row r="1077" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1077" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1077" t="s">
         <v>142</v>
@@ -31961,7 +31961,7 @@
     </row>
     <row r="1078" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1078" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1078" t="s">
         <v>143</v>
@@ -31975,7 +31975,7 @@
     </row>
     <row r="1079" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1079" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1079" t="s">
         <v>144</v>
@@ -31989,7 +31989,7 @@
     </row>
     <row r="1080" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1080" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1080" t="s">
         <v>145</v>
@@ -32003,7 +32003,7 @@
     </row>
     <row r="1081" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1081" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1081" t="s">
         <v>146</v>
@@ -32017,7 +32017,7 @@
     </row>
     <row r="1082" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1082" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1082" t="s">
         <v>147</v>
@@ -32031,7 +32031,7 @@
     </row>
     <row r="1083" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1083" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1083" t="s">
         <v>148</v>
@@ -32045,7 +32045,7 @@
     </row>
     <row r="1084" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1084" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1084" t="s">
         <v>149</v>
@@ -32059,7 +32059,7 @@
     </row>
     <row r="1085" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1085" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1085" t="s">
         <v>150</v>
@@ -32073,7 +32073,7 @@
     </row>
     <row r="1086" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1086" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1086" t="s">
         <v>151</v>
@@ -32087,7 +32087,7 @@
     </row>
     <row r="1087" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1087" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1087" t="s">
         <v>152</v>
@@ -32101,7 +32101,7 @@
     </row>
     <row r="1088" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1088" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1088" t="s">
         <v>153</v>
@@ -32115,7 +32115,7 @@
     </row>
     <row r="1089" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1089" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1089" t="s">
         <v>154</v>
@@ -32129,7 +32129,7 @@
     </row>
     <row r="1090" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1090" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1090" t="s">
         <v>155</v>
@@ -32143,7 +32143,7 @@
     </row>
     <row r="1091" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1091" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1091" t="s">
         <v>156</v>
@@ -32157,7 +32157,7 @@
     </row>
     <row r="1092" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1092" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1092" t="s">
         <v>157</v>
@@ -32171,7 +32171,7 @@
     </row>
     <row r="1093" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1093" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1093" t="s">
         <v>158</v>
@@ -32185,7 +32185,7 @@
     </row>
     <row r="1094" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1094" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1094" t="s">
         <v>159</v>
@@ -32199,7 +32199,7 @@
     </row>
     <row r="1095" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1095" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1095" t="s">
         <v>160</v>
@@ -32213,7 +32213,7 @@
     </row>
     <row r="1096" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1096" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1096" t="s">
         <v>161</v>
@@ -32227,7 +32227,7 @@
     </row>
     <row r="1097" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1097" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1097" t="s">
         <v>162</v>
@@ -32241,7 +32241,7 @@
     </row>
     <row r="1098" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1098" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1098" t="s">
         <v>163</v>
@@ -32255,7 +32255,7 @@
     </row>
     <row r="1099" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1099" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1099" t="s">
         <v>164</v>
@@ -32269,7 +32269,7 @@
     </row>
     <row r="1100" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1100" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1100" t="s">
         <v>165</v>
@@ -32283,7 +32283,7 @@
     </row>
     <row r="1101" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1101" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1101" t="s">
         <v>166</v>
@@ -32297,7 +32297,7 @@
     </row>
     <row r="1102" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1102" t="s">
         <v>167</v>
@@ -32311,7 +32311,7 @@
     </row>
     <row r="1103" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1103" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1103" t="s">
         <v>168</v>
@@ -32325,7 +32325,7 @@
     </row>
     <row r="1104" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1104" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1104" t="s">
         <v>169</v>
@@ -32339,7 +32339,7 @@
     </row>
     <row r="1105" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1105" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1105" t="s">
         <v>170</v>
@@ -32353,7 +32353,7 @@
     </row>
     <row r="1106" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1106" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1106" t="s">
         <v>171</v>
@@ -32367,7 +32367,7 @@
     </row>
     <row r="1107" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1107" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1107" t="s">
         <v>172</v>
@@ -32381,7 +32381,7 @@
     </row>
     <row r="1108" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1108" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1108" t="s">
         <v>173</v>
@@ -32395,7 +32395,7 @@
     </row>
     <row r="1109" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1109" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1109" t="s">
         <v>174</v>
@@ -32409,7 +32409,7 @@
     </row>
     <row r="1110" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1110" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1110" t="s">
         <v>175</v>
@@ -32423,7 +32423,7 @@
     </row>
     <row r="1111" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1111" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1111" t="s">
         <v>176</v>
@@ -32437,7 +32437,7 @@
     </row>
     <row r="1112" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1112" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1112" t="s">
         <v>177</v>
@@ -32451,7 +32451,7 @@
     </row>
     <row r="1113" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1113" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1113" t="s">
         <v>178</v>
@@ -32465,7 +32465,7 @@
     </row>
     <row r="1114" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1114" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1114" t="s">
         <v>179</v>
@@ -32479,7 +32479,7 @@
     </row>
     <row r="1115" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1115" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1115" t="s">
         <v>180</v>
@@ -32493,7 +32493,7 @@
     </row>
     <row r="1116" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1116" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1116" t="s">
         <v>181</v>
@@ -32507,7 +32507,7 @@
     </row>
     <row r="1117" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1117" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1117" t="s">
         <v>182</v>
@@ -32521,7 +32521,7 @@
     </row>
     <row r="1118" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1118" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1118" t="s">
         <v>183</v>
@@ -32535,7 +32535,7 @@
     </row>
     <row r="1119" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1119" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1119" t="s">
         <v>184</v>
@@ -32549,7 +32549,7 @@
     </row>
     <row r="1120" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1120" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1120" t="s">
         <v>185</v>
@@ -32563,7 +32563,7 @@
     </row>
     <row r="1121" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1121" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1121" t="s">
         <v>186</v>
@@ -32577,7 +32577,7 @@
     </row>
     <row r="1122" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1122" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1122" t="s">
         <v>187</v>
@@ -32591,7 +32591,7 @@
     </row>
     <row r="1123" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1123" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1123" t="s">
         <v>188</v>
@@ -32605,7 +32605,7 @@
     </row>
     <row r="1124" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1124" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1124" t="s">
         <v>189</v>
@@ -32619,7 +32619,7 @@
     </row>
     <row r="1125" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1125" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1125" t="s">
         <v>190</v>
@@ -32633,7 +32633,7 @@
     </row>
     <row r="1126" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1126" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1126" t="s">
         <v>191</v>
@@ -32647,7 +32647,7 @@
     </row>
     <row r="1127" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1127" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1127" t="s">
         <v>192</v>
@@ -32661,7 +32661,7 @@
     </row>
     <row r="1128" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1128" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1128" t="s">
         <v>193</v>
@@ -32675,7 +32675,7 @@
     </row>
     <row r="1129" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1129" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1129" t="s">
         <v>194</v>
@@ -32689,7 +32689,7 @@
     </row>
     <row r="1130" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1130" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1130" t="s">
         <v>195</v>
@@ -32703,7 +32703,7 @@
     </row>
     <row r="1131" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1131" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1131" t="s">
         <v>196</v>
@@ -32717,7 +32717,7 @@
     </row>
     <row r="1132" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1132" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1132" t="s">
         <v>197</v>
@@ -32731,7 +32731,7 @@
     </row>
     <row r="1133" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1133" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1133" t="s">
         <v>198</v>
@@ -32745,7 +32745,7 @@
     </row>
     <row r="1134" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1134" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1134" t="s">
         <v>199</v>
@@ -32759,7 +32759,7 @@
     </row>
     <row r="1135" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1135" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1135" t="s">
         <v>200</v>
@@ -32773,7 +32773,7 @@
     </row>
     <row r="1136" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1136" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1136" t="s">
         <v>201</v>
@@ -32787,7 +32787,7 @@
     </row>
     <row r="1137" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1137" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1137" t="s">
         <v>202</v>
@@ -32801,7 +32801,7 @@
     </row>
     <row r="1138" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1138" t="s">
         <v>203</v>
@@ -32815,7 +32815,7 @@
     </row>
     <row r="1139" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1139" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1139" t="s">
         <v>204</v>
@@ -32829,7 +32829,7 @@
     </row>
     <row r="1140" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1140" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1140" t="s">
         <v>205</v>
@@ -32843,7 +32843,7 @@
     </row>
     <row r="1141" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1141" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1141" t="s">
         <v>206</v>
@@ -32857,7 +32857,7 @@
     </row>
     <row r="1142" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1142" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1142" t="s">
         <v>207</v>
@@ -32871,7 +32871,7 @@
     </row>
     <row r="1143" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1143" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1143" t="s">
         <v>208</v>
@@ -32885,7 +32885,7 @@
     </row>
     <row r="1144" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1144" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1144" t="s">
         <v>209</v>
@@ -32899,7 +32899,7 @@
     </row>
     <row r="1145" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1145" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1145" t="s">
         <v>210</v>
@@ -32913,7 +32913,7 @@
     </row>
     <row r="1146" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1146" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1146" t="s">
         <v>211</v>
@@ -32927,7 +32927,7 @@
     </row>
     <row r="1147" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1147" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1147" t="s">
         <v>212</v>
@@ -32941,7 +32941,7 @@
     </row>
     <row r="1148" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1148" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1148" t="s">
         <v>213</v>
@@ -32955,7 +32955,7 @@
     </row>
     <row r="1149" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1149" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1149" t="s">
         <v>214</v>
@@ -32969,7 +32969,7 @@
     </row>
     <row r="1150" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1150" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1150" t="s">
         <v>215</v>
@@ -32983,7 +32983,7 @@
     </row>
     <row r="1151" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1151" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1151" t="s">
         <v>216</v>
@@ -32997,7 +32997,7 @@
     </row>
     <row r="1152" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1152" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J1152" t="s">
         <v>217</v>
@@ -33011,7 +33011,7 @@
     </row>
     <row r="1153" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1153" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1153" t="s">
         <v>123</v>
@@ -33025,7 +33025,7 @@
     </row>
     <row r="1154" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1154" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1154" t="s">
         <v>124</v>
@@ -33039,7 +33039,7 @@
     </row>
     <row r="1155" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1155" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1155" t="s">
         <v>125</v>
@@ -33053,7 +33053,7 @@
     </row>
     <row r="1156" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1156" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1156" t="s">
         <v>126</v>
@@ -33067,7 +33067,7 @@
     </row>
     <row r="1157" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1157" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1157" t="s">
         <v>127</v>
@@ -33081,7 +33081,7 @@
     </row>
     <row r="1158" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1158" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1158" t="s">
         <v>128</v>
@@ -33095,7 +33095,7 @@
     </row>
     <row r="1159" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1159" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1159" t="s">
         <v>129</v>
@@ -33109,7 +33109,7 @@
     </row>
     <row r="1160" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1160" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1160" t="s">
         <v>130</v>
@@ -33123,7 +33123,7 @@
     </row>
     <row r="1161" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1161" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1161" t="s">
         <v>131</v>
@@ -33137,7 +33137,7 @@
     </row>
     <row r="1162" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1162" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1162" t="s">
         <v>132</v>
@@ -33151,7 +33151,7 @@
     </row>
     <row r="1163" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1163" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1163" t="s">
         <v>133</v>
@@ -33165,7 +33165,7 @@
     </row>
     <row r="1164" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1164" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1164" t="s">
         <v>134</v>
@@ -33179,7 +33179,7 @@
     </row>
     <row r="1165" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1165" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1165" t="s">
         <v>135</v>
@@ -33193,7 +33193,7 @@
     </row>
     <row r="1166" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1166" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1166" t="s">
         <v>136</v>
@@ -33207,7 +33207,7 @@
     </row>
     <row r="1167" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1167" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1167" t="s">
         <v>137</v>
@@ -33221,7 +33221,7 @@
     </row>
     <row r="1168" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1168" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1168" t="s">
         <v>138</v>
@@ -33235,7 +33235,7 @@
     </row>
     <row r="1169" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1169" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1169" t="s">
         <v>139</v>
@@ -33249,7 +33249,7 @@
     </row>
     <row r="1170" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1170" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1170" t="s">
         <v>140</v>
@@ -33263,7 +33263,7 @@
     </row>
     <row r="1171" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1171" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1171" t="s">
         <v>141</v>
@@ -33277,7 +33277,7 @@
     </row>
     <row r="1172" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1172" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1172" t="s">
         <v>142</v>
@@ -33291,7 +33291,7 @@
     </row>
     <row r="1173" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1173" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1173" t="s">
         <v>143</v>
@@ -33305,7 +33305,7 @@
     </row>
     <row r="1174" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1174" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1174" t="s">
         <v>144</v>
@@ -33319,7 +33319,7 @@
     </row>
     <row r="1175" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1175" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1175" t="s">
         <v>145</v>
@@ -33333,7 +33333,7 @@
     </row>
     <row r="1176" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1176" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1176" t="s">
         <v>146</v>
@@ -33347,7 +33347,7 @@
     </row>
     <row r="1177" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1177" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1177" t="s">
         <v>147</v>
@@ -33361,7 +33361,7 @@
     </row>
     <row r="1178" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1178" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1178" t="s">
         <v>148</v>
@@ -33375,7 +33375,7 @@
     </row>
     <row r="1179" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1179" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1179" t="s">
         <v>149</v>
@@ -33389,7 +33389,7 @@
     </row>
     <row r="1180" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1180" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1180" t="s">
         <v>150</v>
@@ -33403,7 +33403,7 @@
     </row>
     <row r="1181" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1181" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1181" t="s">
         <v>151</v>
@@ -33417,7 +33417,7 @@
     </row>
     <row r="1182" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1182" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1182" t="s">
         <v>152</v>
@@ -33431,7 +33431,7 @@
     </row>
     <row r="1183" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1183" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1183" t="s">
         <v>153</v>
@@ -33445,7 +33445,7 @@
     </row>
     <row r="1184" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1184" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1184" t="s">
         <v>154</v>
@@ -33459,7 +33459,7 @@
     </row>
     <row r="1185" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1185" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1185" t="s">
         <v>155</v>
@@ -33473,7 +33473,7 @@
     </row>
     <row r="1186" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1186" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1186" t="s">
         <v>156</v>
@@ -33487,7 +33487,7 @@
     </row>
     <row r="1187" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1187" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1187" t="s">
         <v>157</v>
@@ -33501,7 +33501,7 @@
     </row>
     <row r="1188" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1188" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1188" t="s">
         <v>158</v>
@@ -33515,7 +33515,7 @@
     </row>
     <row r="1189" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1189" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1189" t="s">
         <v>159</v>
@@ -33529,7 +33529,7 @@
     </row>
     <row r="1190" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1190" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1190" t="s">
         <v>160</v>
@@ -33543,7 +33543,7 @@
     </row>
     <row r="1191" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1191" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1191" t="s">
         <v>161</v>
@@ -33557,7 +33557,7 @@
     </row>
     <row r="1192" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1192" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1192" t="s">
         <v>162</v>
@@ -33571,7 +33571,7 @@
     </row>
     <row r="1193" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1193" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1193" t="s">
         <v>163</v>
@@ -33585,7 +33585,7 @@
     </row>
     <row r="1194" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1194" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1194" t="s">
         <v>164</v>
@@ -33599,7 +33599,7 @@
     </row>
     <row r="1195" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1195" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1195" t="s">
         <v>165</v>
@@ -33613,7 +33613,7 @@
     </row>
     <row r="1196" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1196" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1196" t="s">
         <v>166</v>
@@ -33627,7 +33627,7 @@
     </row>
     <row r="1197" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1197" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1197" t="s">
         <v>167</v>
@@ -33641,7 +33641,7 @@
     </row>
     <row r="1198" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1198" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1198" t="s">
         <v>168</v>
@@ -33655,7 +33655,7 @@
     </row>
     <row r="1199" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1199" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1199" t="s">
         <v>169</v>
@@ -33669,7 +33669,7 @@
     </row>
     <row r="1200" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1200" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1200" t="s">
         <v>170</v>
@@ -33683,7 +33683,7 @@
     </row>
     <row r="1201" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1201" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1201" t="s">
         <v>171</v>
@@ -33697,7 +33697,7 @@
     </row>
     <row r="1202" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1202" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1202" t="s">
         <v>172</v>
@@ -33711,7 +33711,7 @@
     </row>
     <row r="1203" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1203" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1203" t="s">
         <v>173</v>
@@ -33725,7 +33725,7 @@
     </row>
     <row r="1204" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1204" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1204" t="s">
         <v>174</v>
@@ -33739,7 +33739,7 @@
     </row>
     <row r="1205" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1205" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1205" t="s">
         <v>175</v>
@@ -33753,7 +33753,7 @@
     </row>
     <row r="1206" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1206" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1206" t="s">
         <v>176</v>
@@ -33767,7 +33767,7 @@
     </row>
     <row r="1207" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1207" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1207" t="s">
         <v>177</v>
@@ -33781,7 +33781,7 @@
     </row>
     <row r="1208" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1208" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1208" t="s">
         <v>178</v>
@@ -33795,7 +33795,7 @@
     </row>
     <row r="1209" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1209" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1209" t="s">
         <v>179</v>
@@ -33809,7 +33809,7 @@
     </row>
     <row r="1210" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1210" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1210" t="s">
         <v>180</v>
@@ -33823,7 +33823,7 @@
     </row>
     <row r="1211" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1211" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1211" t="s">
         <v>181</v>
@@ -33837,7 +33837,7 @@
     </row>
     <row r="1212" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1212" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1212" t="s">
         <v>182</v>
@@ -33851,7 +33851,7 @@
     </row>
     <row r="1213" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1213" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1213" t="s">
         <v>183</v>
@@ -33865,7 +33865,7 @@
     </row>
     <row r="1214" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1214" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1214" t="s">
         <v>184</v>
@@ -33879,7 +33879,7 @@
     </row>
     <row r="1215" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1215" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1215" t="s">
         <v>185</v>
@@ -33893,7 +33893,7 @@
     </row>
     <row r="1216" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1216" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1216" t="s">
         <v>186</v>
@@ -33907,7 +33907,7 @@
     </row>
     <row r="1217" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1217" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1217" t="s">
         <v>187</v>
@@ -33921,7 +33921,7 @@
     </row>
     <row r="1218" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1218" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1218" t="s">
         <v>188</v>
@@ -33935,7 +33935,7 @@
     </row>
     <row r="1219" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1219" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1219" t="s">
         <v>189</v>
@@ -33949,7 +33949,7 @@
     </row>
     <row r="1220" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1220" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1220" t="s">
         <v>190</v>
@@ -33963,7 +33963,7 @@
     </row>
     <row r="1221" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1221" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1221" t="s">
         <v>191</v>
@@ -33977,7 +33977,7 @@
     </row>
     <row r="1222" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1222" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1222" t="s">
         <v>192</v>
@@ -33991,7 +33991,7 @@
     </row>
     <row r="1223" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1223" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1223" t="s">
         <v>193</v>
@@ -34005,7 +34005,7 @@
     </row>
     <row r="1224" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1224" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1224" t="s">
         <v>194</v>
@@ -34019,7 +34019,7 @@
     </row>
     <row r="1225" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1225" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1225" t="s">
         <v>195</v>
@@ -34033,7 +34033,7 @@
     </row>
     <row r="1226" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1226" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1226" t="s">
         <v>196</v>
@@ -34047,7 +34047,7 @@
     </row>
     <row r="1227" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1227" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1227" t="s">
         <v>197</v>
@@ -34061,7 +34061,7 @@
     </row>
     <row r="1228" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1228" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1228" t="s">
         <v>198</v>
@@ -34075,7 +34075,7 @@
     </row>
     <row r="1229" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1229" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1229" t="s">
         <v>199</v>
@@ -34089,7 +34089,7 @@
     </row>
     <row r="1230" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1230" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1230" t="s">
         <v>200</v>
@@ -34103,7 +34103,7 @@
     </row>
     <row r="1231" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1231" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1231" t="s">
         <v>201</v>
@@ -34117,7 +34117,7 @@
     </row>
     <row r="1232" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1232" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1232" t="s">
         <v>202</v>
@@ -34131,7 +34131,7 @@
     </row>
     <row r="1233" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1233" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1233" t="s">
         <v>203</v>
@@ -34145,7 +34145,7 @@
     </row>
     <row r="1234" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1234" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1234" t="s">
         <v>204</v>
@@ -34159,7 +34159,7 @@
     </row>
     <row r="1235" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1235" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1235" t="s">
         <v>205</v>
@@ -34173,7 +34173,7 @@
     </row>
     <row r="1236" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1236" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1236" t="s">
         <v>206</v>
@@ -34187,7 +34187,7 @@
     </row>
     <row r="1237" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1237" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1237" t="s">
         <v>207</v>
@@ -34201,7 +34201,7 @@
     </row>
     <row r="1238" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1238" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1238" t="s">
         <v>208</v>
@@ -34215,7 +34215,7 @@
     </row>
     <row r="1239" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1239" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1239" t="s">
         <v>209</v>
@@ -34229,7 +34229,7 @@
     </row>
     <row r="1240" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1240" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1240" t="s">
         <v>210</v>
@@ -34243,7 +34243,7 @@
     </row>
     <row r="1241" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1241" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1241" t="s">
         <v>211</v>
@@ -34257,7 +34257,7 @@
     </row>
     <row r="1242" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1242" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1242" t="s">
         <v>212</v>
@@ -34271,7 +34271,7 @@
     </row>
     <row r="1243" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1243" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1243" t="s">
         <v>213</v>
@@ -34285,7 +34285,7 @@
     </row>
     <row r="1244" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1244" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1244" t="s">
         <v>214</v>
@@ -34299,7 +34299,7 @@
     </row>
     <row r="1245" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1245" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1245" t="s">
         <v>215</v>
@@ -34313,7 +34313,7 @@
     </row>
     <row r="1246" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1246" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1246" t="s">
         <v>216</v>
@@ -34327,7 +34327,7 @@
     </row>
     <row r="1247" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1247" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J1247" t="s">
         <v>217</v>
@@ -34341,7 +34341,7 @@
     </row>
     <row r="1248" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1248" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1248" t="s">
         <v>123</v>
@@ -34355,7 +34355,7 @@
     </row>
     <row r="1249" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1249" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1249" t="s">
         <v>124</v>
@@ -34369,7 +34369,7 @@
     </row>
     <row r="1250" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1250" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1250" t="s">
         <v>125</v>
@@ -34383,7 +34383,7 @@
     </row>
     <row r="1251" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1251" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1251" t="s">
         <v>126</v>
@@ -34397,7 +34397,7 @@
     </row>
     <row r="1252" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1252" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1252" t="s">
         <v>127</v>
@@ -34411,7 +34411,7 @@
     </row>
     <row r="1253" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1253" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1253" t="s">
         <v>128</v>
@@ -34425,7 +34425,7 @@
     </row>
     <row r="1254" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1254" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1254" t="s">
         <v>129</v>
@@ -34439,7 +34439,7 @@
     </row>
     <row r="1255" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1255" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1255" t="s">
         <v>130</v>
@@ -34453,7 +34453,7 @@
     </row>
     <row r="1256" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1256" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1256" t="s">
         <v>131</v>
@@ -34467,7 +34467,7 @@
     </row>
     <row r="1257" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1257" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1257" t="s">
         <v>132</v>
@@ -34481,7 +34481,7 @@
     </row>
     <row r="1258" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1258" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1258" t="s">
         <v>133</v>
@@ -34495,7 +34495,7 @@
     </row>
     <row r="1259" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1259" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1259" t="s">
         <v>134</v>
@@ -34509,7 +34509,7 @@
     </row>
     <row r="1260" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1260" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1260" t="s">
         <v>135</v>
@@ -34523,7 +34523,7 @@
     </row>
     <row r="1261" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1261" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1261" t="s">
         <v>136</v>
@@ -34537,7 +34537,7 @@
     </row>
     <row r="1262" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1262" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1262" t="s">
         <v>137</v>
@@ -34551,7 +34551,7 @@
     </row>
     <row r="1263" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1263" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1263" t="s">
         <v>138</v>
@@ -34565,7 +34565,7 @@
     </row>
     <row r="1264" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1264" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1264" t="s">
         <v>139</v>
@@ -34579,7 +34579,7 @@
     </row>
     <row r="1265" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1265" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1265" t="s">
         <v>140</v>
@@ -34593,7 +34593,7 @@
     </row>
     <row r="1266" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1266" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1266" t="s">
         <v>141</v>
@@ -34607,7 +34607,7 @@
     </row>
     <row r="1267" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1267" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1267" t="s">
         <v>142</v>
@@ -34621,7 +34621,7 @@
     </row>
     <row r="1268" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1268" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1268" t="s">
         <v>143</v>
@@ -34635,7 +34635,7 @@
     </row>
     <row r="1269" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1269" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1269" t="s">
         <v>144</v>
@@ -34649,7 +34649,7 @@
     </row>
     <row r="1270" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1270" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1270" t="s">
         <v>145</v>
@@ -34663,7 +34663,7 @@
     </row>
     <row r="1271" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1271" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1271" t="s">
         <v>146</v>
@@ -34677,7 +34677,7 @@
     </row>
     <row r="1272" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1272" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1272" t="s">
         <v>147</v>
@@ -34691,7 +34691,7 @@
     </row>
     <row r="1273" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1273" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1273" t="s">
         <v>148</v>
@@ -34705,7 +34705,7 @@
     </row>
     <row r="1274" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1274" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1274" t="s">
         <v>149</v>
@@ -34719,7 +34719,7 @@
     </row>
     <row r="1275" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1275" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1275" t="s">
         <v>150</v>
@@ -34733,7 +34733,7 @@
     </row>
     <row r="1276" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1276" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1276" t="s">
         <v>151</v>
@@ -34747,7 +34747,7 @@
     </row>
     <row r="1277" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1277" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1277" t="s">
         <v>152</v>
@@ -34761,7 +34761,7 @@
     </row>
     <row r="1278" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1278" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1278" t="s">
         <v>153</v>
@@ -34775,7 +34775,7 @@
     </row>
     <row r="1279" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1279" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1279" t="s">
         <v>154</v>
@@ -34789,7 +34789,7 @@
     </row>
     <row r="1280" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1280" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1280" t="s">
         <v>155</v>
@@ -34803,7 +34803,7 @@
     </row>
     <row r="1281" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1281" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1281" t="s">
         <v>156</v>
@@ -34817,7 +34817,7 @@
     </row>
     <row r="1282" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1282" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1282" t="s">
         <v>157</v>
@@ -34831,7 +34831,7 @@
     </row>
     <row r="1283" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1283" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1283" t="s">
         <v>158</v>
@@ -34845,7 +34845,7 @@
     </row>
     <row r="1284" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1284" t="s">
         <v>159</v>
@@ -34859,7 +34859,7 @@
     </row>
     <row r="1285" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1285" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1285" t="s">
         <v>160</v>
@@ -34873,7 +34873,7 @@
     </row>
     <row r="1286" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1286" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1286" t="s">
         <v>161</v>
@@ -34887,7 +34887,7 @@
     </row>
     <row r="1287" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1287" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1287" t="s">
         <v>162</v>
@@ -34901,7 +34901,7 @@
     </row>
     <row r="1288" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1288" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1288" t="s">
         <v>163</v>
@@ -34915,7 +34915,7 @@
     </row>
     <row r="1289" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1289" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1289" t="s">
         <v>164</v>
@@ -34929,7 +34929,7 @@
     </row>
     <row r="1290" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1290" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1290" t="s">
         <v>165</v>
@@ -34943,7 +34943,7 @@
     </row>
     <row r="1291" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1291" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1291" t="s">
         <v>166</v>
@@ -34957,7 +34957,7 @@
     </row>
     <row r="1292" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1292" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1292" t="s">
         <v>167</v>
@@ -34971,7 +34971,7 @@
     </row>
     <row r="1293" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1293" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1293" t="s">
         <v>168</v>
@@ -34985,7 +34985,7 @@
     </row>
     <row r="1294" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1294" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1294" t="s">
         <v>169</v>
@@ -34999,7 +34999,7 @@
     </row>
     <row r="1295" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1295" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1295" t="s">
         <v>170</v>
@@ -35013,7 +35013,7 @@
     </row>
     <row r="1296" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1296" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1296" t="s">
         <v>171</v>
@@ -35027,7 +35027,7 @@
     </row>
     <row r="1297" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1297" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1297" t="s">
         <v>172</v>
@@ -35041,7 +35041,7 @@
     </row>
     <row r="1298" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1298" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1298" t="s">
         <v>173</v>
@@ -35055,7 +35055,7 @@
     </row>
     <row r="1299" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1299" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1299" t="s">
         <v>174</v>
@@ -35069,7 +35069,7 @@
     </row>
     <row r="1300" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1300" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1300" t="s">
         <v>175</v>
@@ -35083,7 +35083,7 @@
     </row>
     <row r="1301" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1301" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1301" t="s">
         <v>176</v>
@@ -35097,7 +35097,7 @@
     </row>
     <row r="1302" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1302" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1302" t="s">
         <v>177</v>
@@ -35111,7 +35111,7 @@
     </row>
     <row r="1303" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1303" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1303" t="s">
         <v>178</v>
@@ -35125,7 +35125,7 @@
     </row>
     <row r="1304" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1304" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1304" t="s">
         <v>179</v>
@@ -35139,7 +35139,7 @@
     </row>
     <row r="1305" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1305" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1305" t="s">
         <v>180</v>
@@ -35153,7 +35153,7 @@
     </row>
     <row r="1306" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1306" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1306" t="s">
         <v>181</v>
@@ -35167,7 +35167,7 @@
     </row>
     <row r="1307" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1307" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1307" t="s">
         <v>182</v>
@@ -35181,7 +35181,7 @@
     </row>
     <row r="1308" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1308" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1308" t="s">
         <v>183</v>
@@ -35195,7 +35195,7 @@
     </row>
     <row r="1309" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1309" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1309" t="s">
         <v>184</v>
@@ -35209,7 +35209,7 @@
     </row>
     <row r="1310" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1310" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1310" t="s">
         <v>185</v>
@@ -35223,7 +35223,7 @@
     </row>
     <row r="1311" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1311" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1311" t="s">
         <v>186</v>
@@ -35237,7 +35237,7 @@
     </row>
     <row r="1312" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1312" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1312" t="s">
         <v>187</v>
@@ -35251,7 +35251,7 @@
     </row>
     <row r="1313" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1313" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1313" t="s">
         <v>188</v>
@@ -35265,7 +35265,7 @@
     </row>
     <row r="1314" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1314" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1314" t="s">
         <v>189</v>
@@ -35279,7 +35279,7 @@
     </row>
     <row r="1315" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1315" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1315" t="s">
         <v>190</v>
@@ -35293,7 +35293,7 @@
     </row>
     <row r="1316" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1316" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1316" t="s">
         <v>191</v>
@@ -35307,7 +35307,7 @@
     </row>
     <row r="1317" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1317" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1317" t="s">
         <v>192</v>
@@ -35321,7 +35321,7 @@
     </row>
     <row r="1318" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1318" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1318" t="s">
         <v>193</v>
@@ -35335,7 +35335,7 @@
     </row>
     <row r="1319" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1319" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1319" t="s">
         <v>194</v>
@@ -35349,7 +35349,7 @@
     </row>
     <row r="1320" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1320" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1320" t="s">
         <v>195</v>
@@ -35363,7 +35363,7 @@
     </row>
     <row r="1321" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1321" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1321" t="s">
         <v>196</v>
@@ -35377,7 +35377,7 @@
     </row>
     <row r="1322" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1322" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1322" t="s">
         <v>197</v>
@@ -35391,7 +35391,7 @@
     </row>
     <row r="1323" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1323" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1323" t="s">
         <v>198</v>
@@ -35405,7 +35405,7 @@
     </row>
     <row r="1324" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1324" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1324" t="s">
         <v>199</v>
@@ -35419,7 +35419,7 @@
     </row>
     <row r="1325" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1325" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1325" t="s">
         <v>200</v>
@@ -35433,7 +35433,7 @@
     </row>
     <row r="1326" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1326" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1326" t="s">
         <v>201</v>
@@ -35447,7 +35447,7 @@
     </row>
     <row r="1327" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1327" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1327" t="s">
         <v>202</v>
@@ -35461,7 +35461,7 @@
     </row>
     <row r="1328" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1328" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1328" t="s">
         <v>203</v>
@@ -35475,7 +35475,7 @@
     </row>
     <row r="1329" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1329" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1329" t="s">
         <v>204</v>
@@ -35489,7 +35489,7 @@
     </row>
     <row r="1330" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1330" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1330" t="s">
         <v>205</v>
@@ -35503,7 +35503,7 @@
     </row>
     <row r="1331" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1331" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1331" t="s">
         <v>206</v>
@@ -35517,7 +35517,7 @@
     </row>
     <row r="1332" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1332" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1332" t="s">
         <v>207</v>
@@ -35531,7 +35531,7 @@
     </row>
     <row r="1333" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1333" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1333" t="s">
         <v>208</v>
@@ -35545,7 +35545,7 @@
     </row>
     <row r="1334" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1334" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1334" t="s">
         <v>209</v>
@@ -35559,7 +35559,7 @@
     </row>
     <row r="1335" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1335" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1335" t="s">
         <v>210</v>
@@ -35573,7 +35573,7 @@
     </row>
     <row r="1336" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1336" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1336" t="s">
         <v>211</v>
@@ -35587,7 +35587,7 @@
     </row>
     <row r="1337" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1337" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1337" t="s">
         <v>212</v>
@@ -35601,7 +35601,7 @@
     </row>
     <row r="1338" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1338" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1338" t="s">
         <v>213</v>
@@ -35615,7 +35615,7 @@
     </row>
     <row r="1339" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1339" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1339" t="s">
         <v>214</v>
@@ -35629,7 +35629,7 @@
     </row>
     <row r="1340" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1340" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1340" t="s">
         <v>215</v>
@@ -35643,7 +35643,7 @@
     </row>
     <row r="1341" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1341" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1341" t="s">
         <v>216</v>
@@ -35657,7 +35657,7 @@
     </row>
     <row r="1342" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1342" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J1342" t="s">
         <v>217</v>
@@ -35671,7 +35671,7 @@
     </row>
     <row r="1343" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1343" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1343" t="s">
         <v>123</v>
@@ -35685,7 +35685,7 @@
     </row>
     <row r="1344" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1344" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1344" t="s">
         <v>124</v>
@@ -35699,7 +35699,7 @@
     </row>
     <row r="1345" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1345" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1345" t="s">
         <v>125</v>
@@ -35713,7 +35713,7 @@
     </row>
     <row r="1346" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1346" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1346" t="s">
         <v>126</v>
@@ -35727,7 +35727,7 @@
     </row>
     <row r="1347" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1347" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1347" t="s">
         <v>127</v>
@@ -35741,7 +35741,7 @@
     </row>
     <row r="1348" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1348" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1348" t="s">
         <v>128</v>
@@ -35755,7 +35755,7 @@
     </row>
     <row r="1349" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1349" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1349" t="s">
         <v>129</v>
@@ -35769,7 +35769,7 @@
     </row>
     <row r="1350" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1350" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1350" t="s">
         <v>130</v>
@@ -35783,7 +35783,7 @@
     </row>
     <row r="1351" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1351" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1351" t="s">
         <v>131</v>
@@ -35797,7 +35797,7 @@
     </row>
     <row r="1352" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1352" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1352" t="s">
         <v>132</v>
@@ -35811,7 +35811,7 @@
     </row>
     <row r="1353" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1353" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1353" t="s">
         <v>133</v>
@@ -35825,7 +35825,7 @@
     </row>
     <row r="1354" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1354" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1354" t="s">
         <v>134</v>
@@ -35839,7 +35839,7 @@
     </row>
     <row r="1355" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1355" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1355" t="s">
         <v>135</v>
@@ -35853,7 +35853,7 @@
     </row>
     <row r="1356" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1356" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1356" t="s">
         <v>136</v>
@@ -35867,7 +35867,7 @@
     </row>
     <row r="1357" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1357" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1357" t="s">
         <v>137</v>
@@ -35881,7 +35881,7 @@
     </row>
     <row r="1358" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1358" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1358" t="s">
         <v>138</v>
@@ -35895,7 +35895,7 @@
     </row>
     <row r="1359" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1359" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1359" t="s">
         <v>139</v>
@@ -35909,7 +35909,7 @@
     </row>
     <row r="1360" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1360" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1360" t="s">
         <v>140</v>
@@ -35923,7 +35923,7 @@
     </row>
     <row r="1361" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1361" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1361" t="s">
         <v>141</v>
@@ -35937,7 +35937,7 @@
     </row>
     <row r="1362" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1362" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1362" t="s">
         <v>142</v>
@@ -35951,7 +35951,7 @@
     </row>
     <row r="1363" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1363" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1363" t="s">
         <v>143</v>
@@ -35965,7 +35965,7 @@
     </row>
     <row r="1364" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1364" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1364" t="s">
         <v>144</v>
@@ -35979,7 +35979,7 @@
     </row>
     <row r="1365" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1365" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1365" t="s">
         <v>145</v>
@@ -35993,7 +35993,7 @@
     </row>
     <row r="1366" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1366" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1366" t="s">
         <v>146</v>
@@ -36007,7 +36007,7 @@
     </row>
     <row r="1367" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1367" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1367" t="s">
         <v>147</v>
@@ -36021,7 +36021,7 @@
     </row>
     <row r="1368" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1368" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1368" t="s">
         <v>148</v>
@@ -36035,7 +36035,7 @@
     </row>
     <row r="1369" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1369" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1369" t="s">
         <v>149</v>
@@ -36049,7 +36049,7 @@
     </row>
     <row r="1370" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1370" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1370" t="s">
         <v>150</v>
@@ -36063,7 +36063,7 @@
     </row>
     <row r="1371" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1371" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1371" t="s">
         <v>151</v>
@@ -36077,7 +36077,7 @@
     </row>
     <row r="1372" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1372" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1372" t="s">
         <v>152</v>
@@ -36091,7 +36091,7 @@
     </row>
     <row r="1373" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1373" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1373" t="s">
         <v>153</v>
@@ -36105,7 +36105,7 @@
     </row>
     <row r="1374" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1374" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1374" t="s">
         <v>154</v>
@@ -36119,7 +36119,7 @@
     </row>
     <row r="1375" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1375" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1375" t="s">
         <v>155</v>
@@ -36133,7 +36133,7 @@
     </row>
     <row r="1376" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1376" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1376" t="s">
         <v>156</v>
@@ -36147,7 +36147,7 @@
     </row>
     <row r="1377" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1377" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1377" t="s">
         <v>157</v>
@@ -36161,7 +36161,7 @@
     </row>
     <row r="1378" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1378" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1378" t="s">
         <v>158</v>
@@ -36175,7 +36175,7 @@
     </row>
     <row r="1379" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1379" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1379" t="s">
         <v>159</v>
@@ -36189,7 +36189,7 @@
     </row>
     <row r="1380" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1380" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1380" t="s">
         <v>160</v>
@@ -36203,7 +36203,7 @@
     </row>
     <row r="1381" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1381" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1381" t="s">
         <v>161</v>
@@ -36217,7 +36217,7 @@
     </row>
     <row r="1382" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1382" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1382" t="s">
         <v>162</v>
@@ -36231,7 +36231,7 @@
     </row>
     <row r="1383" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1383" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1383" t="s">
         <v>163</v>
@@ -36245,7 +36245,7 @@
     </row>
     <row r="1384" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1384" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1384" t="s">
         <v>164</v>
@@ -36259,7 +36259,7 @@
     </row>
     <row r="1385" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1385" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1385" t="s">
         <v>165</v>
@@ -36273,7 +36273,7 @@
     </row>
     <row r="1386" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1386" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1386" t="s">
         <v>166</v>
@@ -36287,7 +36287,7 @@
     </row>
     <row r="1387" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1387" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1387" t="s">
         <v>167</v>
@@ -36301,7 +36301,7 @@
     </row>
     <row r="1388" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1388" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1388" t="s">
         <v>168</v>
@@ -36315,7 +36315,7 @@
     </row>
     <row r="1389" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1389" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1389" t="s">
         <v>169</v>
@@ -36329,7 +36329,7 @@
     </row>
     <row r="1390" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1390" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1390" t="s">
         <v>170</v>
@@ -36343,7 +36343,7 @@
     </row>
     <row r="1391" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1391" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1391" t="s">
         <v>171</v>
@@ -36357,7 +36357,7 @@
     </row>
     <row r="1392" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1392" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1392" t="s">
         <v>172</v>
@@ -36371,7 +36371,7 @@
     </row>
     <row r="1393" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1393" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1393" t="s">
         <v>173</v>
@@ -36385,7 +36385,7 @@
     </row>
     <row r="1394" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1394" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1394" t="s">
         <v>174</v>
@@ -36399,7 +36399,7 @@
     </row>
     <row r="1395" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1395" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1395" t="s">
         <v>175</v>
@@ -36413,7 +36413,7 @@
     </row>
     <row r="1396" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1396" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1396" t="s">
         <v>176</v>
@@ -36427,7 +36427,7 @@
     </row>
     <row r="1397" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1397" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1397" t="s">
         <v>177</v>
@@ -36441,7 +36441,7 @@
     </row>
     <row r="1398" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1398" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1398" t="s">
         <v>178</v>
@@ -36455,7 +36455,7 @@
     </row>
     <row r="1399" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1399" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1399" t="s">
         <v>179</v>
@@ -36469,7 +36469,7 @@
     </row>
     <row r="1400" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1400" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1400" t="s">
         <v>180</v>
@@ -36483,7 +36483,7 @@
     </row>
     <row r="1401" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1401" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1401" t="s">
         <v>181</v>
@@ -36497,7 +36497,7 @@
     </row>
     <row r="1402" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1402" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1402" t="s">
         <v>182</v>
@@ -36511,7 +36511,7 @@
     </row>
     <row r="1403" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1403" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1403" t="s">
         <v>183</v>
@@ -36525,7 +36525,7 @@
     </row>
     <row r="1404" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1404" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1404" t="s">
         <v>184</v>
@@ -36539,7 +36539,7 @@
     </row>
     <row r="1405" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1405" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1405" t="s">
         <v>185</v>
@@ -36553,7 +36553,7 @@
     </row>
     <row r="1406" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1406" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1406" t="s">
         <v>186</v>
@@ -36567,7 +36567,7 @@
     </row>
     <row r="1407" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1407" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1407" t="s">
         <v>187</v>
@@ -36581,7 +36581,7 @@
     </row>
     <row r="1408" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1408" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1408" t="s">
         <v>188</v>
@@ -36595,7 +36595,7 @@
     </row>
     <row r="1409" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1409" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1409" t="s">
         <v>189</v>
@@ -36609,7 +36609,7 @@
     </row>
     <row r="1410" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1410" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1410" t="s">
         <v>190</v>
@@ -36623,7 +36623,7 @@
     </row>
     <row r="1411" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1411" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1411" t="s">
         <v>191</v>
@@ -36637,7 +36637,7 @@
     </row>
     <row r="1412" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1412" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1412" t="s">
         <v>192</v>
@@ -36651,7 +36651,7 @@
     </row>
     <row r="1413" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1413" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1413" t="s">
         <v>193</v>
@@ -36665,7 +36665,7 @@
     </row>
     <row r="1414" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1414" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1414" t="s">
         <v>194</v>
@@ -36679,7 +36679,7 @@
     </row>
     <row r="1415" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1415" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1415" t="s">
         <v>195</v>
@@ -36693,7 +36693,7 @@
     </row>
     <row r="1416" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1416" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1416" t="s">
         <v>196</v>
@@ -36707,7 +36707,7 @@
     </row>
     <row r="1417" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1417" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1417" t="s">
         <v>197</v>
@@ -36721,7 +36721,7 @@
     </row>
     <row r="1418" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1418" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1418" t="s">
         <v>198</v>
@@ -36735,7 +36735,7 @@
     </row>
     <row r="1419" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1419" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1419" t="s">
         <v>199</v>
@@ -36749,7 +36749,7 @@
     </row>
     <row r="1420" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1420" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1420" t="s">
         <v>200</v>
@@ -36763,7 +36763,7 @@
     </row>
     <row r="1421" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1421" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1421" t="s">
         <v>201</v>
@@ -36777,7 +36777,7 @@
     </row>
     <row r="1422" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1422" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1422" t="s">
         <v>202</v>
@@ -36791,7 +36791,7 @@
     </row>
     <row r="1423" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1423" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1423" t="s">
         <v>203</v>
@@ -36805,7 +36805,7 @@
     </row>
     <row r="1424" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1424" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1424" t="s">
         <v>204</v>
@@ -36819,7 +36819,7 @@
     </row>
     <row r="1425" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1425" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1425" t="s">
         <v>205</v>
@@ -36833,7 +36833,7 @@
     </row>
     <row r="1426" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1426" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1426" t="s">
         <v>206</v>
@@ -36847,7 +36847,7 @@
     </row>
     <row r="1427" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1427" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1427" t="s">
         <v>207</v>
@@ -36861,7 +36861,7 @@
     </row>
     <row r="1428" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1428" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1428" t="s">
         <v>208</v>
@@ -36875,7 +36875,7 @@
     </row>
     <row r="1429" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1429" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1429" t="s">
         <v>209</v>
@@ -36889,7 +36889,7 @@
     </row>
     <row r="1430" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1430" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1430" t="s">
         <v>210</v>
@@ -36903,7 +36903,7 @@
     </row>
     <row r="1431" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1431" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1431" t="s">
         <v>211</v>
@@ -36917,7 +36917,7 @@
     </row>
     <row r="1432" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1432" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1432" t="s">
         <v>212</v>
@@ -36931,7 +36931,7 @@
     </row>
     <row r="1433" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1433" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1433" t="s">
         <v>213</v>
@@ -36945,7 +36945,7 @@
     </row>
     <row r="1434" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1434" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1434" t="s">
         <v>214</v>
@@ -36959,7 +36959,7 @@
     </row>
     <row r="1435" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1435" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1435" t="s">
         <v>215</v>
@@ -36973,7 +36973,7 @@
     </row>
     <row r="1436" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1436" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1436" t="s">
         <v>216</v>
@@ -36987,7 +36987,7 @@
     </row>
     <row r="1437" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1437" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J1437" t="s">
         <v>217</v>
@@ -37017,12 +37017,12 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>61</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -37071,16 +37071,16 @@
         <v>56</v>
       </c>
       <c r="E5">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8B2293-D976-469A-8FF3-BEFE6A33D914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5617AD0-8682-41EC-AD01-6B5D77A89E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CFD674-5776-4E9C-B058-B78D9D8EA7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -1086,7 +1086,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1097,9 +1097,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1113,9 +1113,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="9" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{45765176-8E4D-467C-8B17-17A7F0C6EBE1}"/>
@@ -4368,7 +4365,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4467,7 +4464,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4566,7 +4563,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4665,7 +4662,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4764,7 +4761,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4863,7 +4860,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4962,7 +4959,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -5061,7 +5058,7 @@
       </c>
       <c r="AX32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="33" spans="9:50" x14ac:dyDescent="0.25">
@@ -5160,7 +5157,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5358,7 +5355,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5457,7 +5454,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5556,7 +5553,7 @@
       </c>
       <c r="AX37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="38" spans="9:50" x14ac:dyDescent="0.25">
@@ -5655,7 +5652,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5742,7 +5739,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5829,7 +5826,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -6003,7 +6000,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -6090,7 +6087,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6177,7 +6174,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6264,7 +6261,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6351,7 +6348,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6438,7 +6435,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6525,7 +6522,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6612,7 +6609,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6786,7 +6783,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6873,7 +6870,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6960,7 +6957,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -7134,7 +7131,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7221,7 +7218,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7308,7 +7305,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7395,7 +7392,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7482,7 +7479,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7569,7 +7566,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7656,7 +7653,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7743,7 +7740,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7830,7 +7827,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7917,7 +7914,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -8004,7 +8001,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -8091,7 +8088,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8178,7 +8175,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8265,7 +8262,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8352,7 +8349,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8439,7 +8436,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8526,7 +8523,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8613,7 +8610,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8700,7 +8697,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8787,7 +8784,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8874,7 +8871,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8961,7 +8958,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -9048,7 +9045,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9135,7 +9132,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9309,7 +9306,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9396,7 +9393,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9483,7 +9480,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9570,7 +9567,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9657,7 +9654,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9744,7 +9741,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9831,7 +9828,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -10005,7 +10002,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -10092,7 +10089,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10179,7 +10176,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10266,7 +10263,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10353,7 +10350,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10440,7 +10437,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10527,7 +10524,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10614,7 +10611,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10701,7 +10698,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10788,7 +10785,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10875,7 +10872,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">
@@ -37377,7 +37374,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E9" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>227</v>
       </c>
     </row>
@@ -37449,7 +37446,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0573AE-84FA-4F18-8D18-B7F3EC5B3273}">
-  <dimension ref="B4:AA41"/>
+  <dimension ref="B4:AA36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
@@ -37733,664 +37730,153 @@
         <v>3218.5</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>243</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C14" t="s">
         <v>99</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D14" t="s">
         <v>244</v>
       </c>
-      <c r="E10">
+      <c r="E14">
         <v>1.016</v>
       </c>
-      <c r="F10">
+      <c r="F14">
         <v>1.016</v>
       </c>
-      <c r="G10">
+      <c r="G14">
         <v>1.016</v>
       </c>
-      <c r="H10">
+      <c r="H14">
         <v>1.016</v>
       </c>
-      <c r="I10">
+      <c r="I14">
         <v>1.016</v>
       </c>
-      <c r="J10">
+      <c r="J14">
         <v>1.016</v>
       </c>
-      <c r="K10">
+      <c r="K14">
         <v>1.016</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L14" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>246</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C15" t="s">
         <v>99</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D15" t="s">
         <v>244</v>
       </c>
-      <c r="E11">
+      <c r="E15">
         <v>1.204</v>
       </c>
-      <c r="F11">
+      <c r="F15">
         <v>1.204</v>
       </c>
-      <c r="G11">
+      <c r="G15">
         <v>1.204</v>
       </c>
-      <c r="H11">
+      <c r="H15">
         <v>1.204</v>
       </c>
-      <c r="I11">
+      <c r="I15">
         <v>1.204</v>
       </c>
-      <c r="J11">
+      <c r="J15">
         <v>1.204</v>
       </c>
-      <c r="K11">
+      <c r="K15">
         <v>1.204</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L15" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>248</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C16" t="s">
         <v>99</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D16" t="s">
         <v>244</v>
       </c>
-      <c r="E12">
+      <c r="E16">
         <v>1.016</v>
       </c>
-      <c r="F12">
+      <c r="F16">
         <v>1.016</v>
       </c>
-      <c r="G12">
+      <c r="G16">
         <v>1.016</v>
       </c>
-      <c r="H12">
+      <c r="H16">
         <v>1.016</v>
       </c>
-      <c r="I12">
+      <c r="I16">
         <v>1.016</v>
       </c>
-      <c r="J12">
+      <c r="J16">
         <v>1.016</v>
       </c>
-      <c r="K12">
+      <c r="K16">
         <v>1.016</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L16" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>250</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C17" t="s">
         <v>99</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D17" t="s">
         <v>244</v>
       </c>
-      <c r="E13">
+      <c r="E17">
         <v>0.99850000000000005</v>
       </c>
-      <c r="F13">
+      <c r="F17">
         <v>0.99850000000000005</v>
       </c>
-      <c r="G13">
+      <c r="G17">
         <v>0.99850000000000005</v>
       </c>
-      <c r="H13">
+      <c r="H17">
         <v>0.99850000000000005</v>
       </c>
-      <c r="I13">
+      <c r="I17">
         <v>0.99850000000000005</v>
       </c>
-      <c r="J13">
+      <c r="J17">
         <v>0.99850000000000005</v>
       </c>
-      <c r="K13">
+      <c r="K17">
         <v>0.99850000000000005</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L17" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
-      <c r="U18" s="20"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="20"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-    </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
-      <c r="U19" s="20"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20"/>
-      <c r="X19" s="20"/>
-      <c r="Y19" s="20"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="20"/>
-    </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-    </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20"/>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="20"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-    </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="20"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="20"/>
-      <c r="X23" s="20"/>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-    </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-    </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-      <c r="U25" s="20"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="20"/>
-      <c r="X25" s="20"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-    </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20"/>
-      <c r="X26" s="20"/>
-      <c r="Y26" s="20"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-    </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-    </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="20"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20"/>
-      <c r="X28" s="20"/>
-      <c r="Y28" s="20"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
-      <c r="U30" s="20"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20"/>
-      <c r="X30" s="20"/>
-      <c r="Y30" s="20"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20"/>
-      <c r="X31" s="20"/>
-      <c r="Y31" s="20"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="U32" s="20"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20"/>
-      <c r="X32" s="20"/>
-      <c r="Y32" s="20"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20"/>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20"/>
-      <c r="U34" s="20"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20"/>
-      <c r="X34" s="20"/>
-      <c r="Y34" s="20"/>
-      <c r="Z34" s="20"/>
-      <c r="AA34" s="20"/>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="20"/>
-      <c r="Z35" s="20"/>
-      <c r="AA35" s="20"/>
-    </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
+    <row r="35" spans="15:25" x14ac:dyDescent="0.25">
+      <c r="O35" s="6"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+    </row>
+    <row r="36" spans="15:25" x14ac:dyDescent="0.25">
       <c r="O36" s="12"/>
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
@@ -38402,148 +37888,6 @@
       <c r="W36" s="12"/>
       <c r="X36" s="12"/>
       <c r="Y36" s="12"/>
-      <c r="Z36" s="20"/>
-      <c r="AA36" s="20"/>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20"/>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-      <c r="Z37" s="20"/>
-      <c r="AA37" s="20"/>
-    </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="20"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20"/>
-      <c r="W38" s="20"/>
-      <c r="X38" s="20"/>
-      <c r="Y38" s="20"/>
-      <c r="Z38" s="20"/>
-      <c r="AA38" s="20"/>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="20"/>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20"/>
-      <c r="R39" s="20"/>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
-      <c r="U39" s="20"/>
-      <c r="V39" s="20"/>
-      <c r="W39" s="20"/>
-      <c r="X39" s="20"/>
-      <c r="Y39" s="20"/>
-      <c r="Z39" s="20"/>
-      <c r="AA39" s="20"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="20"/>
-      <c r="U40" s="20"/>
-      <c r="V40" s="20"/>
-      <c r="W40" s="20"/>
-      <c r="X40" s="20"/>
-      <c r="Y40" s="20"/>
-      <c r="Z40" s="20"/>
-      <c r="AA40" s="20"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
-      <c r="T41" s="20"/>
-      <c r="U41" s="20"/>
-      <c r="V41" s="20"/>
-      <c r="W41" s="20"/>
-      <c r="X41" s="20"/>
-      <c r="Y41" s="20"/>
-      <c r="Z41" s="20"/>
-      <c r="AA41" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CFD674-5776-4E9C-B058-B78D9D8EA7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFF4DA3-2A43-4287-B5E1-ADC1A2873296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8001" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="286">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -926,6 +926,12 @@
   <si>
     <t>Commodity</t>
   </si>
+  <si>
+    <t>COM_PEAK</t>
+  </si>
+  <si>
+    <t>elc</t>
+  </si>
 </sst>
 </file>
 
@@ -1879,6 +1885,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>284</v>
+      </c>
+      <c r="C20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="M26" s="10"/>
     </row>
@@ -4365,7 +4382,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4464,7 +4481,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4563,7 +4580,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4662,7 +4679,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4761,7 +4778,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4860,7 +4877,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4959,7 +4976,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -5157,7 +5174,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5256,7 +5273,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5355,7 +5372,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5553,7 +5570,7 @@
       </c>
       <c r="AX37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="38" spans="9:50" x14ac:dyDescent="0.25">
@@ -5652,7 +5669,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5739,7 +5756,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5826,7 +5843,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -5913,7 +5930,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -6000,7 +6017,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -6087,7 +6104,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6174,7 +6191,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6261,7 +6278,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6348,7 +6365,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6435,7 +6452,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6522,7 +6539,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6609,7 +6626,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6696,7 +6713,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6783,7 +6800,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6870,7 +6887,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6957,7 +6974,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -7044,7 +7061,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7131,7 +7148,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7218,7 +7235,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7305,7 +7322,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7392,7 +7409,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7479,7 +7496,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7566,7 +7583,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7653,7 +7670,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7740,7 +7757,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7914,7 +7931,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -8001,7 +8018,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -8088,7 +8105,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8175,7 +8192,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8262,7 +8279,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8349,7 +8366,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8436,7 +8453,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8523,7 +8540,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8610,7 +8627,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8697,7 +8714,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8784,7 +8801,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8871,7 +8888,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8958,7 +8975,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -9045,7 +9062,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9132,7 +9149,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9219,7 +9236,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9306,7 +9323,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9393,7 +9410,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9480,7 +9497,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9567,7 +9584,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9654,7 +9671,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9741,7 +9758,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9828,7 +9845,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9915,7 +9932,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -10002,7 +10019,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -10089,7 +10106,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10176,7 +10193,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10263,7 +10280,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10350,7 +10367,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10437,7 +10454,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10524,7 +10541,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10611,7 +10628,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10698,7 +10715,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10785,7 +10802,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10872,7 +10889,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.71</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFF4DA3-2A43-4287-B5E1-ADC1A2873296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DAFF1C-AEF9-4E69-ABFD-A2D1EFC4DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="285">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -888,9 +888,6 @@
     <t>e_wof_parnu_laht</t>
   </si>
   <si>
-    <t>TFM_DINS-AT</t>
-  </si>
-  <si>
     <t>Timeslice</t>
   </si>
   <si>
@@ -1092,7 +1089,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1119,6 +1116,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="9" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{45765176-8E4D-467C-8B17-17A7F0C6EBE1}"/>
@@ -1497,13 +1495,13 @@
     </row>
     <row r="4" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>88</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E4" s="9">
         <v>2022</v>
@@ -1527,7 +1525,7 @@
         <v>2050</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O4">
         <v>2022</v>
@@ -1887,10 +1885,10 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" t="s">
         <v>284</v>
-      </c>
-      <c r="C20" t="s">
-        <v>285</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1950,8 +1948,8 @@
       <c r="X1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AB1" s="11" t="s">
-        <v>271</v>
+      <c r="AB1" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="AF1" s="11" t="s">
         <v>67</v>
@@ -2062,13 +2060,13 @@
         <v>1</v>
       </c>
       <c r="AQ2" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="AR2" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="AR2" s="8" t="s">
-        <v>273</v>
-      </c>
       <c r="AS2" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AT2" s="8" t="s">
         <v>11</v>
@@ -2179,7 +2177,7 @@
         <v>121</v>
       </c>
       <c r="AR3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS3" t="s">
         <v>253</v>
@@ -2287,7 +2285,7 @@
         <v>122</v>
       </c>
       <c r="AR4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS4" t="s">
         <v>253</v>
@@ -2392,7 +2390,7 @@
         <v>123</v>
       </c>
       <c r="AR5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS5" t="s">
         <v>253</v>
@@ -2497,7 +2495,7 @@
         <v>124</v>
       </c>
       <c r="AR6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS6" t="s">
         <v>253</v>
@@ -2602,7 +2600,7 @@
         <v>125</v>
       </c>
       <c r="AR7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS7" t="s">
         <v>253</v>
@@ -2707,7 +2705,7 @@
         <v>126</v>
       </c>
       <c r="AR8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS8" t="s">
         <v>253</v>
@@ -2812,7 +2810,7 @@
         <v>127</v>
       </c>
       <c r="AR9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS9" t="s">
         <v>253</v>
@@ -2917,7 +2915,7 @@
         <v>128</v>
       </c>
       <c r="AR10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS10" t="s">
         <v>253</v>
@@ -3016,7 +3014,7 @@
         <v>129</v>
       </c>
       <c r="AR11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS11" t="s">
         <v>253</v>
@@ -3115,7 +3113,7 @@
         <v>130</v>
       </c>
       <c r="AR12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS12" t="s">
         <v>253</v>
@@ -3214,7 +3212,7 @@
         <v>131</v>
       </c>
       <c r="AR13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS13" t="s">
         <v>253</v>
@@ -3313,7 +3311,7 @@
         <v>132</v>
       </c>
       <c r="AR14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS14" t="s">
         <v>253</v>
@@ -3409,7 +3407,7 @@
         <v>133</v>
       </c>
       <c r="AR15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS15" t="s">
         <v>253</v>
@@ -3505,7 +3503,7 @@
         <v>134</v>
       </c>
       <c r="AR16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS16" t="s">
         <v>253</v>
@@ -3601,7 +3599,7 @@
         <v>135</v>
       </c>
       <c r="AR17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS17" t="s">
         <v>253</v>
@@ -3697,7 +3695,7 @@
         <v>136</v>
       </c>
       <c r="AR18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS18" t="s">
         <v>253</v>
@@ -3793,7 +3791,7 @@
         <v>137</v>
       </c>
       <c r="AR19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS19" t="s">
         <v>253</v>
@@ -3889,7 +3887,7 @@
         <v>138</v>
       </c>
       <c r="AR20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS20" t="s">
         <v>253</v>
@@ -3985,7 +3983,7 @@
         <v>139</v>
       </c>
       <c r="AR21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS21" t="s">
         <v>253</v>
@@ -4081,7 +4079,7 @@
         <v>140</v>
       </c>
       <c r="AR22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS22" t="s">
         <v>253</v>
@@ -4177,7 +4175,7 @@
         <v>141</v>
       </c>
       <c r="AR23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS23" t="s">
         <v>253</v>
@@ -4273,7 +4271,7 @@
         <v>142</v>
       </c>
       <c r="AR24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS24" t="s">
         <v>253</v>
@@ -4369,7 +4367,7 @@
         <v>143</v>
       </c>
       <c r="AR25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS25" t="s">
         <v>253</v>
@@ -4382,7 +4380,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4468,7 +4466,7 @@
         <v>144</v>
       </c>
       <c r="AR26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS26" t="s">
         <v>253</v>
@@ -4481,7 +4479,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4567,7 +4565,7 @@
         <v>145</v>
       </c>
       <c r="AR27" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS27" t="s">
         <v>253</v>
@@ -4580,7 +4578,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4666,7 +4664,7 @@
         <v>146</v>
       </c>
       <c r="AR28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS28" t="s">
         <v>253</v>
@@ -4679,7 +4677,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4765,7 +4763,7 @@
         <v>147</v>
       </c>
       <c r="AR29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS29" t="s">
         <v>253</v>
@@ -4778,7 +4776,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4864,7 +4862,7 @@
         <v>148</v>
       </c>
       <c r="AR30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS30" t="s">
         <v>253</v>
@@ -4877,7 +4875,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4963,7 +4961,7 @@
         <v>149</v>
       </c>
       <c r="AR31" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS31" t="s">
         <v>253</v>
@@ -4976,7 +4974,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -5062,7 +5060,7 @@
         <v>150</v>
       </c>
       <c r="AR32" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS32" t="s">
         <v>253</v>
@@ -5075,7 +5073,7 @@
       </c>
       <c r="AX32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="33" spans="9:50" x14ac:dyDescent="0.25">
@@ -5161,7 +5159,7 @@
         <v>151</v>
       </c>
       <c r="AR33" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS33" t="s">
         <v>253</v>
@@ -5174,7 +5172,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5260,7 +5258,7 @@
         <v>152</v>
       </c>
       <c r="AR34" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS34" t="s">
         <v>253</v>
@@ -5273,7 +5271,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5359,7 +5357,7 @@
         <v>153</v>
       </c>
       <c r="AR35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS35" t="s">
         <v>253</v>
@@ -5372,7 +5370,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5458,7 +5456,7 @@
         <v>154</v>
       </c>
       <c r="AR36" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS36" t="s">
         <v>253</v>
@@ -5471,7 +5469,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5557,7 +5555,7 @@
         <v>155</v>
       </c>
       <c r="AR37" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS37" t="s">
         <v>253</v>
@@ -5570,7 +5568,7 @@
       </c>
       <c r="AX37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="38" spans="9:50" x14ac:dyDescent="0.25">
@@ -5656,7 +5654,7 @@
         <v>156</v>
       </c>
       <c r="AR38" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS38" t="s">
         <v>253</v>
@@ -5669,7 +5667,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5743,7 +5741,7 @@
         <v>157</v>
       </c>
       <c r="AR39" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS39" t="s">
         <v>253</v>
@@ -5756,7 +5754,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5830,7 +5828,7 @@
         <v>158</v>
       </c>
       <c r="AR40" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS40" t="s">
         <v>253</v>
@@ -5843,7 +5841,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -5917,7 +5915,7 @@
         <v>159</v>
       </c>
       <c r="AR41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS41" t="s">
         <v>253</v>
@@ -5930,7 +5928,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -6004,7 +6002,7 @@
         <v>160</v>
       </c>
       <c r="AR42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS42" t="s">
         <v>253</v>
@@ -6017,7 +6015,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -6091,7 +6089,7 @@
         <v>161</v>
       </c>
       <c r="AR43" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS43" t="s">
         <v>253</v>
@@ -6104,7 +6102,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6178,7 +6176,7 @@
         <v>162</v>
       </c>
       <c r="AR44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS44" t="s">
         <v>253</v>
@@ -6191,7 +6189,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6265,7 +6263,7 @@
         <v>163</v>
       </c>
       <c r="AR45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS45" t="s">
         <v>253</v>
@@ -6278,7 +6276,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6352,7 +6350,7 @@
         <v>164</v>
       </c>
       <c r="AR46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS46" t="s">
         <v>253</v>
@@ -6365,7 +6363,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6439,7 +6437,7 @@
         <v>165</v>
       </c>
       <c r="AR47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS47" t="s">
         <v>253</v>
@@ -6452,7 +6450,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6526,7 +6524,7 @@
         <v>166</v>
       </c>
       <c r="AR48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS48" t="s">
         <v>253</v>
@@ -6539,7 +6537,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6613,7 +6611,7 @@
         <v>167</v>
       </c>
       <c r="AR49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS49" t="s">
         <v>253</v>
@@ -6626,7 +6624,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6700,7 +6698,7 @@
         <v>168</v>
       </c>
       <c r="AR50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS50" t="s">
         <v>253</v>
@@ -6713,7 +6711,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6787,7 +6785,7 @@
         <v>169</v>
       </c>
       <c r="AR51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS51" t="s">
         <v>253</v>
@@ -6800,7 +6798,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6874,7 +6872,7 @@
         <v>170</v>
       </c>
       <c r="AR52" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS52" t="s">
         <v>253</v>
@@ -6887,7 +6885,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6961,7 +6959,7 @@
         <v>171</v>
       </c>
       <c r="AR53" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS53" t="s">
         <v>253</v>
@@ -6974,7 +6972,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -7048,7 +7046,7 @@
         <v>172</v>
       </c>
       <c r="AR54" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS54" t="s">
         <v>253</v>
@@ -7061,7 +7059,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7135,7 +7133,7 @@
         <v>173</v>
       </c>
       <c r="AR55" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS55" t="s">
         <v>253</v>
@@ -7148,7 +7146,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7222,7 +7220,7 @@
         <v>174</v>
       </c>
       <c r="AR56" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS56" t="s">
         <v>253</v>
@@ -7235,7 +7233,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7309,7 +7307,7 @@
         <v>175</v>
       </c>
       <c r="AR57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS57" t="s">
         <v>253</v>
@@ -7322,7 +7320,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7396,7 +7394,7 @@
         <v>176</v>
       </c>
       <c r="AR58" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS58" t="s">
         <v>253</v>
@@ -7409,7 +7407,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7483,7 +7481,7 @@
         <v>177</v>
       </c>
       <c r="AR59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS59" t="s">
         <v>253</v>
@@ -7496,7 +7494,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7570,7 +7568,7 @@
         <v>178</v>
       </c>
       <c r="AR60" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS60" t="s">
         <v>253</v>
@@ -7583,7 +7581,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7657,7 +7655,7 @@
         <v>179</v>
       </c>
       <c r="AR61" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS61" t="s">
         <v>253</v>
@@ -7670,7 +7668,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7744,7 +7742,7 @@
         <v>180</v>
       </c>
       <c r="AR62" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS62" t="s">
         <v>253</v>
@@ -7757,7 +7755,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7831,7 +7829,7 @@
         <v>181</v>
       </c>
       <c r="AR63" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS63" t="s">
         <v>253</v>
@@ -7844,7 +7842,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7918,7 +7916,7 @@
         <v>182</v>
       </c>
       <c r="AR64" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS64" t="s">
         <v>253</v>
@@ -7931,7 +7929,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -8005,7 +8003,7 @@
         <v>183</v>
       </c>
       <c r="AR65" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS65" t="s">
         <v>253</v>
@@ -8018,7 +8016,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -8092,7 +8090,7 @@
         <v>184</v>
       </c>
       <c r="AR66" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS66" t="s">
         <v>253</v>
@@ -8105,7 +8103,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8179,7 +8177,7 @@
         <v>185</v>
       </c>
       <c r="AR67" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS67" t="s">
         <v>253</v>
@@ -8192,7 +8190,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8266,7 +8264,7 @@
         <v>186</v>
       </c>
       <c r="AR68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS68" t="s">
         <v>253</v>
@@ -8279,7 +8277,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8353,7 +8351,7 @@
         <v>187</v>
       </c>
       <c r="AR69" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS69" t="s">
         <v>253</v>
@@ -8366,7 +8364,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8440,7 +8438,7 @@
         <v>188</v>
       </c>
       <c r="AR70" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS70" t="s">
         <v>253</v>
@@ -8453,7 +8451,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8527,7 +8525,7 @@
         <v>189</v>
       </c>
       <c r="AR71" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS71" t="s">
         <v>253</v>
@@ -8540,7 +8538,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8614,7 +8612,7 @@
         <v>190</v>
       </c>
       <c r="AR72" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS72" t="s">
         <v>253</v>
@@ -8627,7 +8625,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8701,7 +8699,7 @@
         <v>191</v>
       </c>
       <c r="AR73" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS73" t="s">
         <v>253</v>
@@ -8714,7 +8712,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8788,7 +8786,7 @@
         <v>192</v>
       </c>
       <c r="AR74" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS74" t="s">
         <v>253</v>
@@ -8801,7 +8799,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8875,7 +8873,7 @@
         <v>193</v>
       </c>
       <c r="AR75" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS75" t="s">
         <v>253</v>
@@ -8888,7 +8886,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8962,7 +8960,7 @@
         <v>194</v>
       </c>
       <c r="AR76" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS76" t="s">
         <v>253</v>
@@ -8975,7 +8973,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -9049,7 +9047,7 @@
         <v>195</v>
       </c>
       <c r="AR77" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS77" t="s">
         <v>253</v>
@@ -9062,7 +9060,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9136,7 +9134,7 @@
         <v>196</v>
       </c>
       <c r="AR78" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS78" t="s">
         <v>253</v>
@@ -9149,7 +9147,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9223,7 +9221,7 @@
         <v>197</v>
       </c>
       <c r="AR79" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS79" t="s">
         <v>253</v>
@@ -9236,7 +9234,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9310,7 +9308,7 @@
         <v>198</v>
       </c>
       <c r="AR80" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS80" t="s">
         <v>253</v>
@@ -9323,7 +9321,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9397,7 +9395,7 @@
         <v>199</v>
       </c>
       <c r="AR81" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS81" t="s">
         <v>253</v>
@@ -9410,7 +9408,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9484,7 +9482,7 @@
         <v>200</v>
       </c>
       <c r="AR82" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS82" t="s">
         <v>253</v>
@@ -9497,7 +9495,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9571,7 +9569,7 @@
         <v>201</v>
       </c>
       <c r="AR83" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS83" t="s">
         <v>253</v>
@@ -9584,7 +9582,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9658,7 +9656,7 @@
         <v>202</v>
       </c>
       <c r="AR84" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS84" t="s">
         <v>253</v>
@@ -9671,7 +9669,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9745,7 +9743,7 @@
         <v>203</v>
       </c>
       <c r="AR85" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS85" t="s">
         <v>253</v>
@@ -9758,7 +9756,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9832,7 +9830,7 @@
         <v>204</v>
       </c>
       <c r="AR86" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS86" t="s">
         <v>253</v>
@@ -9845,7 +9843,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9919,7 +9917,7 @@
         <v>205</v>
       </c>
       <c r="AR87" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS87" t="s">
         <v>253</v>
@@ -9932,7 +9930,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -10006,7 +10004,7 @@
         <v>206</v>
       </c>
       <c r="AR88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS88" t="s">
         <v>253</v>
@@ -10019,7 +10017,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -10093,7 +10091,7 @@
         <v>207</v>
       </c>
       <c r="AR89" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS89" t="s">
         <v>253</v>
@@ -10106,7 +10104,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10180,7 +10178,7 @@
         <v>208</v>
       </c>
       <c r="AR90" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS90" t="s">
         <v>253</v>
@@ -10193,7 +10191,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.9</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10267,7 +10265,7 @@
         <v>209</v>
       </c>
       <c r="AR91" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS91" t="s">
         <v>253</v>
@@ -10280,7 +10278,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10354,7 +10352,7 @@
         <v>210</v>
       </c>
       <c r="AR92" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS92" t="s">
         <v>253</v>
@@ -10367,7 +10365,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10441,7 +10439,7 @@
         <v>211</v>
       </c>
       <c r="AR93" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS93" t="s">
         <v>253</v>
@@ -10454,7 +10452,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10528,7 +10526,7 @@
         <v>212</v>
       </c>
       <c r="AR94" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS94" t="s">
         <v>253</v>
@@ -10541,7 +10539,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10615,7 +10613,7 @@
         <v>213</v>
       </c>
       <c r="AR95" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS95" t="s">
         <v>253</v>
@@ -10628,7 +10626,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10702,7 +10700,7 @@
         <v>214</v>
       </c>
       <c r="AR96" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS96" t="s">
         <v>253</v>
@@ -10715,7 +10713,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10789,7 +10787,7 @@
         <v>215</v>
       </c>
       <c r="AR97" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS97" t="s">
         <v>253</v>
@@ -10802,7 +10800,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10876,7 +10874,7 @@
         <v>216</v>
       </c>
       <c r="AR98" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AS98" t="s">
         <v>253</v>
@@ -10889,7 +10887,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.94</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">
@@ -30478,7 +30476,7 @@
     </row>
     <row r="963" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I963" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J963" t="s">
         <v>122</v>
@@ -30492,7 +30490,7 @@
     </row>
     <row r="964" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I964" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J964" t="s">
         <v>123</v>
@@ -30506,7 +30504,7 @@
     </row>
     <row r="965" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I965" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J965" t="s">
         <v>124</v>
@@ -30520,7 +30518,7 @@
     </row>
     <row r="966" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I966" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J966" t="s">
         <v>125</v>
@@ -30534,7 +30532,7 @@
     </row>
     <row r="967" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I967" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J967" t="s">
         <v>126</v>
@@ -30548,7 +30546,7 @@
     </row>
     <row r="968" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I968" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J968" t="s">
         <v>127</v>
@@ -30562,7 +30560,7 @@
     </row>
     <row r="969" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I969" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J969" t="s">
         <v>128</v>
@@ -30576,7 +30574,7 @@
     </row>
     <row r="970" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I970" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J970" t="s">
         <v>129</v>
@@ -30590,7 +30588,7 @@
     </row>
     <row r="971" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I971" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J971" t="s">
         <v>130</v>
@@ -30604,7 +30602,7 @@
     </row>
     <row r="972" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I972" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J972" t="s">
         <v>131</v>
@@ -30618,7 +30616,7 @@
     </row>
     <row r="973" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I973" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J973" t="s">
         <v>132</v>
@@ -30632,7 +30630,7 @@
     </row>
     <row r="974" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I974" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J974" t="s">
         <v>133</v>
@@ -30646,7 +30644,7 @@
     </row>
     <row r="975" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I975" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J975" t="s">
         <v>134</v>
@@ -30660,7 +30658,7 @@
     </row>
     <row r="976" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I976" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J976" t="s">
         <v>135</v>
@@ -30674,7 +30672,7 @@
     </row>
     <row r="977" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I977" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J977" t="s">
         <v>136</v>
@@ -30688,7 +30686,7 @@
     </row>
     <row r="978" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I978" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J978" t="s">
         <v>137</v>
@@ -30702,7 +30700,7 @@
     </row>
     <row r="979" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I979" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J979" t="s">
         <v>138</v>
@@ -30716,7 +30714,7 @@
     </row>
     <row r="980" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I980" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J980" t="s">
         <v>139</v>
@@ -30730,7 +30728,7 @@
     </row>
     <row r="981" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I981" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J981" t="s">
         <v>140</v>
@@ -30744,7 +30742,7 @@
     </row>
     <row r="982" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I982" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J982" t="s">
         <v>141</v>
@@ -30758,7 +30756,7 @@
     </row>
     <row r="983" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I983" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J983" t="s">
         <v>142</v>
@@ -30772,7 +30770,7 @@
     </row>
     <row r="984" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I984" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J984" t="s">
         <v>143</v>
@@ -30786,7 +30784,7 @@
     </row>
     <row r="985" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I985" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J985" t="s">
         <v>144</v>
@@ -30800,7 +30798,7 @@
     </row>
     <row r="986" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I986" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J986" t="s">
         <v>145</v>
@@ -30814,7 +30812,7 @@
     </row>
     <row r="987" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I987" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J987" t="s">
         <v>146</v>
@@ -30828,7 +30826,7 @@
     </row>
     <row r="988" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I988" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J988" t="s">
         <v>147</v>
@@ -30842,7 +30840,7 @@
     </row>
     <row r="989" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I989" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J989" t="s">
         <v>148</v>
@@ -30856,7 +30854,7 @@
     </row>
     <row r="990" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I990" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J990" t="s">
         <v>149</v>
@@ -30870,7 +30868,7 @@
     </row>
     <row r="991" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I991" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J991" t="s">
         <v>150</v>
@@ -30884,7 +30882,7 @@
     </row>
     <row r="992" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I992" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J992" t="s">
         <v>151</v>
@@ -30898,7 +30896,7 @@
     </row>
     <row r="993" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I993" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J993" t="s">
         <v>152</v>
@@ -30912,7 +30910,7 @@
     </row>
     <row r="994" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I994" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J994" t="s">
         <v>153</v>
@@ -30926,7 +30924,7 @@
     </row>
     <row r="995" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I995" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J995" t="s">
         <v>154</v>
@@ -30940,7 +30938,7 @@
     </row>
     <row r="996" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I996" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J996" t="s">
         <v>155</v>
@@ -30954,7 +30952,7 @@
     </row>
     <row r="997" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I997" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J997" t="s">
         <v>156</v>
@@ -30968,7 +30966,7 @@
     </row>
     <row r="998" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I998" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J998" t="s">
         <v>157</v>
@@ -30982,7 +30980,7 @@
     </row>
     <row r="999" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I999" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J999" t="s">
         <v>158</v>
@@ -30996,7 +30994,7 @@
     </row>
     <row r="1000" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1000" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1000" t="s">
         <v>159</v>
@@ -31010,7 +31008,7 @@
     </row>
     <row r="1001" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1001" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1001" t="s">
         <v>160</v>
@@ -31024,7 +31022,7 @@
     </row>
     <row r="1002" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1002" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1002" t="s">
         <v>161</v>
@@ -31038,7 +31036,7 @@
     </row>
     <row r="1003" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1003" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1003" t="s">
         <v>162</v>
@@ -31052,7 +31050,7 @@
     </row>
     <row r="1004" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1004" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1004" t="s">
         <v>163</v>
@@ -31066,7 +31064,7 @@
     </row>
     <row r="1005" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1005" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1005" t="s">
         <v>164</v>
@@ -31080,7 +31078,7 @@
     </row>
     <row r="1006" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1006" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1006" t="s">
         <v>165</v>
@@ -31094,7 +31092,7 @@
     </row>
     <row r="1007" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1007" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1007" t="s">
         <v>166</v>
@@ -31108,7 +31106,7 @@
     </row>
     <row r="1008" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1008" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1008" t="s">
         <v>167</v>
@@ -31122,7 +31120,7 @@
     </row>
     <row r="1009" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1009" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1009" t="s">
         <v>168</v>
@@ -31136,7 +31134,7 @@
     </row>
     <row r="1010" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1010" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1010" t="s">
         <v>169</v>
@@ -31150,7 +31148,7 @@
     </row>
     <row r="1011" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1011" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1011" t="s">
         <v>170</v>
@@ -31164,7 +31162,7 @@
     </row>
     <row r="1012" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1012" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1012" t="s">
         <v>171</v>
@@ -31178,7 +31176,7 @@
     </row>
     <row r="1013" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1013" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1013" t="s">
         <v>172</v>
@@ -31192,7 +31190,7 @@
     </row>
     <row r="1014" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1014" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1014" t="s">
         <v>173</v>
@@ -31206,7 +31204,7 @@
     </row>
     <row r="1015" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1015" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1015" t="s">
         <v>174</v>
@@ -31220,7 +31218,7 @@
     </row>
     <row r="1016" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1016" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1016" t="s">
         <v>175</v>
@@ -31234,7 +31232,7 @@
     </row>
     <row r="1017" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1017" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1017" t="s">
         <v>176</v>
@@ -31248,7 +31246,7 @@
     </row>
     <row r="1018" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1018" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1018" t="s">
         <v>177</v>
@@ -31262,7 +31260,7 @@
     </row>
     <row r="1019" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1019" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1019" t="s">
         <v>178</v>
@@ -31276,7 +31274,7 @@
     </row>
     <row r="1020" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1020" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1020" t="s">
         <v>179</v>
@@ -31290,7 +31288,7 @@
     </row>
     <row r="1021" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1021" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1021" t="s">
         <v>180</v>
@@ -31304,7 +31302,7 @@
     </row>
     <row r="1022" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1022" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1022" t="s">
         <v>181</v>
@@ -31318,7 +31316,7 @@
     </row>
     <row r="1023" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1023" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1023" t="s">
         <v>182</v>
@@ -31332,7 +31330,7 @@
     </row>
     <row r="1024" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1024" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1024" t="s">
         <v>183</v>
@@ -31346,7 +31344,7 @@
     </row>
     <row r="1025" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1025" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1025" t="s">
         <v>184</v>
@@ -31360,7 +31358,7 @@
     </row>
     <row r="1026" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1026" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1026" t="s">
         <v>185</v>
@@ -31374,7 +31372,7 @@
     </row>
     <row r="1027" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1027" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1027" t="s">
         <v>186</v>
@@ -31388,7 +31386,7 @@
     </row>
     <row r="1028" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1028" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1028" t="s">
         <v>187</v>
@@ -31402,7 +31400,7 @@
     </row>
     <row r="1029" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1029" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1029" t="s">
         <v>188</v>
@@ -31416,7 +31414,7 @@
     </row>
     <row r="1030" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1030" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1030" t="s">
         <v>189</v>
@@ -31430,7 +31428,7 @@
     </row>
     <row r="1031" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1031" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1031" t="s">
         <v>190</v>
@@ -31444,7 +31442,7 @@
     </row>
     <row r="1032" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1032" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1032" t="s">
         <v>191</v>
@@ -31458,7 +31456,7 @@
     </row>
     <row r="1033" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1033" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1033" t="s">
         <v>192</v>
@@ -31472,7 +31470,7 @@
     </row>
     <row r="1034" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1034" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1034" t="s">
         <v>193</v>
@@ -31486,7 +31484,7 @@
     </row>
     <row r="1035" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1035" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1035" t="s">
         <v>194</v>
@@ -31500,7 +31498,7 @@
     </row>
     <row r="1036" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1036" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1036" t="s">
         <v>195</v>
@@ -31514,7 +31512,7 @@
     </row>
     <row r="1037" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1037" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1037" t="s">
         <v>196</v>
@@ -31528,7 +31526,7 @@
     </row>
     <row r="1038" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1038" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1038" t="s">
         <v>197</v>
@@ -31542,7 +31540,7 @@
     </row>
     <row r="1039" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1039" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1039" t="s">
         <v>198</v>
@@ -31556,7 +31554,7 @@
     </row>
     <row r="1040" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1040" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1040" t="s">
         <v>199</v>
@@ -31570,7 +31568,7 @@
     </row>
     <row r="1041" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1041" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1041" t="s">
         <v>200</v>
@@ -31584,7 +31582,7 @@
     </row>
     <row r="1042" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1042" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1042" t="s">
         <v>201</v>
@@ -31598,7 +31596,7 @@
     </row>
     <row r="1043" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1043" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1043" t="s">
         <v>202</v>
@@ -31612,7 +31610,7 @@
     </row>
     <row r="1044" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1044" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1044" t="s">
         <v>203</v>
@@ -31626,7 +31624,7 @@
     </row>
     <row r="1045" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1045" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1045" t="s">
         <v>204</v>
@@ -31640,7 +31638,7 @@
     </row>
     <row r="1046" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1046" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1046" t="s">
         <v>205</v>
@@ -31654,7 +31652,7 @@
     </row>
     <row r="1047" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1047" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1047" t="s">
         <v>206</v>
@@ -31668,7 +31666,7 @@
     </row>
     <row r="1048" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1048" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1048" t="s">
         <v>207</v>
@@ -31682,7 +31680,7 @@
     </row>
     <row r="1049" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1049" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1049" t="s">
         <v>208</v>
@@ -31696,7 +31694,7 @@
     </row>
     <row r="1050" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1050" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1050" t="s">
         <v>209</v>
@@ -31710,7 +31708,7 @@
     </row>
     <row r="1051" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1051" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1051" t="s">
         <v>210</v>
@@ -31724,7 +31722,7 @@
     </row>
     <row r="1052" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1052" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1052" t="s">
         <v>211</v>
@@ -31738,7 +31736,7 @@
     </row>
     <row r="1053" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1053" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1053" t="s">
         <v>212</v>
@@ -31752,7 +31750,7 @@
     </row>
     <row r="1054" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1054" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1054" t="s">
         <v>213</v>
@@ -31766,7 +31764,7 @@
     </row>
     <row r="1055" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1055" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1055" t="s">
         <v>214</v>
@@ -31780,7 +31778,7 @@
     </row>
     <row r="1056" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1056" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1056" t="s">
         <v>215</v>
@@ -31794,7 +31792,7 @@
     </row>
     <row r="1057" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1057" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1057" t="s">
         <v>216</v>
@@ -31808,7 +31806,7 @@
     </row>
     <row r="1058" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1058" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1058" t="s">
         <v>122</v>
@@ -31822,7 +31820,7 @@
     </row>
     <row r="1059" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1059" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1059" t="s">
         <v>123</v>
@@ -31836,7 +31834,7 @@
     </row>
     <row r="1060" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1060" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1060" t="s">
         <v>124</v>
@@ -31850,7 +31848,7 @@
     </row>
     <row r="1061" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1061" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1061" t="s">
         <v>125</v>
@@ -31864,7 +31862,7 @@
     </row>
     <row r="1062" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1062" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1062" t="s">
         <v>126</v>
@@ -31878,7 +31876,7 @@
     </row>
     <row r="1063" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1063" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1063" t="s">
         <v>127</v>
@@ -31892,7 +31890,7 @@
     </row>
     <row r="1064" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1064" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1064" t="s">
         <v>128</v>
@@ -31906,7 +31904,7 @@
     </row>
     <row r="1065" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1065" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1065" t="s">
         <v>129</v>
@@ -31920,7 +31918,7 @@
     </row>
     <row r="1066" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1066" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1066" t="s">
         <v>130</v>
@@ -31934,7 +31932,7 @@
     </row>
     <row r="1067" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1067" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1067" t="s">
         <v>131</v>
@@ -31948,7 +31946,7 @@
     </row>
     <row r="1068" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1068" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1068" t="s">
         <v>132</v>
@@ -31962,7 +31960,7 @@
     </row>
     <row r="1069" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1069" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1069" t="s">
         <v>133</v>
@@ -31976,7 +31974,7 @@
     </row>
     <row r="1070" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1070" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1070" t="s">
         <v>134</v>
@@ -31990,7 +31988,7 @@
     </row>
     <row r="1071" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1071" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1071" t="s">
         <v>135</v>
@@ -32004,7 +32002,7 @@
     </row>
     <row r="1072" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1072" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1072" t="s">
         <v>136</v>
@@ -32018,7 +32016,7 @@
     </row>
     <row r="1073" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1073" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1073" t="s">
         <v>137</v>
@@ -32032,7 +32030,7 @@
     </row>
     <row r="1074" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1074" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1074" t="s">
         <v>138</v>
@@ -32046,7 +32044,7 @@
     </row>
     <row r="1075" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1075" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1075" t="s">
         <v>139</v>
@@ -32060,7 +32058,7 @@
     </row>
     <row r="1076" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1076" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1076" t="s">
         <v>140</v>
@@ -32074,7 +32072,7 @@
     </row>
     <row r="1077" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1077" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1077" t="s">
         <v>141</v>
@@ -32088,7 +32086,7 @@
     </row>
     <row r="1078" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1078" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1078" t="s">
         <v>142</v>
@@ -32102,7 +32100,7 @@
     </row>
     <row r="1079" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1079" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1079" t="s">
         <v>143</v>
@@ -32116,7 +32114,7 @@
     </row>
     <row r="1080" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1080" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1080" t="s">
         <v>144</v>
@@ -32130,7 +32128,7 @@
     </row>
     <row r="1081" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1081" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1081" t="s">
         <v>145</v>
@@ -32144,7 +32142,7 @@
     </row>
     <row r="1082" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1082" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1082" t="s">
         <v>146</v>
@@ -32158,7 +32156,7 @@
     </row>
     <row r="1083" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1083" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1083" t="s">
         <v>147</v>
@@ -32172,7 +32170,7 @@
     </row>
     <row r="1084" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1084" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1084" t="s">
         <v>148</v>
@@ -32186,7 +32184,7 @@
     </row>
     <row r="1085" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1085" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1085" t="s">
         <v>149</v>
@@ -32200,7 +32198,7 @@
     </row>
     <row r="1086" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1086" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1086" t="s">
         <v>150</v>
@@ -32214,7 +32212,7 @@
     </row>
     <row r="1087" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1087" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1087" t="s">
         <v>151</v>
@@ -32228,7 +32226,7 @@
     </row>
     <row r="1088" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1088" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1088" t="s">
         <v>152</v>
@@ -32242,7 +32240,7 @@
     </row>
     <row r="1089" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1089" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1089" t="s">
         <v>153</v>
@@ -32256,7 +32254,7 @@
     </row>
     <row r="1090" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1090" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1090" t="s">
         <v>154</v>
@@ -32270,7 +32268,7 @@
     </row>
     <row r="1091" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1091" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1091" t="s">
         <v>155</v>
@@ -32284,7 +32282,7 @@
     </row>
     <row r="1092" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1092" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1092" t="s">
         <v>156</v>
@@ -32298,7 +32296,7 @@
     </row>
     <row r="1093" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1093" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1093" t="s">
         <v>157</v>
@@ -32312,7 +32310,7 @@
     </row>
     <row r="1094" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1094" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1094" t="s">
         <v>158</v>
@@ -32326,7 +32324,7 @@
     </row>
     <row r="1095" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1095" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1095" t="s">
         <v>159</v>
@@ -32340,7 +32338,7 @@
     </row>
     <row r="1096" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1096" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1096" t="s">
         <v>160</v>
@@ -32354,7 +32352,7 @@
     </row>
     <row r="1097" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1097" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1097" t="s">
         <v>161</v>
@@ -32368,7 +32366,7 @@
     </row>
     <row r="1098" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1098" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1098" t="s">
         <v>162</v>
@@ -32382,7 +32380,7 @@
     </row>
     <row r="1099" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1099" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1099" t="s">
         <v>163</v>
@@ -32396,7 +32394,7 @@
     </row>
     <row r="1100" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1100" t="s">
         <v>164</v>
@@ -32410,7 +32408,7 @@
     </row>
     <row r="1101" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1101" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1101" t="s">
         <v>165</v>
@@ -32424,7 +32422,7 @@
     </row>
     <row r="1102" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1102" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1102" t="s">
         <v>166</v>
@@ -32438,7 +32436,7 @@
     </row>
     <row r="1103" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1103" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1103" t="s">
         <v>167</v>
@@ -32452,7 +32450,7 @@
     </row>
     <row r="1104" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1104" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1104" t="s">
         <v>168</v>
@@ -32466,7 +32464,7 @@
     </row>
     <row r="1105" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1105" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1105" t="s">
         <v>169</v>
@@ -32480,7 +32478,7 @@
     </row>
     <row r="1106" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1106" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1106" t="s">
         <v>170</v>
@@ -32494,7 +32492,7 @@
     </row>
     <row r="1107" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1107" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1107" t="s">
         <v>171</v>
@@ -32508,7 +32506,7 @@
     </row>
     <row r="1108" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1108" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1108" t="s">
         <v>172</v>
@@ -32522,7 +32520,7 @@
     </row>
     <row r="1109" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1109" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1109" t="s">
         <v>173</v>
@@ -32536,7 +32534,7 @@
     </row>
     <row r="1110" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1110" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1110" t="s">
         <v>174</v>
@@ -32550,7 +32548,7 @@
     </row>
     <row r="1111" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1111" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1111" t="s">
         <v>175</v>
@@ -32564,7 +32562,7 @@
     </row>
     <row r="1112" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1112" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1112" t="s">
         <v>176</v>
@@ -32578,7 +32576,7 @@
     </row>
     <row r="1113" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1113" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1113" t="s">
         <v>177</v>
@@ -32592,7 +32590,7 @@
     </row>
     <row r="1114" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1114" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1114" t="s">
         <v>178</v>
@@ -32606,7 +32604,7 @@
     </row>
     <row r="1115" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1115" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1115" t="s">
         <v>179</v>
@@ -32620,7 +32618,7 @@
     </row>
     <row r="1116" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1116" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1116" t="s">
         <v>180</v>
@@ -32634,7 +32632,7 @@
     </row>
     <row r="1117" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1117" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1117" t="s">
         <v>181</v>
@@ -32648,7 +32646,7 @@
     </row>
     <row r="1118" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1118" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1118" t="s">
         <v>182</v>
@@ -32662,7 +32660,7 @@
     </row>
     <row r="1119" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1119" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1119" t="s">
         <v>183</v>
@@ -32676,7 +32674,7 @@
     </row>
     <row r="1120" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1120" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1120" t="s">
         <v>184</v>
@@ -32690,7 +32688,7 @@
     </row>
     <row r="1121" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1121" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1121" t="s">
         <v>185</v>
@@ -32704,7 +32702,7 @@
     </row>
     <row r="1122" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1122" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1122" t="s">
         <v>186</v>
@@ -32718,7 +32716,7 @@
     </row>
     <row r="1123" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1123" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1123" t="s">
         <v>187</v>
@@ -32732,7 +32730,7 @@
     </row>
     <row r="1124" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1124" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1124" t="s">
         <v>188</v>
@@ -32746,7 +32744,7 @@
     </row>
     <row r="1125" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1125" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1125" t="s">
         <v>189</v>
@@ -32760,7 +32758,7 @@
     </row>
     <row r="1126" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1126" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1126" t="s">
         <v>190</v>
@@ -32774,7 +32772,7 @@
     </row>
     <row r="1127" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1127" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1127" t="s">
         <v>191</v>
@@ -32788,7 +32786,7 @@
     </row>
     <row r="1128" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1128" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1128" t="s">
         <v>192</v>
@@ -32802,7 +32800,7 @@
     </row>
     <row r="1129" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1129" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1129" t="s">
         <v>193</v>
@@ -32816,7 +32814,7 @@
     </row>
     <row r="1130" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1130" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1130" t="s">
         <v>194</v>
@@ -32830,7 +32828,7 @@
     </row>
     <row r="1131" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1131" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1131" t="s">
         <v>195</v>
@@ -32844,7 +32842,7 @@
     </row>
     <row r="1132" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1132" t="s">
         <v>196</v>
@@ -32858,7 +32856,7 @@
     </row>
     <row r="1133" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1133" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1133" t="s">
         <v>197</v>
@@ -32872,7 +32870,7 @@
     </row>
     <row r="1134" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1134" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1134" t="s">
         <v>198</v>
@@ -32886,7 +32884,7 @@
     </row>
     <row r="1135" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1135" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1135" t="s">
         <v>199</v>
@@ -32900,7 +32898,7 @@
     </row>
     <row r="1136" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1136" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1136" t="s">
         <v>200</v>
@@ -32914,7 +32912,7 @@
     </row>
     <row r="1137" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1137" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1137" t="s">
         <v>201</v>
@@ -32928,7 +32926,7 @@
     </row>
     <row r="1138" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1138" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1138" t="s">
         <v>202</v>
@@ -32942,7 +32940,7 @@
     </row>
     <row r="1139" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1139" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1139" t="s">
         <v>203</v>
@@ -32956,7 +32954,7 @@
     </row>
     <row r="1140" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1140" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1140" t="s">
         <v>204</v>
@@ -32970,7 +32968,7 @@
     </row>
     <row r="1141" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1141" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1141" t="s">
         <v>205</v>
@@ -32984,7 +32982,7 @@
     </row>
     <row r="1142" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1142" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1142" t="s">
         <v>206</v>
@@ -32998,7 +32996,7 @@
     </row>
     <row r="1143" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1143" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1143" t="s">
         <v>207</v>
@@ -33012,7 +33010,7 @@
     </row>
     <row r="1144" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1144" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1144" t="s">
         <v>208</v>
@@ -33026,7 +33024,7 @@
     </row>
     <row r="1145" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1145" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1145" t="s">
         <v>209</v>
@@ -33040,7 +33038,7 @@
     </row>
     <row r="1146" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1146" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1146" t="s">
         <v>210</v>
@@ -33054,7 +33052,7 @@
     </row>
     <row r="1147" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1147" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1147" t="s">
         <v>211</v>
@@ -33068,7 +33066,7 @@
     </row>
     <row r="1148" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1148" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1148" t="s">
         <v>212</v>
@@ -33082,7 +33080,7 @@
     </row>
     <row r="1149" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1149" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1149" t="s">
         <v>213</v>
@@ -33096,7 +33094,7 @@
     </row>
     <row r="1150" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1150" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1150" t="s">
         <v>214</v>
@@ -33110,7 +33108,7 @@
     </row>
     <row r="1151" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1151" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1151" t="s">
         <v>215</v>
@@ -33124,7 +33122,7 @@
     </row>
     <row r="1152" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1152" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J1152" t="s">
         <v>216</v>
@@ -33138,7 +33136,7 @@
     </row>
     <row r="1153" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1153" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1153" t="s">
         <v>122</v>
@@ -33152,7 +33150,7 @@
     </row>
     <row r="1154" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1154" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1154" t="s">
         <v>123</v>
@@ -33166,7 +33164,7 @@
     </row>
     <row r="1155" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1155" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1155" t="s">
         <v>124</v>
@@ -33180,7 +33178,7 @@
     </row>
     <row r="1156" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1156" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1156" t="s">
         <v>125</v>
@@ -33194,7 +33192,7 @@
     </row>
     <row r="1157" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1157" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1157" t="s">
         <v>126</v>
@@ -33208,7 +33206,7 @@
     </row>
     <row r="1158" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1158" t="s">
         <v>127</v>
@@ -33222,7 +33220,7 @@
     </row>
     <row r="1159" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1159" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1159" t="s">
         <v>128</v>
@@ -33236,7 +33234,7 @@
     </row>
     <row r="1160" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1160" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1160" t="s">
         <v>129</v>
@@ -33250,7 +33248,7 @@
     </row>
     <row r="1161" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1161" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1161" t="s">
         <v>130</v>
@@ -33264,7 +33262,7 @@
     </row>
     <row r="1162" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1162" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1162" t="s">
         <v>131</v>
@@ -33278,7 +33276,7 @@
     </row>
     <row r="1163" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1163" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1163" t="s">
         <v>132</v>
@@ -33292,7 +33290,7 @@
     </row>
     <row r="1164" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1164" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1164" t="s">
         <v>133</v>
@@ -33306,7 +33304,7 @@
     </row>
     <row r="1165" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1165" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1165" t="s">
         <v>134</v>
@@ -33320,7 +33318,7 @@
     </row>
     <row r="1166" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1166" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1166" t="s">
         <v>135</v>
@@ -33334,7 +33332,7 @@
     </row>
     <row r="1167" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1167" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1167" t="s">
         <v>136</v>
@@ -33348,7 +33346,7 @@
     </row>
     <row r="1168" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1168" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1168" t="s">
         <v>137</v>
@@ -33362,7 +33360,7 @@
     </row>
     <row r="1169" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1169" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1169" t="s">
         <v>138</v>
@@ -33376,7 +33374,7 @@
     </row>
     <row r="1170" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1170" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1170" t="s">
         <v>139</v>
@@ -33390,7 +33388,7 @@
     </row>
     <row r="1171" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1171" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1171" t="s">
         <v>140</v>
@@ -33404,7 +33402,7 @@
     </row>
     <row r="1172" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1172" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1172" t="s">
         <v>141</v>
@@ -33418,7 +33416,7 @@
     </row>
     <row r="1173" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1173" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1173" t="s">
         <v>142</v>
@@ -33432,7 +33430,7 @@
     </row>
     <row r="1174" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1174" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1174" t="s">
         <v>143</v>
@@ -33446,7 +33444,7 @@
     </row>
     <row r="1175" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1175" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1175" t="s">
         <v>144</v>
@@ -33460,7 +33458,7 @@
     </row>
     <row r="1176" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1176" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1176" t="s">
         <v>145</v>
@@ -33474,7 +33472,7 @@
     </row>
     <row r="1177" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1177" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1177" t="s">
         <v>146</v>
@@ -33488,7 +33486,7 @@
     </row>
     <row r="1178" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1178" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1178" t="s">
         <v>147</v>
@@ -33502,7 +33500,7 @@
     </row>
     <row r="1179" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1179" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1179" t="s">
         <v>148</v>
@@ -33516,7 +33514,7 @@
     </row>
     <row r="1180" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1180" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1180" t="s">
         <v>149</v>
@@ -33530,7 +33528,7 @@
     </row>
     <row r="1181" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1181" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1181" t="s">
         <v>150</v>
@@ -33544,7 +33542,7 @@
     </row>
     <row r="1182" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1182" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1182" t="s">
         <v>151</v>
@@ -33558,7 +33556,7 @@
     </row>
     <row r="1183" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1183" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1183" t="s">
         <v>152</v>
@@ -33572,7 +33570,7 @@
     </row>
     <row r="1184" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1184" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1184" t="s">
         <v>153</v>
@@ -33586,7 +33584,7 @@
     </row>
     <row r="1185" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1185" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1185" t="s">
         <v>154</v>
@@ -33600,7 +33598,7 @@
     </row>
     <row r="1186" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1186" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1186" t="s">
         <v>155</v>
@@ -33614,7 +33612,7 @@
     </row>
     <row r="1187" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1187" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1187" t="s">
         <v>156</v>
@@ -33628,7 +33626,7 @@
     </row>
     <row r="1188" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1188" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1188" t="s">
         <v>157</v>
@@ -33642,7 +33640,7 @@
     </row>
     <row r="1189" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1189" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1189" t="s">
         <v>158</v>
@@ -33656,7 +33654,7 @@
     </row>
     <row r="1190" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1190" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1190" t="s">
         <v>159</v>
@@ -33670,7 +33668,7 @@
     </row>
     <row r="1191" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1191" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1191" t="s">
         <v>160</v>
@@ -33684,7 +33682,7 @@
     </row>
     <row r="1192" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1192" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1192" t="s">
         <v>161</v>
@@ -33698,7 +33696,7 @@
     </row>
     <row r="1193" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1193" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1193" t="s">
         <v>162</v>
@@ -33712,7 +33710,7 @@
     </row>
     <row r="1194" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1194" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1194" t="s">
         <v>163</v>
@@ -33726,7 +33724,7 @@
     </row>
     <row r="1195" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1195" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1195" t="s">
         <v>164</v>
@@ -33740,7 +33738,7 @@
     </row>
     <row r="1196" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1196" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1196" t="s">
         <v>165</v>
@@ -33754,7 +33752,7 @@
     </row>
     <row r="1197" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1197" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1197" t="s">
         <v>166</v>
@@ -33768,7 +33766,7 @@
     </row>
     <row r="1198" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1198" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1198" t="s">
         <v>167</v>
@@ -33782,7 +33780,7 @@
     </row>
     <row r="1199" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1199" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1199" t="s">
         <v>168</v>
@@ -33796,7 +33794,7 @@
     </row>
     <row r="1200" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1200" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1200" t="s">
         <v>169</v>
@@ -33810,7 +33808,7 @@
     </row>
     <row r="1201" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1201" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1201" t="s">
         <v>170</v>
@@ -33824,7 +33822,7 @@
     </row>
     <row r="1202" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1202" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1202" t="s">
         <v>171</v>
@@ -33838,7 +33836,7 @@
     </row>
     <row r="1203" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1203" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1203" t="s">
         <v>172</v>
@@ -33852,7 +33850,7 @@
     </row>
     <row r="1204" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1204" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1204" t="s">
         <v>173</v>
@@ -33866,7 +33864,7 @@
     </row>
     <row r="1205" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1205" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1205" t="s">
         <v>174</v>
@@ -33880,7 +33878,7 @@
     </row>
     <row r="1206" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1206" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1206" t="s">
         <v>175</v>
@@ -33894,7 +33892,7 @@
     </row>
     <row r="1207" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1207" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1207" t="s">
         <v>176</v>
@@ -33908,7 +33906,7 @@
     </row>
     <row r="1208" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1208" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1208" t="s">
         <v>177</v>
@@ -33922,7 +33920,7 @@
     </row>
     <row r="1209" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1209" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1209" t="s">
         <v>178</v>
@@ -33936,7 +33934,7 @@
     </row>
     <row r="1210" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1210" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1210" t="s">
         <v>179</v>
@@ -33950,7 +33948,7 @@
     </row>
     <row r="1211" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1211" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1211" t="s">
         <v>180</v>
@@ -33964,7 +33962,7 @@
     </row>
     <row r="1212" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1212" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1212" t="s">
         <v>181</v>
@@ -33978,7 +33976,7 @@
     </row>
     <row r="1213" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1213" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1213" t="s">
         <v>182</v>
@@ -33992,7 +33990,7 @@
     </row>
     <row r="1214" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1214" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1214" t="s">
         <v>183</v>
@@ -34006,7 +34004,7 @@
     </row>
     <row r="1215" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1215" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1215" t="s">
         <v>184</v>
@@ -34020,7 +34018,7 @@
     </row>
     <row r="1216" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1216" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1216" t="s">
         <v>185</v>
@@ -34034,7 +34032,7 @@
     </row>
     <row r="1217" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1217" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1217" t="s">
         <v>186</v>
@@ -34048,7 +34046,7 @@
     </row>
     <row r="1218" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1218" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1218" t="s">
         <v>187</v>
@@ -34062,7 +34060,7 @@
     </row>
     <row r="1219" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1219" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1219" t="s">
         <v>188</v>
@@ -34076,7 +34074,7 @@
     </row>
     <row r="1220" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1220" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1220" t="s">
         <v>189</v>
@@ -34090,7 +34088,7 @@
     </row>
     <row r="1221" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1221" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1221" t="s">
         <v>190</v>
@@ -34104,7 +34102,7 @@
     </row>
     <row r="1222" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1222" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1222" t="s">
         <v>191</v>
@@ -34118,7 +34116,7 @@
     </row>
     <row r="1223" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1223" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1223" t="s">
         <v>192</v>
@@ -34132,7 +34130,7 @@
     </row>
     <row r="1224" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1224" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1224" t="s">
         <v>193</v>
@@ -34146,7 +34144,7 @@
     </row>
     <row r="1225" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1225" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1225" t="s">
         <v>194</v>
@@ -34160,7 +34158,7 @@
     </row>
     <row r="1226" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1226" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1226" t="s">
         <v>195</v>
@@ -34174,7 +34172,7 @@
     </row>
     <row r="1227" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1227" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1227" t="s">
         <v>196</v>
@@ -34188,7 +34186,7 @@
     </row>
     <row r="1228" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1228" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1228" t="s">
         <v>197</v>
@@ -34202,7 +34200,7 @@
     </row>
     <row r="1229" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1229" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1229" t="s">
         <v>198</v>
@@ -34216,7 +34214,7 @@
     </row>
     <row r="1230" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1230" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1230" t="s">
         <v>199</v>
@@ -34230,7 +34228,7 @@
     </row>
     <row r="1231" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1231" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1231" t="s">
         <v>200</v>
@@ -34244,7 +34242,7 @@
     </row>
     <row r="1232" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1232" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1232" t="s">
         <v>201</v>
@@ -34258,7 +34256,7 @@
     </row>
     <row r="1233" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1233" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1233" t="s">
         <v>202</v>
@@ -34272,7 +34270,7 @@
     </row>
     <row r="1234" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1234" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1234" t="s">
         <v>203</v>
@@ -34286,7 +34284,7 @@
     </row>
     <row r="1235" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1235" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1235" t="s">
         <v>204</v>
@@ -34300,7 +34298,7 @@
     </row>
     <row r="1236" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1236" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1236" t="s">
         <v>205</v>
@@ -34314,7 +34312,7 @@
     </row>
     <row r="1237" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1237" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1237" t="s">
         <v>206</v>
@@ -34328,7 +34326,7 @@
     </row>
     <row r="1238" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1238" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1238" t="s">
         <v>207</v>
@@ -34342,7 +34340,7 @@
     </row>
     <row r="1239" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1239" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1239" t="s">
         <v>208</v>
@@ -34356,7 +34354,7 @@
     </row>
     <row r="1240" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1240" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1240" t="s">
         <v>209</v>
@@ -34370,7 +34368,7 @@
     </row>
     <row r="1241" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1241" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1241" t="s">
         <v>210</v>
@@ -34384,7 +34382,7 @@
     </row>
     <row r="1242" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1242" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1242" t="s">
         <v>211</v>
@@ -34398,7 +34396,7 @@
     </row>
     <row r="1243" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1243" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1243" t="s">
         <v>212</v>
@@ -34412,7 +34410,7 @@
     </row>
     <row r="1244" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1244" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1244" t="s">
         <v>213</v>
@@ -34426,7 +34424,7 @@
     </row>
     <row r="1245" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1245" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1245" t="s">
         <v>214</v>
@@ -34440,7 +34438,7 @@
     </row>
     <row r="1246" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1246" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1246" t="s">
         <v>215</v>
@@ -34454,7 +34452,7 @@
     </row>
     <row r="1247" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1247" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J1247" t="s">
         <v>216</v>
@@ -34468,7 +34466,7 @@
     </row>
     <row r="1248" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1248" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1248" t="s">
         <v>122</v>
@@ -34482,7 +34480,7 @@
     </row>
     <row r="1249" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1249" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1249" t="s">
         <v>123</v>
@@ -34496,7 +34494,7 @@
     </row>
     <row r="1250" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1250" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1250" t="s">
         <v>124</v>
@@ -34510,7 +34508,7 @@
     </row>
     <row r="1251" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1251" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1251" t="s">
         <v>125</v>
@@ -34524,7 +34522,7 @@
     </row>
     <row r="1252" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1252" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1252" t="s">
         <v>126</v>
@@ -34538,7 +34536,7 @@
     </row>
     <row r="1253" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1253" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1253" t="s">
         <v>127</v>
@@ -34552,7 +34550,7 @@
     </row>
     <row r="1254" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1254" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1254" t="s">
         <v>128</v>
@@ -34566,7 +34564,7 @@
     </row>
     <row r="1255" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1255" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1255" t="s">
         <v>129</v>
@@ -34580,7 +34578,7 @@
     </row>
     <row r="1256" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1256" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1256" t="s">
         <v>130</v>
@@ -34594,7 +34592,7 @@
     </row>
     <row r="1257" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1257" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1257" t="s">
         <v>131</v>
@@ -34608,7 +34606,7 @@
     </row>
     <row r="1258" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1258" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1258" t="s">
         <v>132</v>
@@ -34622,7 +34620,7 @@
     </row>
     <row r="1259" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1259" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1259" t="s">
         <v>133</v>
@@ -34636,7 +34634,7 @@
     </row>
     <row r="1260" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1260" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1260" t="s">
         <v>134</v>
@@ -34650,7 +34648,7 @@
     </row>
     <row r="1261" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1261" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1261" t="s">
         <v>135</v>
@@ -34664,7 +34662,7 @@
     </row>
     <row r="1262" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1262" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1262" t="s">
         <v>136</v>
@@ -34678,7 +34676,7 @@
     </row>
     <row r="1263" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1263" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1263" t="s">
         <v>137</v>
@@ -34692,7 +34690,7 @@
     </row>
     <row r="1264" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1264" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1264" t="s">
         <v>138</v>
@@ -34706,7 +34704,7 @@
     </row>
     <row r="1265" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1265" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1265" t="s">
         <v>139</v>
@@ -34720,7 +34718,7 @@
     </row>
     <row r="1266" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1266" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1266" t="s">
         <v>140</v>
@@ -34734,7 +34732,7 @@
     </row>
     <row r="1267" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1267" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1267" t="s">
         <v>141</v>
@@ -34748,7 +34746,7 @@
     </row>
     <row r="1268" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1268" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1268" t="s">
         <v>142</v>
@@ -34762,7 +34760,7 @@
     </row>
     <row r="1269" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1269" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1269" t="s">
         <v>143</v>
@@ -34776,7 +34774,7 @@
     </row>
     <row r="1270" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1270" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1270" t="s">
         <v>144</v>
@@ -34790,7 +34788,7 @@
     </row>
     <row r="1271" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1271" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1271" t="s">
         <v>145</v>
@@ -34804,7 +34802,7 @@
     </row>
     <row r="1272" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1272" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1272" t="s">
         <v>146</v>
@@ -34818,7 +34816,7 @@
     </row>
     <row r="1273" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1273" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1273" t="s">
         <v>147</v>
@@ -34832,7 +34830,7 @@
     </row>
     <row r="1274" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1274" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1274" t="s">
         <v>148</v>
@@ -34846,7 +34844,7 @@
     </row>
     <row r="1275" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1275" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1275" t="s">
         <v>149</v>
@@ -34860,7 +34858,7 @@
     </row>
     <row r="1276" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1276" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1276" t="s">
         <v>150</v>
@@ -34874,7 +34872,7 @@
     </row>
     <row r="1277" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1277" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1277" t="s">
         <v>151</v>
@@ -34888,7 +34886,7 @@
     </row>
     <row r="1278" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1278" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1278" t="s">
         <v>152</v>
@@ -34902,7 +34900,7 @@
     </row>
     <row r="1279" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1279" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1279" t="s">
         <v>153</v>
@@ -34916,7 +34914,7 @@
     </row>
     <row r="1280" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1280" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1280" t="s">
         <v>154</v>
@@ -34930,7 +34928,7 @@
     </row>
     <row r="1281" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1281" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1281" t="s">
         <v>155</v>
@@ -34944,7 +34942,7 @@
     </row>
     <row r="1282" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1282" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1282" t="s">
         <v>156</v>
@@ -34958,7 +34956,7 @@
     </row>
     <row r="1283" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1283" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1283" t="s">
         <v>157</v>
@@ -34972,7 +34970,7 @@
     </row>
     <row r="1284" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1284" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1284" t="s">
         <v>158</v>
@@ -34986,7 +34984,7 @@
     </row>
     <row r="1285" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1285" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1285" t="s">
         <v>159</v>
@@ -35000,7 +34998,7 @@
     </row>
     <row r="1286" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1286" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1286" t="s">
         <v>160</v>
@@ -35014,7 +35012,7 @@
     </row>
     <row r="1287" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1287" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1287" t="s">
         <v>161</v>
@@ -35028,7 +35026,7 @@
     </row>
     <row r="1288" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1288" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1288" t="s">
         <v>162</v>
@@ -35042,7 +35040,7 @@
     </row>
     <row r="1289" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1289" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1289" t="s">
         <v>163</v>
@@ -35056,7 +35054,7 @@
     </row>
     <row r="1290" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1290" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1290" t="s">
         <v>164</v>
@@ -35070,7 +35068,7 @@
     </row>
     <row r="1291" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1291" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1291" t="s">
         <v>165</v>
@@ -35084,7 +35082,7 @@
     </row>
     <row r="1292" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1292" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1292" t="s">
         <v>166</v>
@@ -35098,7 +35096,7 @@
     </row>
     <row r="1293" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1293" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1293" t="s">
         <v>167</v>
@@ -35112,7 +35110,7 @@
     </row>
     <row r="1294" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1294" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1294" t="s">
         <v>168</v>
@@ -35126,7 +35124,7 @@
     </row>
     <row r="1295" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1295" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1295" t="s">
         <v>169</v>
@@ -35140,7 +35138,7 @@
     </row>
     <row r="1296" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1296" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1296" t="s">
         <v>170</v>
@@ -35154,7 +35152,7 @@
     </row>
     <row r="1297" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1297" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1297" t="s">
         <v>171</v>
@@ -35168,7 +35166,7 @@
     </row>
     <row r="1298" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1298" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1298" t="s">
         <v>172</v>
@@ -35182,7 +35180,7 @@
     </row>
     <row r="1299" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1299" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1299" t="s">
         <v>173</v>
@@ -35196,7 +35194,7 @@
     </row>
     <row r="1300" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1300" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1300" t="s">
         <v>174</v>
@@ -35210,7 +35208,7 @@
     </row>
     <row r="1301" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1301" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1301" t="s">
         <v>175</v>
@@ -35224,7 +35222,7 @@
     </row>
     <row r="1302" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1302" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1302" t="s">
         <v>176</v>
@@ -35238,7 +35236,7 @@
     </row>
     <row r="1303" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1303" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1303" t="s">
         <v>177</v>
@@ -35252,7 +35250,7 @@
     </row>
     <row r="1304" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1304" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1304" t="s">
         <v>178</v>
@@ -35266,7 +35264,7 @@
     </row>
     <row r="1305" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1305" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1305" t="s">
         <v>179</v>
@@ -35280,7 +35278,7 @@
     </row>
     <row r="1306" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1306" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1306" t="s">
         <v>180</v>
@@ -35294,7 +35292,7 @@
     </row>
     <row r="1307" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1307" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1307" t="s">
         <v>181</v>
@@ -35308,7 +35306,7 @@
     </row>
     <row r="1308" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1308" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1308" t="s">
         <v>182</v>
@@ -35322,7 +35320,7 @@
     </row>
     <row r="1309" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1309" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1309" t="s">
         <v>183</v>
@@ -35336,7 +35334,7 @@
     </row>
     <row r="1310" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1310" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1310" t="s">
         <v>184</v>
@@ -35350,7 +35348,7 @@
     </row>
     <row r="1311" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1311" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1311" t="s">
         <v>185</v>
@@ -35364,7 +35362,7 @@
     </row>
     <row r="1312" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1312" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1312" t="s">
         <v>186</v>
@@ -35378,7 +35376,7 @@
     </row>
     <row r="1313" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1313" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1313" t="s">
         <v>187</v>
@@ -35392,7 +35390,7 @@
     </row>
     <row r="1314" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1314" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1314" t="s">
         <v>188</v>
@@ -35406,7 +35404,7 @@
     </row>
     <row r="1315" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1315" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1315" t="s">
         <v>189</v>
@@ -35420,7 +35418,7 @@
     </row>
     <row r="1316" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1316" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1316" t="s">
         <v>190</v>
@@ -35434,7 +35432,7 @@
     </row>
     <row r="1317" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1317" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1317" t="s">
         <v>191</v>
@@ -35448,7 +35446,7 @@
     </row>
     <row r="1318" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1318" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1318" t="s">
         <v>192</v>
@@ -35462,7 +35460,7 @@
     </row>
     <row r="1319" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1319" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1319" t="s">
         <v>193</v>
@@ -35476,7 +35474,7 @@
     </row>
     <row r="1320" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1320" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1320" t="s">
         <v>194</v>
@@ -35490,7 +35488,7 @@
     </row>
     <row r="1321" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1321" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1321" t="s">
         <v>195</v>
@@ -35504,7 +35502,7 @@
     </row>
     <row r="1322" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1322" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1322" t="s">
         <v>196</v>
@@ -35518,7 +35516,7 @@
     </row>
     <row r="1323" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1323" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1323" t="s">
         <v>197</v>
@@ -35532,7 +35530,7 @@
     </row>
     <row r="1324" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1324" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1324" t="s">
         <v>198</v>
@@ -35546,7 +35544,7 @@
     </row>
     <row r="1325" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1325" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1325" t="s">
         <v>199</v>
@@ -35560,7 +35558,7 @@
     </row>
     <row r="1326" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1326" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1326" t="s">
         <v>200</v>
@@ -35574,7 +35572,7 @@
     </row>
     <row r="1327" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1327" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1327" t="s">
         <v>201</v>
@@ -35588,7 +35586,7 @@
     </row>
     <row r="1328" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1328" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1328" t="s">
         <v>202</v>
@@ -35602,7 +35600,7 @@
     </row>
     <row r="1329" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1329" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1329" t="s">
         <v>203</v>
@@ -35616,7 +35614,7 @@
     </row>
     <row r="1330" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1330" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1330" t="s">
         <v>204</v>
@@ -35630,7 +35628,7 @@
     </row>
     <row r="1331" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1331" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1331" t="s">
         <v>205</v>
@@ -35644,7 +35642,7 @@
     </row>
     <row r="1332" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1332" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1332" t="s">
         <v>206</v>
@@ -35658,7 +35656,7 @@
     </row>
     <row r="1333" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1333" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1333" t="s">
         <v>207</v>
@@ -35672,7 +35670,7 @@
     </row>
     <row r="1334" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1334" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1334" t="s">
         <v>208</v>
@@ -35686,7 +35684,7 @@
     </row>
     <row r="1335" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1335" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1335" t="s">
         <v>209</v>
@@ -35700,7 +35698,7 @@
     </row>
     <row r="1336" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1336" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1336" t="s">
         <v>210</v>
@@ -35714,7 +35712,7 @@
     </row>
     <row r="1337" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1337" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1337" t="s">
         <v>211</v>
@@ -35728,7 +35726,7 @@
     </row>
     <row r="1338" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1338" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1338" t="s">
         <v>212</v>
@@ -35742,7 +35740,7 @@
     </row>
     <row r="1339" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1339" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1339" t="s">
         <v>213</v>
@@ -35756,7 +35754,7 @@
     </row>
     <row r="1340" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1340" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1340" t="s">
         <v>214</v>
@@ -35770,7 +35768,7 @@
     </row>
     <row r="1341" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1341" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1341" t="s">
         <v>215</v>
@@ -35784,7 +35782,7 @@
     </row>
     <row r="1342" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1342" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J1342" t="s">
         <v>216</v>
@@ -35798,7 +35796,7 @@
     </row>
     <row r="1343" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1343" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1343" t="s">
         <v>122</v>
@@ -35812,7 +35810,7 @@
     </row>
     <row r="1344" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1344" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1344" t="s">
         <v>123</v>
@@ -35826,7 +35824,7 @@
     </row>
     <row r="1345" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1345" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1345" t="s">
         <v>124</v>
@@ -35840,7 +35838,7 @@
     </row>
     <row r="1346" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1346" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1346" t="s">
         <v>125</v>
@@ -35854,7 +35852,7 @@
     </row>
     <row r="1347" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1347" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1347" t="s">
         <v>126</v>
@@ -35868,7 +35866,7 @@
     </row>
     <row r="1348" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1348" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1348" t="s">
         <v>127</v>
@@ -35882,7 +35880,7 @@
     </row>
     <row r="1349" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1349" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1349" t="s">
         <v>128</v>
@@ -35896,7 +35894,7 @@
     </row>
     <row r="1350" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1350" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1350" t="s">
         <v>129</v>
@@ -35910,7 +35908,7 @@
     </row>
     <row r="1351" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1351" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1351" t="s">
         <v>130</v>
@@ -35924,7 +35922,7 @@
     </row>
     <row r="1352" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1352" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1352" t="s">
         <v>131</v>
@@ -35938,7 +35936,7 @@
     </row>
     <row r="1353" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1353" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1353" t="s">
         <v>132</v>
@@ -35952,7 +35950,7 @@
     </row>
     <row r="1354" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1354" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1354" t="s">
         <v>133</v>
@@ -35966,7 +35964,7 @@
     </row>
     <row r="1355" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1355" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1355" t="s">
         <v>134</v>
@@ -35980,7 +35978,7 @@
     </row>
     <row r="1356" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1356" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1356" t="s">
         <v>135</v>
@@ -35994,7 +35992,7 @@
     </row>
     <row r="1357" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1357" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1357" t="s">
         <v>136</v>
@@ -36008,7 +36006,7 @@
     </row>
     <row r="1358" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1358" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1358" t="s">
         <v>137</v>
@@ -36022,7 +36020,7 @@
     </row>
     <row r="1359" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1359" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1359" t="s">
         <v>138</v>
@@ -36036,7 +36034,7 @@
     </row>
     <row r="1360" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1360" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1360" t="s">
         <v>139</v>
@@ -36050,7 +36048,7 @@
     </row>
     <row r="1361" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1361" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1361" t="s">
         <v>140</v>
@@ -36064,7 +36062,7 @@
     </row>
     <row r="1362" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1362" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1362" t="s">
         <v>141</v>
@@ -36078,7 +36076,7 @@
     </row>
     <row r="1363" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1363" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1363" t="s">
         <v>142</v>
@@ -36092,7 +36090,7 @@
     </row>
     <row r="1364" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1364" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1364" t="s">
         <v>143</v>
@@ -36106,7 +36104,7 @@
     </row>
     <row r="1365" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1365" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1365" t="s">
         <v>144</v>
@@ -36120,7 +36118,7 @@
     </row>
     <row r="1366" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1366" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1366" t="s">
         <v>145</v>
@@ -36134,7 +36132,7 @@
     </row>
     <row r="1367" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1367" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1367" t="s">
         <v>146</v>
@@ -36148,7 +36146,7 @@
     </row>
     <row r="1368" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1368" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1368" t="s">
         <v>147</v>
@@ -36162,7 +36160,7 @@
     </row>
     <row r="1369" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1369" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1369" t="s">
         <v>148</v>
@@ -36176,7 +36174,7 @@
     </row>
     <row r="1370" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1370" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1370" t="s">
         <v>149</v>
@@ -36190,7 +36188,7 @@
     </row>
     <row r="1371" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1371" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1371" t="s">
         <v>150</v>
@@ -36204,7 +36202,7 @@
     </row>
     <row r="1372" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1372" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1372" t="s">
         <v>151</v>
@@ -36218,7 +36216,7 @@
     </row>
     <row r="1373" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1373" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1373" t="s">
         <v>152</v>
@@ -36232,7 +36230,7 @@
     </row>
     <row r="1374" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1374" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1374" t="s">
         <v>153</v>
@@ -36246,7 +36244,7 @@
     </row>
     <row r="1375" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1375" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1375" t="s">
         <v>154</v>
@@ -36260,7 +36258,7 @@
     </row>
     <row r="1376" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1376" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1376" t="s">
         <v>155</v>
@@ -36274,7 +36272,7 @@
     </row>
     <row r="1377" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1377" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1377" t="s">
         <v>156</v>
@@ -36288,7 +36286,7 @@
     </row>
     <row r="1378" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1378" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1378" t="s">
         <v>157</v>
@@ -36302,7 +36300,7 @@
     </row>
     <row r="1379" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1379" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1379" t="s">
         <v>158</v>
@@ -36316,7 +36314,7 @@
     </row>
     <row r="1380" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1380" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1380" t="s">
         <v>159</v>
@@ -36330,7 +36328,7 @@
     </row>
     <row r="1381" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1381" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1381" t="s">
         <v>160</v>
@@ -36344,7 +36342,7 @@
     </row>
     <row r="1382" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1382" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1382" t="s">
         <v>161</v>
@@ -36358,7 +36356,7 @@
     </row>
     <row r="1383" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1383" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1383" t="s">
         <v>162</v>
@@ -36372,7 +36370,7 @@
     </row>
     <row r="1384" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1384" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1384" t="s">
         <v>163</v>
@@ -36386,7 +36384,7 @@
     </row>
     <row r="1385" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1385" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1385" t="s">
         <v>164</v>
@@ -36400,7 +36398,7 @@
     </row>
     <row r="1386" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1386" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1386" t="s">
         <v>165</v>
@@ -36414,7 +36412,7 @@
     </row>
     <row r="1387" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1387" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1387" t="s">
         <v>166</v>
@@ -36428,7 +36426,7 @@
     </row>
     <row r="1388" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1388" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1388" t="s">
         <v>167</v>
@@ -36442,7 +36440,7 @@
     </row>
     <row r="1389" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1389" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1389" t="s">
         <v>168</v>
@@ -36456,7 +36454,7 @@
     </row>
     <row r="1390" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1390" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1390" t="s">
         <v>169</v>
@@ -36470,7 +36468,7 @@
     </row>
     <row r="1391" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1391" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1391" t="s">
         <v>170</v>
@@ -36484,7 +36482,7 @@
     </row>
     <row r="1392" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1392" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1392" t="s">
         <v>171</v>
@@ -36498,7 +36496,7 @@
     </row>
     <row r="1393" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1393" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1393" t="s">
         <v>172</v>
@@ -36512,7 +36510,7 @@
     </row>
     <row r="1394" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1394" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1394" t="s">
         <v>173</v>
@@ -36526,7 +36524,7 @@
     </row>
     <row r="1395" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1395" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1395" t="s">
         <v>174</v>
@@ -36540,7 +36538,7 @@
     </row>
     <row r="1396" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1396" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1396" t="s">
         <v>175</v>
@@ -36554,7 +36552,7 @@
     </row>
     <row r="1397" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1397" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1397" t="s">
         <v>176</v>
@@ -36568,7 +36566,7 @@
     </row>
     <row r="1398" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1398" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1398" t="s">
         <v>177</v>
@@ -36582,7 +36580,7 @@
     </row>
     <row r="1399" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1399" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1399" t="s">
         <v>178</v>
@@ -36596,7 +36594,7 @@
     </row>
     <row r="1400" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1400" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1400" t="s">
         <v>179</v>
@@ -36610,7 +36608,7 @@
     </row>
     <row r="1401" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1401" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1401" t="s">
         <v>180</v>
@@ -36624,7 +36622,7 @@
     </row>
     <row r="1402" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1402" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1402" t="s">
         <v>181</v>
@@ -36638,7 +36636,7 @@
     </row>
     <row r="1403" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1403" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1403" t="s">
         <v>182</v>
@@ -36652,7 +36650,7 @@
     </row>
     <row r="1404" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1404" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1404" t="s">
         <v>183</v>
@@ -36666,7 +36664,7 @@
     </row>
     <row r="1405" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1405" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1405" t="s">
         <v>184</v>
@@ -36680,7 +36678,7 @@
     </row>
     <row r="1406" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1406" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1406" t="s">
         <v>185</v>
@@ -36694,7 +36692,7 @@
     </row>
     <row r="1407" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1407" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1407" t="s">
         <v>186</v>
@@ -36708,7 +36706,7 @@
     </row>
     <row r="1408" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1408" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1408" t="s">
         <v>187</v>
@@ -36722,7 +36720,7 @@
     </row>
     <row r="1409" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1409" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1409" t="s">
         <v>188</v>
@@ -36736,7 +36734,7 @@
     </row>
     <row r="1410" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1410" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1410" t="s">
         <v>189</v>
@@ -36750,7 +36748,7 @@
     </row>
     <row r="1411" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1411" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1411" t="s">
         <v>190</v>
@@ -36764,7 +36762,7 @@
     </row>
     <row r="1412" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1412" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1412" t="s">
         <v>191</v>
@@ -36778,7 +36776,7 @@
     </row>
     <row r="1413" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1413" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1413" t="s">
         <v>192</v>
@@ -36792,7 +36790,7 @@
     </row>
     <row r="1414" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1414" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1414" t="s">
         <v>193</v>
@@ -36806,7 +36804,7 @@
     </row>
     <row r="1415" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1415" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1415" t="s">
         <v>194</v>
@@ -36820,7 +36818,7 @@
     </row>
     <row r="1416" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1416" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1416" t="s">
         <v>195</v>
@@ -36834,7 +36832,7 @@
     </row>
     <row r="1417" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1417" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1417" t="s">
         <v>196</v>
@@ -36848,7 +36846,7 @@
     </row>
     <row r="1418" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1418" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1418" t="s">
         <v>197</v>
@@ -36862,7 +36860,7 @@
     </row>
     <row r="1419" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1419" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1419" t="s">
         <v>198</v>
@@ -36876,7 +36874,7 @@
     </row>
     <row r="1420" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1420" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1420" t="s">
         <v>199</v>
@@ -36890,7 +36888,7 @@
     </row>
     <row r="1421" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1421" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1421" t="s">
         <v>200</v>
@@ -36904,7 +36902,7 @@
     </row>
     <row r="1422" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1422" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1422" t="s">
         <v>201</v>
@@ -36918,7 +36916,7 @@
     </row>
     <row r="1423" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1423" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1423" t="s">
         <v>202</v>
@@ -36932,7 +36930,7 @@
     </row>
     <row r="1424" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1424" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1424" t="s">
         <v>203</v>
@@ -36946,7 +36944,7 @@
     </row>
     <row r="1425" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1425" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1425" t="s">
         <v>204</v>
@@ -36960,7 +36958,7 @@
     </row>
     <row r="1426" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1426" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1426" t="s">
         <v>205</v>
@@ -36974,7 +36972,7 @@
     </row>
     <row r="1427" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1427" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1427" t="s">
         <v>206</v>
@@ -36988,7 +36986,7 @@
     </row>
     <row r="1428" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1428" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1428" t="s">
         <v>207</v>
@@ -37002,7 +37000,7 @@
     </row>
     <row r="1429" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1429" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1429" t="s">
         <v>208</v>
@@ -37016,7 +37014,7 @@
     </row>
     <row r="1430" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1430" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1430" t="s">
         <v>209</v>
@@ -37030,7 +37028,7 @@
     </row>
     <row r="1431" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1431" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1431" t="s">
         <v>210</v>
@@ -37044,7 +37042,7 @@
     </row>
     <row r="1432" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1432" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1432" t="s">
         <v>211</v>
@@ -37058,7 +37056,7 @@
     </row>
     <row r="1433" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1433" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1433" t="s">
         <v>212</v>
@@ -37072,7 +37070,7 @@
     </row>
     <row r="1434" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1434" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1434" t="s">
         <v>213</v>
@@ -37086,7 +37084,7 @@
     </row>
     <row r="1435" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1435" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1435" t="s">
         <v>214</v>
@@ -37100,7 +37098,7 @@
     </row>
     <row r="1436" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1436" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1436" t="s">
         <v>215</v>
@@ -37114,7 +37112,7 @@
     </row>
     <row r="1437" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I1437" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J1437" t="s">
         <v>216</v>
@@ -37150,7 +37148,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C3" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DAFF1C-AEF9-4E69-ABFD-A2D1EFC4DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92FB753-D999-4695-BC19-F7F163A1C2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="286">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -929,6 +930,9 @@
   <si>
     <t>elc</t>
   </si>
+  <si>
+    <t>TFM_DINS-AT</t>
+  </si>
 </sst>
 </file>
 
@@ -1089,7 +1093,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1116,7 +1120,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="9" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{45765176-8E4D-467C-8B17-17A7F0C6EBE1}"/>
@@ -1488,7 +1491,34 @@
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+      <c r="E3" s="7">
+        <f>SUM(E5:E8)</f>
+        <v>8.4914999999999985</v>
+      </c>
+      <c r="F3" s="7">
+        <f t="shared" ref="F3:K3" si="0">SUM(F5:F8)</f>
+        <v>8.4719999999999995</v>
+      </c>
+      <c r="G3" s="7">
+        <f t="shared" si="0"/>
+        <v>9.109</v>
+      </c>
+      <c r="H3" s="7">
+        <f t="shared" si="0"/>
+        <v>10.274000000000001</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" si="0"/>
+        <v>11.359</v>
+      </c>
+      <c r="J3" s="7">
+        <f t="shared" si="0"/>
+        <v>12.954000000000001</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" si="0"/>
+        <v>14.578999999999999</v>
+      </c>
       <c r="O3" t="s">
         <v>34</v>
       </c>
@@ -1883,14 +1913,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>283</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C24" t="s">
         <v>284</v>
       </c>
-      <c r="E20">
+      <c r="E24">
         <v>1</v>
       </c>
     </row>
@@ -1948,8 +1978,8 @@
       <c r="X1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AB1" s="20" t="s">
-        <v>49</v>
+      <c r="AB1" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="AF1" s="11" t="s">
         <v>67</v>
@@ -4380,7 +4410,7 @@
       </c>
       <c r="AX25" s="2">
         <f ca="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26" spans="9:50" x14ac:dyDescent="0.25">
@@ -4479,7 +4509,7 @@
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:AX89" ca="1" si="1">RANDBETWEEN(70,95)/100</f>
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="27" spans="9:50" x14ac:dyDescent="0.25">
@@ -4578,7 +4608,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4677,7 +4707,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4776,7 +4806,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4875,7 +4905,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -4974,7 +5004,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -5073,7 +5103,7 @@
       </c>
       <c r="AX32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="33" spans="9:50" x14ac:dyDescent="0.25">
@@ -5172,7 +5202,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5271,7 +5301,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5370,7 +5400,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5469,7 +5499,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5667,7 +5697,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5754,7 +5784,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5841,7 +5871,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -6015,7 +6045,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -6102,7 +6132,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6189,7 +6219,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6276,7 +6306,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6363,7 +6393,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6450,7 +6480,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6537,7 +6567,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6624,7 +6654,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6711,7 +6741,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6798,7 +6828,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6885,7 +6915,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -6972,7 +7002,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -7059,7 +7089,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7146,7 +7176,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7233,7 +7263,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7320,7 +7350,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7407,7 +7437,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7494,7 +7524,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7581,7 +7611,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7668,7 +7698,7 @@
       </c>
       <c r="AX61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="62" spans="9:50" x14ac:dyDescent="0.25">
@@ -7755,7 +7785,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7842,7 +7872,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -8016,7 +8046,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -8103,7 +8133,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8190,7 +8220,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8277,7 +8307,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8364,7 +8394,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8451,7 +8481,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8538,7 +8568,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8625,7 +8655,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8712,7 +8742,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8799,7 +8829,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8886,7 +8916,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -8973,7 +9003,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -9060,7 +9090,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9147,7 +9177,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9234,7 +9264,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9321,7 +9351,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9408,7 +9438,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9495,7 +9525,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9582,7 +9612,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9669,7 +9699,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9756,7 +9786,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9843,7 +9873,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9930,7 +9960,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -10017,7 +10047,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -10104,7 +10134,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10191,7 +10221,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.81</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10278,7 +10308,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10365,7 +10395,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10452,7 +10482,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10539,7 +10569,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10626,7 +10656,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10713,7 +10743,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10800,7 +10830,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10887,7 +10917,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
+++ b/VerveStacks_EST/SuppXLS/Scen_bau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92FB753-D999-4695-BC19-F7F163A1C2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D983772C-869C-4C52-AF2C-AFB1FDF277D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8003" uniqueCount="285">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -930,9 +930,6 @@
   <si>
     <t>elc</t>
   </si>
-  <si>
-    <t>TFM_DINS-AT</t>
-  </si>
 </sst>
 </file>
 
@@ -1913,14 +1910,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>283</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C20" t="s">
         <v>284</v>
       </c>
-      <c r="E24">
+      <c r="E20">
         <v>1</v>
       </c>
     </row>
@@ -1979,7 +1976,7 @@
         <v>49</v>
       </c>
       <c r="AB1" s="11" t="s">
-        <v>285</v>
+        <v>49</v>
       </c>
       <c r="AF1" s="11" t="s">
         <v>67</v>
@@ -4608,7 +4605,7 @@
       </c>
       <c r="AX27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="28" spans="9:50" x14ac:dyDescent="0.25">
@@ -4707,7 +4704,7 @@
       </c>
       <c r="AX28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="29" spans="9:50" x14ac:dyDescent="0.25">
@@ -4806,7 +4803,7 @@
       </c>
       <c r="AX29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="30" spans="9:50" x14ac:dyDescent="0.25">
@@ -4905,7 +4902,7 @@
       </c>
       <c r="AX30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="31" spans="9:50" x14ac:dyDescent="0.25">
@@ -5004,7 +5001,7 @@
       </c>
       <c r="AX31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="32" spans="9:50" x14ac:dyDescent="0.25">
@@ -5103,7 +5100,7 @@
       </c>
       <c r="AX32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="33" spans="9:50" x14ac:dyDescent="0.25">
@@ -5202,7 +5199,7 @@
       </c>
       <c r="AX33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="34" spans="9:50" x14ac:dyDescent="0.25">
@@ -5301,7 +5298,7 @@
       </c>
       <c r="AX34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="9:50" x14ac:dyDescent="0.25">
@@ -5400,7 +5397,7 @@
       </c>
       <c r="AX35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="36" spans="9:50" x14ac:dyDescent="0.25">
@@ -5499,7 +5496,7 @@
       </c>
       <c r="AX36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="37" spans="9:50" x14ac:dyDescent="0.25">
@@ -5598,7 +5595,7 @@
       </c>
       <c r="AX37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="38" spans="9:50" x14ac:dyDescent="0.25">
@@ -5697,7 +5694,7 @@
       </c>
       <c r="AX38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39" spans="9:50" x14ac:dyDescent="0.25">
@@ -5784,7 +5781,7 @@
       </c>
       <c r="AX39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="40" spans="9:50" x14ac:dyDescent="0.25">
@@ -5871,7 +5868,7 @@
       </c>
       <c r="AX40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="41" spans="9:50" x14ac:dyDescent="0.25">
@@ -5958,7 +5955,7 @@
       </c>
       <c r="AX41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="42" spans="9:50" x14ac:dyDescent="0.25">
@@ -6045,7 +6042,7 @@
       </c>
       <c r="AX42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="43" spans="9:50" x14ac:dyDescent="0.25">
@@ -6132,7 +6129,7 @@
       </c>
       <c r="AX43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="44" spans="9:50" x14ac:dyDescent="0.25">
@@ -6219,7 +6216,7 @@
       </c>
       <c r="AX44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="45" spans="9:50" x14ac:dyDescent="0.25">
@@ -6306,7 +6303,7 @@
       </c>
       <c r="AX45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="46" spans="9:50" x14ac:dyDescent="0.25">
@@ -6393,7 +6390,7 @@
       </c>
       <c r="AX46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="47" spans="9:50" x14ac:dyDescent="0.25">
@@ -6480,7 +6477,7 @@
       </c>
       <c r="AX47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="48" spans="9:50" x14ac:dyDescent="0.25">
@@ -6567,7 +6564,7 @@
       </c>
       <c r="AX48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="49" spans="9:50" x14ac:dyDescent="0.25">
@@ -6654,7 +6651,7 @@
       </c>
       <c r="AX49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="50" spans="9:50" x14ac:dyDescent="0.25">
@@ -6741,7 +6738,7 @@
       </c>
       <c r="AX50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="51" spans="9:50" x14ac:dyDescent="0.25">
@@ -6828,7 +6825,7 @@
       </c>
       <c r="AX51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="52" spans="9:50" x14ac:dyDescent="0.25">
@@ -6915,7 +6912,7 @@
       </c>
       <c r="AX52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="53" spans="9:50" x14ac:dyDescent="0.25">
@@ -7002,7 +6999,7 @@
       </c>
       <c r="AX53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="54" spans="9:50" x14ac:dyDescent="0.25">
@@ -7089,7 +7086,7 @@
       </c>
       <c r="AX54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="55" spans="9:50" x14ac:dyDescent="0.25">
@@ -7176,7 +7173,7 @@
       </c>
       <c r="AX55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="56" spans="9:50" x14ac:dyDescent="0.25">
@@ -7263,7 +7260,7 @@
       </c>
       <c r="AX56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="57" spans="9:50" x14ac:dyDescent="0.25">
@@ -7350,7 +7347,7 @@
       </c>
       <c r="AX57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="58" spans="9:50" x14ac:dyDescent="0.25">
@@ -7437,7 +7434,7 @@
       </c>
       <c r="AX58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="59" spans="9:50" x14ac:dyDescent="0.25">
@@ -7524,7 +7521,7 @@
       </c>
       <c r="AX59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="60" spans="9:50" x14ac:dyDescent="0.25">
@@ -7611,7 +7608,7 @@
       </c>
       <c r="AX60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="61" spans="9:50" x14ac:dyDescent="0.25">
@@ -7785,7 +7782,7 @@
       </c>
       <c r="AX62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="63" spans="9:50" x14ac:dyDescent="0.25">
@@ -7872,7 +7869,7 @@
       </c>
       <c r="AX63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="64" spans="9:50" x14ac:dyDescent="0.25">
@@ -7959,7 +7956,7 @@
       </c>
       <c r="AX64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="65" spans="9:50" x14ac:dyDescent="0.25">
@@ -8046,7 +8043,7 @@
       </c>
       <c r="AX65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="66" spans="9:50" x14ac:dyDescent="0.25">
@@ -8133,7 +8130,7 @@
       </c>
       <c r="AX66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="67" spans="9:50" x14ac:dyDescent="0.25">
@@ -8220,7 +8217,7 @@
       </c>
       <c r="AX67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="68" spans="9:50" x14ac:dyDescent="0.25">
@@ -8307,7 +8304,7 @@
       </c>
       <c r="AX68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="69" spans="9:50" x14ac:dyDescent="0.25">
@@ -8394,7 +8391,7 @@
       </c>
       <c r="AX69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="70" spans="9:50" x14ac:dyDescent="0.25">
@@ -8481,7 +8478,7 @@
       </c>
       <c r="AX70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="71" spans="9:50" x14ac:dyDescent="0.25">
@@ -8568,7 +8565,7 @@
       </c>
       <c r="AX71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="72" spans="9:50" x14ac:dyDescent="0.25">
@@ -8655,7 +8652,7 @@
       </c>
       <c r="AX72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="73" spans="9:50" x14ac:dyDescent="0.25">
@@ -8742,7 +8739,7 @@
       </c>
       <c r="AX73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="74" spans="9:50" x14ac:dyDescent="0.25">
@@ -8829,7 +8826,7 @@
       </c>
       <c r="AX74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="75" spans="9:50" x14ac:dyDescent="0.25">
@@ -8916,7 +8913,7 @@
       </c>
       <c r="AX75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="76" spans="9:50" x14ac:dyDescent="0.25">
@@ -9003,7 +9000,7 @@
       </c>
       <c r="AX76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="77" spans="9:50" x14ac:dyDescent="0.25">
@@ -9090,7 +9087,7 @@
       </c>
       <c r="AX77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="78" spans="9:50" x14ac:dyDescent="0.25">
@@ -9177,7 +9174,7 @@
       </c>
       <c r="AX78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="79" spans="9:50" x14ac:dyDescent="0.25">
@@ -9264,7 +9261,7 @@
       </c>
       <c r="AX79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="80" spans="9:50" x14ac:dyDescent="0.25">
@@ -9351,7 +9348,7 @@
       </c>
       <c r="AX80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="81" spans="9:50" x14ac:dyDescent="0.25">
@@ -9438,7 +9435,7 @@
       </c>
       <c r="AX81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="82" spans="9:50" x14ac:dyDescent="0.25">
@@ -9525,7 +9522,7 @@
       </c>
       <c r="AX82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="83" spans="9:50" x14ac:dyDescent="0.25">
@@ -9612,7 +9609,7 @@
       </c>
       <c r="AX83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="84" spans="9:50" x14ac:dyDescent="0.25">
@@ -9699,7 +9696,7 @@
       </c>
       <c r="AX84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="85" spans="9:50" x14ac:dyDescent="0.25">
@@ -9786,7 +9783,7 @@
       </c>
       <c r="AX85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.94</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="86" spans="9:50" x14ac:dyDescent="0.25">
@@ -9873,7 +9870,7 @@
       </c>
       <c r="AX86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="87" spans="9:50" x14ac:dyDescent="0.25">
@@ -9960,7 +9957,7 @@
       </c>
       <c r="AX87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="88" spans="9:50" x14ac:dyDescent="0.25">
@@ -10047,7 +10044,7 @@
       </c>
       <c r="AX88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="89" spans="9:50" x14ac:dyDescent="0.25">
@@ -10134,7 +10131,7 @@
       </c>
       <c r="AX89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="90" spans="9:50" x14ac:dyDescent="0.25">
@@ -10221,7 +10218,7 @@
       </c>
       <c r="AX90" s="2">
         <f t="shared" ref="AX90:AX98" ca="1" si="2">RANDBETWEEN(70,95)/100</f>
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="91" spans="9:50" x14ac:dyDescent="0.25">
@@ -10308,7 +10305,7 @@
       </c>
       <c r="AX91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="92" spans="9:50" x14ac:dyDescent="0.25">
@@ -10395,7 +10392,7 @@
       </c>
       <c r="AX92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="93" spans="9:50" x14ac:dyDescent="0.25">
@@ -10482,7 +10479,7 @@
       </c>
       <c r="AX93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="94" spans="9:50" x14ac:dyDescent="0.25">
@@ -10569,7 +10566,7 @@
       </c>
       <c r="AX94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="95" spans="9:50" x14ac:dyDescent="0.25">
@@ -10656,7 +10653,7 @@
       </c>
       <c r="AX95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="96" spans="9:50" x14ac:dyDescent="0.25">
@@ -10743,7 +10740,7 @@
       </c>
       <c r="AX96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="97" spans="9:50" x14ac:dyDescent="0.25">
@@ -10830,7 +10827,7 @@
       </c>
       <c r="AX97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="98" spans="9:50" x14ac:dyDescent="0.25">
@@ -10917,7 +10914,7 @@
       </c>
       <c r="AX98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="99" spans="9:50" x14ac:dyDescent="0.25">
